--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1177</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1914">
   <si>
     <t>en</t>
   </si>
@@ -5398,355 +5398,358 @@
     <t>Twisted Wonderland</t>
   </si>
   <si>
+    <t>ULTRAKILL</t>
+  </si>
+  <si>
+    <t>Umineko - When They Cry</t>
+  </si>
+  <si>
+    <t>Umineko - Ketika Mereka Menangis</t>
+  </si>
+  <si>
+    <t>Undertale</t>
+  </si>
+  <si>
+    <t>Undertale AU</t>
+  </si>
+  <si>
+    <t>Undertale Yellow</t>
+  </si>
+  <si>
+    <t>Undertale Kuning</t>
+  </si>
+  <si>
+    <t>Universal Symbol</t>
+  </si>
+  <si>
+    <t>Simbol Universal</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>Urban Wildlife</t>
+  </si>
+  <si>
+    <t>Satwa Liar Perkotaan</t>
+  </si>
+  <si>
+    <t>V for Vendetta</t>
+  </si>
+  <si>
+    <t>V untuk Vendetta</t>
+  </si>
+  <si>
+    <t>Valentines</t>
+  </si>
+  <si>
+    <t>Kasih Sayang</t>
+  </si>
+  <si>
+    <t>Valorant</t>
+  </si>
+  <si>
+    <t>Vanilla (removed)</t>
+  </si>
+  <si>
+    <t>Vanila (dihapus)</t>
+  </si>
+  <si>
+    <t>Vanilla Block</t>
+  </si>
+  <si>
+    <t>Blok Vanilla</t>
+  </si>
+  <si>
+    <t>Vanilla Food</t>
+  </si>
+  <si>
+    <t>Makanan Vanilla</t>
+  </si>
+  <si>
+    <t>Vanilla Helmet</t>
+  </si>
+  <si>
+    <t>Helm Vanilla</t>
+  </si>
+  <si>
+    <t>Vanilla Item</t>
+  </si>
+  <si>
+    <t>Item Vanilla</t>
+  </si>
+  <si>
+    <t>Vanilla Mob</t>
+  </si>
+  <si>
+    <t>Vault Hunters</t>
+  </si>
+  <si>
+    <t>Pemburu Kubah</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>Sayuran</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Kendaraan</t>
+  </si>
+  <si>
+    <t>Vikings</t>
+  </si>
+  <si>
+    <t>Viking</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Penduduk desa</t>
+  </si>
+  <si>
+    <t>Villager (Desert)</t>
+  </si>
+  <si>
+    <t>Penduduk desa (Gurun)</t>
+  </si>
+  <si>
+    <t>Villager (Jungle)</t>
+  </si>
+  <si>
+    <t>Penduduk desa (Hutan)</t>
+  </si>
+  <si>
+    <t>Villager (Plains)</t>
+  </si>
+  <si>
+    <t>Penduduk desa (Dataran)</t>
+  </si>
+  <si>
+    <t>Villager (Savanna)</t>
+  </si>
+  <si>
+    <t>Penduduk desa (Savana)</t>
+  </si>
+  <si>
+    <t>Villager (Snowy Tundra)</t>
+  </si>
+  <si>
+    <t>Penduduk desa (Tundra Bersalju)</t>
+  </si>
+  <si>
+    <t>Villager (Swamp)</t>
+  </si>
+  <si>
+    <t>Penduduk desa (Rawa)</t>
+  </si>
+  <si>
+    <t>Villager (Taiga)</t>
+  </si>
+  <si>
+    <t>Penduduk desa (Taiga)</t>
+  </si>
+  <si>
+    <t>Virtual Youtuber</t>
+  </si>
+  <si>
+    <t>Youtuber Virtual</t>
+  </si>
+  <si>
+    <t>Vocaloid</t>
+  </si>
+  <si>
+    <t>Voltron</t>
+  </si>
+  <si>
+    <t>Wakfu</t>
+  </si>
+  <si>
+    <t>Walking Dead</t>
+  </si>
+  <si>
+    <t>Wall-E</t>
+  </si>
+  <si>
+    <t>Wallace and Gromit</t>
+  </si>
+  <si>
+    <t>Wallace dan Gromit</t>
+  </si>
+  <si>
+    <t>War of the Worlds</t>
+  </si>
+  <si>
+    <t>Perang Dunia</t>
+  </si>
+  <si>
+    <t>Warcraft</t>
+  </si>
+  <si>
+    <t>Warframe</t>
+  </si>
+  <si>
+    <t>Warhammer</t>
+  </si>
+  <si>
+    <t>Warrior Cats</t>
+  </si>
+  <si>
+    <t>Kucing Prajurit</t>
+  </si>
+  <si>
+    <t>We Bear Bears</t>
+  </si>
+  <si>
+    <t>Kami Beruang Beruang</t>
+  </si>
+  <si>
+    <t>We Happy Few</t>
+  </si>
+  <si>
+    <t>Kami Sedikit Senang</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>Cuaca</t>
+  </si>
+  <si>
+    <t>Welcome Home</t>
+  </si>
+  <si>
+    <t>Selamat datang di rumah</t>
+  </si>
+  <si>
+    <t>Who is this?</t>
+  </si>
+  <si>
+    <t>Siapa ini?</t>
+  </si>
+  <si>
+    <t>Wild Update</t>
+  </si>
+  <si>
+    <t>Pembaruan Liar</t>
+  </si>
+  <si>
+    <t>Wings of Fire</t>
+  </si>
+  <si>
+    <t>Sayap Api</t>
+  </si>
+  <si>
+    <t>Winnie the Pooh</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>Musim dingin</t>
+  </si>
+  <si>
+    <t>Witcher</t>
+  </si>
+  <si>
+    <t>Wonderful Wonder World</t>
+  </si>
+  <si>
+    <t>Dunia Keajaiban yang Indah</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>Kayu</t>
+  </si>
+  <si>
+    <t>Wool</t>
+  </si>
+  <si>
+    <t>Wol</t>
+  </si>
+  <si>
+    <t>Work Safety Helmet</t>
+  </si>
+  <si>
+    <t>Helm Keselamatan Kerja</t>
+  </si>
+  <si>
+    <t>Wreck It Ralph</t>
+  </si>
+  <si>
+    <t>Wybel</t>
+  </si>
+  <si>
+    <t>Wynncraft</t>
+  </si>
+  <si>
+    <t>X-Men</t>
+  </si>
+  <si>
+    <t>Xenoblade Chronicles</t>
+  </si>
+  <si>
+    <t>Yandere Simulator</t>
+  </si>
+  <si>
+    <t>Simulator Yandere</t>
+  </si>
+  <si>
+    <t>Yellow Submarine</t>
+  </si>
+  <si>
+    <t>Kapal Selam Kuning</t>
+  </si>
+  <si>
+    <t>Yokai</t>
+  </si>
+  <si>
+    <t>Yooka Laylee</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>Muda</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>Yu-Gi-Oh</t>
+  </si>
+  <si>
+    <t>Yume Nikki</t>
+  </si>
+  <si>
+    <t>Zero no Tsukaima</t>
+  </si>
+  <si>
+    <t>Zero Wing</t>
+  </si>
+  <si>
+    <t>Zodiac Sign</t>
+  </si>
+  <si>
+    <t>Zodiak</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>Zombie (Vanilla)</t>
+  </si>
+  <si>
+    <t>Zootopia</t>
+  </si>
+  <si>
     <t>Ultrakill</t>
-  </si>
-  <si>
-    <t>Umineko - When They Cry</t>
-  </si>
-  <si>
-    <t>Umineko - Ketika Mereka Menangis</t>
-  </si>
-  <si>
-    <t>Undertale</t>
-  </si>
-  <si>
-    <t>Undertale AU</t>
-  </si>
-  <si>
-    <t>Undertale Yellow</t>
-  </si>
-  <si>
-    <t>Undertale Kuning</t>
-  </si>
-  <si>
-    <t>Universal Symbol</t>
-  </si>
-  <si>
-    <t>Simbol Universal</t>
-  </si>
-  <si>
-    <t>Up</t>
-  </si>
-  <si>
-    <t>Urban Wildlife</t>
-  </si>
-  <si>
-    <t>Satwa Liar Perkotaan</t>
-  </si>
-  <si>
-    <t>V for Vendetta</t>
-  </si>
-  <si>
-    <t>V untuk Vendetta</t>
-  </si>
-  <si>
-    <t>Valentines</t>
-  </si>
-  <si>
-    <t>Kasih Sayang</t>
-  </si>
-  <si>
-    <t>Valorant</t>
-  </si>
-  <si>
-    <t>Vanilla (removed)</t>
-  </si>
-  <si>
-    <t>Vanila (dihapus)</t>
-  </si>
-  <si>
-    <t>Vanilla Block</t>
-  </si>
-  <si>
-    <t>Blok Vanilla</t>
-  </si>
-  <si>
-    <t>Vanilla Food</t>
-  </si>
-  <si>
-    <t>Makanan Vanilla</t>
-  </si>
-  <si>
-    <t>Vanilla Helmet</t>
-  </si>
-  <si>
-    <t>Helm Vanilla</t>
-  </si>
-  <si>
-    <t>Vanilla Item</t>
-  </si>
-  <si>
-    <t>Item Vanilla</t>
-  </si>
-  <si>
-    <t>Vanilla Mob</t>
-  </si>
-  <si>
-    <t>Vault Hunters</t>
-  </si>
-  <si>
-    <t>Pemburu Kubah</t>
-  </si>
-  <si>
-    <t>Vegetable</t>
-  </si>
-  <si>
-    <t>Sayuran</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>Kendaraan</t>
-  </si>
-  <si>
-    <t>Vikings</t>
-  </si>
-  <si>
-    <t>Viking</t>
-  </si>
-  <si>
-    <t>Villager</t>
-  </si>
-  <si>
-    <t>Penduduk desa</t>
-  </si>
-  <si>
-    <t>Villager (Desert)</t>
-  </si>
-  <si>
-    <t>Penduduk desa (Gurun)</t>
-  </si>
-  <si>
-    <t>Villager (Jungle)</t>
-  </si>
-  <si>
-    <t>Penduduk desa (Hutan)</t>
-  </si>
-  <si>
-    <t>Villager (Plains)</t>
-  </si>
-  <si>
-    <t>Penduduk desa (Dataran)</t>
-  </si>
-  <si>
-    <t>Villager (Savanna)</t>
-  </si>
-  <si>
-    <t>Penduduk desa (Savana)</t>
-  </si>
-  <si>
-    <t>Villager (Snowy Tundra)</t>
-  </si>
-  <si>
-    <t>Penduduk desa (Tundra Bersalju)</t>
-  </si>
-  <si>
-    <t>Villager (Swamp)</t>
-  </si>
-  <si>
-    <t>Penduduk desa (Rawa)</t>
-  </si>
-  <si>
-    <t>Villager (Taiga)</t>
-  </si>
-  <si>
-    <t>Penduduk desa (Taiga)</t>
-  </si>
-  <si>
-    <t>Virtual Youtuber</t>
-  </si>
-  <si>
-    <t>Youtuber Virtual</t>
-  </si>
-  <si>
-    <t>Vocaloid</t>
-  </si>
-  <si>
-    <t>Voltron</t>
-  </si>
-  <si>
-    <t>Wakfu</t>
-  </si>
-  <si>
-    <t>Walking Dead</t>
-  </si>
-  <si>
-    <t>Wall-E</t>
-  </si>
-  <si>
-    <t>Wallace and Gromit</t>
-  </si>
-  <si>
-    <t>Wallace dan Gromit</t>
-  </si>
-  <si>
-    <t>War of the Worlds</t>
-  </si>
-  <si>
-    <t>Perang Dunia</t>
-  </si>
-  <si>
-    <t>Warcraft</t>
-  </si>
-  <si>
-    <t>Warframe</t>
-  </si>
-  <si>
-    <t>Warhammer</t>
-  </si>
-  <si>
-    <t>Warrior Cats</t>
-  </si>
-  <si>
-    <t>Kucing Prajurit</t>
-  </si>
-  <si>
-    <t>We Bear Bears</t>
-  </si>
-  <si>
-    <t>Kami Beruang Beruang</t>
-  </si>
-  <si>
-    <t>We Happy Few</t>
-  </si>
-  <si>
-    <t>Kami Sedikit Senang</t>
-  </si>
-  <si>
-    <t>Weather</t>
-  </si>
-  <si>
-    <t>Cuaca</t>
-  </si>
-  <si>
-    <t>Welcome Home</t>
-  </si>
-  <si>
-    <t>Selamat datang di rumah</t>
-  </si>
-  <si>
-    <t>Who is this?</t>
-  </si>
-  <si>
-    <t>Siapa ini?</t>
-  </si>
-  <si>
-    <t>Wild Update</t>
-  </si>
-  <si>
-    <t>Pembaruan Liar</t>
-  </si>
-  <si>
-    <t>Wings of Fire</t>
-  </si>
-  <si>
-    <t>Sayap Api</t>
-  </si>
-  <si>
-    <t>Winnie the Pooh</t>
-  </si>
-  <si>
-    <t>Winter</t>
-  </si>
-  <si>
-    <t>Musim dingin</t>
-  </si>
-  <si>
-    <t>Witcher</t>
-  </si>
-  <si>
-    <t>Wonderful Wonder World</t>
-  </si>
-  <si>
-    <t>Dunia Keajaiban yang Indah</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>Kayu</t>
-  </si>
-  <si>
-    <t>Wool</t>
-  </si>
-  <si>
-    <t>Wol</t>
-  </si>
-  <si>
-    <t>Work Safety Helmet</t>
-  </si>
-  <si>
-    <t>Helm Keselamatan Kerja</t>
-  </si>
-  <si>
-    <t>Wreck It Ralph</t>
-  </si>
-  <si>
-    <t>Wybel</t>
-  </si>
-  <si>
-    <t>Wynncraft</t>
-  </si>
-  <si>
-    <t>X-Men</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles</t>
-  </si>
-  <si>
-    <t>Yandere Simulator</t>
-  </si>
-  <si>
-    <t>Simulator Yandere</t>
-  </si>
-  <si>
-    <t>Yellow Submarine</t>
-  </si>
-  <si>
-    <t>Kapal Selam Kuning</t>
-  </si>
-  <si>
-    <t>Yokai</t>
-  </si>
-  <si>
-    <t>Yooka Laylee</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>Muda</t>
-  </si>
-  <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>Yu-Gi-Oh</t>
-  </si>
-  <si>
-    <t>Yume Nikki</t>
-  </si>
-  <si>
-    <t>Zero no Tsukaima</t>
-  </si>
-  <si>
-    <t>Zero Wing</t>
-  </si>
-  <si>
-    <t>Zodiac Sign</t>
-  </si>
-  <si>
-    <t>Zodiak</t>
-  </si>
-  <si>
-    <t>Zombie</t>
-  </si>
-  <si>
-    <t>Zombie (Vanilla)</t>
-  </si>
-  <si>
-    <t>Zootopia</t>
   </si>
   <si>
     <t>Hypixel (Mutations) Tag</t>
@@ -6102,7 +6105,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1177"/>
+  <dimension ref="A1:B1178"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -15514,19 +15517,27 @@
         <v>1910</v>
       </c>
       <c r="B1176" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="B1177" t="s">
         <v>1912</v>
       </c>
     </row>
+    <row r="1178" spans="1:2">
+      <c r="A1178" t="s">
+        <v>1913</v>
+      </c>
+      <c r="B1178" t="s">
+        <v>1913</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1177"/>
+  <autoFilter ref="A1:B1178"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1915">
   <si>
     <t>en</t>
   </si>
@@ -3944,6 +3944,9 @@
   </si>
   <si>
     <t>Objek Sumber Terbuka</t>
+  </si>
+  <si>
+    <t>Opus Magnum</t>
   </si>
   <si>
     <t>Orb</t>
@@ -6105,7 +6108,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1178"/>
+  <dimension ref="A1:B1179"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -12509,52 +12512,52 @@
         <v>1311</v>
       </c>
       <c r="B800" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B801" t="s">
         <v>1313</v>
-      </c>
-      <c r="B801" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B802" t="s">
         <v>1315</v>
-      </c>
-      <c r="B802" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B803" t="s">
         <v>1317</v>
-      </c>
-      <c r="B803" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B804" t="s">
         <v>1319</v>
-      </c>
-      <c r="B804" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B805" t="s">
         <v>1321</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B806" t="s">
         <v>1323</v>
@@ -12581,84 +12584,84 @@
         <v>1326</v>
       </c>
       <c r="B809" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B810" t="s">
         <v>1328</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B811" t="s">
         <v>1330</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B812" t="s">
         <v>1332</v>
-      </c>
-      <c r="B812" t="s">
-        <v>1333</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B813" t="s">
         <v>1334</v>
-      </c>
-      <c r="B813" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B814" t="s">
         <v>1336</v>
-      </c>
-      <c r="B814" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B815" t="s">
         <v>1338</v>
-      </c>
-      <c r="B815" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B816" t="s">
         <v>1340</v>
-      </c>
-      <c r="B816" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B817" t="s">
         <v>1342</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1343</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B818" t="s">
         <v>1344</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="B819" t="s">
         <v>1346</v>
@@ -12669,20 +12672,20 @@
         <v>1347</v>
       </c>
       <c r="B820" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B821" t="s">
         <v>1349</v>
-      </c>
-      <c r="B821" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
       <c r="B822" t="s">
         <v>1351</v>
@@ -12701,12 +12704,12 @@
         <v>1353</v>
       </c>
       <c r="B824" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B825" t="s">
         <v>1355</v>
@@ -12717,12 +12720,12 @@
         <v>1356</v>
       </c>
       <c r="B826" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
       <c r="B827" t="s">
         <v>1358</v>
@@ -12749,12 +12752,12 @@
         <v>1361</v>
       </c>
       <c r="B830" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="B831" t="s">
         <v>1363</v>
@@ -12797,36 +12800,36 @@
         <v>1368</v>
       </c>
       <c r="B836" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B837" t="s">
         <v>1370</v>
-      </c>
-      <c r="B837" t="s">
-        <v>1371</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B838" t="s">
         <v>1372</v>
-      </c>
-      <c r="B838" t="s">
-        <v>1373</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B839" t="s">
         <v>1374</v>
-      </c>
-      <c r="B839" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="B840" t="s">
         <v>1376</v>
@@ -12837,20 +12840,20 @@
         <v>1377</v>
       </c>
       <c r="B841" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B842" t="s">
         <v>1379</v>
-      </c>
-      <c r="B842" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
       <c r="B843" t="s">
         <v>1381</v>
@@ -12877,108 +12880,108 @@
         <v>1384</v>
       </c>
       <c r="B846" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B847" t="s">
         <v>1386</v>
-      </c>
-      <c r="B847" t="s">
-        <v>1387</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B848" t="s">
         <v>1388</v>
-      </c>
-      <c r="B848" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B849" t="s">
         <v>1390</v>
-      </c>
-      <c r="B849" t="s">
-        <v>1391</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B850" t="s">
         <v>1392</v>
-      </c>
-      <c r="B850" t="s">
-        <v>1393</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B851" t="s">
         <v>1394</v>
-      </c>
-      <c r="B851" t="s">
-        <v>1395</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B852" t="s">
         <v>1396</v>
-      </c>
-      <c r="B852" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B853" t="s">
         <v>1398</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1399</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B854" t="s">
         <v>1400</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B855" t="s">
         <v>1402</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B856" t="s">
         <v>1404</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B857" t="s">
         <v>1406</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B858" t="s">
         <v>1408</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1409</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="B859" t="s">
         <v>1410</v>
@@ -13013,12 +13016,12 @@
         <v>1414</v>
       </c>
       <c r="B863" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B864" t="s">
         <v>1416</v>
@@ -13069,36 +13072,36 @@
         <v>1422</v>
       </c>
       <c r="B870" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B871" t="s">
         <v>1424</v>
-      </c>
-      <c r="B871" t="s">
-        <v>1425</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B872" t="s">
         <v>1426</v>
-      </c>
-      <c r="B872" t="s">
-        <v>1427</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B873" t="s">
         <v>1428</v>
-      </c>
-      <c r="B873" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B874" t="s">
         <v>1430</v>
@@ -13109,36 +13112,36 @@
         <v>1431</v>
       </c>
       <c r="B875" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B876" t="s">
         <v>1433</v>
-      </c>
-      <c r="B876" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B877" t="s">
         <v>1435</v>
-      </c>
-      <c r="B877" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B878" t="s">
         <v>1437</v>
-      </c>
-      <c r="B878" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B879" t="s">
         <v>1439</v>
@@ -13149,28 +13152,28 @@
         <v>1440</v>
       </c>
       <c r="B880" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B881" t="s">
         <v>1442</v>
-      </c>
-      <c r="B881" t="s">
-        <v>1443</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B882" t="s">
         <v>1444</v>
-      </c>
-      <c r="B882" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B883" t="s">
         <v>1446</v>
@@ -13189,44 +13192,44 @@
         <v>1448</v>
       </c>
       <c r="B885" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B886" t="s">
         <v>1450</v>
-      </c>
-      <c r="B886" t="s">
-        <v>1451</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B887" t="s">
         <v>1452</v>
-      </c>
-      <c r="B887" t="s">
-        <v>1453</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B888" t="s">
         <v>1454</v>
-      </c>
-      <c r="B888" t="s">
-        <v>1455</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B889" t="s">
         <v>1456</v>
-      </c>
-      <c r="B889" t="s">
-        <v>1457</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B890" t="s">
         <v>1458</v>
@@ -13237,12 +13240,12 @@
         <v>1459</v>
       </c>
       <c r="B891" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B892" t="s">
         <v>1461</v>
@@ -13253,36 +13256,36 @@
         <v>1462</v>
       </c>
       <c r="B893" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B894" t="s">
         <v>1464</v>
-      </c>
-      <c r="B894" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B895" t="s">
         <v>1466</v>
-      </c>
-      <c r="B895" t="s">
-        <v>1467</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B896" t="s">
         <v>1468</v>
-      </c>
-      <c r="B896" t="s">
-        <v>1469</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B897" t="s">
         <v>1470</v>
@@ -13301,44 +13304,44 @@
         <v>1472</v>
       </c>
       <c r="B899" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B900" t="s">
         <v>1474</v>
-      </c>
-      <c r="B900" t="s">
-        <v>1475</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B901" t="s">
         <v>1476</v>
-      </c>
-      <c r="B901" t="s">
-        <v>1477</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B902" t="s">
         <v>1478</v>
-      </c>
-      <c r="B902" t="s">
-        <v>1479</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B903" t="s">
         <v>1480</v>
-      </c>
-      <c r="B903" t="s">
-        <v>1481</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B904" t="s">
         <v>1482</v>
@@ -13389,36 +13392,36 @@
         <v>1488</v>
       </c>
       <c r="B910" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B911" t="s">
         <v>1490</v>
-      </c>
-      <c r="B911" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B912" t="s">
         <v>1492</v>
-      </c>
-      <c r="B912" t="s">
-        <v>1493</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B913" t="s">
         <v>1494</v>
-      </c>
-      <c r="B913" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="B914" t="s">
         <v>1496</v>
@@ -13445,44 +13448,44 @@
         <v>1499</v>
       </c>
       <c r="B917" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B918" t="s">
         <v>1501</v>
-      </c>
-      <c r="B918" t="s">
-        <v>1502</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B919" t="s">
         <v>1503</v>
-      </c>
-      <c r="B919" t="s">
-        <v>1504</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B920" t="s">
         <v>1505</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1506</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B921" t="s">
         <v>1507</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B922" t="s">
         <v>1509</v>
@@ -13501,36 +13504,36 @@
         <v>1511</v>
       </c>
       <c r="B924" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B925" t="s">
         <v>1513</v>
-      </c>
-      <c r="B925" t="s">
-        <v>1514</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B926" t="s">
         <v>1515</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B927" t="s">
         <v>1517</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B928" t="s">
         <v>1519</v>
@@ -13541,20 +13544,20 @@
         <v>1520</v>
       </c>
       <c r="B929" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B930" t="s">
         <v>1522</v>
-      </c>
-      <c r="B930" t="s">
-        <v>1523</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="B931" t="s">
         <v>1524</v>
@@ -13565,20 +13568,20 @@
         <v>1525</v>
       </c>
       <c r="B932" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B933" t="s">
         <v>1527</v>
-      </c>
-      <c r="B933" t="s">
-        <v>1528</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B934" t="s">
         <v>1529</v>
@@ -13589,12 +13592,12 @@
         <v>1530</v>
       </c>
       <c r="B935" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B936" t="s">
         <v>1532</v>
@@ -13605,20 +13608,20 @@
         <v>1533</v>
       </c>
       <c r="B937" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B938" t="s">
         <v>1535</v>
-      </c>
-      <c r="B938" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B939" t="s">
         <v>1537</v>
@@ -13629,12 +13632,12 @@
         <v>1538</v>
       </c>
       <c r="B940" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="B941" t="s">
         <v>1540</v>
@@ -13661,28 +13664,28 @@
         <v>1543</v>
       </c>
       <c r="B944" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B945" t="s">
         <v>1545</v>
-      </c>
-      <c r="B945" t="s">
-        <v>1546</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B946" t="s">
         <v>1547</v>
-      </c>
-      <c r="B946" t="s">
-        <v>1548</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B947" t="s">
         <v>1549</v>
@@ -13725,36 +13728,36 @@
         <v>1554</v>
       </c>
       <c r="B952" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B953" t="s">
         <v>1556</v>
-      </c>
-      <c r="B953" t="s">
-        <v>1557</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B954" t="s">
         <v>1558</v>
-      </c>
-      <c r="B954" t="s">
-        <v>1559</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B955" t="s">
         <v>1560</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1561</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B956" t="s">
         <v>1562</v>
@@ -13781,52 +13784,52 @@
         <v>1565</v>
       </c>
       <c r="B959" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B960" t="s">
         <v>1567</v>
-      </c>
-      <c r="B960" t="s">
-        <v>1568</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B961" t="s">
         <v>1569</v>
-      </c>
-      <c r="B961" t="s">
-        <v>1570</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B962" t="s">
         <v>1571</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1572</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B963" t="s">
         <v>1573</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1574</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B964" t="s">
         <v>1575</v>
-      </c>
-      <c r="B964" t="s">
-        <v>1576</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="B965" t="s">
         <v>1577</v>
@@ -13853,12 +13856,12 @@
         <v>1580</v>
       </c>
       <c r="B968" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B969" t="s">
         <v>1582</v>
@@ -13877,44 +13880,44 @@
         <v>1584</v>
       </c>
       <c r="B971" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B972" t="s">
         <v>1586</v>
-      </c>
-      <c r="B972" t="s">
-        <v>1587</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B973" t="s">
         <v>1588</v>
-      </c>
-      <c r="B973" t="s">
-        <v>1589</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B974" t="s">
         <v>1590</v>
-      </c>
-      <c r="B974" t="s">
-        <v>1591</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B975" t="s">
         <v>1592</v>
-      </c>
-      <c r="B975" t="s">
-        <v>1593</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
       <c r="B976" t="s">
         <v>1594</v>
@@ -13925,28 +13928,28 @@
         <v>1595</v>
       </c>
       <c r="B977" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B978" t="s">
         <v>1597</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1598</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B979" t="s">
         <v>1599</v>
-      </c>
-      <c r="B979" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
       <c r="B980" t="s">
         <v>1601</v>
@@ -13957,20 +13960,20 @@
         <v>1602</v>
       </c>
       <c r="B981" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B982" t="s">
         <v>1604</v>
-      </c>
-      <c r="B982" t="s">
-        <v>1605</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B983" t="s">
         <v>1606</v>
@@ -14005,52 +14008,52 @@
         <v>1610</v>
       </c>
       <c r="B987" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B988" t="s">
         <v>1612</v>
-      </c>
-      <c r="B988" t="s">
-        <v>1613</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B989" t="s">
         <v>1614</v>
-      </c>
-      <c r="B989" t="s">
-        <v>1615</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B990" t="s">
         <v>1616</v>
-      </c>
-      <c r="B990" t="s">
-        <v>1617</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B991" t="s">
         <v>1618</v>
-      </c>
-      <c r="B991" t="s">
-        <v>1619</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B992" t="s">
         <v>1620</v>
-      </c>
-      <c r="B992" t="s">
-        <v>1621</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="B993" t="s">
         <v>1622</v>
@@ -14061,20 +14064,20 @@
         <v>1623</v>
       </c>
       <c r="B994" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B995" t="s">
         <v>1625</v>
-      </c>
-      <c r="B995" t="s">
-        <v>1626</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="B996" t="s">
         <v>1627</v>
@@ -14101,12 +14104,12 @@
         <v>1630</v>
       </c>
       <c r="B999" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
       <c r="B1000" t="s">
         <v>1632</v>
@@ -14117,20 +14120,20 @@
         <v>1633</v>
       </c>
       <c r="B1001" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B1002" t="s">
         <v>1635</v>
-      </c>
-      <c r="B1002" t="s">
-        <v>1636</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="B1003" t="s">
         <v>1637</v>
@@ -14149,28 +14152,28 @@
         <v>1639</v>
       </c>
       <c r="B1005" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B1006" t="s">
         <v>1641</v>
-      </c>
-      <c r="B1006" t="s">
-        <v>1642</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B1007" t="s">
         <v>1643</v>
-      </c>
-      <c r="B1007" t="s">
-        <v>1644</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="B1008" t="s">
         <v>1645</v>
@@ -14181,20 +14184,20 @@
         <v>1646</v>
       </c>
       <c r="B1009" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B1010" t="s">
         <v>1648</v>
-      </c>
-      <c r="B1010" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="B1011" t="s">
         <v>1650</v>
@@ -14205,20 +14208,20 @@
         <v>1651</v>
       </c>
       <c r="B1012" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B1013" t="s">
         <v>1653</v>
-      </c>
-      <c r="B1013" t="s">
-        <v>1654</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="B1014" t="s">
         <v>1655</v>
@@ -14253,20 +14256,20 @@
         <v>1659</v>
       </c>
       <c r="B1018" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B1019" t="s">
         <v>1661</v>
-      </c>
-      <c r="B1019" t="s">
-        <v>1662</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="B1020" t="s">
         <v>1663</v>
@@ -14277,28 +14280,28 @@
         <v>1664</v>
       </c>
       <c r="B1021" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B1022" t="s">
         <v>1666</v>
-      </c>
-      <c r="B1022" t="s">
-        <v>1667</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B1023" t="s">
         <v>1668</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>1669</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="B1024" t="s">
         <v>1670</v>
@@ -14309,12 +14312,12 @@
         <v>1671</v>
       </c>
       <c r="B1025" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="B1026" t="s">
         <v>1673</v>
@@ -14333,12 +14336,12 @@
         <v>1675</v>
       </c>
       <c r="B1028" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="B1029" t="s">
         <v>1677</v>
@@ -14349,12 +14352,12 @@
         <v>1678</v>
       </c>
       <c r="B1030" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
       <c r="B1031" t="s">
         <v>1680</v>
@@ -14373,12 +14376,12 @@
         <v>1682</v>
       </c>
       <c r="B1033" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="B1034" t="s">
         <v>1684</v>
@@ -14397,12 +14400,12 @@
         <v>1686</v>
       </c>
       <c r="B1036" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="B1037" t="s">
         <v>1688</v>
@@ -14413,36 +14416,36 @@
         <v>1689</v>
       </c>
       <c r="B1038" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B1039" t="s">
         <v>1691</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>1692</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B1040" t="s">
         <v>1693</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>1694</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B1041" t="s">
         <v>1695</v>
-      </c>
-      <c r="B1041" t="s">
-        <v>1696</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="B1042" t="s">
         <v>1697</v>
@@ -14453,12 +14456,12 @@
         <v>1698</v>
       </c>
       <c r="B1043" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="B1044" t="s">
         <v>1700</v>
@@ -14469,44 +14472,44 @@
         <v>1701</v>
       </c>
       <c r="B1045" t="s">
-        <v>1702</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B1046" t="s">
         <v>1703</v>
-      </c>
-      <c r="B1046" t="s">
-        <v>1704</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B1047" t="s">
         <v>1705</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>1706</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B1048" t="s">
         <v>1707</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>1708</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B1049" t="s">
         <v>1709</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>1710</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="B1050" t="s">
         <v>1711</v>
@@ -14541,52 +14544,52 @@
         <v>1715</v>
       </c>
       <c r="B1054" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
+        <v>1716</v>
+      </c>
+      <c r="B1055" t="s">
         <v>1717</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>1718</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B1056" t="s">
         <v>1719</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>1720</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B1057" t="s">
         <v>1721</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>1722</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B1058" t="s">
         <v>1723</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B1059" t="s">
         <v>1725</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1726</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="B1060" t="s">
         <v>1727</v>
@@ -14597,12 +14600,12 @@
         <v>1728</v>
       </c>
       <c r="B1061" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="B1062" t="s">
         <v>1730</v>
@@ -14621,52 +14624,52 @@
         <v>1732</v>
       </c>
       <c r="B1064" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B1065" t="s">
         <v>1734</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B1066" t="s">
         <v>1736</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>1737</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B1067" t="s">
         <v>1738</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>1739</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B1068" t="s">
         <v>1740</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>1741</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B1069" t="s">
         <v>1742</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>1743</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="B1070" t="s">
         <v>1744</v>
@@ -14677,12 +14680,12 @@
         <v>1745</v>
       </c>
       <c r="B1071" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="B1072" t="s">
         <v>1747</v>
@@ -14701,12 +14704,12 @@
         <v>1749</v>
       </c>
       <c r="B1074" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="B1075" t="s">
         <v>1751</v>
@@ -14749,20 +14752,20 @@
         <v>1756</v>
       </c>
       <c r="B1080" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B1081" t="s">
         <v>1758</v>
-      </c>
-      <c r="B1081" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="B1082" t="s">
         <v>1760</v>
@@ -14781,20 +14784,20 @@
         <v>1762</v>
       </c>
       <c r="B1084" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
+        <v>1763</v>
+      </c>
+      <c r="B1085" t="s">
         <v>1764</v>
-      </c>
-      <c r="B1085" t="s">
-        <v>1765</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
       <c r="B1086" t="s">
         <v>1766</v>
@@ -14805,36 +14808,36 @@
         <v>1767</v>
       </c>
       <c r="B1087" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B1088" t="s">
         <v>1769</v>
-      </c>
-      <c r="B1088" t="s">
-        <v>1770</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
+        <v>1770</v>
+      </c>
+      <c r="B1089" t="s">
         <v>1771</v>
-      </c>
-      <c r="B1089" t="s">
-        <v>1772</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B1090" t="s">
         <v>1773</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B1091" t="s">
         <v>1775</v>
@@ -14853,44 +14856,44 @@
         <v>1777</v>
       </c>
       <c r="B1093" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B1094" t="s">
         <v>1779</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>1780</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>1780</v>
+      </c>
+      <c r="B1095" t="s">
         <v>1781</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>1782</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
+        <v>1782</v>
+      </c>
+      <c r="B1096" t="s">
         <v>1783</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>1784</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>1784</v>
+      </c>
+      <c r="B1097" t="s">
         <v>1785</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>1786</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="B1098" t="s">
         <v>1787</v>
@@ -14901,20 +14904,20 @@
         <v>1788</v>
       </c>
       <c r="B1099" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B1100" t="s">
         <v>1790</v>
-      </c>
-      <c r="B1100" t="s">
-        <v>1791</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="B1101" t="s">
         <v>1792</v>
@@ -14933,12 +14936,12 @@
         <v>1794</v>
       </c>
       <c r="B1103" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="B1104" t="s">
         <v>1796</v>
@@ -14957,20 +14960,20 @@
         <v>1798</v>
       </c>
       <c r="B1106" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B1107" t="s">
         <v>1800</v>
-      </c>
-      <c r="B1107" t="s">
-        <v>1801</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="B1108" t="s">
         <v>1802</v>
@@ -14981,28 +14984,28 @@
         <v>1803</v>
       </c>
       <c r="B1109" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B1110" t="s">
         <v>1805</v>
-      </c>
-      <c r="B1110" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
+        <v>1806</v>
+      </c>
+      <c r="B1111" t="s">
         <v>1807</v>
-      </c>
-      <c r="B1111" t="s">
-        <v>1808</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="B1112" t="s">
         <v>1809</v>
@@ -15013,44 +15016,44 @@
         <v>1810</v>
       </c>
       <c r="B1113" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
+        <v>1811</v>
+      </c>
+      <c r="B1114" t="s">
         <v>1812</v>
-      </c>
-      <c r="B1114" t="s">
-        <v>1813</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
+        <v>1813</v>
+      </c>
+      <c r="B1115" t="s">
         <v>1814</v>
-      </c>
-      <c r="B1115" t="s">
-        <v>1815</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
+        <v>1815</v>
+      </c>
+      <c r="B1116" t="s">
         <v>1816</v>
-      </c>
-      <c r="B1116" t="s">
-        <v>1817</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B1117" t="s">
         <v>1818</v>
-      </c>
-      <c r="B1117" t="s">
-        <v>1819</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="B1118" t="s">
         <v>1820</v>
@@ -15061,108 +15064,108 @@
         <v>1821</v>
       </c>
       <c r="B1119" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1120" t="s">
         <v>1823</v>
-      </c>
-      <c r="B1120" t="s">
-        <v>1824</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B1121" t="s">
         <v>1825</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1122" t="s">
         <v>1827</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>1828</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B1123" t="s">
         <v>1829</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>1830</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1831</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1832</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1833</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1834</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1835</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1836</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1837</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1838</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1839</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1840</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1841</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1843</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1845</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="B1132" t="s">
         <v>1847</v>
@@ -15205,20 +15208,20 @@
         <v>1852</v>
       </c>
       <c r="B1137" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1854</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1855</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1856</v>
+        <v>1855</v>
       </c>
       <c r="B1139" t="s">
         <v>1856</v>
@@ -15245,68 +15248,68 @@
         <v>1859</v>
       </c>
       <c r="B1142" t="s">
-        <v>1860</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B1143" t="s">
         <v>1861</v>
-      </c>
-      <c r="B1143" t="s">
-        <v>1862</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1144" t="s">
         <v>1863</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>1864</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>1864</v>
+      </c>
+      <c r="B1145" t="s">
         <v>1865</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>1866</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B1146" t="s">
         <v>1867</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>1868</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B1147" t="s">
         <v>1869</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>1870</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B1148" t="s">
         <v>1871</v>
-      </c>
-      <c r="B1148" t="s">
-        <v>1872</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B1149" t="s">
         <v>1873</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>1874</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="B1150" t="s">
         <v>1875</v>
@@ -15317,12 +15320,12 @@
         <v>1876</v>
       </c>
       <c r="B1151" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="B1152" t="s">
         <v>1878</v>
@@ -15333,36 +15336,36 @@
         <v>1879</v>
       </c>
       <c r="B1153" t="s">
-        <v>1880</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B1154" t="s">
         <v>1881</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>1882</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B1155" t="s">
         <v>1883</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>1884</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B1156" t="s">
         <v>1885</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>1886</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="B1157" t="s">
         <v>1887</v>
@@ -15405,20 +15408,20 @@
         <v>1892</v>
       </c>
       <c r="B1162" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B1163" t="s">
         <v>1894</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>1895</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B1164" t="s">
         <v>1896</v>
@@ -15437,12 +15440,12 @@
         <v>1898</v>
       </c>
       <c r="B1166" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B1167" t="s">
         <v>1900</v>
@@ -15485,12 +15488,12 @@
         <v>1905</v>
       </c>
       <c r="B1172" t="s">
-        <v>1906</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
       <c r="B1173" t="s">
         <v>1907</v>
@@ -15525,19 +15528,27 @@
         <v>1911</v>
       </c>
       <c r="B1177" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="B1178" t="s">
         <v>1913</v>
       </c>
     </row>
+    <row r="1179" spans="1:2">
+      <c r="A1179" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B1179" t="s">
+        <v>1914</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1178"/>
+  <autoFilter ref="A1:B1179"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1179</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1916">
   <si>
     <t>en</t>
   </si>
@@ -815,6 +815,9 @@
   </si>
   <si>
     <t>Cawan</t>
+  </si>
+  <si>
+    <t>Chaos Cubed</t>
   </si>
   <si>
     <t>Charlie and the Chocolate Factory</t>
@@ -6108,7 +6111,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1179"/>
+  <dimension ref="A1:B1180"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -7416,60 +7419,60 @@
         <v>266</v>
       </c>
       <c r="B163" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>267</v>
+      </c>
+      <c r="B164" t="s">
         <v>268</v>
-      </c>
-      <c r="B164" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
+        <v>269</v>
+      </c>
+      <c r="B165" t="s">
         <v>270</v>
-      </c>
-      <c r="B165" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
+        <v>271</v>
+      </c>
+      <c r="B166" t="s">
         <v>272</v>
-      </c>
-      <c r="B166" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
+        <v>273</v>
+      </c>
+      <c r="B167" t="s">
         <v>274</v>
-      </c>
-      <c r="B167" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
+        <v>275</v>
+      </c>
+      <c r="B168" t="s">
         <v>276</v>
-      </c>
-      <c r="B168" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
+        <v>277</v>
+      </c>
+      <c r="B169" t="s">
         <v>278</v>
-      </c>
-      <c r="B169" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B170" t="s">
         <v>280</v>
@@ -7480,44 +7483,44 @@
         <v>281</v>
       </c>
       <c r="B171" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" t="s">
+        <v>282</v>
+      </c>
+      <c r="B172" t="s">
         <v>283</v>
-      </c>
-      <c r="B172" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
+        <v>284</v>
+      </c>
+      <c r="B173" t="s">
         <v>285</v>
-      </c>
-      <c r="B173" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
+        <v>286</v>
+      </c>
+      <c r="B174" t="s">
         <v>287</v>
-      </c>
-      <c r="B174" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
+        <v>288</v>
+      </c>
+      <c r="B175" t="s">
         <v>289</v>
-      </c>
-      <c r="B175" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B176" t="s">
         <v>291</v>
@@ -7560,140 +7563,140 @@
         <v>296</v>
       </c>
       <c r="B181" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
+        <v>297</v>
+      </c>
+      <c r="B182" t="s">
         <v>298</v>
-      </c>
-      <c r="B182" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
+        <v>299</v>
+      </c>
+      <c r="B183" t="s">
         <v>300</v>
-      </c>
-      <c r="B183" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
+        <v>301</v>
+      </c>
+      <c r="B184" t="s">
         <v>302</v>
-      </c>
-      <c r="B184" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
+        <v>303</v>
+      </c>
+      <c r="B185" t="s">
         <v>304</v>
-      </c>
-      <c r="B185" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
+        <v>305</v>
+      </c>
+      <c r="B186" t="s">
         <v>306</v>
-      </c>
-      <c r="B186" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
+        <v>307</v>
+      </c>
+      <c r="B187" t="s">
         <v>308</v>
-      </c>
-      <c r="B187" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
+        <v>309</v>
+      </c>
+      <c r="B188" t="s">
         <v>310</v>
-      </c>
-      <c r="B188" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
+        <v>311</v>
+      </c>
+      <c r="B189" t="s">
         <v>312</v>
-      </c>
-      <c r="B189" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
+        <v>313</v>
+      </c>
+      <c r="B190" t="s">
         <v>314</v>
-      </c>
-      <c r="B190" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
+        <v>315</v>
+      </c>
+      <c r="B191" t="s">
         <v>316</v>
-      </c>
-      <c r="B191" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
+        <v>317</v>
+      </c>
+      <c r="B192" t="s">
         <v>318</v>
-      </c>
-      <c r="B192" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
+        <v>319</v>
+      </c>
+      <c r="B193" t="s">
         <v>320</v>
-      </c>
-      <c r="B193" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
+        <v>321</v>
+      </c>
+      <c r="B194" t="s">
         <v>322</v>
-      </c>
-      <c r="B194" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
+        <v>323</v>
+      </c>
+      <c r="B195" t="s">
         <v>324</v>
-      </c>
-      <c r="B195" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
+        <v>325</v>
+      </c>
+      <c r="B196" t="s">
         <v>326</v>
-      </c>
-      <c r="B196" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
+        <v>327</v>
+      </c>
+      <c r="B197" t="s">
         <v>328</v>
-      </c>
-      <c r="B197" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B198" t="s">
         <v>330</v>
@@ -7704,44 +7707,44 @@
         <v>331</v>
       </c>
       <c r="B199" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
+        <v>332</v>
+      </c>
+      <c r="B200" t="s">
         <v>333</v>
-      </c>
-      <c r="B200" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
+        <v>334</v>
+      </c>
+      <c r="B201" t="s">
         <v>335</v>
-      </c>
-      <c r="B201" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
+        <v>336</v>
+      </c>
+      <c r="B202" t="s">
         <v>337</v>
-      </c>
-      <c r="B202" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
+        <v>338</v>
+      </c>
+      <c r="B203" t="s">
         <v>339</v>
-      </c>
-      <c r="B203" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B204" t="s">
         <v>341</v>
@@ -7752,28 +7755,28 @@
         <v>342</v>
       </c>
       <c r="B205" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
+        <v>343</v>
+      </c>
+      <c r="B206" t="s">
         <v>344</v>
-      </c>
-      <c r="B206" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
+        <v>345</v>
+      </c>
+      <c r="B207" t="s">
         <v>346</v>
-      </c>
-      <c r="B207" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B208" t="s">
         <v>348</v>
@@ -7784,44 +7787,44 @@
         <v>349</v>
       </c>
       <c r="B209" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
+        <v>350</v>
+      </c>
+      <c r="B210" t="s">
         <v>351</v>
-      </c>
-      <c r="B210" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
+        <v>352</v>
+      </c>
+      <c r="B211" t="s">
         <v>353</v>
-      </c>
-      <c r="B211" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
+        <v>354</v>
+      </c>
+      <c r="B212" t="s">
         <v>355</v>
-      </c>
-      <c r="B212" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
+        <v>356</v>
+      </c>
+      <c r="B213" t="s">
         <v>357</v>
-      </c>
-      <c r="B213" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B214" t="s">
         <v>359</v>
@@ -7832,20 +7835,20 @@
         <v>360</v>
       </c>
       <c r="B215" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
+        <v>361</v>
+      </c>
+      <c r="B216" t="s">
         <v>362</v>
-      </c>
-      <c r="B216" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B217" t="s">
         <v>364</v>
@@ -7896,12 +7899,12 @@
         <v>370</v>
       </c>
       <c r="B223" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B224" t="s">
         <v>372</v>
@@ -7912,12 +7915,12 @@
         <v>373</v>
       </c>
       <c r="B225" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B226" t="s">
         <v>375</v>
@@ -7928,28 +7931,28 @@
         <v>376</v>
       </c>
       <c r="B227" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
+        <v>377</v>
+      </c>
+      <c r="B228" t="s">
         <v>378</v>
-      </c>
-      <c r="B228" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
+        <v>379</v>
+      </c>
+      <c r="B229" t="s">
         <v>380</v>
-      </c>
-      <c r="B229" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B230" t="s">
         <v>382</v>
@@ -7960,20 +7963,20 @@
         <v>383</v>
       </c>
       <c r="B231" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
+        <v>384</v>
+      </c>
+      <c r="B232" t="s">
         <v>385</v>
-      </c>
-      <c r="B232" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B233" t="s">
         <v>387</v>
@@ -8000,44 +8003,44 @@
         <v>390</v>
       </c>
       <c r="B236" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
+        <v>391</v>
+      </c>
+      <c r="B237" t="s">
         <v>392</v>
-      </c>
-      <c r="B237" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
+        <v>393</v>
+      </c>
+      <c r="B238" t="s">
         <v>394</v>
-      </c>
-      <c r="B238" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
+        <v>395</v>
+      </c>
+      <c r="B239" t="s">
         <v>396</v>
-      </c>
-      <c r="B239" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
+        <v>397</v>
+      </c>
+      <c r="B240" t="s">
         <v>398</v>
-      </c>
-      <c r="B240" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B241" t="s">
         <v>400</v>
@@ -8048,12 +8051,12 @@
         <v>401</v>
       </c>
       <c r="B242" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="243" spans="1:2">
       <c r="A243" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B243" t="s">
         <v>403</v>
@@ -8064,28 +8067,28 @@
         <v>404</v>
       </c>
       <c r="B244" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="245" spans="1:2">
       <c r="A245" t="s">
+        <v>405</v>
+      </c>
+      <c r="B245" t="s">
         <v>406</v>
-      </c>
-      <c r="B245" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
+        <v>407</v>
+      </c>
+      <c r="B246" t="s">
         <v>408</v>
-      </c>
-      <c r="B246" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B247" t="s">
         <v>410</v>
@@ -8096,20 +8099,20 @@
         <v>411</v>
       </c>
       <c r="B248" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="249" spans="1:2">
       <c r="A249" t="s">
+        <v>412</v>
+      </c>
+      <c r="B249" t="s">
         <v>413</v>
-      </c>
-      <c r="B249" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B250" t="s">
         <v>415</v>
@@ -8120,12 +8123,12 @@
         <v>416</v>
       </c>
       <c r="B251" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B252" t="s">
         <v>418</v>
@@ -8144,20 +8147,20 @@
         <v>420</v>
       </c>
       <c r="B254" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
+        <v>421</v>
+      </c>
+      <c r="B255" t="s">
         <v>422</v>
-      </c>
-      <c r="B255" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B256" t="s">
         <v>424</v>
@@ -8176,84 +8179,84 @@
         <v>426</v>
       </c>
       <c r="B258" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
+        <v>427</v>
+      </c>
+      <c r="B259" t="s">
         <v>428</v>
-      </c>
-      <c r="B259" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
+        <v>429</v>
+      </c>
+      <c r="B260" t="s">
         <v>430</v>
-      </c>
-      <c r="B260" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
+        <v>431</v>
+      </c>
+      <c r="B261" t="s">
         <v>432</v>
-      </c>
-      <c r="B261" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
+        <v>433</v>
+      </c>
+      <c r="B262" t="s">
         <v>434</v>
-      </c>
-      <c r="B262" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" t="s">
+        <v>435</v>
+      </c>
+      <c r="B263" t="s">
         <v>436</v>
-      </c>
-      <c r="B263" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
+        <v>437</v>
+      </c>
+      <c r="B264" t="s">
         <v>438</v>
-      </c>
-      <c r="B264" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
+        <v>439</v>
+      </c>
+      <c r="B265" t="s">
         <v>440</v>
-      </c>
-      <c r="B265" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
+        <v>441</v>
+      </c>
+      <c r="B266" t="s">
         <v>442</v>
-      </c>
-      <c r="B266" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
+        <v>443</v>
+      </c>
+      <c r="B267" t="s">
         <v>444</v>
-      </c>
-      <c r="B267" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B268" t="s">
         <v>446</v>
@@ -8280,12 +8283,12 @@
         <v>449</v>
       </c>
       <c r="B271" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B272" t="s">
         <v>451</v>
@@ -8296,12 +8299,12 @@
         <v>452</v>
       </c>
       <c r="B273" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B274" t="s">
         <v>454</v>
@@ -8320,12 +8323,12 @@
         <v>456</v>
       </c>
       <c r="B276" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B277" t="s">
         <v>458</v>
@@ -8336,28 +8339,28 @@
         <v>459</v>
       </c>
       <c r="B278" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
+        <v>460</v>
+      </c>
+      <c r="B279" t="s">
         <v>461</v>
-      </c>
-      <c r="B279" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
+        <v>462</v>
+      </c>
+      <c r="B280" t="s">
         <v>463</v>
-      </c>
-      <c r="B280" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B281" t="s">
         <v>465</v>
@@ -8384,12 +8387,12 @@
         <v>468</v>
       </c>
       <c r="B284" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B285" t="s">
         <v>470</v>
@@ -8400,28 +8403,28 @@
         <v>471</v>
       </c>
       <c r="B286" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
+        <v>472</v>
+      </c>
+      <c r="B287" t="s">
         <v>473</v>
-      </c>
-      <c r="B287" t="s">
-        <v>474</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
+        <v>474</v>
+      </c>
+      <c r="B288" t="s">
         <v>475</v>
-      </c>
-      <c r="B288" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B289" t="s">
         <v>477</v>
@@ -8432,36 +8435,36 @@
         <v>478</v>
       </c>
       <c r="B290" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
+        <v>479</v>
+      </c>
+      <c r="B291" t="s">
         <v>480</v>
-      </c>
-      <c r="B291" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
+        <v>481</v>
+      </c>
+      <c r="B292" t="s">
         <v>482</v>
-      </c>
-      <c r="B292" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
+        <v>483</v>
+      </c>
+      <c r="B293" t="s">
         <v>484</v>
-      </c>
-      <c r="B293" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B294" t="s">
         <v>486</v>
@@ -8480,28 +8483,28 @@
         <v>488</v>
       </c>
       <c r="B296" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
+        <v>489</v>
+      </c>
+      <c r="B297" t="s">
         <v>490</v>
-      </c>
-      <c r="B297" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
+        <v>491</v>
+      </c>
+      <c r="B298" t="s">
         <v>492</v>
-      </c>
-      <c r="B298" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B299" t="s">
         <v>494</v>
@@ -8536,44 +8539,44 @@
         <v>498</v>
       </c>
       <c r="B303" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
+        <v>499</v>
+      </c>
+      <c r="B304" t="s">
         <v>500</v>
-      </c>
-      <c r="B304" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
+        <v>501</v>
+      </c>
+      <c r="B305" t="s">
         <v>502</v>
-      </c>
-      <c r="B305" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
+        <v>503</v>
+      </c>
+      <c r="B306" t="s">
         <v>504</v>
-      </c>
-      <c r="B306" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" t="s">
+        <v>505</v>
+      </c>
+      <c r="B307" t="s">
         <v>506</v>
-      </c>
-      <c r="B307" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B308" t="s">
         <v>508</v>
@@ -8592,20 +8595,20 @@
         <v>510</v>
       </c>
       <c r="B310" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
+        <v>511</v>
+      </c>
+      <c r="B311" t="s">
         <v>512</v>
-      </c>
-      <c r="B311" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B312" t="s">
         <v>514</v>
@@ -8624,23 +8627,23 @@
         <v>516</v>
       </c>
       <c r="B314" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
+        <v>517</v>
+      </c>
+      <c r="B315" t="s">
         <v>518</v>
-      </c>
-      <c r="B315" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
+        <v>519</v>
+      </c>
+      <c r="B316" t="s">
         <v>520</v>
-      </c>
-      <c r="B316" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="317" spans="1:2">
@@ -8648,12 +8651,12 @@
         <v>521</v>
       </c>
       <c r="B317" t="s">
-        <v>522</v>
+        <v>175</v>
       </c>
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B318" t="s">
         <v>523</v>
@@ -8664,12 +8667,12 @@
         <v>524</v>
       </c>
       <c r="B319" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B320" t="s">
         <v>526</v>
@@ -8680,20 +8683,20 @@
         <v>527</v>
       </c>
       <c r="B321" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
+        <v>528</v>
+      </c>
+      <c r="B322" t="s">
         <v>529</v>
-      </c>
-      <c r="B322" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B323" t="s">
         <v>531</v>
@@ -8704,12 +8707,12 @@
         <v>532</v>
       </c>
       <c r="B324" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B325" t="s">
         <v>534</v>
@@ -8720,28 +8723,28 @@
         <v>535</v>
       </c>
       <c r="B326" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
+        <v>536</v>
+      </c>
+      <c r="B327" t="s">
         <v>537</v>
-      </c>
-      <c r="B327" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
+        <v>538</v>
+      </c>
+      <c r="B328" t="s">
         <v>539</v>
-      </c>
-      <c r="B328" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B329" t="s">
         <v>541</v>
@@ -8752,52 +8755,52 @@
         <v>542</v>
       </c>
       <c r="B330" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
+        <v>543</v>
+      </c>
+      <c r="B331" t="s">
         <v>544</v>
-      </c>
-      <c r="B331" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
+        <v>545</v>
+      </c>
+      <c r="B332" t="s">
         <v>546</v>
-      </c>
-      <c r="B332" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
+        <v>547</v>
+      </c>
+      <c r="B333" t="s">
         <v>548</v>
-      </c>
-      <c r="B333" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
+        <v>549</v>
+      </c>
+      <c r="B334" t="s">
         <v>550</v>
-      </c>
-      <c r="B334" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
+        <v>551</v>
+      </c>
+      <c r="B335" t="s">
         <v>552</v>
-      </c>
-      <c r="B335" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B336" t="s">
         <v>554</v>
@@ -8816,12 +8819,12 @@
         <v>556</v>
       </c>
       <c r="B338" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B339" t="s">
         <v>558</v>
@@ -8832,52 +8835,52 @@
         <v>559</v>
       </c>
       <c r="B340" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
+        <v>560</v>
+      </c>
+      <c r="B341" t="s">
         <v>561</v>
-      </c>
-      <c r="B341" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
+        <v>562</v>
+      </c>
+      <c r="B342" t="s">
         <v>563</v>
-      </c>
-      <c r="B342" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
+        <v>564</v>
+      </c>
+      <c r="B343" t="s">
         <v>565</v>
-      </c>
-      <c r="B343" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
+        <v>566</v>
+      </c>
+      <c r="B344" t="s">
         <v>567</v>
-      </c>
-      <c r="B344" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
+        <v>568</v>
+      </c>
+      <c r="B345" t="s">
         <v>569</v>
-      </c>
-      <c r="B345" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B346" t="s">
         <v>571</v>
@@ -8888,100 +8891,100 @@
         <v>572</v>
       </c>
       <c r="B347" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
+        <v>573</v>
+      </c>
+      <c r="B348" t="s">
         <v>574</v>
-      </c>
-      <c r="B348" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
+        <v>575</v>
+      </c>
+      <c r="B349" t="s">
         <v>576</v>
-      </c>
-      <c r="B349" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
+        <v>577</v>
+      </c>
+      <c r="B350" t="s">
         <v>578</v>
-      </c>
-      <c r="B350" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
+        <v>579</v>
+      </c>
+      <c r="B351" t="s">
         <v>580</v>
-      </c>
-      <c r="B351" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
+        <v>581</v>
+      </c>
+      <c r="B352" t="s">
         <v>582</v>
-      </c>
-      <c r="B352" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
+        <v>583</v>
+      </c>
+      <c r="B353" t="s">
         <v>584</v>
-      </c>
-      <c r="B353" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
+        <v>585</v>
+      </c>
+      <c r="B354" t="s">
         <v>586</v>
-      </c>
-      <c r="B354" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
+        <v>587</v>
+      </c>
+      <c r="B355" t="s">
         <v>588</v>
-      </c>
-      <c r="B355" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
+        <v>589</v>
+      </c>
+      <c r="B356" t="s">
         <v>590</v>
-      </c>
-      <c r="B356" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
+        <v>591</v>
+      </c>
+      <c r="B357" t="s">
         <v>592</v>
-      </c>
-      <c r="B357" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
+        <v>593</v>
+      </c>
+      <c r="B358" t="s">
         <v>594</v>
-      </c>
-      <c r="B358" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B359" t="s">
         <v>596</v>
@@ -8992,28 +8995,28 @@
         <v>597</v>
       </c>
       <c r="B360" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
+        <v>598</v>
+      </c>
+      <c r="B361" t="s">
         <v>599</v>
-      </c>
-      <c r="B361" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
+        <v>600</v>
+      </c>
+      <c r="B362" t="s">
         <v>601</v>
-      </c>
-      <c r="B362" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B363" t="s">
         <v>603</v>
@@ -9024,28 +9027,28 @@
         <v>604</v>
       </c>
       <c r="B364" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="365" spans="1:2">
       <c r="A365" t="s">
+        <v>605</v>
+      </c>
+      <c r="B365" t="s">
         <v>606</v>
-      </c>
-      <c r="B365" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
+        <v>607</v>
+      </c>
+      <c r="B366" t="s">
         <v>608</v>
-      </c>
-      <c r="B366" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B367" t="s">
         <v>610</v>
@@ -9064,60 +9067,60 @@
         <v>612</v>
       </c>
       <c r="B369" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="370" spans="1:2">
       <c r="A370" t="s">
+        <v>613</v>
+      </c>
+      <c r="B370" t="s">
         <v>614</v>
-      </c>
-      <c r="B370" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
+        <v>615</v>
+      </c>
+      <c r="B371" t="s">
         <v>616</v>
-      </c>
-      <c r="B371" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
+        <v>617</v>
+      </c>
+      <c r="B372" t="s">
         <v>618</v>
-      </c>
-      <c r="B372" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
+        <v>619</v>
+      </c>
+      <c r="B373" t="s">
         <v>620</v>
-      </c>
-      <c r="B373" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
+        <v>621</v>
+      </c>
+      <c r="B374" t="s">
         <v>622</v>
-      </c>
-      <c r="B374" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" t="s">
+        <v>623</v>
+      </c>
+      <c r="B375" t="s">
         <v>624</v>
-      </c>
-      <c r="B375" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="376" spans="1:2">
       <c r="A376" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B376" t="s">
         <v>626</v>
@@ -9128,12 +9131,12 @@
         <v>627</v>
       </c>
       <c r="B377" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B378" t="s">
         <v>629</v>
@@ -9144,52 +9147,52 @@
         <v>630</v>
       </c>
       <c r="B379" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" t="s">
+        <v>631</v>
+      </c>
+      <c r="B380" t="s">
         <v>632</v>
-      </c>
-      <c r="B380" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
+        <v>633</v>
+      </c>
+      <c r="B381" t="s">
         <v>634</v>
-      </c>
-      <c r="B381" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
+        <v>635</v>
+      </c>
+      <c r="B382" t="s">
         <v>636</v>
-      </c>
-      <c r="B382" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
+        <v>637</v>
+      </c>
+      <c r="B383" t="s">
         <v>638</v>
-      </c>
-      <c r="B383" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" t="s">
+        <v>639</v>
+      </c>
+      <c r="B384" t="s">
         <v>640</v>
-      </c>
-      <c r="B384" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B385" t="s">
         <v>642</v>
@@ -9200,36 +9203,36 @@
         <v>643</v>
       </c>
       <c r="B386" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="387" spans="1:2">
       <c r="A387" t="s">
+        <v>644</v>
+      </c>
+      <c r="B387" t="s">
         <v>645</v>
-      </c>
-      <c r="B387" t="s">
-        <v>646</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
+        <v>646</v>
+      </c>
+      <c r="B388" t="s">
         <v>647</v>
-      </c>
-      <c r="B388" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
+        <v>648</v>
+      </c>
+      <c r="B389" t="s">
         <v>649</v>
-      </c>
-      <c r="B389" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B390" t="s">
         <v>651</v>
@@ -9240,60 +9243,60 @@
         <v>652</v>
       </c>
       <c r="B391" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" t="s">
+        <v>653</v>
+      </c>
+      <c r="B392" t="s">
         <v>654</v>
-      </c>
-      <c r="B392" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" t="s">
+        <v>655</v>
+      </c>
+      <c r="B393" t="s">
         <v>656</v>
-      </c>
-      <c r="B393" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
+        <v>657</v>
+      </c>
+      <c r="B394" t="s">
         <v>658</v>
-      </c>
-      <c r="B394" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
+        <v>659</v>
+      </c>
+      <c r="B395" t="s">
         <v>660</v>
-      </c>
-      <c r="B395" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
+        <v>661</v>
+      </c>
+      <c r="B396" t="s">
         <v>662</v>
-      </c>
-      <c r="B396" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
+        <v>663</v>
+      </c>
+      <c r="B397" t="s">
         <v>664</v>
-      </c>
-      <c r="B397" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B398" t="s">
         <v>666</v>
@@ -9304,20 +9307,20 @@
         <v>667</v>
       </c>
       <c r="B399" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
+        <v>668</v>
+      </c>
+      <c r="B400" t="s">
         <v>669</v>
-      </c>
-      <c r="B400" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B401" t="s">
         <v>671</v>
@@ -9352,12 +9355,12 @@
         <v>675</v>
       </c>
       <c r="B405" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B406" t="s">
         <v>677</v>
@@ -9376,116 +9379,116 @@
         <v>679</v>
       </c>
       <c r="B408" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="409" spans="1:2">
       <c r="A409" t="s">
+        <v>680</v>
+      </c>
+      <c r="B409" t="s">
         <v>681</v>
-      </c>
-      <c r="B409" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
+        <v>682</v>
+      </c>
+      <c r="B410" t="s">
         <v>683</v>
-      </c>
-      <c r="B410" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
+        <v>684</v>
+      </c>
+      <c r="B411" t="s">
         <v>685</v>
-      </c>
-      <c r="B411" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
+        <v>686</v>
+      </c>
+      <c r="B412" t="s">
         <v>687</v>
-      </c>
-      <c r="B412" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="413" spans="1:2">
       <c r="A413" t="s">
+        <v>688</v>
+      </c>
+      <c r="B413" t="s">
         <v>689</v>
-      </c>
-      <c r="B413" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
+        <v>690</v>
+      </c>
+      <c r="B414" t="s">
         <v>691</v>
-      </c>
-      <c r="B414" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
+        <v>692</v>
+      </c>
+      <c r="B415" t="s">
         <v>693</v>
-      </c>
-      <c r="B415" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
+        <v>694</v>
+      </c>
+      <c r="B416" t="s">
         <v>695</v>
-      </c>
-      <c r="B416" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" t="s">
+        <v>696</v>
+      </c>
+      <c r="B417" t="s">
         <v>697</v>
-      </c>
-      <c r="B417" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
+        <v>698</v>
+      </c>
+      <c r="B418" t="s">
         <v>699</v>
-      </c>
-      <c r="B418" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
+        <v>700</v>
+      </c>
+      <c r="B419" t="s">
         <v>701</v>
-      </c>
-      <c r="B419" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
+        <v>702</v>
+      </c>
+      <c r="B420" t="s">
         <v>703</v>
-      </c>
-      <c r="B420" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
+        <v>704</v>
+      </c>
+      <c r="B421" t="s">
         <v>705</v>
-      </c>
-      <c r="B421" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B422" t="s">
         <v>707</v>
@@ -9496,28 +9499,28 @@
         <v>708</v>
       </c>
       <c r="B423" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="424" spans="1:2">
       <c r="A424" t="s">
+        <v>709</v>
+      </c>
+      <c r="B424" t="s">
         <v>710</v>
-      </c>
-      <c r="B424" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="425" spans="1:2">
       <c r="A425" t="s">
+        <v>711</v>
+      </c>
+      <c r="B425" t="s">
         <v>712</v>
-      </c>
-      <c r="B425" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="426" spans="1:2">
       <c r="A426" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B426" t="s">
         <v>714</v>
@@ -9528,36 +9531,36 @@
         <v>715</v>
       </c>
       <c r="B427" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="428" spans="1:2">
       <c r="A428" t="s">
+        <v>716</v>
+      </c>
+      <c r="B428" t="s">
         <v>717</v>
-      </c>
-      <c r="B428" t="s">
-        <v>718</v>
       </c>
     </row>
     <row r="429" spans="1:2">
       <c r="A429" t="s">
+        <v>718</v>
+      </c>
+      <c r="B429" t="s">
         <v>719</v>
-      </c>
-      <c r="B429" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="430" spans="1:2">
       <c r="A430" t="s">
+        <v>720</v>
+      </c>
+      <c r="B430" t="s">
         <v>721</v>
-      </c>
-      <c r="B430" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B431" t="s">
         <v>723</v>
@@ -9568,20 +9571,20 @@
         <v>724</v>
       </c>
       <c r="B432" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" t="s">
+        <v>725</v>
+      </c>
+      <c r="B433" t="s">
         <v>726</v>
-      </c>
-      <c r="B433" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B434" t="s">
         <v>728</v>
@@ -9592,12 +9595,12 @@
         <v>729</v>
       </c>
       <c r="B435" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B436" t="s">
         <v>731</v>
@@ -9608,60 +9611,60 @@
         <v>732</v>
       </c>
       <c r="B437" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
+        <v>733</v>
+      </c>
+      <c r="B438" t="s">
         <v>734</v>
-      </c>
-      <c r="B438" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
+        <v>735</v>
+      </c>
+      <c r="B439" t="s">
         <v>736</v>
-      </c>
-      <c r="B439" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
+        <v>737</v>
+      </c>
+      <c r="B440" t="s">
         <v>738</v>
-      </c>
-      <c r="B440" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" t="s">
+        <v>739</v>
+      </c>
+      <c r="B441" t="s">
         <v>740</v>
-      </c>
-      <c r="B441" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
+        <v>741</v>
+      </c>
+      <c r="B442" t="s">
         <v>742</v>
-      </c>
-      <c r="B442" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
+        <v>743</v>
+      </c>
+      <c r="B443" t="s">
         <v>744</v>
-      </c>
-      <c r="B443" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B444" t="s">
         <v>746</v>
@@ -9672,12 +9675,12 @@
         <v>747</v>
       </c>
       <c r="B445" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B446" t="s">
         <v>749</v>
@@ -9688,12 +9691,12 @@
         <v>750</v>
       </c>
       <c r="B447" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="448" spans="1:2">
       <c r="A448" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B448" t="s">
         <v>752</v>
@@ -9704,12 +9707,12 @@
         <v>753</v>
       </c>
       <c r="B449" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B450" t="s">
         <v>755</v>
@@ -9720,20 +9723,20 @@
         <v>756</v>
       </c>
       <c r="B451" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
+        <v>757</v>
+      </c>
+      <c r="B452" t="s">
         <v>758</v>
-      </c>
-      <c r="B452" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B453" t="s">
         <v>760</v>
@@ -9744,76 +9747,76 @@
         <v>761</v>
       </c>
       <c r="B454" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" t="s">
+        <v>762</v>
+      </c>
+      <c r="B455" t="s">
         <v>763</v>
-      </c>
-      <c r="B455" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="456" spans="1:2">
       <c r="A456" t="s">
+        <v>764</v>
+      </c>
+      <c r="B456" t="s">
         <v>765</v>
-      </c>
-      <c r="B456" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
+        <v>766</v>
+      </c>
+      <c r="B457" t="s">
         <v>767</v>
-      </c>
-      <c r="B457" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
+        <v>768</v>
+      </c>
+      <c r="B458" t="s">
         <v>769</v>
-      </c>
-      <c r="B458" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
+        <v>770</v>
+      </c>
+      <c r="B459" t="s">
         <v>771</v>
-      </c>
-      <c r="B459" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="460" spans="1:2">
       <c r="A460" t="s">
+        <v>772</v>
+      </c>
+      <c r="B460" t="s">
         <v>773</v>
-      </c>
-      <c r="B460" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" t="s">
+        <v>774</v>
+      </c>
+      <c r="B461" t="s">
         <v>775</v>
-      </c>
-      <c r="B461" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" t="s">
+        <v>776</v>
+      </c>
+      <c r="B462" t="s">
         <v>777</v>
-      </c>
-      <c r="B462" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B463" t="s">
         <v>779</v>
@@ -9832,7 +9835,7 @@
         <v>781</v>
       </c>
       <c r="B465" t="s">
-        <v>522</v>
+        <v>781</v>
       </c>
     </row>
     <row r="466" spans="1:2">
@@ -9840,7 +9843,7 @@
         <v>782</v>
       </c>
       <c r="B466" t="s">
-        <v>782</v>
+        <v>523</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -9848,15 +9851,15 @@
         <v>783</v>
       </c>
       <c r="B467" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
+        <v>784</v>
+      </c>
+      <c r="B468" t="s">
         <v>785</v>
-      </c>
-      <c r="B468" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -9864,20 +9867,20 @@
         <v>786</v>
       </c>
       <c r="B469" t="s">
-        <v>787</v>
+        <v>138</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
+        <v>787</v>
+      </c>
+      <c r="B470" t="s">
         <v>788</v>
-      </c>
-      <c r="B470" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B471" t="s">
         <v>790</v>
@@ -9888,7 +9891,7 @@
         <v>791</v>
       </c>
       <c r="B472" t="s">
-        <v>522</v>
+        <v>791</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -9896,7 +9899,7 @@
         <v>792</v>
       </c>
       <c r="B473" t="s">
-        <v>792</v>
+        <v>523</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -9920,28 +9923,28 @@
         <v>795</v>
       </c>
       <c r="B476" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
+        <v>796</v>
+      </c>
+      <c r="B477" t="s">
         <v>797</v>
-      </c>
-      <c r="B477" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
+        <v>798</v>
+      </c>
+      <c r="B478" t="s">
         <v>799</v>
-      </c>
-      <c r="B478" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B479" t="s">
         <v>801</v>
@@ -9952,12 +9955,12 @@
         <v>802</v>
       </c>
       <c r="B480" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B481" t="s">
         <v>804</v>
@@ -9968,20 +9971,20 @@
         <v>805</v>
       </c>
       <c r="B482" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
+        <v>806</v>
+      </c>
+      <c r="B483" t="s">
         <v>807</v>
-      </c>
-      <c r="B483" t="s">
-        <v>808</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B484" t="s">
         <v>809</v>
@@ -10032,164 +10035,164 @@
         <v>815</v>
       </c>
       <c r="B490" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
+        <v>816</v>
+      </c>
+      <c r="B491" t="s">
         <v>817</v>
-      </c>
-      <c r="B491" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
+        <v>818</v>
+      </c>
+      <c r="B492" t="s">
         <v>819</v>
-      </c>
-      <c r="B492" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
+        <v>820</v>
+      </c>
+      <c r="B493" t="s">
         <v>821</v>
-      </c>
-      <c r="B493" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
+        <v>822</v>
+      </c>
+      <c r="B494" t="s">
         <v>823</v>
-      </c>
-      <c r="B494" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" t="s">
+        <v>824</v>
+      </c>
+      <c r="B495" t="s">
         <v>825</v>
-      </c>
-      <c r="B495" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="496" spans="1:2">
       <c r="A496" t="s">
+        <v>826</v>
+      </c>
+      <c r="B496" t="s">
         <v>827</v>
-      </c>
-      <c r="B496" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="497" spans="1:2">
       <c r="A497" t="s">
+        <v>828</v>
+      </c>
+      <c r="B497" t="s">
         <v>829</v>
-      </c>
-      <c r="B497" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="498" spans="1:2">
       <c r="A498" t="s">
+        <v>830</v>
+      </c>
+      <c r="B498" t="s">
         <v>831</v>
-      </c>
-      <c r="B498" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="499" spans="1:2">
       <c r="A499" t="s">
+        <v>832</v>
+      </c>
+      <c r="B499" t="s">
         <v>833</v>
-      </c>
-      <c r="B499" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="500" spans="1:2">
       <c r="A500" t="s">
+        <v>834</v>
+      </c>
+      <c r="B500" t="s">
         <v>835</v>
-      </c>
-      <c r="B500" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="501" spans="1:2">
       <c r="A501" t="s">
+        <v>836</v>
+      </c>
+      <c r="B501" t="s">
         <v>837</v>
-      </c>
-      <c r="B501" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="502" spans="1:2">
       <c r="A502" t="s">
+        <v>838</v>
+      </c>
+      <c r="B502" t="s">
         <v>839</v>
-      </c>
-      <c r="B502" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="503" spans="1:2">
       <c r="A503" t="s">
+        <v>840</v>
+      </c>
+      <c r="B503" t="s">
         <v>841</v>
-      </c>
-      <c r="B503" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="504" spans="1:2">
       <c r="A504" t="s">
+        <v>842</v>
+      </c>
+      <c r="B504" t="s">
         <v>843</v>
-      </c>
-      <c r="B504" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="505" spans="1:2">
       <c r="A505" t="s">
+        <v>844</v>
+      </c>
+      <c r="B505" t="s">
         <v>845</v>
-      </c>
-      <c r="B505" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="506" spans="1:2">
       <c r="A506" t="s">
+        <v>846</v>
+      </c>
+      <c r="B506" t="s">
         <v>847</v>
-      </c>
-      <c r="B506" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="507" spans="1:2">
       <c r="A507" t="s">
+        <v>848</v>
+      </c>
+      <c r="B507" t="s">
         <v>849</v>
-      </c>
-      <c r="B507" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="508" spans="1:2">
       <c r="A508" t="s">
+        <v>850</v>
+      </c>
+      <c r="B508" t="s">
         <v>851</v>
-      </c>
-      <c r="B508" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="509" spans="1:2">
       <c r="A509" t="s">
+        <v>852</v>
+      </c>
+      <c r="B509" t="s">
         <v>853</v>
-      </c>
-      <c r="B509" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B510" t="s">
         <v>855</v>
@@ -10200,12 +10203,12 @@
         <v>856</v>
       </c>
       <c r="B511" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="512" spans="1:2">
       <c r="A512" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B512" t="s">
         <v>858</v>
@@ -10232,28 +10235,28 @@
         <v>861</v>
       </c>
       <c r="B515" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
+        <v>862</v>
+      </c>
+      <c r="B516" t="s">
         <v>863</v>
-      </c>
-      <c r="B516" t="s">
-        <v>864</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
+        <v>864</v>
+      </c>
+      <c r="B517" t="s">
         <v>865</v>
-      </c>
-      <c r="B517" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B518" t="s">
         <v>867</v>
@@ -10280,28 +10283,28 @@
         <v>870</v>
       </c>
       <c r="B521" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" t="s">
+        <v>871</v>
+      </c>
+      <c r="B522" t="s">
         <v>872</v>
-      </c>
-      <c r="B522" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
+        <v>873</v>
+      </c>
+      <c r="B523" t="s">
         <v>874</v>
-      </c>
-      <c r="B523" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B524" t="s">
         <v>876</v>
@@ -10312,52 +10315,52 @@
         <v>877</v>
       </c>
       <c r="B525" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" t="s">
+        <v>878</v>
+      </c>
+      <c r="B526" t="s">
         <v>879</v>
-      </c>
-      <c r="B526" t="s">
-        <v>880</v>
       </c>
     </row>
     <row r="527" spans="1:2">
       <c r="A527" t="s">
+        <v>880</v>
+      </c>
+      <c r="B527" t="s">
         <v>881</v>
-      </c>
-      <c r="B527" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" t="s">
+        <v>882</v>
+      </c>
+      <c r="B528" t="s">
         <v>883</v>
-      </c>
-      <c r="B528" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
+        <v>884</v>
+      </c>
+      <c r="B529" t="s">
         <v>885</v>
-      </c>
-      <c r="B529" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
+        <v>886</v>
+      </c>
+      <c r="B530" t="s">
         <v>887</v>
-      </c>
-      <c r="B530" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B531" t="s">
         <v>889</v>
@@ -10368,20 +10371,20 @@
         <v>890</v>
       </c>
       <c r="B532" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="533" spans="1:2">
       <c r="A533" t="s">
+        <v>891</v>
+      </c>
+      <c r="B533" t="s">
         <v>892</v>
-      </c>
-      <c r="B533" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B534" t="s">
         <v>894</v>
@@ -10400,12 +10403,12 @@
         <v>896</v>
       </c>
       <c r="B536" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B537" t="s">
         <v>898</v>
@@ -10448,28 +10451,28 @@
         <v>903</v>
       </c>
       <c r="B542" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
+        <v>904</v>
+      </c>
+      <c r="B543" t="s">
         <v>905</v>
-      </c>
-      <c r="B543" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
+        <v>906</v>
+      </c>
+      <c r="B544" t="s">
         <v>907</v>
-      </c>
-      <c r="B544" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B545" t="s">
         <v>909</v>
@@ -10488,12 +10491,12 @@
         <v>911</v>
       </c>
       <c r="B547" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B548" t="s">
         <v>913</v>
@@ -10504,12 +10507,12 @@
         <v>914</v>
       </c>
       <c r="B549" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B550" t="s">
         <v>916</v>
@@ -10536,12 +10539,12 @@
         <v>919</v>
       </c>
       <c r="B553" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B554" t="s">
         <v>921</v>
@@ -10552,68 +10555,68 @@
         <v>922</v>
       </c>
       <c r="B555" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
+        <v>923</v>
+      </c>
+      <c r="B556" t="s">
         <v>924</v>
-      </c>
-      <c r="B556" t="s">
-        <v>925</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
+        <v>925</v>
+      </c>
+      <c r="B557" t="s">
         <v>926</v>
-      </c>
-      <c r="B557" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
+        <v>927</v>
+      </c>
+      <c r="B558" t="s">
         <v>928</v>
-      </c>
-      <c r="B558" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
+        <v>929</v>
+      </c>
+      <c r="B559" t="s">
         <v>930</v>
-      </c>
-      <c r="B559" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
+        <v>931</v>
+      </c>
+      <c r="B560" t="s">
         <v>932</v>
-      </c>
-      <c r="B560" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
+        <v>933</v>
+      </c>
+      <c r="B561" t="s">
         <v>934</v>
-      </c>
-      <c r="B561" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
+        <v>935</v>
+      </c>
+      <c r="B562" t="s">
         <v>936</v>
-      </c>
-      <c r="B562" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B563" t="s">
         <v>938</v>
@@ -10632,20 +10635,20 @@
         <v>940</v>
       </c>
       <c r="B565" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
+        <v>941</v>
+      </c>
+      <c r="B566" t="s">
         <v>942</v>
-      </c>
-      <c r="B566" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B567" t="s">
         <v>944</v>
@@ -10656,20 +10659,20 @@
         <v>945</v>
       </c>
       <c r="B568" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
+        <v>946</v>
+      </c>
+      <c r="B569" t="s">
         <v>947</v>
-      </c>
-      <c r="B569" t="s">
-        <v>948</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B570" t="s">
         <v>949</v>
@@ -10680,28 +10683,28 @@
         <v>950</v>
       </c>
       <c r="B571" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
+        <v>951</v>
+      </c>
+      <c r="B572" t="s">
         <v>952</v>
-      </c>
-      <c r="B572" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
+        <v>953</v>
+      </c>
+      <c r="B573" t="s">
         <v>954</v>
-      </c>
-      <c r="B573" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B574" t="s">
         <v>956</v>
@@ -10712,12 +10715,12 @@
         <v>957</v>
       </c>
       <c r="B575" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B576" t="s">
         <v>959</v>
@@ -10728,12 +10731,12 @@
         <v>960</v>
       </c>
       <c r="B577" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B578" t="s">
         <v>962</v>
@@ -10744,20 +10747,20 @@
         <v>963</v>
       </c>
       <c r="B579" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
+        <v>964</v>
+      </c>
+      <c r="B580" t="s">
         <v>965</v>
-      </c>
-      <c r="B580" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B581" t="s">
         <v>967</v>
@@ -10784,12 +10787,12 @@
         <v>970</v>
       </c>
       <c r="B584" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B585" t="s">
         <v>972</v>
@@ -10800,12 +10803,12 @@
         <v>973</v>
       </c>
       <c r="B586" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B587" t="s">
         <v>975</v>
@@ -10816,44 +10819,44 @@
         <v>976</v>
       </c>
       <c r="B588" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
+        <v>977</v>
+      </c>
+      <c r="B589" t="s">
         <v>978</v>
-      </c>
-      <c r="B589" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
+        <v>979</v>
+      </c>
+      <c r="B590" t="s">
         <v>980</v>
-      </c>
-      <c r="B590" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
+        <v>981</v>
+      </c>
+      <c r="B591" t="s">
         <v>982</v>
-      </c>
-      <c r="B591" t="s">
-        <v>983</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
+        <v>983</v>
+      </c>
+      <c r="B592" t="s">
         <v>984</v>
-      </c>
-      <c r="B592" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B593" t="s">
         <v>986</v>
@@ -10864,68 +10867,68 @@
         <v>987</v>
       </c>
       <c r="B594" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
+        <v>988</v>
+      </c>
+      <c r="B595" t="s">
         <v>989</v>
-      </c>
-      <c r="B595" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
+        <v>990</v>
+      </c>
+      <c r="B596" t="s">
         <v>991</v>
-      </c>
-      <c r="B596" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
+        <v>992</v>
+      </c>
+      <c r="B597" t="s">
         <v>993</v>
-      </c>
-      <c r="B597" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
+        <v>994</v>
+      </c>
+      <c r="B598" t="s">
         <v>995</v>
-      </c>
-      <c r="B598" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
+        <v>996</v>
+      </c>
+      <c r="B599" t="s">
         <v>997</v>
-      </c>
-      <c r="B599" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
+        <v>998</v>
+      </c>
+      <c r="B600" t="s">
         <v>999</v>
-      </c>
-      <c r="B600" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B601" t="s">
         <v>1001</v>
-      </c>
-      <c r="B601" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B602" t="s">
         <v>1003</v>
@@ -10936,20 +10939,20 @@
         <v>1004</v>
       </c>
       <c r="B603" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B604" t="s">
         <v>1006</v>
-      </c>
-      <c r="B604" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B605" t="s">
         <v>1008</v>
@@ -10960,44 +10963,44 @@
         <v>1009</v>
       </c>
       <c r="B606" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B607" t="s">
         <v>1011</v>
-      </c>
-      <c r="B607" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B608" t="s">
         <v>1013</v>
-      </c>
-      <c r="B608" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B609" t="s">
         <v>1015</v>
-      </c>
-      <c r="B609" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B610" t="s">
         <v>1017</v>
-      </c>
-      <c r="B610" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B611" t="s">
         <v>1019</v>
@@ -11024,12 +11027,12 @@
         <v>1022</v>
       </c>
       <c r="B614" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B615" t="s">
         <v>1024</v>
@@ -11040,28 +11043,28 @@
         <v>1025</v>
       </c>
       <c r="B616" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B617" t="s">
         <v>1027</v>
-      </c>
-      <c r="B617" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B618" t="s">
         <v>1029</v>
-      </c>
-      <c r="B618" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B619" t="s">
         <v>1031</v>
@@ -11072,36 +11075,36 @@
         <v>1032</v>
       </c>
       <c r="B620" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B621" t="s">
         <v>1034</v>
-      </c>
-      <c r="B621" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B622" t="s">
         <v>1036</v>
-      </c>
-      <c r="B622" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B623" t="s">
         <v>1038</v>
-      </c>
-      <c r="B623" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B624" t="s">
         <v>1040</v>
@@ -11176,12 +11179,12 @@
         <v>1049</v>
       </c>
       <c r="B633" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B634" t="s">
         <v>1051</v>
@@ -11200,12 +11203,12 @@
         <v>1053</v>
       </c>
       <c r="B636" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B637" t="s">
         <v>1055</v>
@@ -11232,12 +11235,12 @@
         <v>1058</v>
       </c>
       <c r="B640" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B641" t="s">
         <v>1060</v>
@@ -11272,36 +11275,36 @@
         <v>1064</v>
       </c>
       <c r="B645" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B646" t="s">
         <v>1066</v>
-      </c>
-      <c r="B646" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B647" t="s">
         <v>1068</v>
-      </c>
-      <c r="B647" t="s">
-        <v>1069</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B648" t="s">
         <v>1070</v>
-      </c>
-      <c r="B648" t="s">
-        <v>1071</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B649" t="s">
         <v>1072</v>
@@ -11320,20 +11323,20 @@
         <v>1074</v>
       </c>
       <c r="B651" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B652" t="s">
         <v>1076</v>
-      </c>
-      <c r="B652" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B653" t="s">
         <v>1078</v>
@@ -11352,20 +11355,20 @@
         <v>1080</v>
       </c>
       <c r="B655" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B656" t="s">
         <v>1082</v>
-      </c>
-      <c r="B656" t="s">
-        <v>1083</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B657" t="s">
         <v>1084</v>
@@ -11376,12 +11379,12 @@
         <v>1085</v>
       </c>
       <c r="B658" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B659" t="s">
         <v>1087</v>
@@ -11400,36 +11403,36 @@
         <v>1089</v>
       </c>
       <c r="B661" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B662" t="s">
         <v>1091</v>
-      </c>
-      <c r="B662" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B663" t="s">
         <v>1093</v>
-      </c>
-      <c r="B663" t="s">
-        <v>1094</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B664" t="s">
         <v>1095</v>
-      </c>
-      <c r="B664" t="s">
-        <v>1096</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B665" t="s">
         <v>1097</v>
@@ -11472,20 +11475,20 @@
         <v>1102</v>
       </c>
       <c r="B670" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B671" t="s">
         <v>1104</v>
-      </c>
-      <c r="B671" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B672" t="s">
         <v>1106</v>
@@ -11496,20 +11499,20 @@
         <v>1107</v>
       </c>
       <c r="B673" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B674" t="s">
         <v>1109</v>
-      </c>
-      <c r="B674" t="s">
-        <v>1110</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B675" t="s">
         <v>1111</v>
@@ -11520,12 +11523,12 @@
         <v>1112</v>
       </c>
       <c r="B676" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B677" t="s">
         <v>1114</v>
@@ -11544,28 +11547,28 @@
         <v>1116</v>
       </c>
       <c r="B679" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B680" t="s">
         <v>1118</v>
-      </c>
-      <c r="B680" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B681" t="s">
         <v>1120</v>
-      </c>
-      <c r="B681" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B682" t="s">
         <v>1122</v>
@@ -11584,84 +11587,84 @@
         <v>1124</v>
       </c>
       <c r="B684" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B685" t="s">
         <v>1126</v>
-      </c>
-      <c r="B685" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B686" t="s">
         <v>1128</v>
-      </c>
-      <c r="B686" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B687" t="s">
         <v>1130</v>
-      </c>
-      <c r="B687" t="s">
-        <v>1131</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B688" t="s">
         <v>1132</v>
-      </c>
-      <c r="B688" t="s">
-        <v>1133</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B689" t="s">
         <v>1134</v>
-      </c>
-      <c r="B689" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B690" t="s">
         <v>1136</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B691" t="s">
         <v>1138</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B692" t="s">
         <v>1140</v>
-      </c>
-      <c r="B692" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B693" t="s">
         <v>1142</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B694" t="s">
         <v>1144</v>
@@ -11672,44 +11675,44 @@
         <v>1145</v>
       </c>
       <c r="B695" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="696" spans="1:2">
       <c r="A696" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B696" t="s">
         <v>1147</v>
-      </c>
-      <c r="B696" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="697" spans="1:2">
       <c r="A697" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B697" t="s">
         <v>1149</v>
-      </c>
-      <c r="B697" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="698" spans="1:2">
       <c r="A698" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B698" t="s">
         <v>1151</v>
-      </c>
-      <c r="B698" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B699" t="s">
         <v>1153</v>
-      </c>
-      <c r="B699" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="700" spans="1:2">
       <c r="A700" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="B700" t="s">
         <v>1155</v>
@@ -11720,12 +11723,12 @@
         <v>1156</v>
       </c>
       <c r="B701" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B702" t="s">
         <v>1158</v>
@@ -11744,12 +11747,12 @@
         <v>1160</v>
       </c>
       <c r="B704" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B705" t="s">
         <v>1162</v>
@@ -11776,12 +11779,12 @@
         <v>1165</v>
       </c>
       <c r="B708" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B709" t="s">
         <v>1167</v>
@@ -11808,12 +11811,12 @@
         <v>1170</v>
       </c>
       <c r="B712" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B713" t="s">
         <v>1172</v>
@@ -11824,60 +11827,60 @@
         <v>1173</v>
       </c>
       <c r="B714" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B715" t="s">
         <v>1175</v>
-      </c>
-      <c r="B715" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B716" t="s">
         <v>1177</v>
-      </c>
-      <c r="B716" t="s">
-        <v>1178</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B717" t="s">
         <v>1179</v>
-      </c>
-      <c r="B717" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B718" t="s">
         <v>1181</v>
-      </c>
-      <c r="B718" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B719" t="s">
         <v>1183</v>
-      </c>
-      <c r="B719" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B720" t="s">
         <v>1185</v>
-      </c>
-      <c r="B720" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B721" t="s">
         <v>1187</v>
@@ -11888,76 +11891,76 @@
         <v>1188</v>
       </c>
       <c r="B722" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B723" t="s">
         <v>1190</v>
-      </c>
-      <c r="B723" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B724" t="s">
         <v>1192</v>
-      </c>
-      <c r="B724" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B725" t="s">
         <v>1194</v>
-      </c>
-      <c r="B725" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B726" t="s">
         <v>1196</v>
-      </c>
-      <c r="B726" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B727" t="s">
         <v>1198</v>
-      </c>
-      <c r="B727" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B728" t="s">
         <v>1200</v>
-      </c>
-      <c r="B728" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B729" t="s">
         <v>1202</v>
-      </c>
-      <c r="B729" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B730" t="s">
         <v>1204</v>
-      </c>
-      <c r="B730" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="B731" t="s">
         <v>1206</v>
@@ -11968,28 +11971,28 @@
         <v>1207</v>
       </c>
       <c r="B732" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B733" t="s">
         <v>1209</v>
-      </c>
-      <c r="B733" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B734" t="s">
         <v>1211</v>
-      </c>
-      <c r="B734" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B735" t="s">
         <v>1213</v>
@@ -12000,12 +12003,12 @@
         <v>1214</v>
       </c>
       <c r="B736" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B737" t="s">
         <v>1216</v>
@@ -12056,20 +12059,20 @@
         <v>1222</v>
       </c>
       <c r="B743" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B744" t="s">
         <v>1224</v>
-      </c>
-      <c r="B744" t="s">
-        <v>1225</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B745" t="s">
         <v>1226</v>
@@ -12104,60 +12107,60 @@
         <v>1230</v>
       </c>
       <c r="B749" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B750" t="s">
         <v>1232</v>
-      </c>
-      <c r="B750" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B751" t="s">
         <v>1234</v>
-      </c>
-      <c r="B751" t="s">
-        <v>1235</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B752" t="s">
         <v>1236</v>
-      </c>
-      <c r="B752" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B753" t="s">
         <v>1238</v>
-      </c>
-      <c r="B753" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B754" t="s">
         <v>1240</v>
-      </c>
-      <c r="B754" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B755" t="s">
         <v>1242</v>
-      </c>
-      <c r="B755" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B756" t="s">
         <v>1244</v>
@@ -12176,12 +12179,12 @@
         <v>1246</v>
       </c>
       <c r="B758" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B759" t="s">
         <v>1248</v>
@@ -12200,12 +12203,12 @@
         <v>1250</v>
       </c>
       <c r="B761" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="762" spans="1:2">
       <c r="A762" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B762" t="s">
         <v>1252</v>
@@ -12224,44 +12227,44 @@
         <v>1254</v>
       </c>
       <c r="B764" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B765" t="s">
         <v>1256</v>
-      </c>
-      <c r="B765" t="s">
-        <v>1257</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B766" t="s">
         <v>1258</v>
-      </c>
-      <c r="B766" t="s">
-        <v>1259</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B767" t="s">
         <v>1260</v>
-      </c>
-      <c r="B767" t="s">
-        <v>1261</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B768" t="s">
         <v>1262</v>
-      </c>
-      <c r="B768" t="s">
-        <v>1263</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B769" t="s">
         <v>1264</v>
@@ -12272,36 +12275,36 @@
         <v>1265</v>
       </c>
       <c r="B770" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B771" t="s">
         <v>1267</v>
-      </c>
-      <c r="B771" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B772" t="s">
         <v>1269</v>
-      </c>
-      <c r="B772" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B773" t="s">
         <v>1271</v>
-      </c>
-      <c r="B773" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="774" spans="1:2">
       <c r="A774" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B774" t="s">
         <v>1273</v>
@@ -12312,68 +12315,68 @@
         <v>1274</v>
       </c>
       <c r="B775" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B776" t="s">
         <v>1276</v>
-      </c>
-      <c r="B776" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B777" t="s">
         <v>1278</v>
-      </c>
-      <c r="B777" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B778" t="s">
         <v>1280</v>
-      </c>
-      <c r="B778" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B779" t="s">
         <v>1282</v>
-      </c>
-      <c r="B779" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B780" t="s">
         <v>1284</v>
-      </c>
-      <c r="B780" t="s">
-        <v>1285</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B781" t="s">
         <v>1286</v>
-      </c>
-      <c r="B781" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B782" t="s">
         <v>1288</v>
-      </c>
-      <c r="B782" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B783" t="s">
         <v>1290</v>
@@ -12400,20 +12403,20 @@
         <v>1293</v>
       </c>
       <c r="B786" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B787" t="s">
         <v>1295</v>
-      </c>
-      <c r="B787" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B788" t="s">
         <v>1297</v>
@@ -12424,12 +12427,12 @@
         <v>1298</v>
       </c>
       <c r="B789" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B790" t="s">
         <v>1300</v>
@@ -12488,12 +12491,12 @@
         <v>1307</v>
       </c>
       <c r="B797" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B798" t="s">
         <v>1309</v>
@@ -12520,52 +12523,52 @@
         <v>1312</v>
       </c>
       <c r="B801" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B802" t="s">
         <v>1314</v>
-      </c>
-      <c r="B802" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B803" t="s">
         <v>1316</v>
-      </c>
-      <c r="B803" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B804" t="s">
         <v>1318</v>
-      </c>
-      <c r="B804" t="s">
-        <v>1319</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B805" t="s">
         <v>1320</v>
-      </c>
-      <c r="B805" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B806" t="s">
         <v>1322</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B807" t="s">
         <v>1324</v>
@@ -12592,84 +12595,84 @@
         <v>1327</v>
       </c>
       <c r="B810" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B811" t="s">
         <v>1329</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B812" t="s">
         <v>1331</v>
-      </c>
-      <c r="B812" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B813" t="s">
         <v>1333</v>
-      </c>
-      <c r="B813" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B814" t="s">
         <v>1335</v>
-      </c>
-      <c r="B814" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B815" t="s">
         <v>1337</v>
-      </c>
-      <c r="B815" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B816" t="s">
         <v>1339</v>
-      </c>
-      <c r="B816" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B817" t="s">
         <v>1341</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B818" t="s">
         <v>1343</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B819" t="s">
         <v>1345</v>
-      </c>
-      <c r="B819" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B820" t="s">
         <v>1347</v>
@@ -12680,20 +12683,20 @@
         <v>1348</v>
       </c>
       <c r="B821" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B822" t="s">
         <v>1350</v>
-      </c>
-      <c r="B822" t="s">
-        <v>1351</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="B823" t="s">
         <v>1352</v>
@@ -12712,12 +12715,12 @@
         <v>1354</v>
       </c>
       <c r="B825" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B826" t="s">
         <v>1356</v>
@@ -12728,12 +12731,12 @@
         <v>1357</v>
       </c>
       <c r="B827" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
       <c r="B828" t="s">
         <v>1359</v>
@@ -12760,12 +12763,12 @@
         <v>1362</v>
       </c>
       <c r="B831" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B832" t="s">
         <v>1364</v>
@@ -12808,36 +12811,36 @@
         <v>1369</v>
       </c>
       <c r="B837" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B838" t="s">
         <v>1371</v>
-      </c>
-      <c r="B838" t="s">
-        <v>1372</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B839" t="s">
         <v>1373</v>
-      </c>
-      <c r="B839" t="s">
-        <v>1374</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B840" t="s">
         <v>1375</v>
-      </c>
-      <c r="B840" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
       <c r="B841" t="s">
         <v>1377</v>
@@ -12848,20 +12851,20 @@
         <v>1378</v>
       </c>
       <c r="B842" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B843" t="s">
         <v>1380</v>
-      </c>
-      <c r="B843" t="s">
-        <v>1381</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
       <c r="B844" t="s">
         <v>1382</v>
@@ -12888,108 +12891,108 @@
         <v>1385</v>
       </c>
       <c r="B847" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B848" t="s">
         <v>1387</v>
-      </c>
-      <c r="B848" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B849" t="s">
         <v>1389</v>
-      </c>
-      <c r="B849" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B850" t="s">
         <v>1391</v>
-      </c>
-      <c r="B850" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B851" t="s">
         <v>1393</v>
-      </c>
-      <c r="B851" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B852" t="s">
         <v>1395</v>
-      </c>
-      <c r="B852" t="s">
-        <v>1396</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B853" t="s">
         <v>1397</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1398</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B854" t="s">
         <v>1399</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B855" t="s">
         <v>1401</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B856" t="s">
         <v>1403</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B857" t="s">
         <v>1405</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1406</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B858" t="s">
         <v>1407</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B859" t="s">
         <v>1409</v>
-      </c>
-      <c r="B859" t="s">
-        <v>1410</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
       <c r="B860" t="s">
         <v>1411</v>
@@ -13024,12 +13027,12 @@
         <v>1415</v>
       </c>
       <c r="B864" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B865" t="s">
         <v>1417</v>
@@ -13080,36 +13083,36 @@
         <v>1423</v>
       </c>
       <c r="B871" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B872" t="s">
         <v>1425</v>
-      </c>
-      <c r="B872" t="s">
-        <v>1426</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B873" t="s">
         <v>1427</v>
-      </c>
-      <c r="B873" t="s">
-        <v>1428</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B874" t="s">
         <v>1429</v>
-      </c>
-      <c r="B874" t="s">
-        <v>1430</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B875" t="s">
         <v>1431</v>
@@ -13120,36 +13123,36 @@
         <v>1432</v>
       </c>
       <c r="B876" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B877" t="s">
         <v>1434</v>
-      </c>
-      <c r="B877" t="s">
-        <v>1435</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B878" t="s">
         <v>1436</v>
-      </c>
-      <c r="B878" t="s">
-        <v>1437</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B879" t="s">
         <v>1438</v>
-      </c>
-      <c r="B879" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B880" t="s">
         <v>1440</v>
@@ -13160,28 +13163,28 @@
         <v>1441</v>
       </c>
       <c r="B881" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B882" t="s">
         <v>1443</v>
-      </c>
-      <c r="B882" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B883" t="s">
         <v>1445</v>
-      </c>
-      <c r="B883" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B884" t="s">
         <v>1447</v>
@@ -13200,44 +13203,44 @@
         <v>1449</v>
       </c>
       <c r="B886" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B887" t="s">
         <v>1451</v>
-      </c>
-      <c r="B887" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B888" t="s">
         <v>1453</v>
-      </c>
-      <c r="B888" t="s">
-        <v>1454</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B889" t="s">
         <v>1455</v>
-      </c>
-      <c r="B889" t="s">
-        <v>1456</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B890" t="s">
         <v>1457</v>
-      </c>
-      <c r="B890" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B891" t="s">
         <v>1459</v>
@@ -13248,12 +13251,12 @@
         <v>1460</v>
       </c>
       <c r="B892" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B893" t="s">
         <v>1462</v>
@@ -13264,36 +13267,36 @@
         <v>1463</v>
       </c>
       <c r="B894" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B895" t="s">
         <v>1465</v>
-      </c>
-      <c r="B895" t="s">
-        <v>1466</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B896" t="s">
         <v>1467</v>
-      </c>
-      <c r="B896" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B897" t="s">
         <v>1469</v>
-      </c>
-      <c r="B897" t="s">
-        <v>1470</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B898" t="s">
         <v>1471</v>
@@ -13312,44 +13315,44 @@
         <v>1473</v>
       </c>
       <c r="B900" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B901" t="s">
         <v>1475</v>
-      </c>
-      <c r="B901" t="s">
-        <v>1476</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B902" t="s">
         <v>1477</v>
-      </c>
-      <c r="B902" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B903" t="s">
         <v>1479</v>
-      </c>
-      <c r="B903" t="s">
-        <v>1480</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B904" t="s">
         <v>1481</v>
-      </c>
-      <c r="B904" t="s">
-        <v>1482</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B905" t="s">
         <v>1483</v>
@@ -13400,36 +13403,36 @@
         <v>1489</v>
       </c>
       <c r="B911" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B912" t="s">
         <v>1491</v>
-      </c>
-      <c r="B912" t="s">
-        <v>1492</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B913" t="s">
         <v>1493</v>
-      </c>
-      <c r="B913" t="s">
-        <v>1494</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B914" t="s">
         <v>1495</v>
-      </c>
-      <c r="B914" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="B915" t="s">
         <v>1497</v>
@@ -13456,44 +13459,44 @@
         <v>1500</v>
       </c>
       <c r="B918" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B919" t="s">
         <v>1502</v>
-      </c>
-      <c r="B919" t="s">
-        <v>1503</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B920" t="s">
         <v>1504</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B921" t="s">
         <v>1506</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B922" t="s">
         <v>1508</v>
-      </c>
-      <c r="B922" t="s">
-        <v>1509</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B923" t="s">
         <v>1510</v>
@@ -13512,36 +13515,36 @@
         <v>1512</v>
       </c>
       <c r="B925" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B926" t="s">
         <v>1514</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1515</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B927" t="s">
         <v>1516</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1517</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B928" t="s">
         <v>1518</v>
-      </c>
-      <c r="B928" t="s">
-        <v>1519</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="B929" t="s">
         <v>1520</v>
@@ -13552,20 +13555,20 @@
         <v>1521</v>
       </c>
       <c r="B930" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B931" t="s">
         <v>1523</v>
-      </c>
-      <c r="B931" t="s">
-        <v>1524</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B932" t="s">
         <v>1525</v>
@@ -13576,20 +13579,20 @@
         <v>1526</v>
       </c>
       <c r="B933" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B934" t="s">
         <v>1528</v>
-      </c>
-      <c r="B934" t="s">
-        <v>1529</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B935" t="s">
         <v>1530</v>
@@ -13600,12 +13603,12 @@
         <v>1531</v>
       </c>
       <c r="B936" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B937" t="s">
         <v>1533</v>
@@ -13616,20 +13619,20 @@
         <v>1534</v>
       </c>
       <c r="B938" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B939" t="s">
         <v>1536</v>
-      </c>
-      <c r="B939" t="s">
-        <v>1537</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B940" t="s">
         <v>1538</v>
@@ -13640,12 +13643,12 @@
         <v>1539</v>
       </c>
       <c r="B941" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B942" t="s">
         <v>1541</v>
@@ -13672,28 +13675,28 @@
         <v>1544</v>
       </c>
       <c r="B945" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B946" t="s">
         <v>1546</v>
-      </c>
-      <c r="B946" t="s">
-        <v>1547</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B947" t="s">
         <v>1548</v>
-      </c>
-      <c r="B947" t="s">
-        <v>1549</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="B948" t="s">
         <v>1550</v>
@@ -13736,36 +13739,36 @@
         <v>1555</v>
       </c>
       <c r="B953" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B954" t="s">
         <v>1557</v>
-      </c>
-      <c r="B954" t="s">
-        <v>1558</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B955" t="s">
         <v>1559</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1560</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B956" t="s">
         <v>1561</v>
-      </c>
-      <c r="B956" t="s">
-        <v>1562</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B957" t="s">
         <v>1563</v>
@@ -13792,52 +13795,52 @@
         <v>1566</v>
       </c>
       <c r="B960" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B961" t="s">
         <v>1568</v>
-      </c>
-      <c r="B961" t="s">
-        <v>1569</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B962" t="s">
         <v>1570</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B963" t="s">
         <v>1572</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1573</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B964" t="s">
         <v>1574</v>
-      </c>
-      <c r="B964" t="s">
-        <v>1575</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B965" t="s">
         <v>1576</v>
-      </c>
-      <c r="B965" t="s">
-        <v>1577</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="B966" t="s">
         <v>1578</v>
@@ -13864,12 +13867,12 @@
         <v>1581</v>
       </c>
       <c r="B969" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B970" t="s">
         <v>1583</v>
@@ -13888,44 +13891,44 @@
         <v>1585</v>
       </c>
       <c r="B972" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B973" t="s">
         <v>1587</v>
-      </c>
-      <c r="B973" t="s">
-        <v>1588</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B974" t="s">
         <v>1589</v>
-      </c>
-      <c r="B974" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B975" t="s">
         <v>1591</v>
-      </c>
-      <c r="B975" t="s">
-        <v>1592</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B976" t="s">
         <v>1593</v>
-      </c>
-      <c r="B976" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="B977" t="s">
         <v>1595</v>
@@ -13936,28 +13939,28 @@
         <v>1596</v>
       </c>
       <c r="B978" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B979" t="s">
         <v>1598</v>
-      </c>
-      <c r="B979" t="s">
-        <v>1599</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B980" t="s">
         <v>1600</v>
-      </c>
-      <c r="B980" t="s">
-        <v>1601</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B981" t="s">
         <v>1602</v>
@@ -13968,20 +13971,20 @@
         <v>1603</v>
       </c>
       <c r="B982" t="s">
-        <v>1604</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B983" t="s">
         <v>1605</v>
-      </c>
-      <c r="B983" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B984" t="s">
         <v>1607</v>
@@ -14016,52 +14019,52 @@
         <v>1611</v>
       </c>
       <c r="B988" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B989" t="s">
         <v>1613</v>
-      </c>
-      <c r="B989" t="s">
-        <v>1614</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B990" t="s">
         <v>1615</v>
-      </c>
-      <c r="B990" t="s">
-        <v>1616</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B991" t="s">
         <v>1617</v>
-      </c>
-      <c r="B991" t="s">
-        <v>1618</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B992" t="s">
         <v>1619</v>
-      </c>
-      <c r="B992" t="s">
-        <v>1620</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B993" t="s">
         <v>1621</v>
-      </c>
-      <c r="B993" t="s">
-        <v>1622</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="B994" t="s">
         <v>1623</v>
@@ -14072,20 +14075,20 @@
         <v>1624</v>
       </c>
       <c r="B995" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B996" t="s">
         <v>1626</v>
-      </c>
-      <c r="B996" t="s">
-        <v>1627</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B997" t="s">
         <v>1628</v>
@@ -14112,12 +14115,12 @@
         <v>1631</v>
       </c>
       <c r="B1000" t="s">
-        <v>1632</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1633</v>
+        <v>1632</v>
       </c>
       <c r="B1001" t="s">
         <v>1633</v>
@@ -14128,20 +14131,20 @@
         <v>1634</v>
       </c>
       <c r="B1002" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B1003" t="s">
         <v>1636</v>
-      </c>
-      <c r="B1003" t="s">
-        <v>1637</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B1004" t="s">
         <v>1638</v>
@@ -14160,28 +14163,28 @@
         <v>1640</v>
       </c>
       <c r="B1006" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B1007" t="s">
         <v>1642</v>
-      </c>
-      <c r="B1007" t="s">
-        <v>1643</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B1008" t="s">
         <v>1644</v>
-      </c>
-      <c r="B1008" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="B1009" t="s">
         <v>1646</v>
@@ -14192,20 +14195,20 @@
         <v>1647</v>
       </c>
       <c r="B1010" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B1011" t="s">
         <v>1649</v>
-      </c>
-      <c r="B1011" t="s">
-        <v>1650</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="B1012" t="s">
         <v>1651</v>
@@ -14216,20 +14219,20 @@
         <v>1652</v>
       </c>
       <c r="B1013" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B1014" t="s">
         <v>1654</v>
-      </c>
-      <c r="B1014" t="s">
-        <v>1655</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="B1015" t="s">
         <v>1656</v>
@@ -14264,20 +14267,20 @@
         <v>1660</v>
       </c>
       <c r="B1019" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B1020" t="s">
         <v>1662</v>
-      </c>
-      <c r="B1020" t="s">
-        <v>1663</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="B1021" t="s">
         <v>1664</v>
@@ -14288,28 +14291,28 @@
         <v>1665</v>
       </c>
       <c r="B1022" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B1023" t="s">
         <v>1667</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>1668</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B1024" t="s">
         <v>1669</v>
-      </c>
-      <c r="B1024" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="B1025" t="s">
         <v>1671</v>
@@ -14320,12 +14323,12 @@
         <v>1672</v>
       </c>
       <c r="B1026" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="B1027" t="s">
         <v>1674</v>
@@ -14344,12 +14347,12 @@
         <v>1676</v>
       </c>
       <c r="B1029" t="s">
-        <v>1677</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="B1030" t="s">
         <v>1678</v>
@@ -14360,12 +14363,12 @@
         <v>1679</v>
       </c>
       <c r="B1031" t="s">
-        <v>1680</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="B1032" t="s">
         <v>1681</v>
@@ -14384,12 +14387,12 @@
         <v>1683</v>
       </c>
       <c r="B1034" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B1035" t="s">
         <v>1685</v>
@@ -14408,12 +14411,12 @@
         <v>1687</v>
       </c>
       <c r="B1037" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="B1038" t="s">
         <v>1689</v>
@@ -14424,36 +14427,36 @@
         <v>1690</v>
       </c>
       <c r="B1039" t="s">
-        <v>1691</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B1040" t="s">
         <v>1692</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>1693</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
+        <v>1693</v>
+      </c>
+      <c r="B1041" t="s">
         <v>1694</v>
-      </c>
-      <c r="B1041" t="s">
-        <v>1695</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
+        <v>1695</v>
+      </c>
+      <c r="B1042" t="s">
         <v>1696</v>
-      </c>
-      <c r="B1042" t="s">
-        <v>1697</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="B1043" t="s">
         <v>1698</v>
@@ -14464,12 +14467,12 @@
         <v>1699</v>
       </c>
       <c r="B1044" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="B1045" t="s">
         <v>1701</v>
@@ -14480,44 +14483,44 @@
         <v>1702</v>
       </c>
       <c r="B1046" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B1047" t="s">
         <v>1704</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B1048" t="s">
         <v>1706</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>1707</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B1049" t="s">
         <v>1708</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>1709</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B1050" t="s">
         <v>1710</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>1711</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="B1051" t="s">
         <v>1712</v>
@@ -14552,52 +14555,52 @@
         <v>1716</v>
       </c>
       <c r="B1055" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B1056" t="s">
         <v>1718</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>1719</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B1057" t="s">
         <v>1720</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>1721</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1058" t="s">
         <v>1722</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>1723</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B1059" t="s">
         <v>1724</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1725</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B1060" t="s">
         <v>1726</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>1727</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="B1061" t="s">
         <v>1728</v>
@@ -14608,12 +14611,12 @@
         <v>1729</v>
       </c>
       <c r="B1062" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="B1063" t="s">
         <v>1731</v>
@@ -14632,52 +14635,52 @@
         <v>1733</v>
       </c>
       <c r="B1065" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1066" t="s">
         <v>1735</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>1736</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B1067" t="s">
         <v>1737</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B1068" t="s">
         <v>1739</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>1740</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B1069" t="s">
         <v>1741</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>1742</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B1070" t="s">
         <v>1743</v>
-      </c>
-      <c r="B1070" t="s">
-        <v>1744</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="B1071" t="s">
         <v>1745</v>
@@ -14688,12 +14691,12 @@
         <v>1746</v>
       </c>
       <c r="B1072" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B1073" t="s">
         <v>1748</v>
@@ -14712,12 +14715,12 @@
         <v>1750</v>
       </c>
       <c r="B1075" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="B1076" t="s">
         <v>1752</v>
@@ -14760,20 +14763,20 @@
         <v>1757</v>
       </c>
       <c r="B1081" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
+        <v>1758</v>
+      </c>
+      <c r="B1082" t="s">
         <v>1759</v>
-      </c>
-      <c r="B1082" t="s">
-        <v>1760</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="B1083" t="s">
         <v>1761</v>
@@ -14792,20 +14795,20 @@
         <v>1763</v>
       </c>
       <c r="B1085" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
+        <v>1764</v>
+      </c>
+      <c r="B1086" t="s">
         <v>1765</v>
-      </c>
-      <c r="B1086" t="s">
-        <v>1766</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B1087" t="s">
         <v>1767</v>
@@ -14816,36 +14819,36 @@
         <v>1768</v>
       </c>
       <c r="B1088" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B1089" t="s">
         <v>1770</v>
-      </c>
-      <c r="B1089" t="s">
-        <v>1771</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
+        <v>1771</v>
+      </c>
+      <c r="B1090" t="s">
         <v>1772</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>1773</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
+        <v>1773</v>
+      </c>
+      <c r="B1091" t="s">
         <v>1774</v>
-      </c>
-      <c r="B1091" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1776</v>
+        <v>1775</v>
       </c>
       <c r="B1092" t="s">
         <v>1776</v>
@@ -14864,44 +14867,44 @@
         <v>1778</v>
       </c>
       <c r="B1094" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>1779</v>
+      </c>
+      <c r="B1095" t="s">
         <v>1780</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>1781</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B1096" t="s">
         <v>1782</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B1097" t="s">
         <v>1784</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B1098" t="s">
         <v>1786</v>
-      </c>
-      <c r="B1098" t="s">
-        <v>1787</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1788</v>
+        <v>1787</v>
       </c>
       <c r="B1099" t="s">
         <v>1788</v>
@@ -14912,20 +14915,20 @@
         <v>1789</v>
       </c>
       <c r="B1100" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B1101" t="s">
         <v>1791</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>1792</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="B1102" t="s">
         <v>1793</v>
@@ -14944,12 +14947,12 @@
         <v>1795</v>
       </c>
       <c r="B1104" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="B1105" t="s">
         <v>1797</v>
@@ -14968,20 +14971,20 @@
         <v>1799</v>
       </c>
       <c r="B1107" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B1108" t="s">
         <v>1801</v>
-      </c>
-      <c r="B1108" t="s">
-        <v>1802</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="B1109" t="s">
         <v>1803</v>
@@ -14992,28 +14995,28 @@
         <v>1804</v>
       </c>
       <c r="B1110" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
+        <v>1805</v>
+      </c>
+      <c r="B1111" t="s">
         <v>1806</v>
-      </c>
-      <c r="B1111" t="s">
-        <v>1807</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B1112" t="s">
         <v>1808</v>
-      </c>
-      <c r="B1112" t="s">
-        <v>1809</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="B1113" t="s">
         <v>1810</v>
@@ -15024,44 +15027,44 @@
         <v>1811</v>
       </c>
       <c r="B1114" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
+        <v>1812</v>
+      </c>
+      <c r="B1115" t="s">
         <v>1813</v>
-      </c>
-      <c r="B1115" t="s">
-        <v>1814</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B1116" t="s">
         <v>1815</v>
-      </c>
-      <c r="B1116" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
+        <v>1816</v>
+      </c>
+      <c r="B1117" t="s">
         <v>1817</v>
-      </c>
-      <c r="B1117" t="s">
-        <v>1818</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B1118" t="s">
         <v>1819</v>
-      </c>
-      <c r="B1118" t="s">
-        <v>1820</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1821</v>
+        <v>1820</v>
       </c>
       <c r="B1119" t="s">
         <v>1821</v>
@@ -15072,108 +15075,108 @@
         <v>1822</v>
       </c>
       <c r="B1120" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B1121" t="s">
         <v>1824</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>1825</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>1825</v>
+      </c>
+      <c r="B1122" t="s">
         <v>1826</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>1827</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>1827</v>
+      </c>
+      <c r="B1123" t="s">
         <v>1828</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>1829</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1830</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1831</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1832</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1833</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1834</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1835</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1836</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1837</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1838</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1839</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1840</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1841</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1842</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1843</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1844</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1845</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1846</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1847</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="B1133" t="s">
         <v>1848</v>
@@ -15216,20 +15219,20 @@
         <v>1853</v>
       </c>
       <c r="B1138" t="s">
-        <v>1854</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B1139" t="s">
         <v>1855</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>1856</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="B1140" t="s">
         <v>1857</v>
@@ -15256,68 +15259,68 @@
         <v>1860</v>
       </c>
       <c r="B1143" t="s">
-        <v>1861</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
+        <v>1861</v>
+      </c>
+      <c r="B1144" t="s">
         <v>1862</v>
-      </c>
-      <c r="B1144" t="s">
-        <v>1863</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B1145" t="s">
         <v>1864</v>
-      </c>
-      <c r="B1145" t="s">
-        <v>1865</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B1146" t="s">
         <v>1866</v>
-      </c>
-      <c r="B1146" t="s">
-        <v>1867</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>1867</v>
+      </c>
+      <c r="B1147" t="s">
         <v>1868</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>1869</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B1148" t="s">
         <v>1870</v>
-      </c>
-      <c r="B1148" t="s">
-        <v>1871</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B1149" t="s">
         <v>1872</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>1873</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>1873</v>
+      </c>
+      <c r="B1150" t="s">
         <v>1874</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>1875</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="B1151" t="s">
         <v>1876</v>
@@ -15328,12 +15331,12 @@
         <v>1877</v>
       </c>
       <c r="B1152" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="B1153" t="s">
         <v>1879</v>
@@ -15344,36 +15347,36 @@
         <v>1880</v>
       </c>
       <c r="B1154" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B1155" t="s">
         <v>1882</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>1883</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B1156" t="s">
         <v>1884</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>1885</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B1157" t="s">
         <v>1886</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>1887</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="B1158" t="s">
         <v>1888</v>
@@ -15416,20 +15419,20 @@
         <v>1893</v>
       </c>
       <c r="B1163" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>1894</v>
+      </c>
+      <c r="B1164" t="s">
         <v>1895</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>1896</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B1165" t="s">
         <v>1897</v>
@@ -15448,12 +15451,12 @@
         <v>1899</v>
       </c>
       <c r="B1167" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="B1168" t="s">
         <v>1901</v>
@@ -15496,12 +15499,12 @@
         <v>1906</v>
       </c>
       <c r="B1173" t="s">
-        <v>1907</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B1174" t="s">
         <v>1908</v>
@@ -15536,19 +15539,27 @@
         <v>1912</v>
       </c>
       <c r="B1178" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B1179" t="s">
         <v>1914</v>
       </c>
     </row>
+    <row r="1180" spans="1:2">
+      <c r="A1180" t="s">
+        <v>1915</v>
+      </c>
+      <c r="B1180" t="s">
+        <v>1915</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1179"/>
+  <autoFilter ref="A1:B1180"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1918">
   <si>
     <t>en</t>
   </si>
@@ -4262,6 +4262,12 @@
   </si>
   <si>
     <t>Pop Team Epic</t>
+  </si>
+  <si>
+    <t>Popee the Performer</t>
+  </si>
+  <si>
+    <t>Popee si Pemain</t>
   </si>
   <si>
     <t>POPGOES</t>
@@ -6111,7 +6117,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1180"/>
+  <dimension ref="A1:B1181"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13027,12 +13033,12 @@
         <v>1415</v>
       </c>
       <c r="B864" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B865" t="s">
         <v>1417</v>
@@ -13043,52 +13049,52 @@
         <v>1418</v>
       </c>
       <c r="B866" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B867" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B868" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B869" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B870" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B871" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B872" t="s">
         <v>1425</v>
@@ -13123,12 +13129,12 @@
         <v>1432</v>
       </c>
       <c r="B876" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B877" t="s">
         <v>1434</v>
@@ -13163,12 +13169,12 @@
         <v>1441</v>
       </c>
       <c r="B881" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B882" t="s">
         <v>1443</v>
@@ -13195,20 +13201,20 @@
         <v>1448</v>
       </c>
       <c r="B885" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B886" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B887" t="s">
         <v>1451</v>
@@ -13251,12 +13257,12 @@
         <v>1460</v>
       </c>
       <c r="B892" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B893" t="s">
         <v>1462</v>
@@ -13267,12 +13273,12 @@
         <v>1463</v>
       </c>
       <c r="B894" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B895" t="s">
         <v>1465</v>
@@ -13307,20 +13313,20 @@
         <v>1472</v>
       </c>
       <c r="B899" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B900" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B901" t="s">
         <v>1475</v>
@@ -13363,52 +13369,52 @@
         <v>1484</v>
       </c>
       <c r="B906" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B907" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B908" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B909" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B910" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B911" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B912" t="s">
         <v>1491</v>
@@ -13443,28 +13449,28 @@
         <v>1498</v>
       </c>
       <c r="B916" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B917" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B918" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B919" t="s">
         <v>1502</v>
@@ -13507,20 +13513,20 @@
         <v>1511</v>
       </c>
       <c r="B924" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B925" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B926" t="s">
         <v>1514</v>
@@ -13555,12 +13561,12 @@
         <v>1521</v>
       </c>
       <c r="B930" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B931" t="s">
         <v>1523</v>
@@ -13579,12 +13585,12 @@
         <v>1526</v>
       </c>
       <c r="B933" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B934" t="s">
         <v>1528</v>
@@ -13603,12 +13609,12 @@
         <v>1531</v>
       </c>
       <c r="B936" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B937" t="s">
         <v>1533</v>
@@ -13619,12 +13625,12 @@
         <v>1534</v>
       </c>
       <c r="B938" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B939" t="s">
         <v>1536</v>
@@ -13643,12 +13649,12 @@
         <v>1539</v>
       </c>
       <c r="B941" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B942" t="s">
         <v>1541</v>
@@ -13659,28 +13665,28 @@
         <v>1542</v>
       </c>
       <c r="B943" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B944" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B945" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B946" t="s">
         <v>1546</v>
@@ -13707,44 +13713,44 @@
         <v>1551</v>
       </c>
       <c r="B949" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B950" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B951" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B952" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B953" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B954" t="s">
         <v>1557</v>
@@ -13779,28 +13785,28 @@
         <v>1564</v>
       </c>
       <c r="B958" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B959" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B960" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B961" t="s">
         <v>1568</v>
@@ -13851,28 +13857,28 @@
         <v>1579</v>
       </c>
       <c r="B967" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B968" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B969" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B970" t="s">
         <v>1583</v>
@@ -13883,20 +13889,20 @@
         <v>1584</v>
       </c>
       <c r="B971" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B972" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B973" t="s">
         <v>1587</v>
@@ -13939,12 +13945,12 @@
         <v>1596</v>
       </c>
       <c r="B978" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B979" t="s">
         <v>1598</v>
@@ -13971,12 +13977,12 @@
         <v>1603</v>
       </c>
       <c r="B982" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B983" t="s">
         <v>1605</v>
@@ -13995,36 +14001,36 @@
         <v>1608</v>
       </c>
       <c r="B985" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B986" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B987" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B988" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B989" t="s">
         <v>1613</v>
@@ -14075,12 +14081,12 @@
         <v>1624</v>
       </c>
       <c r="B995" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B996" t="s">
         <v>1626</v>
@@ -14099,28 +14105,28 @@
         <v>1629</v>
       </c>
       <c r="B998" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B999" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B1000" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B1001" t="s">
         <v>1633</v>
@@ -14131,12 +14137,12 @@
         <v>1634</v>
       </c>
       <c r="B1002" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B1003" t="s">
         <v>1636</v>
@@ -14155,20 +14161,20 @@
         <v>1639</v>
       </c>
       <c r="B1005" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B1006" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B1007" t="s">
         <v>1642</v>
@@ -14195,12 +14201,12 @@
         <v>1647</v>
       </c>
       <c r="B1010" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B1011" t="s">
         <v>1649</v>
@@ -14219,12 +14225,12 @@
         <v>1652</v>
       </c>
       <c r="B1013" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B1014" t="s">
         <v>1654</v>
@@ -14243,36 +14249,36 @@
         <v>1657</v>
       </c>
       <c r="B1016" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B1017" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B1018" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B1019" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B1020" t="s">
         <v>1662</v>
@@ -14291,12 +14297,12 @@
         <v>1665</v>
       </c>
       <c r="B1022" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B1023" t="s">
         <v>1667</v>
@@ -14323,12 +14329,12 @@
         <v>1672</v>
       </c>
       <c r="B1026" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1027" t="s">
         <v>1674</v>
@@ -14339,20 +14345,20 @@
         <v>1675</v>
       </c>
       <c r="B1028" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B1029" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1030" t="s">
         <v>1678</v>
@@ -14363,12 +14369,12 @@
         <v>1679</v>
       </c>
       <c r="B1031" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1032" t="s">
         <v>1681</v>
@@ -14379,20 +14385,20 @@
         <v>1682</v>
       </c>
       <c r="B1033" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1034" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1035" t="s">
         <v>1685</v>
@@ -14403,20 +14409,20 @@
         <v>1686</v>
       </c>
       <c r="B1036" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1037" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1038" t="s">
         <v>1689</v>
@@ -14427,12 +14433,12 @@
         <v>1690</v>
       </c>
       <c r="B1039" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1040" t="s">
         <v>1692</v>
@@ -14467,12 +14473,12 @@
         <v>1699</v>
       </c>
       <c r="B1044" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1045" t="s">
         <v>1701</v>
@@ -14483,12 +14489,12 @@
         <v>1702</v>
       </c>
       <c r="B1046" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1047" t="s">
         <v>1704</v>
@@ -14531,36 +14537,36 @@
         <v>1713</v>
       </c>
       <c r="B1052" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1053" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1054" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B1055" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1056" t="s">
         <v>1718</v>
@@ -14611,12 +14617,12 @@
         <v>1729</v>
       </c>
       <c r="B1062" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B1063" t="s">
         <v>1731</v>
@@ -14627,20 +14633,20 @@
         <v>1732</v>
       </c>
       <c r="B1064" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1065" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B1066" t="s">
         <v>1735</v>
@@ -14691,12 +14697,12 @@
         <v>1746</v>
       </c>
       <c r="B1072" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B1073" t="s">
         <v>1748</v>
@@ -14707,20 +14713,20 @@
         <v>1749</v>
       </c>
       <c r="B1074" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B1075" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B1076" t="s">
         <v>1752</v>
@@ -14731,44 +14737,44 @@
         <v>1753</v>
       </c>
       <c r="B1077" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B1078" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B1079" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B1080" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B1081" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B1082" t="s">
         <v>1759</v>
@@ -14787,20 +14793,20 @@
         <v>1762</v>
       </c>
       <c r="B1084" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B1085" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B1086" t="s">
         <v>1765</v>
@@ -14819,12 +14825,12 @@
         <v>1768</v>
       </c>
       <c r="B1088" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B1089" t="s">
         <v>1770</v>
@@ -14859,20 +14865,20 @@
         <v>1777</v>
       </c>
       <c r="B1093" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="B1094" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B1095" t="s">
         <v>1780</v>
@@ -14915,12 +14921,12 @@
         <v>1789</v>
       </c>
       <c r="B1100" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B1101" t="s">
         <v>1791</v>
@@ -14939,20 +14945,20 @@
         <v>1794</v>
       </c>
       <c r="B1103" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B1104" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1105" t="s">
         <v>1797</v>
@@ -14963,20 +14969,20 @@
         <v>1798</v>
       </c>
       <c r="B1106" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B1107" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B1108" t="s">
         <v>1801</v>
@@ -14995,12 +15001,12 @@
         <v>1804</v>
       </c>
       <c r="B1110" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="B1111" t="s">
         <v>1806</v>
@@ -15027,12 +15033,12 @@
         <v>1811</v>
       </c>
       <c r="B1114" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B1115" t="s">
         <v>1813</v>
@@ -15075,12 +15081,12 @@
         <v>1822</v>
       </c>
       <c r="B1120" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B1121" t="s">
         <v>1824</v>
@@ -15187,44 +15193,44 @@
         <v>1849</v>
       </c>
       <c r="B1134" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="B1135" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="B1136" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B1137" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B1138" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1139" t="s">
         <v>1855</v>
@@ -15243,28 +15249,28 @@
         <v>1858</v>
       </c>
       <c r="B1141" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="B1142" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="B1143" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B1144" t="s">
         <v>1862</v>
@@ -15331,12 +15337,12 @@
         <v>1877</v>
       </c>
       <c r="B1152" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B1153" t="s">
         <v>1879</v>
@@ -15347,12 +15353,12 @@
         <v>1880</v>
       </c>
       <c r="B1154" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1155" t="s">
         <v>1882</v>
@@ -15387,44 +15393,44 @@
         <v>1889</v>
       </c>
       <c r="B1159" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="B1160" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="B1161" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B1162" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B1163" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B1164" t="s">
         <v>1895</v>
@@ -15443,20 +15449,20 @@
         <v>1898</v>
       </c>
       <c r="B1166" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B1167" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B1168" t="s">
         <v>1901</v>
@@ -15467,44 +15473,44 @@
         <v>1902</v>
       </c>
       <c r="B1169" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B1170" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B1171" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="B1172" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1173" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1174" t="s">
         <v>1908</v>
@@ -15515,36 +15521,36 @@
         <v>1909</v>
       </c>
       <c r="B1175" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B1176" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B1177" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B1178" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B1179" t="s">
         <v>1914</v>
@@ -15555,11 +15561,19 @@
         <v>1915</v>
       </c>
       <c r="B1180" t="s">
-        <v>1915</v>
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:2">
+      <c r="A1181" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B1181" t="s">
+        <v>1917</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1180"/>
+  <autoFilter ref="A1:B1181"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1918">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1920">
   <si>
     <t>en</t>
   </si>
@@ -5285,6 +5285,12 @@
   </si>
   <si>
     <t>Tinker's Construct</t>
+  </si>
+  <si>
+    <t>Tiny Takeover</t>
+  </si>
+  <si>
+    <t>Pengambilalihan Kecil</t>
   </si>
   <si>
     <t>Titanfall</t>
@@ -6117,7 +6123,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1181"/>
+  <dimension ref="A1:B1182"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14753,36 +14759,36 @@
         <v>1756</v>
       </c>
       <c r="B1079" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="B1080" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B1081" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B1082" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B1083" t="s">
         <v>1761</v>
@@ -14801,20 +14807,20 @@
         <v>1764</v>
       </c>
       <c r="B1085" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B1086" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B1087" t="s">
         <v>1767</v>
@@ -14833,12 +14839,12 @@
         <v>1770</v>
       </c>
       <c r="B1089" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B1090" t="s">
         <v>1772</v>
@@ -14873,20 +14879,20 @@
         <v>1779</v>
       </c>
       <c r="B1094" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B1095" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B1096" t="s">
         <v>1782</v>
@@ -14929,12 +14935,12 @@
         <v>1791</v>
       </c>
       <c r="B1101" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1102" t="s">
         <v>1793</v>
@@ -14953,20 +14959,20 @@
         <v>1796</v>
       </c>
       <c r="B1104" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B1105" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B1106" t="s">
         <v>1799</v>
@@ -14977,20 +14983,20 @@
         <v>1800</v>
       </c>
       <c r="B1107" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B1108" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B1109" t="s">
         <v>1803</v>
@@ -15009,12 +15015,12 @@
         <v>1806</v>
       </c>
       <c r="B1111" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B1112" t="s">
         <v>1808</v>
@@ -15041,12 +15047,12 @@
         <v>1813</v>
       </c>
       <c r="B1115" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B1116" t="s">
         <v>1815</v>
@@ -15089,12 +15095,12 @@
         <v>1824</v>
       </c>
       <c r="B1121" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="B1122" t="s">
         <v>1826</v>
@@ -15201,44 +15207,44 @@
         <v>1851</v>
       </c>
       <c r="B1135" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="B1136" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="B1137" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="B1138" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B1139" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="B1140" t="s">
         <v>1857</v>
@@ -15257,28 +15263,28 @@
         <v>1860</v>
       </c>
       <c r="B1142" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B1143" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1144" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1145" t="s">
         <v>1864</v>
@@ -15345,12 +15351,12 @@
         <v>1879</v>
       </c>
       <c r="B1153" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1154" t="s">
         <v>1881</v>
@@ -15361,12 +15367,12 @@
         <v>1882</v>
       </c>
       <c r="B1155" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B1156" t="s">
         <v>1884</v>
@@ -15401,44 +15407,44 @@
         <v>1891</v>
       </c>
       <c r="B1160" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B1161" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="B1162" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="B1163" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B1164" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="B1165" t="s">
         <v>1897</v>
@@ -15457,20 +15463,20 @@
         <v>1900</v>
       </c>
       <c r="B1167" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B1168" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B1169" t="s">
         <v>1903</v>
@@ -15481,44 +15487,44 @@
         <v>1904</v>
       </c>
       <c r="B1170" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="B1171" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1172" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1173" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B1174" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B1175" t="s">
         <v>1910</v>
@@ -15529,36 +15535,36 @@
         <v>1911</v>
       </c>
       <c r="B1176" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B1177" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B1178" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1179" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B1180" t="s">
         <v>1916</v>
@@ -15569,11 +15575,19 @@
         <v>1917</v>
       </c>
       <c r="B1181" t="s">
-        <v>1917</v>
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:2">
+      <c r="A1182" t="s">
+        <v>1919</v>
+      </c>
+      <c r="B1182" t="s">
+        <v>1919</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1181"/>
+  <autoFilter ref="A1:B1182"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1927">
   <si>
     <t>en</t>
   </si>
@@ -2911,6 +2911,9 @@
     <t>Hypixel</t>
   </si>
   <si>
+    <t>Hypixel (Abiphone)</t>
+  </si>
+  <si>
     <t>Hypixel (Attribute Shard)</t>
   </si>
   <si>
@@ -2929,6 +2932,12 @@
     <t>Hypixel (Gear)</t>
   </si>
   <si>
+    <t>Hypixel (Gemstone)</t>
+  </si>
+  <si>
+    <t>Hypixel (Batu Permata)</t>
+  </si>
+  <si>
     <t>Hypixel (Minion)</t>
   </si>
   <si>
@@ -2941,6 +2950,12 @@
     <t>Hypixel (NPC)</t>
   </si>
   <si>
+    <t>Hypixel (Pet Items)</t>
+  </si>
+  <si>
+    <t>Hypixel (Item Hewan Peliharaan)</t>
+  </si>
+  <si>
     <t>Hypixel (Pets)</t>
   </si>
   <si>
@@ -2948,6 +2963,12 @@
   </si>
   <si>
     <t>Hypixel (Reforge Stone)</t>
+  </si>
+  <si>
+    <t>Hypixel (Runes)</t>
+  </si>
+  <si>
+    <t>Hypixel (Rune)</t>
   </si>
   <si>
     <t>Hypixel (Sacks)</t>
@@ -6123,7 +6144,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1182"/>
+  <dimension ref="A1:B1186"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -10767,20 +10788,20 @@
         <v>964</v>
       </c>
       <c r="B580" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
+        <v>965</v>
+      </c>
+      <c r="B581" t="s">
         <v>966</v>
-      </c>
-      <c r="B581" t="s">
-        <v>967</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="B582" t="s">
         <v>968</v>
@@ -10855,28 +10876,28 @@
         <v>981</v>
       </c>
       <c r="B591" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
+        <v>982</v>
+      </c>
+      <c r="B592" t="s">
         <v>983</v>
-      </c>
-      <c r="B592" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
+        <v>984</v>
+      </c>
+      <c r="B593" t="s">
         <v>985</v>
-      </c>
-      <c r="B593" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B594" t="s">
         <v>987</v>
@@ -10911,44 +10932,44 @@
         <v>994</v>
       </c>
       <c r="B598" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
+        <v>995</v>
+      </c>
+      <c r="B599" t="s">
         <v>996</v>
-      </c>
-      <c r="B599" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
+        <v>997</v>
+      </c>
+      <c r="B600" t="s">
         <v>998</v>
-      </c>
-      <c r="B600" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
+        <v>999</v>
+      </c>
+      <c r="B601" t="s">
         <v>1000</v>
-      </c>
-      <c r="B601" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B602" t="s">
         <v>1002</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B603" t="s">
         <v>1004</v>
@@ -10975,12 +10996,12 @@
         <v>1009</v>
       </c>
       <c r="B606" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B607" t="s">
         <v>1011</v>
@@ -11007,20 +11028,20 @@
         <v>1016</v>
       </c>
       <c r="B610" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B611" t="s">
         <v>1018</v>
-      </c>
-      <c r="B611" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B612" t="s">
         <v>1020</v>
@@ -11031,44 +11052,44 @@
         <v>1021</v>
       </c>
       <c r="B613" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B614" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="B615" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="B616" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B617" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B618" t="s">
         <v>1029</v>
@@ -11119,12 +11140,12 @@
         <v>1039</v>
       </c>
       <c r="B624" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B625" t="s">
         <v>1041</v>
@@ -11135,180 +11156,180 @@
         <v>1042</v>
       </c>
       <c r="B626" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B627" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B628" t="s">
-        <v>1044</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
       <c r="B629" t="s">
-        <v>1045</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
       <c r="B630" t="s">
-        <v>1046</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
       <c r="B631" t="s">
-        <v>1047</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="B632" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="B633" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B634" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B635" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="B636" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B637" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B638" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="B639" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B640" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="B641" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="B642" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B643" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B644" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B645" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="B646" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B647" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B648" t="s">
         <v>1070</v>
@@ -11319,12 +11340,12 @@
         <v>1071</v>
       </c>
       <c r="B649" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B650" t="s">
         <v>1073</v>
@@ -11335,68 +11356,68 @@
         <v>1074</v>
       </c>
       <c r="B651" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B652" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B653" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B654" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="655" spans="1:2">
       <c r="A655" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B655" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B656" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B657" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B658" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B659" t="s">
         <v>1087</v>
@@ -11407,36 +11428,36 @@
         <v>1088</v>
       </c>
       <c r="B660" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B661" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="B662" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B663" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B664" t="s">
         <v>1095</v>
@@ -11447,12 +11468,12 @@
         <v>1096</v>
       </c>
       <c r="B665" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B666" t="s">
         <v>1098</v>
@@ -11463,60 +11484,60 @@
         <v>1099</v>
       </c>
       <c r="B667" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B668" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B669" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="B670" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="B671" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B672" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B673" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B674" t="s">
         <v>1109</v>
@@ -11535,12 +11556,12 @@
         <v>1112</v>
       </c>
       <c r="B676" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B677" t="s">
         <v>1114</v>
@@ -11551,36 +11572,36 @@
         <v>1115</v>
       </c>
       <c r="B678" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B679" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="B680" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B681" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B682" t="s">
         <v>1122</v>
@@ -11599,28 +11620,28 @@
         <v>1124</v>
       </c>
       <c r="B684" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B685" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B686" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B687" t="s">
         <v>1130</v>
@@ -11631,60 +11652,60 @@
         <v>1131</v>
       </c>
       <c r="B688" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B689" t="s">
         <v>1133</v>
-      </c>
-      <c r="B689" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B690" t="s">
         <v>1135</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B691" t="s">
         <v>1137</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B692" t="s">
         <v>1139</v>
-      </c>
-      <c r="B692" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B693" t="s">
         <v>1141</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B694" t="s">
         <v>1143</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B695" t="s">
         <v>1145</v>
@@ -11719,20 +11740,20 @@
         <v>1152</v>
       </c>
       <c r="B699" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="700" spans="1:2">
       <c r="A700" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B700" t="s">
         <v>1154</v>
-      </c>
-      <c r="B700" t="s">
-        <v>1155</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B701" t="s">
         <v>1156</v>
@@ -11751,108 +11772,108 @@
         <v>1159</v>
       </c>
       <c r="B703" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B704" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="B705" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B706" t="s">
-        <v>1163</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="B707" t="s">
-        <v>1164</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="B708" t="s">
-        <v>1165</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="B709" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="B710" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="B711" t="s">
-        <v>1169</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B712" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="B713" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="B714" t="s">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="B715" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B716" t="s">
         <v>1177</v>
@@ -11871,36 +11892,36 @@
         <v>1180</v>
       </c>
       <c r="B718" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B719" t="s">
         <v>1182</v>
-      </c>
-      <c r="B719" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B720" t="s">
         <v>1184</v>
-      </c>
-      <c r="B720" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B721" t="s">
         <v>1186</v>
-      </c>
-      <c r="B721" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B722" t="s">
         <v>1188</v>
@@ -11935,52 +11956,52 @@
         <v>1195</v>
       </c>
       <c r="B726" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B727" t="s">
         <v>1197</v>
-      </c>
-      <c r="B727" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B728" t="s">
         <v>1199</v>
-      </c>
-      <c r="B728" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B729" t="s">
         <v>1201</v>
-      </c>
-      <c r="B729" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B730" t="s">
         <v>1203</v>
-      </c>
-      <c r="B730" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B731" t="s">
         <v>1205</v>
-      </c>
-      <c r="B731" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B732" t="s">
         <v>1207</v>
@@ -12031,116 +12052,116 @@
         <v>1217</v>
       </c>
       <c r="B738" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B739" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="B740" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="B741" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B742" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B743" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B744" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B745" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B746" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B747" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B748" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="B749" t="s">
-        <v>1230</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="B750" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="B751" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B752" t="s">
         <v>1236</v>
@@ -12151,36 +12172,36 @@
         <v>1237</v>
       </c>
       <c r="B753" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B754" t="s">
         <v>1239</v>
-      </c>
-      <c r="B754" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B755" t="s">
         <v>1241</v>
-      </c>
-      <c r="B755" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B756" t="s">
         <v>1243</v>
-      </c>
-      <c r="B756" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B757" t="s">
         <v>1245</v>
@@ -12191,76 +12212,76 @@
         <v>1246</v>
       </c>
       <c r="B758" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B759" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B760" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="B761" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="762" spans="1:2">
       <c r="A762" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B762" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B763" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="B764" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="B765" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B766" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B767" t="s">
         <v>1260</v>
@@ -12271,20 +12292,20 @@
         <v>1261</v>
       </c>
       <c r="B768" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B769" t="s">
         <v>1263</v>
-      </c>
-      <c r="B769" t="s">
-        <v>1264</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="B770" t="s">
         <v>1265</v>
@@ -12319,12 +12340,12 @@
         <v>1272</v>
       </c>
       <c r="B774" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="775" spans="1:2">
       <c r="A775" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B775" t="s">
         <v>1274</v>
@@ -12359,44 +12380,44 @@
         <v>1281</v>
       </c>
       <c r="B779" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B780" t="s">
         <v>1283</v>
-      </c>
-      <c r="B780" t="s">
-        <v>1284</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B781" t="s">
         <v>1285</v>
-      </c>
-      <c r="B781" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B782" t="s">
         <v>1287</v>
-      </c>
-      <c r="B782" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B783" t="s">
         <v>1289</v>
-      </c>
-      <c r="B783" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B784" t="s">
         <v>1291</v>
@@ -12407,44 +12428,44 @@
         <v>1292</v>
       </c>
       <c r="B785" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B786" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="B787" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="B788" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B789" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B790" t="s">
         <v>1300</v>
@@ -12455,108 +12476,108 @@
         <v>1301</v>
       </c>
       <c r="B791" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B792" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="B793" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="B794" t="s">
-        <v>1304</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="B795" t="s">
-        <v>1305</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
       <c r="B796" t="s">
-        <v>1306</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
       <c r="B797" t="s">
-        <v>1307</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1308</v>
+        <v>1311</v>
       </c>
       <c r="B798" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="B799" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="B800" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="B801" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="B802" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="B803" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B804" t="s">
         <v>1318</v>
@@ -12567,28 +12588,28 @@
         <v>1319</v>
       </c>
       <c r="B805" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B806" t="s">
         <v>1321</v>
-      </c>
-      <c r="B806" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B807" t="s">
         <v>1323</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B808" t="s">
         <v>1325</v>
@@ -12599,36 +12620,36 @@
         <v>1326</v>
       </c>
       <c r="B809" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B810" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="B811" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="B812" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B813" t="s">
         <v>1333</v>
@@ -12639,60 +12660,60 @@
         <v>1334</v>
       </c>
       <c r="B814" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B815" t="s">
         <v>1336</v>
-      </c>
-      <c r="B815" t="s">
-        <v>1337</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B816" t="s">
         <v>1338</v>
-      </c>
-      <c r="B816" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B817" t="s">
         <v>1340</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B818" t="s">
         <v>1342</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1343</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B819" t="s">
         <v>1344</v>
-      </c>
-      <c r="B819" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B820" t="s">
         <v>1346</v>
-      </c>
-      <c r="B820" t="s">
-        <v>1347</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B821" t="s">
         <v>1348</v>
@@ -12719,132 +12740,132 @@
         <v>1353</v>
       </c>
       <c r="B824" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B825" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B826" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B827" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="B828" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B829" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B830" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="B831" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="B832" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="B833" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="B834" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="B835" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="B836" t="s">
-        <v>1368</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
       <c r="B837" t="s">
-        <v>1369</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1370</v>
+        <v>1373</v>
       </c>
       <c r="B838" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="B839" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B840" t="s">
         <v>1375</v>
@@ -12855,12 +12876,12 @@
         <v>1376</v>
       </c>
       <c r="B841" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="B842" t="s">
         <v>1378</v>
@@ -12887,44 +12908,44 @@
         <v>1383</v>
       </c>
       <c r="B845" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B846" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B847" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="B848" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="B849" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B850" t="s">
         <v>1391</v>
@@ -12935,84 +12956,84 @@
         <v>1392</v>
       </c>
       <c r="B851" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B852" t="s">
         <v>1394</v>
-      </c>
-      <c r="B852" t="s">
-        <v>1395</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B853" t="s">
         <v>1396</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B854" t="s">
         <v>1398</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1399</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B855" t="s">
         <v>1400</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B856" t="s">
         <v>1402</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B857" t="s">
         <v>1404</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B858" t="s">
         <v>1406</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B859" t="s">
         <v>1408</v>
-      </c>
-      <c r="B859" t="s">
-        <v>1409</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B860" t="s">
         <v>1410</v>
-      </c>
-      <c r="B860" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
       <c r="B861" t="s">
         <v>1412</v>
@@ -13023,108 +13044,108 @@
         <v>1413</v>
       </c>
       <c r="B862" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B863" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="B864" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="B865" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="B866" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B867" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B868" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="B869" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="B870" t="s">
-        <v>1423</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="B871" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
       <c r="B872" t="s">
-        <v>1425</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1426</v>
+        <v>1429</v>
       </c>
       <c r="B873" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="B874" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B875" t="s">
         <v>1431</v>
@@ -13135,12 +13156,12 @@
         <v>1432</v>
       </c>
       <c r="B876" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B877" t="s">
         <v>1434</v>
@@ -13175,12 +13196,12 @@
         <v>1441</v>
       </c>
       <c r="B881" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
       <c r="B882" t="s">
         <v>1443</v>
@@ -13223,28 +13244,28 @@
         <v>1451</v>
       </c>
       <c r="B887" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B888" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B889" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B890" t="s">
         <v>1457</v>
@@ -13255,20 +13276,20 @@
         <v>1458</v>
       </c>
       <c r="B891" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B892" t="s">
         <v>1460</v>
-      </c>
-      <c r="B892" t="s">
-        <v>1461</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="B893" t="s">
         <v>1462</v>
@@ -13287,20 +13308,20 @@
         <v>1465</v>
       </c>
       <c r="B895" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B896" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B897" t="s">
         <v>1469</v>
@@ -13319,12 +13340,12 @@
         <v>1472</v>
       </c>
       <c r="B899" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B900" t="s">
         <v>1474</v>
@@ -13335,28 +13356,28 @@
         <v>1475</v>
       </c>
       <c r="B901" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B902" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B903" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B904" t="s">
         <v>1481</v>
@@ -13367,20 +13388,20 @@
         <v>1482</v>
       </c>
       <c r="B905" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B906" t="s">
         <v>1484</v>
-      </c>
-      <c r="B906" t="s">
-        <v>1485</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B907" t="s">
         <v>1486</v>
@@ -13391,60 +13412,60 @@
         <v>1487</v>
       </c>
       <c r="B908" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B909" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="B910" t="s">
-        <v>1489</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
       <c r="B911" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="B912" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="B913" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="B914" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B915" t="s">
         <v>1497</v>
@@ -13455,12 +13476,12 @@
         <v>1498</v>
       </c>
       <c r="B916" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="B917" t="s">
         <v>1500</v>
@@ -13471,36 +13492,36 @@
         <v>1501</v>
       </c>
       <c r="B918" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B919" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="B920" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="B921" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B922" t="s">
         <v>1508</v>
@@ -13511,20 +13532,20 @@
         <v>1509</v>
       </c>
       <c r="B923" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B924" t="s">
         <v>1511</v>
-      </c>
-      <c r="B924" t="s">
-        <v>1512</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B925" t="s">
         <v>1513</v>
@@ -13535,28 +13556,28 @@
         <v>1514</v>
       </c>
       <c r="B926" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B927" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B928" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B929" t="s">
         <v>1520</v>
@@ -13567,12 +13588,12 @@
         <v>1521</v>
       </c>
       <c r="B930" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="B931" t="s">
         <v>1523</v>
@@ -13599,12 +13620,12 @@
         <v>1528</v>
       </c>
       <c r="B934" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B935" t="s">
         <v>1530</v>
@@ -13623,12 +13644,12 @@
         <v>1533</v>
       </c>
       <c r="B937" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B938" t="s">
         <v>1535</v>
@@ -13639,20 +13660,20 @@
         <v>1536</v>
       </c>
       <c r="B939" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B940" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B941" t="s">
         <v>1540</v>
@@ -13663,12 +13684,12 @@
         <v>1541</v>
       </c>
       <c r="B942" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B943" t="s">
         <v>1543</v>
@@ -13679,44 +13700,44 @@
         <v>1544</v>
       </c>
       <c r="B944" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B945" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B946" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="B947" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="B948" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B949" t="s">
         <v>1552</v>
@@ -13735,52 +13756,52 @@
         <v>1554</v>
       </c>
       <c r="B951" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B952" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B953" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="B954" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="B955" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="B956" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B957" t="s">
         <v>1563</v>
@@ -13791,12 +13812,12 @@
         <v>1564</v>
       </c>
       <c r="B958" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B959" t="s">
         <v>1566</v>
@@ -13807,36 +13828,36 @@
         <v>1567</v>
       </c>
       <c r="B960" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B961" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="B962" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="B963" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B964" t="s">
         <v>1574</v>
@@ -13847,28 +13868,28 @@
         <v>1575</v>
       </c>
       <c r="B965" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B966" t="s">
         <v>1577</v>
-      </c>
-      <c r="B966" t="s">
-        <v>1578</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B967" t="s">
         <v>1579</v>
-      </c>
-      <c r="B967" t="s">
-        <v>1580</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="B968" t="s">
         <v>1581</v>
@@ -13879,60 +13900,60 @@
         <v>1582</v>
       </c>
       <c r="B969" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B970" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="B971" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B972" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="B973" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="B974" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B975" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B976" t="s">
         <v>1593</v>
@@ -13943,20 +13964,20 @@
         <v>1594</v>
       </c>
       <c r="B977" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B978" t="s">
         <v>1596</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1597</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="B979" t="s">
         <v>1598</v>
@@ -14015,52 +14036,52 @@
         <v>1610</v>
       </c>
       <c r="B986" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B987" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B988" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="B989" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="B990" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="B991" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B992" t="s">
         <v>1619</v>
@@ -14071,28 +14092,28 @@
         <v>1620</v>
       </c>
       <c r="B993" t="s">
-        <v>1621</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B994" t="s">
         <v>1622</v>
-      </c>
-      <c r="B994" t="s">
-        <v>1623</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B995" t="s">
         <v>1624</v>
-      </c>
-      <c r="B995" t="s">
-        <v>1625</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="B996" t="s">
         <v>1626</v>
@@ -14119,52 +14140,52 @@
         <v>1631</v>
       </c>
       <c r="B999" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B1000" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B1001" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="B1002" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="B1003" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="B1004" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B1005" t="s">
         <v>1640</v>
@@ -14175,36 +14196,36 @@
         <v>1641</v>
       </c>
       <c r="B1006" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B1007" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1008" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B1009" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B1010" t="s">
         <v>1648</v>
@@ -14239,12 +14260,12 @@
         <v>1654</v>
       </c>
       <c r="B1014" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B1015" t="s">
         <v>1656</v>
@@ -14263,60 +14284,60 @@
         <v>1659</v>
       </c>
       <c r="B1017" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B1018" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B1019" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="B1020" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="B1021" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="B1022" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B1023" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B1024" t="s">
         <v>1669</v>
@@ -14359,108 +14380,108 @@
         <v>1677</v>
       </c>
       <c r="B1029" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1030" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="B1031" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1032" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="B1033" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1034" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1035" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="B1036" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1037" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="B1038" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="B1039" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1040" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="B1041" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1042" t="s">
         <v>1696</v>
@@ -14479,12 +14500,12 @@
         <v>1699</v>
       </c>
       <c r="B1044" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="B1045" t="s">
         <v>1701</v>
@@ -14503,20 +14524,20 @@
         <v>1704</v>
       </c>
       <c r="B1047" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1048" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1049" t="s">
         <v>1708</v>
@@ -14535,20 +14556,20 @@
         <v>1711</v>
       </c>
       <c r="B1051" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B1052" t="s">
         <v>1713</v>
-      </c>
-      <c r="B1052" t="s">
-        <v>1714</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="B1053" t="s">
         <v>1715</v>
@@ -14559,44 +14580,44 @@
         <v>1716</v>
       </c>
       <c r="B1054" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1055" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="B1056" t="s">
-        <v>1718</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="B1057" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="B1058" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B1059" t="s">
         <v>1724</v>
@@ -14607,28 +14628,28 @@
         <v>1725</v>
       </c>
       <c r="B1060" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B1061" t="s">
         <v>1727</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>1728</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B1062" t="s">
         <v>1729</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>1730</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="B1063" t="s">
         <v>1731</v>
@@ -14647,36 +14668,36 @@
         <v>1734</v>
       </c>
       <c r="B1065" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B1066" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="B1067" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B1068" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="B1069" t="s">
         <v>1741</v>
@@ -14687,28 +14708,28 @@
         <v>1742</v>
       </c>
       <c r="B1070" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B1071" t="s">
         <v>1744</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>1745</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B1072" t="s">
         <v>1746</v>
-      </c>
-      <c r="B1072" t="s">
-        <v>1747</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B1073" t="s">
         <v>1748</v>
@@ -14727,132 +14748,132 @@
         <v>1751</v>
       </c>
       <c r="B1075" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B1076" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="B1077" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B1078" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="B1079" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="B1080" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B1081" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="B1082" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="B1083" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="B1084" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="B1085" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B1086" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B1087" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B1088" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B1089" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B1090" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B1091" t="s">
         <v>1774</v>
@@ -14879,12 +14900,12 @@
         <v>1779</v>
       </c>
       <c r="B1094" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="B1095" t="s">
         <v>1781</v>
@@ -14895,28 +14916,28 @@
         <v>1782</v>
       </c>
       <c r="B1096" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B1097" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B1098" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B1099" t="s">
         <v>1788</v>
@@ -14927,20 +14948,20 @@
         <v>1789</v>
       </c>
       <c r="B1100" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B1101" t="s">
         <v>1791</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>1792</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="B1102" t="s">
         <v>1793</v>
@@ -14967,68 +14988,68 @@
         <v>1798</v>
       </c>
       <c r="B1105" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B1106" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B1107" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B1108" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="B1109" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="B1110" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B1111" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="B1112" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1113" t="s">
         <v>1810</v>
@@ -15087,20 +15108,20 @@
         <v>1822</v>
       </c>
       <c r="B1120" t="s">
-        <v>1823</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>1823</v>
+      </c>
+      <c r="B1121" t="s">
         <v>1824</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>1825</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="B1122" t="s">
         <v>1826</v>
@@ -15135,84 +15156,84 @@
         <v>1833</v>
       </c>
       <c r="B1126" t="s">
-        <v>1834</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1834</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1835</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1836</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1836</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1837</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1838</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1838</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1839</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1840</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1841</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1843</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1845</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1847</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1849</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1850</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B1135" t="s">
         <v>1851</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>1852</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="B1136" t="s">
         <v>1853</v>
@@ -15223,92 +15244,92 @@
         <v>1854</v>
       </c>
       <c r="B1137" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="B1138" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="B1139" t="s">
-        <v>1856</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
       <c r="B1140" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1858</v>
+        <v>1861</v>
       </c>
       <c r="B1141" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="B1142" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1143" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1144" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B1145" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="B1146" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="B1147" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B1148" t="s">
         <v>1870</v>
@@ -15319,44 +15340,44 @@
         <v>1871</v>
       </c>
       <c r="B1149" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B1150" t="s">
         <v>1873</v>
-      </c>
-      <c r="B1150" t="s">
-        <v>1874</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B1151" t="s">
         <v>1875</v>
-      </c>
-      <c r="B1151" t="s">
-        <v>1876</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
+        <v>1876</v>
+      </c>
+      <c r="B1152" t="s">
         <v>1877</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>1878</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B1153" t="s">
         <v>1879</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>1880</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="B1154" t="s">
         <v>1881</v>
@@ -15375,20 +15396,20 @@
         <v>1884</v>
       </c>
       <c r="B1156" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="B1157" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="B1158" t="s">
         <v>1888</v>
@@ -15407,12 +15428,12 @@
         <v>1891</v>
       </c>
       <c r="B1160" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="B1161" t="s">
         <v>1893</v>
@@ -15423,171 +15444,203 @@
         <v>1894</v>
       </c>
       <c r="B1162" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B1163" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="B1164" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="B1165" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1898</v>
+        <v>1901</v>
       </c>
       <c r="B1166" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="B1167" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B1168" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B1169" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B1170" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1171" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="B1172" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="B1173" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="B1174" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1910</v>
+        <v>1913</v>
       </c>
       <c r="B1175" t="s">
-        <v>1910</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
       <c r="B1176" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="B1177" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="B1178" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="B1179" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="B1180" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="B1181" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="B1182" t="s">
-        <v>1919</v>
+        <v>1921</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:2">
+      <c r="A1183" t="s">
+        <v>1922</v>
+      </c>
+      <c r="B1183" t="s">
+        <v>1922</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:2">
+      <c r="A1184" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B1184" t="s">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:2">
+      <c r="A1185" t="s">
+        <v>1924</v>
+      </c>
+      <c r="B1185" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:2">
+      <c r="A1186" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B1186" t="s">
+        <v>1926</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1182"/>
+  <autoFilter ref="A1:B1186"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1186</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1927">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1929">
   <si>
     <t>en</t>
   </si>
@@ -4343,6 +4343,12 @@
   </si>
   <si>
     <t>Prof Layton</t>
+  </si>
+  <si>
+    <t>Project Zomboid</t>
+  </si>
+  <si>
+    <t>Proyek Zomboid</t>
   </si>
   <si>
     <t>Pumpkin</t>
@@ -6144,7 +6150,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1186"/>
+  <dimension ref="A1:B1187"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13236,12 +13242,12 @@
         <v>1450</v>
       </c>
       <c r="B886" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B887" t="s">
         <v>1452</v>
@@ -13268,20 +13274,20 @@
         <v>1457</v>
       </c>
       <c r="B890" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B891" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B892" t="s">
         <v>1460</v>
@@ -13324,12 +13330,12 @@
         <v>1469</v>
       </c>
       <c r="B897" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B898" t="s">
         <v>1471</v>
@@ -13340,12 +13346,12 @@
         <v>1472</v>
       </c>
       <c r="B899" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B900" t="s">
         <v>1474</v>
@@ -13380,20 +13386,20 @@
         <v>1481</v>
       </c>
       <c r="B904" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B905" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B906" t="s">
         <v>1484</v>
@@ -13436,52 +13442,52 @@
         <v>1493</v>
       </c>
       <c r="B911" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B912" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B913" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B914" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B915" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B916" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B917" t="s">
         <v>1500</v>
@@ -13516,28 +13522,28 @@
         <v>1507</v>
       </c>
       <c r="B921" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B922" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B923" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B924" t="s">
         <v>1511</v>
@@ -13580,20 +13586,20 @@
         <v>1520</v>
       </c>
       <c r="B929" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B930" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B931" t="s">
         <v>1523</v>
@@ -13628,12 +13634,12 @@
         <v>1530</v>
       </c>
       <c r="B935" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B936" t="s">
         <v>1532</v>
@@ -13652,12 +13658,12 @@
         <v>1535</v>
       </c>
       <c r="B938" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B939" t="s">
         <v>1537</v>
@@ -13676,12 +13682,12 @@
         <v>1540</v>
       </c>
       <c r="B941" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B942" t="s">
         <v>1542</v>
@@ -13692,12 +13698,12 @@
         <v>1543</v>
       </c>
       <c r="B943" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B944" t="s">
         <v>1545</v>
@@ -13716,12 +13722,12 @@
         <v>1548</v>
       </c>
       <c r="B946" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B947" t="s">
         <v>1550</v>
@@ -13732,28 +13738,28 @@
         <v>1551</v>
       </c>
       <c r="B948" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B949" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B950" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B951" t="s">
         <v>1555</v>
@@ -13780,44 +13786,44 @@
         <v>1560</v>
       </c>
       <c r="B954" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B955" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B956" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B957" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B958" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B959" t="s">
         <v>1566</v>
@@ -13852,28 +13858,28 @@
         <v>1573</v>
       </c>
       <c r="B963" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B964" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B965" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B966" t="s">
         <v>1577</v>
@@ -13924,28 +13930,28 @@
         <v>1588</v>
       </c>
       <c r="B972" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B973" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B974" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B975" t="s">
         <v>1592</v>
@@ -13956,20 +13962,20 @@
         <v>1593</v>
       </c>
       <c r="B976" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B977" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B978" t="s">
         <v>1596</v>
@@ -14012,12 +14018,12 @@
         <v>1605</v>
       </c>
       <c r="B983" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B984" t="s">
         <v>1607</v>
@@ -14044,12 +14050,12 @@
         <v>1612</v>
       </c>
       <c r="B987" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B988" t="s">
         <v>1614</v>
@@ -14068,36 +14074,36 @@
         <v>1617</v>
       </c>
       <c r="B990" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B991" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B992" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B993" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B994" t="s">
         <v>1622</v>
@@ -14148,12 +14154,12 @@
         <v>1633</v>
       </c>
       <c r="B1000" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B1001" t="s">
         <v>1635</v>
@@ -14172,28 +14178,28 @@
         <v>1638</v>
       </c>
       <c r="B1003" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B1004" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B1005" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B1006" t="s">
         <v>1642</v>
@@ -14204,12 +14210,12 @@
         <v>1643</v>
       </c>
       <c r="B1007" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B1008" t="s">
         <v>1645</v>
@@ -14228,20 +14234,20 @@
         <v>1648</v>
       </c>
       <c r="B1010" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B1011" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B1012" t="s">
         <v>1651</v>
@@ -14268,12 +14274,12 @@
         <v>1656</v>
       </c>
       <c r="B1015" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B1016" t="s">
         <v>1658</v>
@@ -14292,12 +14298,12 @@
         <v>1661</v>
       </c>
       <c r="B1018" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B1019" t="s">
         <v>1663</v>
@@ -14316,36 +14322,36 @@
         <v>1666</v>
       </c>
       <c r="B1021" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B1022" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B1023" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B1024" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B1025" t="s">
         <v>1671</v>
@@ -14364,12 +14370,12 @@
         <v>1674</v>
       </c>
       <c r="B1027" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1028" t="s">
         <v>1676</v>
@@ -14396,12 +14402,12 @@
         <v>1681</v>
       </c>
       <c r="B1031" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1032" t="s">
         <v>1683</v>
@@ -14412,20 +14418,20 @@
         <v>1684</v>
       </c>
       <c r="B1033" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1034" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B1035" t="s">
         <v>1687</v>
@@ -14436,12 +14442,12 @@
         <v>1688</v>
       </c>
       <c r="B1036" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1037" t="s">
         <v>1690</v>
@@ -14452,20 +14458,20 @@
         <v>1691</v>
       </c>
       <c r="B1038" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1039" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1040" t="s">
         <v>1694</v>
@@ -14476,20 +14482,20 @@
         <v>1695</v>
       </c>
       <c r="B1041" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1042" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1043" t="s">
         <v>1698</v>
@@ -14500,12 +14506,12 @@
         <v>1699</v>
       </c>
       <c r="B1044" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1045" t="s">
         <v>1701</v>
@@ -14540,12 +14546,12 @@
         <v>1708</v>
       </c>
       <c r="B1049" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1050" t="s">
         <v>1710</v>
@@ -14556,12 +14562,12 @@
         <v>1711</v>
       </c>
       <c r="B1051" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1052" t="s">
         <v>1713</v>
@@ -14604,36 +14610,36 @@
         <v>1722</v>
       </c>
       <c r="B1057" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B1058" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B1059" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="B1060" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B1061" t="s">
         <v>1727</v>
@@ -14684,12 +14690,12 @@
         <v>1738</v>
       </c>
       <c r="B1067" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="B1068" t="s">
         <v>1740</v>
@@ -14700,20 +14706,20 @@
         <v>1741</v>
       </c>
       <c r="B1069" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B1070" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="B1071" t="s">
         <v>1744</v>
@@ -14764,12 +14770,12 @@
         <v>1755</v>
       </c>
       <c r="B1077" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="B1078" t="s">
         <v>1757</v>
@@ -14780,20 +14786,20 @@
         <v>1758</v>
       </c>
       <c r="B1079" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B1080" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="B1081" t="s">
         <v>1761</v>
@@ -14804,12 +14810,12 @@
         <v>1762</v>
       </c>
       <c r="B1082" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B1083" t="s">
         <v>1764</v>
@@ -14820,36 +14826,36 @@
         <v>1765</v>
       </c>
       <c r="B1084" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B1085" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B1086" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B1087" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B1088" t="s">
         <v>1770</v>
@@ -14868,20 +14874,20 @@
         <v>1773</v>
       </c>
       <c r="B1090" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B1091" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B1092" t="s">
         <v>1776</v>
@@ -14900,12 +14906,12 @@
         <v>1779</v>
       </c>
       <c r="B1094" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B1095" t="s">
         <v>1781</v>
@@ -14940,20 +14946,20 @@
         <v>1788</v>
       </c>
       <c r="B1099" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="B1100" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B1101" t="s">
         <v>1791</v>
@@ -14996,12 +15002,12 @@
         <v>1800</v>
       </c>
       <c r="B1106" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B1107" t="s">
         <v>1802</v>
@@ -15020,20 +15026,20 @@
         <v>1805</v>
       </c>
       <c r="B1109" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="B1110" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B1111" t="s">
         <v>1808</v>
@@ -15044,20 +15050,20 @@
         <v>1809</v>
       </c>
       <c r="B1112" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B1113" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1114" t="s">
         <v>1812</v>
@@ -15076,12 +15082,12 @@
         <v>1815</v>
       </c>
       <c r="B1116" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B1117" t="s">
         <v>1817</v>
@@ -15108,12 +15114,12 @@
         <v>1822</v>
       </c>
       <c r="B1120" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B1121" t="s">
         <v>1824</v>
@@ -15156,12 +15162,12 @@
         <v>1833</v>
       </c>
       <c r="B1126" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="B1127" t="s">
         <v>1835</v>
@@ -15268,44 +15274,44 @@
         <v>1860</v>
       </c>
       <c r="B1140" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="B1141" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="B1142" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="B1143" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B1144" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="B1145" t="s">
         <v>1866</v>
@@ -15324,28 +15330,28 @@
         <v>1869</v>
       </c>
       <c r="B1147" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B1148" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B1149" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="B1150" t="s">
         <v>1873</v>
@@ -15412,12 +15418,12 @@
         <v>1888</v>
       </c>
       <c r="B1158" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="B1159" t="s">
         <v>1890</v>
@@ -15428,12 +15434,12 @@
         <v>1891</v>
       </c>
       <c r="B1160" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B1161" t="s">
         <v>1893</v>
@@ -15468,44 +15474,44 @@
         <v>1900</v>
       </c>
       <c r="B1165" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B1166" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B1167" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="B1168" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B1169" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="B1170" t="s">
         <v>1906</v>
@@ -15524,20 +15530,20 @@
         <v>1909</v>
       </c>
       <c r="B1172" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B1173" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B1174" t="s">
         <v>1912</v>
@@ -15548,44 +15554,44 @@
         <v>1913</v>
       </c>
       <c r="B1175" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1176" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B1177" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B1178" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="B1179" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B1180" t="s">
         <v>1919</v>
@@ -15596,36 +15602,36 @@
         <v>1920</v>
       </c>
       <c r="B1181" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B1182" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B1183" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B1184" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B1185" t="s">
         <v>1925</v>
@@ -15636,11 +15642,19 @@
         <v>1926</v>
       </c>
       <c r="B1186" t="s">
-        <v>1926</v>
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:2">
+      <c r="A1187" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B1187" t="s">
+        <v>1928</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1186"/>
+  <autoFilter ref="A1:B1187"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1187</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1930">
   <si>
     <t>en</t>
   </si>
@@ -359,6 +359,9 @@
   </si>
   <si>
     <t>Baka dan Ujian</t>
+  </si>
+  <si>
+    <t>Bakugan</t>
   </si>
   <si>
     <t>Baldi's Basics</t>
@@ -6150,7 +6153,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1187"/>
+  <dimension ref="A1:B1188"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -6706,20 +6709,20 @@
         <v>114</v>
       </c>
       <c r="B69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
+        <v>115</v>
+      </c>
+      <c r="B70" t="s">
         <v>116</v>
-      </c>
-      <c r="B70" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B71" t="s">
         <v>118</v>
@@ -6762,28 +6765,28 @@
         <v>123</v>
       </c>
       <c r="B76" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" t="s">
         <v>125</v>
-      </c>
-      <c r="B77" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" t="s">
         <v>127</v>
-      </c>
-      <c r="B78" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B79" t="s">
         <v>129</v>
@@ -6794,12 +6797,12 @@
         <v>130</v>
       </c>
       <c r="B80" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B81" t="s">
         <v>132</v>
@@ -6810,28 +6813,28 @@
         <v>133</v>
       </c>
       <c r="B82" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
+        <v>134</v>
+      </c>
+      <c r="B83" t="s">
         <v>135</v>
-      </c>
-      <c r="B83" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
+        <v>136</v>
+      </c>
+      <c r="B84" t="s">
         <v>137</v>
-      </c>
-      <c r="B84" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B85" t="s">
         <v>139</v>
@@ -6850,36 +6853,36 @@
         <v>141</v>
       </c>
       <c r="B87" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
+        <v>142</v>
+      </c>
+      <c r="B88" t="s">
         <v>143</v>
-      </c>
-      <c r="B88" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" t="s">
+        <v>144</v>
+      </c>
+      <c r="B89" t="s">
         <v>145</v>
-      </c>
-      <c r="B89" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
+        <v>146</v>
+      </c>
+      <c r="B90" t="s">
         <v>147</v>
-      </c>
-      <c r="B90" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B91" t="s">
         <v>149</v>
@@ -6890,12 +6893,12 @@
         <v>150</v>
       </c>
       <c r="B92" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B93" t="s">
         <v>152</v>
@@ -6906,20 +6909,20 @@
         <v>153</v>
       </c>
       <c r="B94" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
+        <v>154</v>
+      </c>
+      <c r="B95" t="s">
         <v>155</v>
-      </c>
-      <c r="B95" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B96" t="s">
         <v>157</v>
@@ -6946,20 +6949,20 @@
         <v>160</v>
       </c>
       <c r="B99" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
+        <v>161</v>
+      </c>
+      <c r="B100" t="s">
         <v>162</v>
-      </c>
-      <c r="B100" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B101" t="s">
         <v>164</v>
@@ -6970,12 +6973,12 @@
         <v>165</v>
       </c>
       <c r="B102" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B103" t="s">
         <v>167</v>
@@ -6986,12 +6989,12 @@
         <v>168</v>
       </c>
       <c r="B104" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B105" t="s">
         <v>170</v>
@@ -7002,12 +7005,12 @@
         <v>171</v>
       </c>
       <c r="B106" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B107" t="s">
         <v>173</v>
@@ -7018,28 +7021,28 @@
         <v>174</v>
       </c>
       <c r="B108" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
+        <v>175</v>
+      </c>
+      <c r="B109" t="s">
         <v>176</v>
-      </c>
-      <c r="B109" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
+        <v>177</v>
+      </c>
+      <c r="B110" t="s">
         <v>178</v>
-      </c>
-      <c r="B110" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B111" t="s">
         <v>180</v>
@@ -7058,20 +7061,20 @@
         <v>182</v>
       </c>
       <c r="B113" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
+        <v>183</v>
+      </c>
+      <c r="B114" t="s">
         <v>184</v>
-      </c>
-      <c r="B114" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B115" t="s">
         <v>186</v>
@@ -7082,36 +7085,36 @@
         <v>187</v>
       </c>
       <c r="B116" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>188</v>
+      </c>
+      <c r="B117" t="s">
         <v>189</v>
-      </c>
-      <c r="B117" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>190</v>
+      </c>
+      <c r="B118" t="s">
         <v>191</v>
-      </c>
-      <c r="B118" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>192</v>
+      </c>
+      <c r="B119" t="s">
         <v>193</v>
-      </c>
-      <c r="B119" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B120" t="s">
         <v>195</v>
@@ -7146,12 +7149,12 @@
         <v>199</v>
       </c>
       <c r="B124" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B125" t="s">
         <v>201</v>
@@ -7162,36 +7165,36 @@
         <v>202</v>
       </c>
       <c r="B126" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
+        <v>203</v>
+      </c>
+      <c r="B127" t="s">
         <v>204</v>
-      </c>
-      <c r="B127" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
+        <v>205</v>
+      </c>
+      <c r="B128" t="s">
         <v>206</v>
-      </c>
-      <c r="B128" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
+        <v>207</v>
+      </c>
+      <c r="B129" t="s">
         <v>208</v>
-      </c>
-      <c r="B129" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B130" t="s">
         <v>210</v>
@@ -7226,20 +7229,20 @@
         <v>214</v>
       </c>
       <c r="B134" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
+        <v>215</v>
+      </c>
+      <c r="B135" t="s">
         <v>216</v>
-      </c>
-      <c r="B135" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B136" t="s">
         <v>218</v>
@@ -7258,20 +7261,20 @@
         <v>220</v>
       </c>
       <c r="B138" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>221</v>
+      </c>
+      <c r="B139" t="s">
         <v>222</v>
-      </c>
-      <c r="B139" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B140" t="s">
         <v>224</v>
@@ -7282,52 +7285,52 @@
         <v>225</v>
       </c>
       <c r="B141" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
+        <v>226</v>
+      </c>
+      <c r="B142" t="s">
         <v>227</v>
-      </c>
-      <c r="B142" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
+        <v>228</v>
+      </c>
+      <c r="B143" t="s">
         <v>229</v>
-      </c>
-      <c r="B143" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" t="s">
+        <v>230</v>
+      </c>
+      <c r="B144" t="s">
         <v>231</v>
-      </c>
-      <c r="B144" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
+        <v>232</v>
+      </c>
+      <c r="B145" t="s">
         <v>233</v>
-      </c>
-      <c r="B145" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
+        <v>234</v>
+      </c>
+      <c r="B146" t="s">
         <v>235</v>
-      </c>
-      <c r="B146" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B147" t="s">
         <v>237</v>
@@ -7338,36 +7341,36 @@
         <v>238</v>
       </c>
       <c r="B148" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
+        <v>239</v>
+      </c>
+      <c r="B149" t="s">
         <v>240</v>
-      </c>
-      <c r="B149" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" t="s">
+        <v>241</v>
+      </c>
+      <c r="B150" t="s">
         <v>242</v>
-      </c>
-      <c r="B150" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
+        <v>243</v>
+      </c>
+      <c r="B151" t="s">
         <v>244</v>
-      </c>
-      <c r="B151" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B152" t="s">
         <v>246</v>
@@ -7378,52 +7381,52 @@
         <v>247</v>
       </c>
       <c r="B153" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>248</v>
+      </c>
+      <c r="B154" t="s">
         <v>249</v>
-      </c>
-      <c r="B154" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>250</v>
+      </c>
+      <c r="B155" t="s">
         <v>251</v>
-      </c>
-      <c r="B155" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>252</v>
+      </c>
+      <c r="B156" t="s">
         <v>253</v>
-      </c>
-      <c r="B156" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>254</v>
+      </c>
+      <c r="B157" t="s">
         <v>255</v>
-      </c>
-      <c r="B157" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>256</v>
+      </c>
+      <c r="B158" t="s">
         <v>257</v>
-      </c>
-      <c r="B158" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B159" t="s">
         <v>259</v>
@@ -7434,28 +7437,28 @@
         <v>260</v>
       </c>
       <c r="B160" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>261</v>
+      </c>
+      <c r="B161" t="s">
         <v>262</v>
-      </c>
-      <c r="B161" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>263</v>
+      </c>
+      <c r="B162" t="s">
         <v>264</v>
-      </c>
-      <c r="B162" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B163" t="s">
         <v>266</v>
@@ -7466,60 +7469,60 @@
         <v>267</v>
       </c>
       <c r="B164" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
+        <v>268</v>
+      </c>
+      <c r="B165" t="s">
         <v>269</v>
-      </c>
-      <c r="B165" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
+        <v>270</v>
+      </c>
+      <c r="B166" t="s">
         <v>271</v>
-      </c>
-      <c r="B166" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
+        <v>272</v>
+      </c>
+      <c r="B167" t="s">
         <v>273</v>
-      </c>
-      <c r="B167" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
+        <v>274</v>
+      </c>
+      <c r="B168" t="s">
         <v>275</v>
-      </c>
-      <c r="B168" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
+        <v>276</v>
+      </c>
+      <c r="B169" t="s">
         <v>277</v>
-      </c>
-      <c r="B169" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>278</v>
+      </c>
+      <c r="B170" t="s">
         <v>279</v>
-      </c>
-      <c r="B170" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B171" t="s">
         <v>281</v>
@@ -7530,44 +7533,44 @@
         <v>282</v>
       </c>
       <c r="B172" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
+        <v>283</v>
+      </c>
+      <c r="B173" t="s">
         <v>284</v>
-      </c>
-      <c r="B173" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
+        <v>285</v>
+      </c>
+      <c r="B174" t="s">
         <v>286</v>
-      </c>
-      <c r="B174" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
+        <v>287</v>
+      </c>
+      <c r="B175" t="s">
         <v>288</v>
-      </c>
-      <c r="B175" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
+        <v>289</v>
+      </c>
+      <c r="B176" t="s">
         <v>290</v>
-      </c>
-      <c r="B176" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B177" t="s">
         <v>292</v>
@@ -7610,140 +7613,140 @@
         <v>297</v>
       </c>
       <c r="B182" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
+        <v>298</v>
+      </c>
+      <c r="B183" t="s">
         <v>299</v>
-      </c>
-      <c r="B183" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
+        <v>300</v>
+      </c>
+      <c r="B184" t="s">
         <v>301</v>
-      </c>
-      <c r="B184" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
+        <v>302</v>
+      </c>
+      <c r="B185" t="s">
         <v>303</v>
-      </c>
-      <c r="B185" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
+        <v>304</v>
+      </c>
+      <c r="B186" t="s">
         <v>305</v>
-      </c>
-      <c r="B186" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
+        <v>306</v>
+      </c>
+      <c r="B187" t="s">
         <v>307</v>
-      </c>
-      <c r="B187" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
+        <v>308</v>
+      </c>
+      <c r="B188" t="s">
         <v>309</v>
-      </c>
-      <c r="B188" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
+        <v>310</v>
+      </c>
+      <c r="B189" t="s">
         <v>311</v>
-      </c>
-      <c r="B189" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
+        <v>312</v>
+      </c>
+      <c r="B190" t="s">
         <v>313</v>
-      </c>
-      <c r="B190" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
+        <v>314</v>
+      </c>
+      <c r="B191" t="s">
         <v>315</v>
-      </c>
-      <c r="B191" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
+        <v>316</v>
+      </c>
+      <c r="B192" t="s">
         <v>317</v>
-      </c>
-      <c r="B192" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
+        <v>318</v>
+      </c>
+      <c r="B193" t="s">
         <v>319</v>
-      </c>
-      <c r="B193" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
+        <v>320</v>
+      </c>
+      <c r="B194" t="s">
         <v>321</v>
-      </c>
-      <c r="B194" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
+        <v>322</v>
+      </c>
+      <c r="B195" t="s">
         <v>323</v>
-      </c>
-      <c r="B195" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
+        <v>324</v>
+      </c>
+      <c r="B196" t="s">
         <v>325</v>
-      </c>
-      <c r="B196" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
+        <v>326</v>
+      </c>
+      <c r="B197" t="s">
         <v>327</v>
-      </c>
-      <c r="B197" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
+        <v>328</v>
+      </c>
+      <c r="B198" t="s">
         <v>329</v>
-      </c>
-      <c r="B198" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B199" t="s">
         <v>331</v>
@@ -7754,44 +7757,44 @@
         <v>332</v>
       </c>
       <c r="B200" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
+        <v>333</v>
+      </c>
+      <c r="B201" t="s">
         <v>334</v>
-      </c>
-      <c r="B201" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
+        <v>335</v>
+      </c>
+      <c r="B202" t="s">
         <v>336</v>
-      </c>
-      <c r="B202" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
+        <v>337</v>
+      </c>
+      <c r="B203" t="s">
         <v>338</v>
-      </c>
-      <c r="B203" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
+        <v>339</v>
+      </c>
+      <c r="B204" t="s">
         <v>340</v>
-      </c>
-      <c r="B204" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B205" t="s">
         <v>342</v>
@@ -7802,28 +7805,28 @@
         <v>343</v>
       </c>
       <c r="B206" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
+        <v>344</v>
+      </c>
+      <c r="B207" t="s">
         <v>345</v>
-      </c>
-      <c r="B207" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
+        <v>346</v>
+      </c>
+      <c r="B208" t="s">
         <v>347</v>
-      </c>
-      <c r="B208" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B209" t="s">
         <v>349</v>
@@ -7834,44 +7837,44 @@
         <v>350</v>
       </c>
       <c r="B210" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
+        <v>351</v>
+      </c>
+      <c r="B211" t="s">
         <v>352</v>
-      </c>
-      <c r="B211" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
+        <v>353</v>
+      </c>
+      <c r="B212" t="s">
         <v>354</v>
-      </c>
-      <c r="B212" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
+        <v>355</v>
+      </c>
+      <c r="B213" t="s">
         <v>356</v>
-      </c>
-      <c r="B213" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
+        <v>357</v>
+      </c>
+      <c r="B214" t="s">
         <v>358</v>
-      </c>
-      <c r="B214" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B215" t="s">
         <v>360</v>
@@ -7882,20 +7885,20 @@
         <v>361</v>
       </c>
       <c r="B216" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
+        <v>362</v>
+      </c>
+      <c r="B217" t="s">
         <v>363</v>
-      </c>
-      <c r="B217" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B218" t="s">
         <v>365</v>
@@ -7946,12 +7949,12 @@
         <v>371</v>
       </c>
       <c r="B224" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B225" t="s">
         <v>373</v>
@@ -7962,12 +7965,12 @@
         <v>374</v>
       </c>
       <c r="B226" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B227" t="s">
         <v>376</v>
@@ -7978,28 +7981,28 @@
         <v>377</v>
       </c>
       <c r="B228" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
+        <v>378</v>
+      </c>
+      <c r="B229" t="s">
         <v>379</v>
-      </c>
-      <c r="B229" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
+        <v>380</v>
+      </c>
+      <c r="B230" t="s">
         <v>381</v>
-      </c>
-      <c r="B230" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B231" t="s">
         <v>383</v>
@@ -8010,20 +8013,20 @@
         <v>384</v>
       </c>
       <c r="B232" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
+        <v>385</v>
+      </c>
+      <c r="B233" t="s">
         <v>386</v>
-      </c>
-      <c r="B233" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B234" t="s">
         <v>388</v>
@@ -8050,44 +8053,44 @@
         <v>391</v>
       </c>
       <c r="B237" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
+        <v>392</v>
+      </c>
+      <c r="B238" t="s">
         <v>393</v>
-      </c>
-      <c r="B238" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
+        <v>394</v>
+      </c>
+      <c r="B239" t="s">
         <v>395</v>
-      </c>
-      <c r="B239" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
+        <v>396</v>
+      </c>
+      <c r="B240" t="s">
         <v>397</v>
-      </c>
-      <c r="B240" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
+        <v>398</v>
+      </c>
+      <c r="B241" t="s">
         <v>399</v>
-      </c>
-      <c r="B241" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B242" t="s">
         <v>401</v>
@@ -8098,12 +8101,12 @@
         <v>402</v>
       </c>
       <c r="B243" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B244" t="s">
         <v>404</v>
@@ -8114,28 +8117,28 @@
         <v>405</v>
       </c>
       <c r="B245" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
+        <v>406</v>
+      </c>
+      <c r="B246" t="s">
         <v>407</v>
-      </c>
-      <c r="B246" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
+        <v>408</v>
+      </c>
+      <c r="B247" t="s">
         <v>409</v>
-      </c>
-      <c r="B247" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B248" t="s">
         <v>411</v>
@@ -8146,20 +8149,20 @@
         <v>412</v>
       </c>
       <c r="B249" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
+        <v>413</v>
+      </c>
+      <c r="B250" t="s">
         <v>414</v>
-      </c>
-      <c r="B250" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B251" t="s">
         <v>416</v>
@@ -8170,12 +8173,12 @@
         <v>417</v>
       </c>
       <c r="B252" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B253" t="s">
         <v>419</v>
@@ -8194,20 +8197,20 @@
         <v>421</v>
       </c>
       <c r="B255" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
+        <v>422</v>
+      </c>
+      <c r="B256" t="s">
         <v>423</v>
-      </c>
-      <c r="B256" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B257" t="s">
         <v>425</v>
@@ -8226,84 +8229,84 @@
         <v>427</v>
       </c>
       <c r="B259" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
+        <v>428</v>
+      </c>
+      <c r="B260" t="s">
         <v>429</v>
-      </c>
-      <c r="B260" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
+        <v>430</v>
+      </c>
+      <c r="B261" t="s">
         <v>431</v>
-      </c>
-      <c r="B261" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
+        <v>432</v>
+      </c>
+      <c r="B262" t="s">
         <v>433</v>
-      </c>
-      <c r="B262" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" t="s">
+        <v>434</v>
+      </c>
+      <c r="B263" t="s">
         <v>435</v>
-      </c>
-      <c r="B263" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
+        <v>436</v>
+      </c>
+      <c r="B264" t="s">
         <v>437</v>
-      </c>
-      <c r="B264" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
+        <v>438</v>
+      </c>
+      <c r="B265" t="s">
         <v>439</v>
-      </c>
-      <c r="B265" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
+        <v>440</v>
+      </c>
+      <c r="B266" t="s">
         <v>441</v>
-      </c>
-      <c r="B266" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
+        <v>442</v>
+      </c>
+      <c r="B267" t="s">
         <v>443</v>
-      </c>
-      <c r="B267" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
+        <v>444</v>
+      </c>
+      <c r="B268" t="s">
         <v>445</v>
-      </c>
-      <c r="B268" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B269" t="s">
         <v>447</v>
@@ -8330,12 +8333,12 @@
         <v>450</v>
       </c>
       <c r="B272" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B273" t="s">
         <v>452</v>
@@ -8346,12 +8349,12 @@
         <v>453</v>
       </c>
       <c r="B274" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B275" t="s">
         <v>455</v>
@@ -8370,12 +8373,12 @@
         <v>457</v>
       </c>
       <c r="B277" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B278" t="s">
         <v>459</v>
@@ -8386,28 +8389,28 @@
         <v>460</v>
       </c>
       <c r="B279" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
+        <v>461</v>
+      </c>
+      <c r="B280" t="s">
         <v>462</v>
-      </c>
-      <c r="B280" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
+        <v>463</v>
+      </c>
+      <c r="B281" t="s">
         <v>464</v>
-      </c>
-      <c r="B281" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B282" t="s">
         <v>466</v>
@@ -8434,12 +8437,12 @@
         <v>469</v>
       </c>
       <c r="B285" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B286" t="s">
         <v>471</v>
@@ -8450,28 +8453,28 @@
         <v>472</v>
       </c>
       <c r="B287" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
+        <v>473</v>
+      </c>
+      <c r="B288" t="s">
         <v>474</v>
-      </c>
-      <c r="B288" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
+        <v>475</v>
+      </c>
+      <c r="B289" t="s">
         <v>476</v>
-      </c>
-      <c r="B289" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B290" t="s">
         <v>478</v>
@@ -8482,36 +8485,36 @@
         <v>479</v>
       </c>
       <c r="B291" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
+        <v>480</v>
+      </c>
+      <c r="B292" t="s">
         <v>481</v>
-      </c>
-      <c r="B292" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
+        <v>482</v>
+      </c>
+      <c r="B293" t="s">
         <v>483</v>
-      </c>
-      <c r="B293" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
+        <v>484</v>
+      </c>
+      <c r="B294" t="s">
         <v>485</v>
-      </c>
-      <c r="B294" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B295" t="s">
         <v>487</v>
@@ -8530,28 +8533,28 @@
         <v>489</v>
       </c>
       <c r="B297" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
+        <v>490</v>
+      </c>
+      <c r="B298" t="s">
         <v>491</v>
-      </c>
-      <c r="B298" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
+        <v>492</v>
+      </c>
+      <c r="B299" t="s">
         <v>493</v>
-      </c>
-      <c r="B299" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B300" t="s">
         <v>495</v>
@@ -8586,44 +8589,44 @@
         <v>499</v>
       </c>
       <c r="B304" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
+        <v>500</v>
+      </c>
+      <c r="B305" t="s">
         <v>501</v>
-      </c>
-      <c r="B305" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
+        <v>502</v>
+      </c>
+      <c r="B306" t="s">
         <v>503</v>
-      </c>
-      <c r="B306" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" t="s">
+        <v>504</v>
+      </c>
+      <c r="B307" t="s">
         <v>505</v>
-      </c>
-      <c r="B307" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
+        <v>506</v>
+      </c>
+      <c r="B308" t="s">
         <v>507</v>
-      </c>
-      <c r="B308" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B309" t="s">
         <v>509</v>
@@ -8642,20 +8645,20 @@
         <v>511</v>
       </c>
       <c r="B311" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
+        <v>512</v>
+      </c>
+      <c r="B312" t="s">
         <v>513</v>
-      </c>
-      <c r="B312" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B313" t="s">
         <v>515</v>
@@ -8674,23 +8677,23 @@
         <v>517</v>
       </c>
       <c r="B315" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
+        <v>518</v>
+      </c>
+      <c r="B316" t="s">
         <v>519</v>
-      </c>
-      <c r="B316" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
+        <v>520</v>
+      </c>
+      <c r="B317" t="s">
         <v>521</v>
-      </c>
-      <c r="B317" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="318" spans="1:2">
@@ -8698,12 +8701,12 @@
         <v>522</v>
       </c>
       <c r="B318" t="s">
-        <v>523</v>
+        <v>176</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B319" t="s">
         <v>524</v>
@@ -8714,12 +8717,12 @@
         <v>525</v>
       </c>
       <c r="B320" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B321" t="s">
         <v>527</v>
@@ -8730,20 +8733,20 @@
         <v>528</v>
       </c>
       <c r="B322" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
+        <v>529</v>
+      </c>
+      <c r="B323" t="s">
         <v>530</v>
-      </c>
-      <c r="B323" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B324" t="s">
         <v>532</v>
@@ -8754,12 +8757,12 @@
         <v>533</v>
       </c>
       <c r="B325" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B326" t="s">
         <v>535</v>
@@ -8770,28 +8773,28 @@
         <v>536</v>
       </c>
       <c r="B327" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
+        <v>537</v>
+      </c>
+      <c r="B328" t="s">
         <v>538</v>
-      </c>
-      <c r="B328" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
+        <v>539</v>
+      </c>
+      <c r="B329" t="s">
         <v>540</v>
-      </c>
-      <c r="B329" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B330" t="s">
         <v>542</v>
@@ -8802,52 +8805,52 @@
         <v>543</v>
       </c>
       <c r="B331" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
+        <v>544</v>
+      </c>
+      <c r="B332" t="s">
         <v>545</v>
-      </c>
-      <c r="B332" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
+        <v>546</v>
+      </c>
+      <c r="B333" t="s">
         <v>547</v>
-      </c>
-      <c r="B333" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
+        <v>548</v>
+      </c>
+      <c r="B334" t="s">
         <v>549</v>
-      </c>
-      <c r="B334" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
+        <v>550</v>
+      </c>
+      <c r="B335" t="s">
         <v>551</v>
-      </c>
-      <c r="B335" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
+        <v>552</v>
+      </c>
+      <c r="B336" t="s">
         <v>553</v>
-      </c>
-      <c r="B336" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B337" t="s">
         <v>555</v>
@@ -8866,12 +8869,12 @@
         <v>557</v>
       </c>
       <c r="B339" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B340" t="s">
         <v>559</v>
@@ -8882,52 +8885,52 @@
         <v>560</v>
       </c>
       <c r="B341" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
+        <v>561</v>
+      </c>
+      <c r="B342" t="s">
         <v>562</v>
-      </c>
-      <c r="B342" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
+        <v>563</v>
+      </c>
+      <c r="B343" t="s">
         <v>564</v>
-      </c>
-      <c r="B343" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
+        <v>565</v>
+      </c>
+      <c r="B344" t="s">
         <v>566</v>
-      </c>
-      <c r="B344" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
+        <v>567</v>
+      </c>
+      <c r="B345" t="s">
         <v>568</v>
-      </c>
-      <c r="B345" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
+        <v>569</v>
+      </c>
+      <c r="B346" t="s">
         <v>570</v>
-      </c>
-      <c r="B346" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B347" t="s">
         <v>572</v>
@@ -8938,100 +8941,100 @@
         <v>573</v>
       </c>
       <c r="B348" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
+        <v>574</v>
+      </c>
+      <c r="B349" t="s">
         <v>575</v>
-      </c>
-      <c r="B349" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
+        <v>576</v>
+      </c>
+      <c r="B350" t="s">
         <v>577</v>
-      </c>
-      <c r="B350" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
+        <v>578</v>
+      </c>
+      <c r="B351" t="s">
         <v>579</v>
-      </c>
-      <c r="B351" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
+        <v>580</v>
+      </c>
+      <c r="B352" t="s">
         <v>581</v>
-      </c>
-      <c r="B352" t="s">
-        <v>582</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
+        <v>582</v>
+      </c>
+      <c r="B353" t="s">
         <v>583</v>
-      </c>
-      <c r="B353" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
+        <v>584</v>
+      </c>
+      <c r="B354" t="s">
         <v>585</v>
-      </c>
-      <c r="B354" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
+        <v>586</v>
+      </c>
+      <c r="B355" t="s">
         <v>587</v>
-      </c>
-      <c r="B355" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
+        <v>588</v>
+      </c>
+      <c r="B356" t="s">
         <v>589</v>
-      </c>
-      <c r="B356" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
+        <v>590</v>
+      </c>
+      <c r="B357" t="s">
         <v>591</v>
-      </c>
-      <c r="B357" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
+        <v>592</v>
+      </c>
+      <c r="B358" t="s">
         <v>593</v>
-      </c>
-      <c r="B358" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
+        <v>594</v>
+      </c>
+      <c r="B359" t="s">
         <v>595</v>
-      </c>
-      <c r="B359" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B360" t="s">
         <v>597</v>
@@ -9042,28 +9045,28 @@
         <v>598</v>
       </c>
       <c r="B361" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
+        <v>599</v>
+      </c>
+      <c r="B362" t="s">
         <v>600</v>
-      </c>
-      <c r="B362" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
+        <v>601</v>
+      </c>
+      <c r="B363" t="s">
         <v>602</v>
-      </c>
-      <c r="B363" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B364" t="s">
         <v>604</v>
@@ -9074,28 +9077,28 @@
         <v>605</v>
       </c>
       <c r="B365" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
+        <v>606</v>
+      </c>
+      <c r="B366" t="s">
         <v>607</v>
-      </c>
-      <c r="B366" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
+        <v>608</v>
+      </c>
+      <c r="B367" t="s">
         <v>609</v>
-      </c>
-      <c r="B367" t="s">
-        <v>610</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B368" t="s">
         <v>611</v>
@@ -9114,60 +9117,60 @@
         <v>613</v>
       </c>
       <c r="B370" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
+        <v>614</v>
+      </c>
+      <c r="B371" t="s">
         <v>615</v>
-      </c>
-      <c r="B371" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
+        <v>616</v>
+      </c>
+      <c r="B372" t="s">
         <v>617</v>
-      </c>
-      <c r="B372" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
+        <v>618</v>
+      </c>
+      <c r="B373" t="s">
         <v>619</v>
-      </c>
-      <c r="B373" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
+        <v>620</v>
+      </c>
+      <c r="B374" t="s">
         <v>621</v>
-      </c>
-      <c r="B374" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" t="s">
+        <v>622</v>
+      </c>
+      <c r="B375" t="s">
         <v>623</v>
-      </c>
-      <c r="B375" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="376" spans="1:2">
       <c r="A376" t="s">
+        <v>624</v>
+      </c>
+      <c r="B376" t="s">
         <v>625</v>
-      </c>
-      <c r="B376" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B377" t="s">
         <v>627</v>
@@ -9178,12 +9181,12 @@
         <v>628</v>
       </c>
       <c r="B378" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="379" spans="1:2">
       <c r="A379" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B379" t="s">
         <v>630</v>
@@ -9194,52 +9197,52 @@
         <v>631</v>
       </c>
       <c r="B380" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
+        <v>632</v>
+      </c>
+      <c r="B381" t="s">
         <v>633</v>
-      </c>
-      <c r="B381" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
+        <v>634</v>
+      </c>
+      <c r="B382" t="s">
         <v>635</v>
-      </c>
-      <c r="B382" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
+        <v>636</v>
+      </c>
+      <c r="B383" t="s">
         <v>637</v>
-      </c>
-      <c r="B383" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" t="s">
+        <v>638</v>
+      </c>
+      <c r="B384" t="s">
         <v>639</v>
-      </c>
-      <c r="B384" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
+        <v>640</v>
+      </c>
+      <c r="B385" t="s">
         <v>641</v>
-      </c>
-      <c r="B385" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B386" t="s">
         <v>643</v>
@@ -9250,36 +9253,36 @@
         <v>644</v>
       </c>
       <c r="B387" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
+        <v>645</v>
+      </c>
+      <c r="B388" t="s">
         <v>646</v>
-      </c>
-      <c r="B388" t="s">
-        <v>647</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
+        <v>647</v>
+      </c>
+      <c r="B389" t="s">
         <v>648</v>
-      </c>
-      <c r="B389" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
+        <v>649</v>
+      </c>
+      <c r="B390" t="s">
         <v>650</v>
-      </c>
-      <c r="B390" t="s">
-        <v>651</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B391" t="s">
         <v>652</v>
@@ -9290,60 +9293,60 @@
         <v>653</v>
       </c>
       <c r="B392" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" t="s">
+        <v>654</v>
+      </c>
+      <c r="B393" t="s">
         <v>655</v>
-      </c>
-      <c r="B393" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
+        <v>656</v>
+      </c>
+      <c r="B394" t="s">
         <v>657</v>
-      </c>
-      <c r="B394" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
+        <v>658</v>
+      </c>
+      <c r="B395" t="s">
         <v>659</v>
-      </c>
-      <c r="B395" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
+        <v>660</v>
+      </c>
+      <c r="B396" t="s">
         <v>661</v>
-      </c>
-      <c r="B396" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
+        <v>662</v>
+      </c>
+      <c r="B397" t="s">
         <v>663</v>
-      </c>
-      <c r="B397" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
+        <v>664</v>
+      </c>
+      <c r="B398" t="s">
         <v>665</v>
-      </c>
-      <c r="B398" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B399" t="s">
         <v>667</v>
@@ -9354,20 +9357,20 @@
         <v>668</v>
       </c>
       <c r="B400" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
+        <v>669</v>
+      </c>
+      <c r="B401" t="s">
         <v>670</v>
-      </c>
-      <c r="B401" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B402" t="s">
         <v>672</v>
@@ -9402,12 +9405,12 @@
         <v>676</v>
       </c>
       <c r="B406" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B407" t="s">
         <v>678</v>
@@ -9426,116 +9429,116 @@
         <v>680</v>
       </c>
       <c r="B409" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
+        <v>681</v>
+      </c>
+      <c r="B410" t="s">
         <v>682</v>
-      </c>
-      <c r="B410" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
+        <v>683</v>
+      </c>
+      <c r="B411" t="s">
         <v>684</v>
-      </c>
-      <c r="B411" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
+        <v>685</v>
+      </c>
+      <c r="B412" t="s">
         <v>686</v>
-      </c>
-      <c r="B412" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="413" spans="1:2">
       <c r="A413" t="s">
+        <v>687</v>
+      </c>
+      <c r="B413" t="s">
         <v>688</v>
-      </c>
-      <c r="B413" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
+        <v>689</v>
+      </c>
+      <c r="B414" t="s">
         <v>690</v>
-      </c>
-      <c r="B414" t="s">
-        <v>691</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
+        <v>691</v>
+      </c>
+      <c r="B415" t="s">
         <v>692</v>
-      </c>
-      <c r="B415" t="s">
-        <v>693</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
+        <v>693</v>
+      </c>
+      <c r="B416" t="s">
         <v>694</v>
-      </c>
-      <c r="B416" t="s">
-        <v>695</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" t="s">
+        <v>695</v>
+      </c>
+      <c r="B417" t="s">
         <v>696</v>
-      </c>
-      <c r="B417" t="s">
-        <v>697</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
+        <v>697</v>
+      </c>
+      <c r="B418" t="s">
         <v>698</v>
-      </c>
-      <c r="B418" t="s">
-        <v>699</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
+        <v>699</v>
+      </c>
+      <c r="B419" t="s">
         <v>700</v>
-      </c>
-      <c r="B419" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
+        <v>701</v>
+      </c>
+      <c r="B420" t="s">
         <v>702</v>
-      </c>
-      <c r="B420" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
+        <v>703</v>
+      </c>
+      <c r="B421" t="s">
         <v>704</v>
-      </c>
-      <c r="B421" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" t="s">
+        <v>705</v>
+      </c>
+      <c r="B422" t="s">
         <v>706</v>
-      </c>
-      <c r="B422" t="s">
-        <v>707</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B423" t="s">
         <v>708</v>
@@ -9546,28 +9549,28 @@
         <v>709</v>
       </c>
       <c r="B424" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="425" spans="1:2">
       <c r="A425" t="s">
+        <v>710</v>
+      </c>
+      <c r="B425" t="s">
         <v>711</v>
-      </c>
-      <c r="B425" t="s">
-        <v>712</v>
       </c>
     </row>
     <row r="426" spans="1:2">
       <c r="A426" t="s">
+        <v>712</v>
+      </c>
+      <c r="B426" t="s">
         <v>713</v>
-      </c>
-      <c r="B426" t="s">
-        <v>714</v>
       </c>
     </row>
     <row r="427" spans="1:2">
       <c r="A427" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B427" t="s">
         <v>715</v>
@@ -9578,36 +9581,36 @@
         <v>716</v>
       </c>
       <c r="B428" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="429" spans="1:2">
       <c r="A429" t="s">
+        <v>717</v>
+      </c>
+      <c r="B429" t="s">
         <v>718</v>
-      </c>
-      <c r="B429" t="s">
-        <v>719</v>
       </c>
     </row>
     <row r="430" spans="1:2">
       <c r="A430" t="s">
+        <v>719</v>
+      </c>
+      <c r="B430" t="s">
         <v>720</v>
-      </c>
-      <c r="B430" t="s">
-        <v>721</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
+        <v>721</v>
+      </c>
+      <c r="B431" t="s">
         <v>722</v>
-      </c>
-      <c r="B431" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B432" t="s">
         <v>724</v>
@@ -9618,20 +9621,20 @@
         <v>725</v>
       </c>
       <c r="B433" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
+        <v>726</v>
+      </c>
+      <c r="B434" t="s">
         <v>727</v>
-      </c>
-      <c r="B434" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B435" t="s">
         <v>729</v>
@@ -9642,12 +9645,12 @@
         <v>730</v>
       </c>
       <c r="B436" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B437" t="s">
         <v>732</v>
@@ -9658,60 +9661,60 @@
         <v>733</v>
       </c>
       <c r="B438" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
+        <v>734</v>
+      </c>
+      <c r="B439" t="s">
         <v>735</v>
-      </c>
-      <c r="B439" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
+        <v>736</v>
+      </c>
+      <c r="B440" t="s">
         <v>737</v>
-      </c>
-      <c r="B440" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" t="s">
+        <v>738</v>
+      </c>
+      <c r="B441" t="s">
         <v>739</v>
-      </c>
-      <c r="B441" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
+        <v>740</v>
+      </c>
+      <c r="B442" t="s">
         <v>741</v>
-      </c>
-      <c r="B442" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
+        <v>742</v>
+      </c>
+      <c r="B443" t="s">
         <v>743</v>
-      </c>
-      <c r="B443" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" t="s">
+        <v>744</v>
+      </c>
+      <c r="B444" t="s">
         <v>745</v>
-      </c>
-      <c r="B444" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B445" t="s">
         <v>747</v>
@@ -9722,12 +9725,12 @@
         <v>748</v>
       </c>
       <c r="B446" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B447" t="s">
         <v>750</v>
@@ -9738,12 +9741,12 @@
         <v>751</v>
       </c>
       <c r="B448" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B449" t="s">
         <v>753</v>
@@ -9754,12 +9757,12 @@
         <v>754</v>
       </c>
       <c r="B450" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B451" t="s">
         <v>756</v>
@@ -9770,20 +9773,20 @@
         <v>757</v>
       </c>
       <c r="B452" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" t="s">
+        <v>758</v>
+      </c>
+      <c r="B453" t="s">
         <v>759</v>
-      </c>
-      <c r="B453" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B454" t="s">
         <v>761</v>
@@ -9794,76 +9797,76 @@
         <v>762</v>
       </c>
       <c r="B455" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="456" spans="1:2">
       <c r="A456" t="s">
+        <v>763</v>
+      </c>
+      <c r="B456" t="s">
         <v>764</v>
-      </c>
-      <c r="B456" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
+        <v>765</v>
+      </c>
+      <c r="B457" t="s">
         <v>766</v>
-      </c>
-      <c r="B457" t="s">
-        <v>767</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
+        <v>767</v>
+      </c>
+      <c r="B458" t="s">
         <v>768</v>
-      </c>
-      <c r="B458" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
+        <v>769</v>
+      </c>
+      <c r="B459" t="s">
         <v>770</v>
-      </c>
-      <c r="B459" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="460" spans="1:2">
       <c r="A460" t="s">
+        <v>771</v>
+      </c>
+      <c r="B460" t="s">
         <v>772</v>
-      </c>
-      <c r="B460" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" t="s">
+        <v>773</v>
+      </c>
+      <c r="B461" t="s">
         <v>774</v>
-      </c>
-      <c r="B461" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" t="s">
+        <v>775</v>
+      </c>
+      <c r="B462" t="s">
         <v>776</v>
-      </c>
-      <c r="B462" t="s">
-        <v>777</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
+        <v>777</v>
+      </c>
+      <c r="B463" t="s">
         <v>778</v>
-      </c>
-      <c r="B463" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B464" t="s">
         <v>780</v>
@@ -9882,7 +9885,7 @@
         <v>782</v>
       </c>
       <c r="B466" t="s">
-        <v>523</v>
+        <v>782</v>
       </c>
     </row>
     <row r="467" spans="1:2">
@@ -9890,7 +9893,7 @@
         <v>783</v>
       </c>
       <c r="B467" t="s">
-        <v>783</v>
+        <v>524</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -9898,15 +9901,15 @@
         <v>784</v>
       </c>
       <c r="B468" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
+        <v>785</v>
+      </c>
+      <c r="B469" t="s">
         <v>786</v>
-      </c>
-      <c r="B469" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="470" spans="1:2">
@@ -9914,20 +9917,20 @@
         <v>787</v>
       </c>
       <c r="B470" t="s">
-        <v>788</v>
+        <v>139</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
+        <v>788</v>
+      </c>
+      <c r="B471" t="s">
         <v>789</v>
-      </c>
-      <c r="B471" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B472" t="s">
         <v>791</v>
@@ -9938,7 +9941,7 @@
         <v>792</v>
       </c>
       <c r="B473" t="s">
-        <v>523</v>
+        <v>792</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -9946,7 +9949,7 @@
         <v>793</v>
       </c>
       <c r="B474" t="s">
-        <v>793</v>
+        <v>524</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -9970,28 +9973,28 @@
         <v>796</v>
       </c>
       <c r="B477" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
+        <v>797</v>
+      </c>
+      <c r="B478" t="s">
         <v>798</v>
-      </c>
-      <c r="B478" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
+        <v>799</v>
+      </c>
+      <c r="B479" t="s">
         <v>800</v>
-      </c>
-      <c r="B479" t="s">
-        <v>801</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B480" t="s">
         <v>802</v>
@@ -10002,12 +10005,12 @@
         <v>803</v>
       </c>
       <c r="B481" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B482" t="s">
         <v>805</v>
@@ -10018,20 +10021,20 @@
         <v>806</v>
       </c>
       <c r="B483" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
+        <v>807</v>
+      </c>
+      <c r="B484" t="s">
         <v>808</v>
-      </c>
-      <c r="B484" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B485" t="s">
         <v>810</v>
@@ -10082,164 +10085,164 @@
         <v>816</v>
       </c>
       <c r="B491" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
+        <v>817</v>
+      </c>
+      <c r="B492" t="s">
         <v>818</v>
-      </c>
-      <c r="B492" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
+        <v>819</v>
+      </c>
+      <c r="B493" t="s">
         <v>820</v>
-      </c>
-      <c r="B493" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
+        <v>821</v>
+      </c>
+      <c r="B494" t="s">
         <v>822</v>
-      </c>
-      <c r="B494" t="s">
-        <v>823</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" t="s">
+        <v>823</v>
+      </c>
+      <c r="B495" t="s">
         <v>824</v>
-      </c>
-      <c r="B495" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="496" spans="1:2">
       <c r="A496" t="s">
+        <v>825</v>
+      </c>
+      <c r="B496" t="s">
         <v>826</v>
-      </c>
-      <c r="B496" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="497" spans="1:2">
       <c r="A497" t="s">
+        <v>827</v>
+      </c>
+      <c r="B497" t="s">
         <v>828</v>
-      </c>
-      <c r="B497" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="498" spans="1:2">
       <c r="A498" t="s">
+        <v>829</v>
+      </c>
+      <c r="B498" t="s">
         <v>830</v>
-      </c>
-      <c r="B498" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="499" spans="1:2">
       <c r="A499" t="s">
+        <v>831</v>
+      </c>
+      <c r="B499" t="s">
         <v>832</v>
-      </c>
-      <c r="B499" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="500" spans="1:2">
       <c r="A500" t="s">
+        <v>833</v>
+      </c>
+      <c r="B500" t="s">
         <v>834</v>
-      </c>
-      <c r="B500" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="501" spans="1:2">
       <c r="A501" t="s">
+        <v>835</v>
+      </c>
+      <c r="B501" t="s">
         <v>836</v>
-      </c>
-      <c r="B501" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="502" spans="1:2">
       <c r="A502" t="s">
+        <v>837</v>
+      </c>
+      <c r="B502" t="s">
         <v>838</v>
-      </c>
-      <c r="B502" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="503" spans="1:2">
       <c r="A503" t="s">
+        <v>839</v>
+      </c>
+      <c r="B503" t="s">
         <v>840</v>
-      </c>
-      <c r="B503" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="504" spans="1:2">
       <c r="A504" t="s">
+        <v>841</v>
+      </c>
+      <c r="B504" t="s">
         <v>842</v>
-      </c>
-      <c r="B504" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="505" spans="1:2">
       <c r="A505" t="s">
+        <v>843</v>
+      </c>
+      <c r="B505" t="s">
         <v>844</v>
-      </c>
-      <c r="B505" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="506" spans="1:2">
       <c r="A506" t="s">
+        <v>845</v>
+      </c>
+      <c r="B506" t="s">
         <v>846</v>
-      </c>
-      <c r="B506" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="507" spans="1:2">
       <c r="A507" t="s">
+        <v>847</v>
+      </c>
+      <c r="B507" t="s">
         <v>848</v>
-      </c>
-      <c r="B507" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="508" spans="1:2">
       <c r="A508" t="s">
+        <v>849</v>
+      </c>
+      <c r="B508" t="s">
         <v>850</v>
-      </c>
-      <c r="B508" t="s">
-        <v>851</v>
       </c>
     </row>
     <row r="509" spans="1:2">
       <c r="A509" t="s">
+        <v>851</v>
+      </c>
+      <c r="B509" t="s">
         <v>852</v>
-      </c>
-      <c r="B509" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" t="s">
+        <v>853</v>
+      </c>
+      <c r="B510" t="s">
         <v>854</v>
-      </c>
-      <c r="B510" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="511" spans="1:2">
       <c r="A511" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B511" t="s">
         <v>856</v>
@@ -10250,12 +10253,12 @@
         <v>857</v>
       </c>
       <c r="B512" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B513" t="s">
         <v>859</v>
@@ -10282,28 +10285,28 @@
         <v>862</v>
       </c>
       <c r="B516" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
+        <v>863</v>
+      </c>
+      <c r="B517" t="s">
         <v>864</v>
-      </c>
-      <c r="B517" t="s">
-        <v>865</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
+        <v>865</v>
+      </c>
+      <c r="B518" t="s">
         <v>866</v>
-      </c>
-      <c r="B518" t="s">
-        <v>867</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B519" t="s">
         <v>868</v>
@@ -10330,28 +10333,28 @@
         <v>871</v>
       </c>
       <c r="B522" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
+        <v>872</v>
+      </c>
+      <c r="B523" t="s">
         <v>873</v>
-      </c>
-      <c r="B523" t="s">
-        <v>874</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
+        <v>874</v>
+      </c>
+      <c r="B524" t="s">
         <v>875</v>
-      </c>
-      <c r="B524" t="s">
-        <v>876</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B525" t="s">
         <v>877</v>
@@ -10362,52 +10365,52 @@
         <v>878</v>
       </c>
       <c r="B526" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="527" spans="1:2">
       <c r="A527" t="s">
+        <v>879</v>
+      </c>
+      <c r="B527" t="s">
         <v>880</v>
-      </c>
-      <c r="B527" t="s">
-        <v>881</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" t="s">
+        <v>881</v>
+      </c>
+      <c r="B528" t="s">
         <v>882</v>
-      </c>
-      <c r="B528" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
+        <v>883</v>
+      </c>
+      <c r="B529" t="s">
         <v>884</v>
-      </c>
-      <c r="B529" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
+        <v>885</v>
+      </c>
+      <c r="B530" t="s">
         <v>886</v>
-      </c>
-      <c r="B530" t="s">
-        <v>887</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
+        <v>887</v>
+      </c>
+      <c r="B531" t="s">
         <v>888</v>
-      </c>
-      <c r="B531" t="s">
-        <v>889</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B532" t="s">
         <v>890</v>
@@ -10418,20 +10421,20 @@
         <v>891</v>
       </c>
       <c r="B533" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
+        <v>892</v>
+      </c>
+      <c r="B534" t="s">
         <v>893</v>
-      </c>
-      <c r="B534" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B535" t="s">
         <v>895</v>
@@ -10450,12 +10453,12 @@
         <v>897</v>
       </c>
       <c r="B537" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B538" t="s">
         <v>899</v>
@@ -10498,28 +10501,28 @@
         <v>904</v>
       </c>
       <c r="B543" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
+        <v>905</v>
+      </c>
+      <c r="B544" t="s">
         <v>906</v>
-      </c>
-      <c r="B544" t="s">
-        <v>907</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
+        <v>907</v>
+      </c>
+      <c r="B545" t="s">
         <v>908</v>
-      </c>
-      <c r="B545" t="s">
-        <v>909</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B546" t="s">
         <v>910</v>
@@ -10538,12 +10541,12 @@
         <v>912</v>
       </c>
       <c r="B548" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B549" t="s">
         <v>914</v>
@@ -10554,12 +10557,12 @@
         <v>915</v>
       </c>
       <c r="B550" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B551" t="s">
         <v>917</v>
@@ -10586,12 +10589,12 @@
         <v>920</v>
       </c>
       <c r="B554" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B555" t="s">
         <v>922</v>
@@ -10602,68 +10605,68 @@
         <v>923</v>
       </c>
       <c r="B556" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
+        <v>924</v>
+      </c>
+      <c r="B557" t="s">
         <v>925</v>
-      </c>
-      <c r="B557" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
+        <v>926</v>
+      </c>
+      <c r="B558" t="s">
         <v>927</v>
-      </c>
-      <c r="B558" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
+        <v>928</v>
+      </c>
+      <c r="B559" t="s">
         <v>929</v>
-      </c>
-      <c r="B559" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
+        <v>930</v>
+      </c>
+      <c r="B560" t="s">
         <v>931</v>
-      </c>
-      <c r="B560" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
+        <v>932</v>
+      </c>
+      <c r="B561" t="s">
         <v>933</v>
-      </c>
-      <c r="B561" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
+        <v>934</v>
+      </c>
+      <c r="B562" t="s">
         <v>935</v>
-      </c>
-      <c r="B562" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
+        <v>936</v>
+      </c>
+      <c r="B563" t="s">
         <v>937</v>
-      </c>
-      <c r="B563" t="s">
-        <v>938</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B564" t="s">
         <v>939</v>
@@ -10682,20 +10685,20 @@
         <v>941</v>
       </c>
       <c r="B566" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
+        <v>942</v>
+      </c>
+      <c r="B567" t="s">
         <v>943</v>
-      </c>
-      <c r="B567" t="s">
-        <v>944</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B568" t="s">
         <v>945</v>
@@ -10706,20 +10709,20 @@
         <v>946</v>
       </c>
       <c r="B569" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
+        <v>947</v>
+      </c>
+      <c r="B570" t="s">
         <v>948</v>
-      </c>
-      <c r="B570" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B571" t="s">
         <v>950</v>
@@ -10730,28 +10733,28 @@
         <v>951</v>
       </c>
       <c r="B572" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
+        <v>952</v>
+      </c>
+      <c r="B573" t="s">
         <v>953</v>
-      </c>
-      <c r="B573" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
+        <v>954</v>
+      </c>
+      <c r="B574" t="s">
         <v>955</v>
-      </c>
-      <c r="B574" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B575" t="s">
         <v>957</v>
@@ -10762,12 +10765,12 @@
         <v>958</v>
       </c>
       <c r="B576" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B577" t="s">
         <v>960</v>
@@ -10778,12 +10781,12 @@
         <v>961</v>
       </c>
       <c r="B578" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B579" t="s">
         <v>963</v>
@@ -10802,20 +10805,20 @@
         <v>965</v>
       </c>
       <c r="B581" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
+        <v>966</v>
+      </c>
+      <c r="B582" t="s">
         <v>967</v>
-      </c>
-      <c r="B582" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B583" t="s">
         <v>969</v>
@@ -10834,12 +10837,12 @@
         <v>971</v>
       </c>
       <c r="B585" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B586" t="s">
         <v>973</v>
@@ -10850,12 +10853,12 @@
         <v>974</v>
       </c>
       <c r="B587" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="B588" t="s">
         <v>976</v>
@@ -10866,20 +10869,20 @@
         <v>977</v>
       </c>
       <c r="B589" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
+        <v>978</v>
+      </c>
+      <c r="B590" t="s">
         <v>979</v>
-      </c>
-      <c r="B590" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B591" t="s">
         <v>981</v>
@@ -10890,52 +10893,52 @@
         <v>982</v>
       </c>
       <c r="B592" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
+        <v>983</v>
+      </c>
+      <c r="B593" t="s">
         <v>984</v>
-      </c>
-      <c r="B593" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
+        <v>985</v>
+      </c>
+      <c r="B594" t="s">
         <v>986</v>
-      </c>
-      <c r="B594" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
+        <v>987</v>
+      </c>
+      <c r="B595" t="s">
         <v>988</v>
-      </c>
-      <c r="B595" t="s">
-        <v>989</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
+        <v>989</v>
+      </c>
+      <c r="B596" t="s">
         <v>990</v>
-      </c>
-      <c r="B596" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
+        <v>991</v>
+      </c>
+      <c r="B597" t="s">
         <v>992</v>
-      </c>
-      <c r="B597" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B598" t="s">
         <v>994</v>
@@ -10946,68 +10949,68 @@
         <v>995</v>
       </c>
       <c r="B599" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
+        <v>996</v>
+      </c>
+      <c r="B600" t="s">
         <v>997</v>
-      </c>
-      <c r="B600" t="s">
-        <v>998</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
+        <v>998</v>
+      </c>
+      <c r="B601" t="s">
         <v>999</v>
-      </c>
-      <c r="B601" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B602" t="s">
         <v>1001</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B603" t="s">
         <v>1003</v>
-      </c>
-      <c r="B603" t="s">
-        <v>1004</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B604" t="s">
         <v>1005</v>
-      </c>
-      <c r="B604" t="s">
-        <v>1006</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B605" t="s">
         <v>1007</v>
-      </c>
-      <c r="B605" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B606" t="s">
         <v>1009</v>
-      </c>
-      <c r="B606" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B607" t="s">
         <v>1011</v>
@@ -11018,20 +11021,20 @@
         <v>1012</v>
       </c>
       <c r="B608" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B609" t="s">
         <v>1014</v>
-      </c>
-      <c r="B609" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B610" t="s">
         <v>1016</v>
@@ -11042,44 +11045,44 @@
         <v>1017</v>
       </c>
       <c r="B611" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B612" t="s">
         <v>1019</v>
-      </c>
-      <c r="B612" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B613" t="s">
         <v>1021</v>
-      </c>
-      <c r="B613" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B614" t="s">
         <v>1023</v>
-      </c>
-      <c r="B614" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B615" t="s">
         <v>1025</v>
-      </c>
-      <c r="B615" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B616" t="s">
         <v>1027</v>
@@ -11106,12 +11109,12 @@
         <v>1030</v>
       </c>
       <c r="B619" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B620" t="s">
         <v>1032</v>
@@ -11122,28 +11125,28 @@
         <v>1033</v>
       </c>
       <c r="B621" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B622" t="s">
         <v>1035</v>
-      </c>
-      <c r="B622" t="s">
-        <v>1036</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B623" t="s">
         <v>1037</v>
-      </c>
-      <c r="B623" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B624" t="s">
         <v>1039</v>
@@ -11154,36 +11157,36 @@
         <v>1040</v>
       </c>
       <c r="B625" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B626" t="s">
         <v>1042</v>
-      </c>
-      <c r="B626" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B627" t="s">
         <v>1044</v>
-      </c>
-      <c r="B627" t="s">
-        <v>1045</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B628" t="s">
         <v>1046</v>
-      </c>
-      <c r="B628" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B629" t="s">
         <v>1048</v>
@@ -11258,12 +11261,12 @@
         <v>1057</v>
       </c>
       <c r="B638" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B639" t="s">
         <v>1059</v>
@@ -11282,12 +11285,12 @@
         <v>1061</v>
       </c>
       <c r="B641" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B642" t="s">
         <v>1063</v>
@@ -11314,12 +11317,12 @@
         <v>1066</v>
       </c>
       <c r="B645" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B646" t="s">
         <v>1068</v>
@@ -11354,36 +11357,36 @@
         <v>1072</v>
       </c>
       <c r="B650" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B651" t="s">
         <v>1074</v>
-      </c>
-      <c r="B651" t="s">
-        <v>1075</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B652" t="s">
         <v>1076</v>
-      </c>
-      <c r="B652" t="s">
-        <v>1077</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B653" t="s">
         <v>1078</v>
-      </c>
-      <c r="B653" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B654" t="s">
         <v>1080</v>
@@ -11402,20 +11405,20 @@
         <v>1082</v>
       </c>
       <c r="B656" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B657" t="s">
         <v>1084</v>
-      </c>
-      <c r="B657" t="s">
-        <v>1085</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B658" t="s">
         <v>1086</v>
@@ -11434,20 +11437,20 @@
         <v>1088</v>
       </c>
       <c r="B660" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B661" t="s">
         <v>1090</v>
-      </c>
-      <c r="B661" t="s">
-        <v>1091</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B662" t="s">
         <v>1092</v>
@@ -11458,12 +11461,12 @@
         <v>1093</v>
       </c>
       <c r="B663" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B664" t="s">
         <v>1095</v>
@@ -11482,36 +11485,36 @@
         <v>1097</v>
       </c>
       <c r="B666" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B667" t="s">
         <v>1099</v>
-      </c>
-      <c r="B667" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B668" t="s">
         <v>1101</v>
-      </c>
-      <c r="B668" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B669" t="s">
         <v>1103</v>
-      </c>
-      <c r="B669" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B670" t="s">
         <v>1105</v>
@@ -11554,20 +11557,20 @@
         <v>1110</v>
       </c>
       <c r="B675" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B676" t="s">
         <v>1112</v>
-      </c>
-      <c r="B676" t="s">
-        <v>1113</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B677" t="s">
         <v>1114</v>
@@ -11578,20 +11581,20 @@
         <v>1115</v>
       </c>
       <c r="B678" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B679" t="s">
         <v>1117</v>
-      </c>
-      <c r="B679" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B680" t="s">
         <v>1119</v>
@@ -11602,12 +11605,12 @@
         <v>1120</v>
       </c>
       <c r="B681" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B682" t="s">
         <v>1122</v>
@@ -11626,28 +11629,28 @@
         <v>1124</v>
       </c>
       <c r="B684" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B685" t="s">
         <v>1126</v>
-      </c>
-      <c r="B685" t="s">
-        <v>1127</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B686" t="s">
         <v>1128</v>
-      </c>
-      <c r="B686" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B687" t="s">
         <v>1130</v>
@@ -11666,84 +11669,84 @@
         <v>1132</v>
       </c>
       <c r="B689" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B690" t="s">
         <v>1134</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1135</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B691" t="s">
         <v>1136</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1137</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B692" t="s">
         <v>1138</v>
-      </c>
-      <c r="B692" t="s">
-        <v>1139</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B693" t="s">
         <v>1140</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B694" t="s">
         <v>1142</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B695" t="s">
         <v>1144</v>
-      </c>
-      <c r="B695" t="s">
-        <v>1145</v>
       </c>
     </row>
     <row r="696" spans="1:2">
       <c r="A696" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B696" t="s">
         <v>1146</v>
-      </c>
-      <c r="B696" t="s">
-        <v>1147</v>
       </c>
     </row>
     <row r="697" spans="1:2">
       <c r="A697" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B697" t="s">
         <v>1148</v>
-      </c>
-      <c r="B697" t="s">
-        <v>1149</v>
       </c>
     </row>
     <row r="698" spans="1:2">
       <c r="A698" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B698" t="s">
         <v>1150</v>
-      </c>
-      <c r="B698" t="s">
-        <v>1151</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B699" t="s">
         <v>1152</v>
@@ -11754,44 +11757,44 @@
         <v>1153</v>
       </c>
       <c r="B700" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B701" t="s">
         <v>1155</v>
-      </c>
-      <c r="B701" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B702" t="s">
         <v>1157</v>
-      </c>
-      <c r="B702" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B703" t="s">
         <v>1159</v>
-      </c>
-      <c r="B703" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B704" t="s">
         <v>1161</v>
-      </c>
-      <c r="B704" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B705" t="s">
         <v>1163</v>
@@ -11802,12 +11805,12 @@
         <v>1164</v>
       </c>
       <c r="B706" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="B707" t="s">
         <v>1166</v>
@@ -11826,12 +11829,12 @@
         <v>1168</v>
       </c>
       <c r="B709" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B710" t="s">
         <v>1170</v>
@@ -11858,12 +11861,12 @@
         <v>1173</v>
       </c>
       <c r="B713" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B714" t="s">
         <v>1175</v>
@@ -11890,12 +11893,12 @@
         <v>1178</v>
       </c>
       <c r="B717" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B718" t="s">
         <v>1180</v>
@@ -11906,60 +11909,60 @@
         <v>1181</v>
       </c>
       <c r="B719" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B720" t="s">
         <v>1183</v>
-      </c>
-      <c r="B720" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B721" t="s">
         <v>1185</v>
-      </c>
-      <c r="B721" t="s">
-        <v>1186</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B722" t="s">
         <v>1187</v>
-      </c>
-      <c r="B722" t="s">
-        <v>1188</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B723" t="s">
         <v>1189</v>
-      </c>
-      <c r="B723" t="s">
-        <v>1190</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B724" t="s">
         <v>1191</v>
-      </c>
-      <c r="B724" t="s">
-        <v>1192</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B725" t="s">
         <v>1193</v>
-      </c>
-      <c r="B725" t="s">
-        <v>1194</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B726" t="s">
         <v>1195</v>
@@ -11970,76 +11973,76 @@
         <v>1196</v>
       </c>
       <c r="B727" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B728" t="s">
         <v>1198</v>
-      </c>
-      <c r="B728" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B729" t="s">
         <v>1200</v>
-      </c>
-      <c r="B729" t="s">
-        <v>1201</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B730" t="s">
         <v>1202</v>
-      </c>
-      <c r="B730" t="s">
-        <v>1203</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B731" t="s">
         <v>1204</v>
-      </c>
-      <c r="B731" t="s">
-        <v>1205</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B732" t="s">
         <v>1206</v>
-      </c>
-      <c r="B732" t="s">
-        <v>1207</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B733" t="s">
         <v>1208</v>
-      </c>
-      <c r="B733" t="s">
-        <v>1209</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B734" t="s">
         <v>1210</v>
-      </c>
-      <c r="B734" t="s">
-        <v>1211</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B735" t="s">
         <v>1212</v>
-      </c>
-      <c r="B735" t="s">
-        <v>1213</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B736" t="s">
         <v>1214</v>
@@ -12050,28 +12053,28 @@
         <v>1215</v>
       </c>
       <c r="B737" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B738" t="s">
         <v>1217</v>
-      </c>
-      <c r="B738" t="s">
-        <v>1218</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B739" t="s">
         <v>1219</v>
-      </c>
-      <c r="B739" t="s">
-        <v>1220</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="B740" t="s">
         <v>1221</v>
@@ -12082,12 +12085,12 @@
         <v>1222</v>
       </c>
       <c r="B741" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B742" t="s">
         <v>1224</v>
@@ -12138,20 +12141,20 @@
         <v>1230</v>
       </c>
       <c r="B748" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B749" t="s">
         <v>1232</v>
-      </c>
-      <c r="B749" t="s">
-        <v>1233</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B750" t="s">
         <v>1234</v>
@@ -12186,60 +12189,60 @@
         <v>1238</v>
       </c>
       <c r="B754" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B755" t="s">
         <v>1240</v>
-      </c>
-      <c r="B755" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B756" t="s">
         <v>1242</v>
-      </c>
-      <c r="B756" t="s">
-        <v>1243</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B757" t="s">
         <v>1244</v>
-      </c>
-      <c r="B757" t="s">
-        <v>1245</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B758" t="s">
         <v>1246</v>
-      </c>
-      <c r="B758" t="s">
-        <v>1247</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B759" t="s">
         <v>1248</v>
-      </c>
-      <c r="B759" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B760" t="s">
         <v>1250</v>
-      </c>
-      <c r="B760" t="s">
-        <v>1251</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B761" t="s">
         <v>1252</v>
@@ -12258,12 +12261,12 @@
         <v>1254</v>
       </c>
       <c r="B763" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B764" t="s">
         <v>1256</v>
@@ -12282,12 +12285,12 @@
         <v>1258</v>
       </c>
       <c r="B766" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B767" t="s">
         <v>1260</v>
@@ -12306,44 +12309,44 @@
         <v>1262</v>
       </c>
       <c r="B769" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B770" t="s">
         <v>1264</v>
-      </c>
-      <c r="B770" t="s">
-        <v>1265</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B771" t="s">
         <v>1266</v>
-      </c>
-      <c r="B771" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B772" t="s">
         <v>1268</v>
-      </c>
-      <c r="B772" t="s">
-        <v>1269</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B773" t="s">
         <v>1270</v>
-      </c>
-      <c r="B773" t="s">
-        <v>1271</v>
       </c>
     </row>
     <row r="774" spans="1:2">
       <c r="A774" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B774" t="s">
         <v>1272</v>
@@ -12354,36 +12357,36 @@
         <v>1273</v>
       </c>
       <c r="B775" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B776" t="s">
         <v>1275</v>
-      </c>
-      <c r="B776" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B777" t="s">
         <v>1277</v>
-      </c>
-      <c r="B777" t="s">
-        <v>1278</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B778" t="s">
         <v>1279</v>
-      </c>
-      <c r="B778" t="s">
-        <v>1280</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B779" t="s">
         <v>1281</v>
@@ -12394,68 +12397,68 @@
         <v>1282</v>
       </c>
       <c r="B780" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B781" t="s">
         <v>1284</v>
-      </c>
-      <c r="B781" t="s">
-        <v>1285</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B782" t="s">
         <v>1286</v>
-      </c>
-      <c r="B782" t="s">
-        <v>1287</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B783" t="s">
         <v>1288</v>
-      </c>
-      <c r="B783" t="s">
-        <v>1289</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B784" t="s">
         <v>1290</v>
-      </c>
-      <c r="B784" t="s">
-        <v>1291</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B785" t="s">
         <v>1292</v>
-      </c>
-      <c r="B785" t="s">
-        <v>1293</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B786" t="s">
         <v>1294</v>
-      </c>
-      <c r="B786" t="s">
-        <v>1295</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B787" t="s">
         <v>1296</v>
-      </c>
-      <c r="B787" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B788" t="s">
         <v>1298</v>
@@ -12482,20 +12485,20 @@
         <v>1301</v>
       </c>
       <c r="B791" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B792" t="s">
         <v>1303</v>
-      </c>
-      <c r="B792" t="s">
-        <v>1304</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B793" t="s">
         <v>1305</v>
@@ -12506,12 +12509,12 @@
         <v>1306</v>
       </c>
       <c r="B794" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B795" t="s">
         <v>1308</v>
@@ -12570,12 +12573,12 @@
         <v>1315</v>
       </c>
       <c r="B802" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B803" t="s">
         <v>1317</v>
@@ -12602,52 +12605,52 @@
         <v>1320</v>
       </c>
       <c r="B806" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B807" t="s">
         <v>1322</v>
-      </c>
-      <c r="B807" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B808" t="s">
         <v>1324</v>
-      </c>
-      <c r="B808" t="s">
-        <v>1325</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B809" t="s">
         <v>1326</v>
-      </c>
-      <c r="B809" t="s">
-        <v>1327</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B810" t="s">
         <v>1328</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1329</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B811" t="s">
         <v>1330</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1331</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B812" t="s">
         <v>1332</v>
@@ -12674,84 +12677,84 @@
         <v>1335</v>
       </c>
       <c r="B815" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B816" t="s">
         <v>1337</v>
-      </c>
-      <c r="B816" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B817" t="s">
         <v>1339</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B818" t="s">
         <v>1341</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B819" t="s">
         <v>1343</v>
-      </c>
-      <c r="B819" t="s">
-        <v>1344</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B820" t="s">
         <v>1345</v>
-      </c>
-      <c r="B820" t="s">
-        <v>1346</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B821" t="s">
         <v>1347</v>
-      </c>
-      <c r="B821" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B822" t="s">
         <v>1349</v>
-      </c>
-      <c r="B822" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B823" t="s">
         <v>1351</v>
-      </c>
-      <c r="B823" t="s">
-        <v>1352</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B824" t="s">
         <v>1353</v>
-      </c>
-      <c r="B824" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
       <c r="B825" t="s">
         <v>1355</v>
@@ -12762,20 +12765,20 @@
         <v>1356</v>
       </c>
       <c r="B826" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B827" t="s">
         <v>1358</v>
-      </c>
-      <c r="B827" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="B828" t="s">
         <v>1360</v>
@@ -12794,12 +12797,12 @@
         <v>1362</v>
       </c>
       <c r="B830" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
       <c r="B831" t="s">
         <v>1364</v>
@@ -12810,12 +12813,12 @@
         <v>1365</v>
       </c>
       <c r="B832" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="B833" t="s">
         <v>1367</v>
@@ -12842,12 +12845,12 @@
         <v>1370</v>
       </c>
       <c r="B836" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B837" t="s">
         <v>1372</v>
@@ -12890,36 +12893,36 @@
         <v>1377</v>
       </c>
       <c r="B842" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B843" t="s">
         <v>1379</v>
-      </c>
-      <c r="B843" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B844" t="s">
         <v>1381</v>
-      </c>
-      <c r="B844" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B845" t="s">
         <v>1383</v>
-      </c>
-      <c r="B845" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
       <c r="B846" t="s">
         <v>1385</v>
@@ -12930,20 +12933,20 @@
         <v>1386</v>
       </c>
       <c r="B847" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B848" t="s">
         <v>1388</v>
-      </c>
-      <c r="B848" t="s">
-        <v>1389</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
       <c r="B849" t="s">
         <v>1390</v>
@@ -12970,108 +12973,108 @@
         <v>1393</v>
       </c>
       <c r="B852" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B853" t="s">
         <v>1395</v>
-      </c>
-      <c r="B853" t="s">
-        <v>1396</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B854" t="s">
         <v>1397</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1398</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B855" t="s">
         <v>1399</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B856" t="s">
         <v>1401</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B857" t="s">
         <v>1403</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B858" t="s">
         <v>1405</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1406</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B859" t="s">
         <v>1407</v>
-      </c>
-      <c r="B859" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B860" t="s">
         <v>1409</v>
-      </c>
-      <c r="B860" t="s">
-        <v>1410</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B861" t="s">
         <v>1411</v>
-      </c>
-      <c r="B861" t="s">
-        <v>1412</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B862" t="s">
         <v>1413</v>
-      </c>
-      <c r="B862" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B863" t="s">
         <v>1415</v>
-      </c>
-      <c r="B863" t="s">
-        <v>1416</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B864" t="s">
         <v>1417</v>
-      </c>
-      <c r="B864" t="s">
-        <v>1418</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B865" t="s">
         <v>1419</v>
@@ -13098,12 +13101,12 @@
         <v>1422</v>
       </c>
       <c r="B868" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B869" t="s">
         <v>1424</v>
@@ -13114,12 +13117,12 @@
         <v>1425</v>
       </c>
       <c r="B870" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B871" t="s">
         <v>1427</v>
@@ -13170,36 +13173,36 @@
         <v>1433</v>
       </c>
       <c r="B877" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B878" t="s">
         <v>1435</v>
-      </c>
-      <c r="B878" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B879" t="s">
         <v>1437</v>
-      </c>
-      <c r="B879" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B880" t="s">
         <v>1439</v>
-      </c>
-      <c r="B880" t="s">
-        <v>1440</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B881" t="s">
         <v>1441</v>
@@ -13210,44 +13213,44 @@
         <v>1442</v>
       </c>
       <c r="B882" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B883" t="s">
         <v>1444</v>
-      </c>
-      <c r="B883" t="s">
-        <v>1445</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B884" t="s">
         <v>1446</v>
-      </c>
-      <c r="B884" t="s">
-        <v>1447</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B885" t="s">
         <v>1448</v>
-      </c>
-      <c r="B885" t="s">
-        <v>1449</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B886" t="s">
         <v>1450</v>
-      </c>
-      <c r="B886" t="s">
-        <v>1451</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B887" t="s">
         <v>1452</v>
@@ -13258,28 +13261,28 @@
         <v>1453</v>
       </c>
       <c r="B888" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B889" t="s">
         <v>1455</v>
-      </c>
-      <c r="B889" t="s">
-        <v>1456</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B890" t="s">
         <v>1457</v>
-      </c>
-      <c r="B890" t="s">
-        <v>1458</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="B891" t="s">
         <v>1459</v>
@@ -13298,44 +13301,44 @@
         <v>1461</v>
       </c>
       <c r="B893" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B894" t="s">
         <v>1463</v>
-      </c>
-      <c r="B894" t="s">
-        <v>1464</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B895" t="s">
         <v>1465</v>
-      </c>
-      <c r="B895" t="s">
-        <v>1466</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B896" t="s">
         <v>1467</v>
-      </c>
-      <c r="B896" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B897" t="s">
         <v>1469</v>
-      </c>
-      <c r="B897" t="s">
-        <v>1470</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B898" t="s">
         <v>1471</v>
@@ -13346,12 +13349,12 @@
         <v>1472</v>
       </c>
       <c r="B899" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B900" t="s">
         <v>1474</v>
@@ -13362,36 +13365,36 @@
         <v>1475</v>
       </c>
       <c r="B901" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B902" t="s">
         <v>1477</v>
-      </c>
-      <c r="B902" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B903" t="s">
         <v>1479</v>
-      </c>
-      <c r="B903" t="s">
-        <v>1480</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B904" t="s">
         <v>1481</v>
-      </c>
-      <c r="B904" t="s">
-        <v>1482</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B905" t="s">
         <v>1483</v>
@@ -13410,44 +13413,44 @@
         <v>1485</v>
       </c>
       <c r="B907" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B908" t="s">
         <v>1487</v>
-      </c>
-      <c r="B908" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B909" t="s">
         <v>1489</v>
-      </c>
-      <c r="B909" t="s">
-        <v>1490</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B910" t="s">
         <v>1491</v>
-      </c>
-      <c r="B910" t="s">
-        <v>1492</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B911" t="s">
         <v>1493</v>
-      </c>
-      <c r="B911" t="s">
-        <v>1494</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="B912" t="s">
         <v>1495</v>
@@ -13498,36 +13501,36 @@
         <v>1501</v>
       </c>
       <c r="B918" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B919" t="s">
         <v>1503</v>
-      </c>
-      <c r="B919" t="s">
-        <v>1504</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B920" t="s">
         <v>1505</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1506</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B921" t="s">
         <v>1507</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B922" t="s">
         <v>1509</v>
@@ -13554,44 +13557,44 @@
         <v>1512</v>
       </c>
       <c r="B925" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B926" t="s">
         <v>1514</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1515</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B927" t="s">
         <v>1516</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1517</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B928" t="s">
         <v>1518</v>
-      </c>
-      <c r="B928" t="s">
-        <v>1519</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
+        <v>1519</v>
+      </c>
+      <c r="B929" t="s">
         <v>1520</v>
-      </c>
-      <c r="B929" t="s">
-        <v>1521</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B930" t="s">
         <v>1522</v>
@@ -13610,36 +13613,36 @@
         <v>1524</v>
       </c>
       <c r="B932" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B933" t="s">
         <v>1526</v>
-      </c>
-      <c r="B933" t="s">
-        <v>1527</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B934" t="s">
         <v>1528</v>
-      </c>
-      <c r="B934" t="s">
-        <v>1529</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B935" t="s">
         <v>1530</v>
-      </c>
-      <c r="B935" t="s">
-        <v>1531</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B936" t="s">
         <v>1532</v>
@@ -13650,20 +13653,20 @@
         <v>1533</v>
       </c>
       <c r="B937" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B938" t="s">
         <v>1535</v>
-      </c>
-      <c r="B938" t="s">
-        <v>1536</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B939" t="s">
         <v>1537</v>
@@ -13674,20 +13677,20 @@
         <v>1538</v>
       </c>
       <c r="B940" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B941" t="s">
         <v>1540</v>
-      </c>
-      <c r="B941" t="s">
-        <v>1541</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
       <c r="B942" t="s">
         <v>1542</v>
@@ -13698,12 +13701,12 @@
         <v>1543</v>
       </c>
       <c r="B943" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="B944" t="s">
         <v>1545</v>
@@ -13714,20 +13717,20 @@
         <v>1546</v>
       </c>
       <c r="B945" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B946" t="s">
         <v>1548</v>
-      </c>
-      <c r="B946" t="s">
-        <v>1549</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
       <c r="B947" t="s">
         <v>1550</v>
@@ -13738,12 +13741,12 @@
         <v>1551</v>
       </c>
       <c r="B948" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B949" t="s">
         <v>1553</v>
@@ -13770,28 +13773,28 @@
         <v>1556</v>
       </c>
       <c r="B952" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B953" t="s">
         <v>1558</v>
-      </c>
-      <c r="B953" t="s">
-        <v>1559</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B954" t="s">
         <v>1560</v>
-      </c>
-      <c r="B954" t="s">
-        <v>1561</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B955" t="s">
         <v>1562</v>
@@ -13834,36 +13837,36 @@
         <v>1567</v>
       </c>
       <c r="B960" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B961" t="s">
         <v>1569</v>
-      </c>
-      <c r="B961" t="s">
-        <v>1570</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B962" t="s">
         <v>1571</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1572</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B963" t="s">
         <v>1573</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1574</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B964" t="s">
         <v>1575</v>
@@ -13890,52 +13893,52 @@
         <v>1578</v>
       </c>
       <c r="B967" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B968" t="s">
         <v>1580</v>
-      </c>
-      <c r="B968" t="s">
-        <v>1581</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B969" t="s">
         <v>1582</v>
-      </c>
-      <c r="B969" t="s">
-        <v>1583</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B970" t="s">
         <v>1584</v>
-      </c>
-      <c r="B970" t="s">
-        <v>1585</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B971" t="s">
         <v>1586</v>
-      </c>
-      <c r="B971" t="s">
-        <v>1587</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B972" t="s">
         <v>1588</v>
-      </c>
-      <c r="B972" t="s">
-        <v>1589</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="B973" t="s">
         <v>1590</v>
@@ -13962,12 +13965,12 @@
         <v>1593</v>
       </c>
       <c r="B976" t="s">
-        <v>1594</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
       <c r="B977" t="s">
         <v>1595</v>
@@ -13986,44 +13989,44 @@
         <v>1597</v>
       </c>
       <c r="B979" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B980" t="s">
         <v>1599</v>
-      </c>
-      <c r="B980" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B981" t="s">
         <v>1601</v>
-      </c>
-      <c r="B981" t="s">
-        <v>1602</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B982" t="s">
         <v>1603</v>
-      </c>
-      <c r="B982" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B983" t="s">
         <v>1605</v>
-      </c>
-      <c r="B983" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B984" t="s">
         <v>1607</v>
@@ -14034,28 +14037,28 @@
         <v>1608</v>
       </c>
       <c r="B985" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B986" t="s">
         <v>1610</v>
-      </c>
-      <c r="B986" t="s">
-        <v>1611</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B987" t="s">
         <v>1612</v>
-      </c>
-      <c r="B987" t="s">
-        <v>1613</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1614</v>
+        <v>1613</v>
       </c>
       <c r="B988" t="s">
         <v>1614</v>
@@ -14066,20 +14069,20 @@
         <v>1615</v>
       </c>
       <c r="B989" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B990" t="s">
         <v>1617</v>
-      </c>
-      <c r="B990" t="s">
-        <v>1618</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="B991" t="s">
         <v>1619</v>
@@ -14114,52 +14117,52 @@
         <v>1623</v>
       </c>
       <c r="B995" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B996" t="s">
         <v>1625</v>
-      </c>
-      <c r="B996" t="s">
-        <v>1626</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B997" t="s">
         <v>1627</v>
-      </c>
-      <c r="B997" t="s">
-        <v>1628</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B998" t="s">
         <v>1629</v>
-      </c>
-      <c r="B998" t="s">
-        <v>1630</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B999" t="s">
         <v>1631</v>
-      </c>
-      <c r="B999" t="s">
-        <v>1632</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B1000" t="s">
         <v>1633</v>
-      </c>
-      <c r="B1000" t="s">
-        <v>1634</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="B1001" t="s">
         <v>1635</v>
@@ -14170,20 +14173,20 @@
         <v>1636</v>
       </c>
       <c r="B1002" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B1003" t="s">
         <v>1638</v>
-      </c>
-      <c r="B1003" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="B1004" t="s">
         <v>1640</v>
@@ -14210,12 +14213,12 @@
         <v>1643</v>
       </c>
       <c r="B1007" t="s">
-        <v>1644</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="B1008" t="s">
         <v>1645</v>
@@ -14226,20 +14229,20 @@
         <v>1646</v>
       </c>
       <c r="B1009" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B1010" t="s">
         <v>1648</v>
-      </c>
-      <c r="B1010" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="B1011" t="s">
         <v>1650</v>
@@ -14258,28 +14261,28 @@
         <v>1652</v>
       </c>
       <c r="B1013" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B1014" t="s">
         <v>1654</v>
-      </c>
-      <c r="B1014" t="s">
-        <v>1655</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B1015" t="s">
         <v>1656</v>
-      </c>
-      <c r="B1015" t="s">
-        <v>1657</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="B1016" t="s">
         <v>1658</v>
@@ -14290,20 +14293,20 @@
         <v>1659</v>
       </c>
       <c r="B1017" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B1018" t="s">
         <v>1661</v>
-      </c>
-      <c r="B1018" t="s">
-        <v>1662</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="B1019" t="s">
         <v>1663</v>
@@ -14314,20 +14317,20 @@
         <v>1664</v>
       </c>
       <c r="B1020" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B1021" t="s">
         <v>1666</v>
-      </c>
-      <c r="B1021" t="s">
-        <v>1667</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="B1022" t="s">
         <v>1668</v>
@@ -14362,20 +14365,20 @@
         <v>1672</v>
       </c>
       <c r="B1026" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B1027" t="s">
         <v>1674</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>1675</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="B1028" t="s">
         <v>1676</v>
@@ -14386,28 +14389,28 @@
         <v>1677</v>
       </c>
       <c r="B1029" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B1030" t="s">
         <v>1679</v>
-      </c>
-      <c r="B1030" t="s">
-        <v>1680</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B1031" t="s">
         <v>1681</v>
-      </c>
-      <c r="B1031" t="s">
-        <v>1682</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="B1032" t="s">
         <v>1683</v>
@@ -14418,12 +14421,12 @@
         <v>1684</v>
       </c>
       <c r="B1033" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="B1034" t="s">
         <v>1686</v>
@@ -14442,12 +14445,12 @@
         <v>1688</v>
       </c>
       <c r="B1036" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="B1037" t="s">
         <v>1690</v>
@@ -14458,12 +14461,12 @@
         <v>1691</v>
       </c>
       <c r="B1038" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="B1039" t="s">
         <v>1693</v>
@@ -14482,12 +14485,12 @@
         <v>1695</v>
       </c>
       <c r="B1041" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="B1042" t="s">
         <v>1697</v>
@@ -14506,12 +14509,12 @@
         <v>1699</v>
       </c>
       <c r="B1044" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="B1045" t="s">
         <v>1701</v>
@@ -14522,36 +14525,36 @@
         <v>1702</v>
       </c>
       <c r="B1046" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B1047" t="s">
         <v>1704</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>1705</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B1048" t="s">
         <v>1706</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>1707</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B1049" t="s">
         <v>1708</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>1709</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="B1050" t="s">
         <v>1710</v>
@@ -14562,12 +14565,12 @@
         <v>1711</v>
       </c>
       <c r="B1051" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="B1052" t="s">
         <v>1713</v>
@@ -14578,44 +14581,44 @@
         <v>1714</v>
       </c>
       <c r="B1053" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B1054" t="s">
         <v>1716</v>
-      </c>
-      <c r="B1054" t="s">
-        <v>1717</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B1055" t="s">
         <v>1718</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>1719</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B1056" t="s">
         <v>1720</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>1721</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1057" t="s">
         <v>1722</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>1723</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="B1058" t="s">
         <v>1724</v>
@@ -14650,52 +14653,52 @@
         <v>1728</v>
       </c>
       <c r="B1062" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
+        <v>1729</v>
+      </c>
+      <c r="B1063" t="s">
         <v>1730</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>1731</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
+        <v>1731</v>
+      </c>
+      <c r="B1064" t="s">
         <v>1732</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>1733</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>1733</v>
+      </c>
+      <c r="B1065" t="s">
         <v>1734</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>1735</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>1735</v>
+      </c>
+      <c r="B1066" t="s">
         <v>1736</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>1737</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>1737</v>
+      </c>
+      <c r="B1067" t="s">
         <v>1738</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>1739</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="B1068" t="s">
         <v>1740</v>
@@ -14706,12 +14709,12 @@
         <v>1741</v>
       </c>
       <c r="B1069" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B1070" t="s">
         <v>1743</v>
@@ -14730,52 +14733,52 @@
         <v>1745</v>
       </c>
       <c r="B1072" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B1073" t="s">
         <v>1747</v>
-      </c>
-      <c r="B1073" t="s">
-        <v>1748</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B1074" t="s">
         <v>1749</v>
-      </c>
-      <c r="B1074" t="s">
-        <v>1750</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B1075" t="s">
         <v>1751</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>1752</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
+        <v>1752</v>
+      </c>
+      <c r="B1076" t="s">
         <v>1753</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>1754</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B1077" t="s">
         <v>1755</v>
-      </c>
-      <c r="B1077" t="s">
-        <v>1756</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="B1078" t="s">
         <v>1757</v>
@@ -14786,12 +14789,12 @@
         <v>1758</v>
       </c>
       <c r="B1079" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="B1080" t="s">
         <v>1760</v>
@@ -14810,12 +14813,12 @@
         <v>1762</v>
       </c>
       <c r="B1082" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="B1083" t="s">
         <v>1764</v>
@@ -14826,12 +14829,12 @@
         <v>1765</v>
       </c>
       <c r="B1084" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B1085" t="s">
         <v>1767</v>
@@ -14866,20 +14869,20 @@
         <v>1771</v>
       </c>
       <c r="B1089" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
+        <v>1772</v>
+      </c>
+      <c r="B1090" t="s">
         <v>1773</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>1774</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B1091" t="s">
         <v>1775</v>
@@ -14898,20 +14901,20 @@
         <v>1777</v>
       </c>
       <c r="B1093" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B1094" t="s">
         <v>1779</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>1780</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
       <c r="B1095" t="s">
         <v>1781</v>
@@ -14922,36 +14925,36 @@
         <v>1782</v>
       </c>
       <c r="B1096" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>1783</v>
+      </c>
+      <c r="B1097" t="s">
         <v>1784</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>1785</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
+        <v>1785</v>
+      </c>
+      <c r="B1098" t="s">
         <v>1786</v>
-      </c>
-      <c r="B1098" t="s">
-        <v>1787</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
+        <v>1787</v>
+      </c>
+      <c r="B1099" t="s">
         <v>1788</v>
-      </c>
-      <c r="B1099" t="s">
-        <v>1789</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="B1100" t="s">
         <v>1790</v>
@@ -14970,44 +14973,44 @@
         <v>1792</v>
       </c>
       <c r="B1102" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
+        <v>1793</v>
+      </c>
+      <c r="B1103" t="s">
         <v>1794</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>1795</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
+        <v>1795</v>
+      </c>
+      <c r="B1104" t="s">
         <v>1796</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>1797</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>1797</v>
+      </c>
+      <c r="B1105" t="s">
         <v>1798</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>1799</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B1106" t="s">
         <v>1800</v>
-      </c>
-      <c r="B1106" t="s">
-        <v>1801</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="B1107" t="s">
         <v>1802</v>
@@ -15018,20 +15021,20 @@
         <v>1803</v>
       </c>
       <c r="B1108" t="s">
-        <v>1804</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
+        <v>1804</v>
+      </c>
+      <c r="B1109" t="s">
         <v>1805</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>1806</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="B1110" t="s">
         <v>1807</v>
@@ -15050,12 +15053,12 @@
         <v>1809</v>
       </c>
       <c r="B1112" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1811</v>
+        <v>1810</v>
       </c>
       <c r="B1113" t="s">
         <v>1811</v>
@@ -15074,20 +15077,20 @@
         <v>1813</v>
       </c>
       <c r="B1115" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
+        <v>1814</v>
+      </c>
+      <c r="B1116" t="s">
         <v>1815</v>
-      </c>
-      <c r="B1116" t="s">
-        <v>1816</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="B1117" t="s">
         <v>1817</v>
@@ -15098,28 +15101,28 @@
         <v>1818</v>
       </c>
       <c r="B1118" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
+        <v>1819</v>
+      </c>
+      <c r="B1119" t="s">
         <v>1820</v>
-      </c>
-      <c r="B1119" t="s">
-        <v>1821</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
+        <v>1821</v>
+      </c>
+      <c r="B1120" t="s">
         <v>1822</v>
-      </c>
-      <c r="B1120" t="s">
-        <v>1823</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1824</v>
+        <v>1823</v>
       </c>
       <c r="B1121" t="s">
         <v>1824</v>
@@ -15130,44 +15133,44 @@
         <v>1825</v>
       </c>
       <c r="B1122" t="s">
-        <v>1826</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B1123" t="s">
         <v>1827</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>1828</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1828</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1829</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1830</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1830</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1831</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1832</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1832</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1833</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1834</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1835</v>
+        <v>1834</v>
       </c>
       <c r="B1127" t="s">
         <v>1835</v>
@@ -15178,108 +15181,108 @@
         <v>1836</v>
       </c>
       <c r="B1128" t="s">
-        <v>1837</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1837</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1838</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1839</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1839</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1840</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1841</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1842</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1843</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1843</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1844</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1845</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1845</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1846</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1847</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1847</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1848</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1849</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>1849</v>
+      </c>
+      <c r="B1135" t="s">
         <v>1850</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>1851</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B1136" t="s">
         <v>1852</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>1853</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B1137" t="s">
         <v>1854</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>1855</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1855</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1856</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1857</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>1857</v>
+      </c>
+      <c r="B1139" t="s">
         <v>1858</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>1859</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>1859</v>
+      </c>
+      <c r="B1140" t="s">
         <v>1860</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>1861</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="B1141" t="s">
         <v>1862</v>
@@ -15322,20 +15325,20 @@
         <v>1867</v>
       </c>
       <c r="B1146" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B1147" t="s">
         <v>1869</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>1870</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="B1148" t="s">
         <v>1871</v>
@@ -15362,68 +15365,68 @@
         <v>1874</v>
       </c>
       <c r="B1151" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B1152" t="s">
         <v>1876</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>1877</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B1153" t="s">
         <v>1878</v>
-      </c>
-      <c r="B1153" t="s">
-        <v>1879</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B1154" t="s">
         <v>1880</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>1881</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B1155" t="s">
         <v>1882</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>1883</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B1156" t="s">
         <v>1884</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>1885</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B1157" t="s">
         <v>1886</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>1887</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B1158" t="s">
         <v>1888</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>1889</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="B1159" t="s">
         <v>1890</v>
@@ -15434,12 +15437,12 @@
         <v>1891</v>
       </c>
       <c r="B1160" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="B1161" t="s">
         <v>1893</v>
@@ -15450,36 +15453,36 @@
         <v>1894</v>
       </c>
       <c r="B1162" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>1895</v>
+      </c>
+      <c r="B1163" t="s">
         <v>1896</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>1897</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>1897</v>
+      </c>
+      <c r="B1164" t="s">
         <v>1898</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>1899</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B1165" t="s">
         <v>1900</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>1901</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B1166" t="s">
         <v>1902</v>
@@ -15522,20 +15525,20 @@
         <v>1907</v>
       </c>
       <c r="B1171" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B1172" t="s">
         <v>1909</v>
-      </c>
-      <c r="B1172" t="s">
-        <v>1910</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B1173" t="s">
         <v>1911</v>
@@ -15554,12 +15557,12 @@
         <v>1913</v>
       </c>
       <c r="B1175" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B1176" t="s">
         <v>1915</v>
@@ -15602,12 +15605,12 @@
         <v>1920</v>
       </c>
       <c r="B1181" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="B1182" t="s">
         <v>1922</v>
@@ -15642,19 +15645,27 @@
         <v>1926</v>
       </c>
       <c r="B1186" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B1187" t="s">
         <v>1928</v>
       </c>
     </row>
+    <row r="1188" spans="1:2">
+      <c r="A1188" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B1188" t="s">
+        <v>1929</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1187"/>
+  <autoFilter ref="A1:B1188"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1188</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1932">
   <si>
     <t>en</t>
   </si>
@@ -4673,6 +4673,12 @@
   </si>
   <si>
     <t>Shadows of Mordor</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>Hiu</t>
   </si>
   <si>
     <t>Sheep</t>
@@ -6153,7 +6159,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1188"/>
+  <dimension ref="A1:B1189"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13757,28 +13763,28 @@
         <v>1554</v>
       </c>
       <c r="B950" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B951" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B952" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B953" t="s">
         <v>1558</v>
@@ -13805,44 +13811,44 @@
         <v>1563</v>
       </c>
       <c r="B956" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B957" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B958" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B959" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B960" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B961" t="s">
         <v>1569</v>
@@ -13877,28 +13883,28 @@
         <v>1576</v>
       </c>
       <c r="B965" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B966" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B967" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B968" t="s">
         <v>1580</v>
@@ -13949,28 +13955,28 @@
         <v>1591</v>
       </c>
       <c r="B974" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B975" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B976" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B977" t="s">
         <v>1595</v>
@@ -13981,20 +13987,20 @@
         <v>1596</v>
       </c>
       <c r="B978" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B979" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B980" t="s">
         <v>1599</v>
@@ -14037,12 +14043,12 @@
         <v>1608</v>
       </c>
       <c r="B985" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B986" t="s">
         <v>1610</v>
@@ -14069,12 +14075,12 @@
         <v>1615</v>
       </c>
       <c r="B989" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B990" t="s">
         <v>1617</v>
@@ -14093,36 +14099,36 @@
         <v>1620</v>
       </c>
       <c r="B992" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B993" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B994" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B995" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B996" t="s">
         <v>1625</v>
@@ -14173,12 +14179,12 @@
         <v>1636</v>
       </c>
       <c r="B1002" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B1003" t="s">
         <v>1638</v>
@@ -14197,28 +14203,28 @@
         <v>1641</v>
       </c>
       <c r="B1005" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B1006" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1007" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B1008" t="s">
         <v>1645</v>
@@ -14229,12 +14235,12 @@
         <v>1646</v>
       </c>
       <c r="B1009" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B1010" t="s">
         <v>1648</v>
@@ -14253,20 +14259,20 @@
         <v>1651</v>
       </c>
       <c r="B1012" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B1013" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B1014" t="s">
         <v>1654</v>
@@ -14293,12 +14299,12 @@
         <v>1659</v>
       </c>
       <c r="B1017" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B1018" t="s">
         <v>1661</v>
@@ -14317,12 +14323,12 @@
         <v>1664</v>
       </c>
       <c r="B1020" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1021" t="s">
         <v>1666</v>
@@ -14341,36 +14347,36 @@
         <v>1669</v>
       </c>
       <c r="B1023" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B1024" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B1025" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B1026" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1027" t="s">
         <v>1674</v>
@@ -14389,12 +14395,12 @@
         <v>1677</v>
       </c>
       <c r="B1029" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1030" t="s">
         <v>1679</v>
@@ -14421,12 +14427,12 @@
         <v>1684</v>
       </c>
       <c r="B1033" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1034" t="s">
         <v>1686</v>
@@ -14437,20 +14443,20 @@
         <v>1687</v>
       </c>
       <c r="B1035" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1036" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1037" t="s">
         <v>1690</v>
@@ -14461,12 +14467,12 @@
         <v>1691</v>
       </c>
       <c r="B1038" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1039" t="s">
         <v>1693</v>
@@ -14477,20 +14483,20 @@
         <v>1694</v>
       </c>
       <c r="B1040" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1041" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1042" t="s">
         <v>1697</v>
@@ -14501,20 +14507,20 @@
         <v>1698</v>
       </c>
       <c r="B1043" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1044" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1045" t="s">
         <v>1701</v>
@@ -14525,12 +14531,12 @@
         <v>1702</v>
       </c>
       <c r="B1046" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1047" t="s">
         <v>1704</v>
@@ -14565,12 +14571,12 @@
         <v>1711</v>
       </c>
       <c r="B1051" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1052" t="s">
         <v>1713</v>
@@ -14581,12 +14587,12 @@
         <v>1714</v>
       </c>
       <c r="B1053" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1054" t="s">
         <v>1716</v>
@@ -14629,36 +14635,36 @@
         <v>1725</v>
       </c>
       <c r="B1059" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="B1060" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="B1061" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="B1062" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1063" t="s">
         <v>1730</v>
@@ -14709,12 +14715,12 @@
         <v>1741</v>
       </c>
       <c r="B1069" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="B1070" t="s">
         <v>1743</v>
@@ -14725,20 +14731,20 @@
         <v>1744</v>
       </c>
       <c r="B1071" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B1072" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="B1073" t="s">
         <v>1747</v>
@@ -14789,12 +14795,12 @@
         <v>1758</v>
       </c>
       <c r="B1079" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="B1080" t="s">
         <v>1760</v>
@@ -14805,20 +14811,20 @@
         <v>1761</v>
       </c>
       <c r="B1081" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B1082" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="B1083" t="s">
         <v>1764</v>
@@ -14829,12 +14835,12 @@
         <v>1765</v>
       </c>
       <c r="B1084" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B1085" t="s">
         <v>1767</v>
@@ -14845,36 +14851,36 @@
         <v>1768</v>
       </c>
       <c r="B1086" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B1087" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B1088" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B1089" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B1090" t="s">
         <v>1773</v>
@@ -14893,20 +14899,20 @@
         <v>1776</v>
       </c>
       <c r="B1092" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B1093" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="B1094" t="s">
         <v>1779</v>
@@ -14925,12 +14931,12 @@
         <v>1782</v>
       </c>
       <c r="B1096" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B1097" t="s">
         <v>1784</v>
@@ -14965,20 +14971,20 @@
         <v>1791</v>
       </c>
       <c r="B1101" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1102" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="B1103" t="s">
         <v>1794</v>
@@ -15021,12 +15027,12 @@
         <v>1803</v>
       </c>
       <c r="B1108" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="B1109" t="s">
         <v>1805</v>
@@ -15045,20 +15051,20 @@
         <v>1808</v>
       </c>
       <c r="B1111" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1112" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="B1113" t="s">
         <v>1811</v>
@@ -15069,20 +15075,20 @@
         <v>1812</v>
       </c>
       <c r="B1114" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B1115" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B1116" t="s">
         <v>1815</v>
@@ -15101,12 +15107,12 @@
         <v>1818</v>
       </c>
       <c r="B1118" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B1119" t="s">
         <v>1820</v>
@@ -15133,12 +15139,12 @@
         <v>1825</v>
       </c>
       <c r="B1122" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B1123" t="s">
         <v>1827</v>
@@ -15181,12 +15187,12 @@
         <v>1836</v>
       </c>
       <c r="B1128" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="B1129" t="s">
         <v>1838</v>
@@ -15293,44 +15299,44 @@
         <v>1863</v>
       </c>
       <c r="B1142" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="B1143" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="B1144" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="B1145" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B1146" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="B1147" t="s">
         <v>1869</v>
@@ -15349,28 +15355,28 @@
         <v>1872</v>
       </c>
       <c r="B1149" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B1150" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B1151" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B1152" t="s">
         <v>1876</v>
@@ -15437,12 +15443,12 @@
         <v>1891</v>
       </c>
       <c r="B1160" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="B1161" t="s">
         <v>1893</v>
@@ -15453,12 +15459,12 @@
         <v>1894</v>
       </c>
       <c r="B1162" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B1163" t="s">
         <v>1896</v>
@@ -15493,44 +15499,44 @@
         <v>1903</v>
       </c>
       <c r="B1167" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B1168" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="B1169" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="B1170" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1171" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B1172" t="s">
         <v>1909</v>
@@ -15549,20 +15555,20 @@
         <v>1912</v>
       </c>
       <c r="B1174" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B1175" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1176" t="s">
         <v>1915</v>
@@ -15573,44 +15579,44 @@
         <v>1916</v>
       </c>
       <c r="B1177" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="B1178" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B1179" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="B1180" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="B1181" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B1182" t="s">
         <v>1922</v>
@@ -15621,36 +15627,36 @@
         <v>1923</v>
       </c>
       <c r="B1183" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B1184" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B1185" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B1186" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1187" t="s">
         <v>1928</v>
@@ -15661,11 +15667,19 @@
         <v>1929</v>
       </c>
       <c r="B1188" t="s">
-        <v>1929</v>
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:2">
+      <c r="A1189" t="s">
+        <v>1931</v>
+      </c>
+      <c r="B1189" t="s">
+        <v>1931</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1188"/>
+  <autoFilter ref="A1:B1189"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -1618,6 +1618,9 @@
     <t>Dongeng</t>
   </si>
   <si>
+    <t>Fall Drop</t>
+  </si>
+  <si>
     <t>Fall Guys</t>
   </si>
   <si>
@@ -5810,9 +5813,6 @@
   </si>
   <si>
     <t>Tag Hypixel (Mutasi)</t>
-  </si>
-  <si>
-    <t>Fall Drop</t>
   </si>
 </sst>
 </file>
@@ -8771,12 +8771,12 @@
         <v>534</v>
       </c>
       <c r="B326" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B327" t="s">
         <v>536</v>
@@ -8787,28 +8787,28 @@
         <v>537</v>
       </c>
       <c r="B328" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
+        <v>538</v>
+      </c>
+      <c r="B329" t="s">
         <v>539</v>
-      </c>
-      <c r="B329" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
+        <v>540</v>
+      </c>
+      <c r="B330" t="s">
         <v>541</v>
-      </c>
-      <c r="B330" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B331" t="s">
         <v>543</v>
@@ -8819,52 +8819,52 @@
         <v>544</v>
       </c>
       <c r="B332" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
+        <v>545</v>
+      </c>
+      <c r="B333" t="s">
         <v>546</v>
-      </c>
-      <c r="B333" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
+        <v>547</v>
+      </c>
+      <c r="B334" t="s">
         <v>548</v>
-      </c>
-      <c r="B334" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
+        <v>549</v>
+      </c>
+      <c r="B335" t="s">
         <v>550</v>
-      </c>
-      <c r="B335" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
+        <v>551</v>
+      </c>
+      <c r="B336" t="s">
         <v>552</v>
-      </c>
-      <c r="B336" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
+        <v>553</v>
+      </c>
+      <c r="B337" t="s">
         <v>554</v>
-      </c>
-      <c r="B337" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B338" t="s">
         <v>556</v>
@@ -8883,12 +8883,12 @@
         <v>558</v>
       </c>
       <c r="B340" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B341" t="s">
         <v>560</v>
@@ -8899,52 +8899,52 @@
         <v>561</v>
       </c>
       <c r="B342" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
+        <v>562</v>
+      </c>
+      <c r="B343" t="s">
         <v>563</v>
-      </c>
-      <c r="B343" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
+        <v>564</v>
+      </c>
+      <c r="B344" t="s">
         <v>565</v>
-      </c>
-      <c r="B344" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
+        <v>566</v>
+      </c>
+      <c r="B345" t="s">
         <v>567</v>
-      </c>
-      <c r="B345" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
+        <v>568</v>
+      </c>
+      <c r="B346" t="s">
         <v>569</v>
-      </c>
-      <c r="B346" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
+        <v>570</v>
+      </c>
+      <c r="B347" t="s">
         <v>571</v>
-      </c>
-      <c r="B347" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B348" t="s">
         <v>573</v>
@@ -8955,100 +8955,100 @@
         <v>574</v>
       </c>
       <c r="B349" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
+        <v>575</v>
+      </c>
+      <c r="B350" t="s">
         <v>576</v>
-      </c>
-      <c r="B350" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
+        <v>577</v>
+      </c>
+      <c r="B351" t="s">
         <v>578</v>
-      </c>
-      <c r="B351" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
+        <v>579</v>
+      </c>
+      <c r="B352" t="s">
         <v>580</v>
-      </c>
-      <c r="B352" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
+        <v>581</v>
+      </c>
+      <c r="B353" t="s">
         <v>582</v>
-      </c>
-      <c r="B353" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
+        <v>583</v>
+      </c>
+      <c r="B354" t="s">
         <v>584</v>
-      </c>
-      <c r="B354" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
+        <v>585</v>
+      </c>
+      <c r="B355" t="s">
         <v>586</v>
-      </c>
-      <c r="B355" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
+        <v>587</v>
+      </c>
+      <c r="B356" t="s">
         <v>588</v>
-      </c>
-      <c r="B356" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
+        <v>589</v>
+      </c>
+      <c r="B357" t="s">
         <v>590</v>
-      </c>
-      <c r="B357" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
+        <v>591</v>
+      </c>
+      <c r="B358" t="s">
         <v>592</v>
-      </c>
-      <c r="B358" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
+        <v>593</v>
+      </c>
+      <c r="B359" t="s">
         <v>594</v>
-      </c>
-      <c r="B359" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
+        <v>595</v>
+      </c>
+      <c r="B360" t="s">
         <v>596</v>
-      </c>
-      <c r="B360" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B361" t="s">
         <v>598</v>
@@ -9059,28 +9059,28 @@
         <v>599</v>
       </c>
       <c r="B362" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
+        <v>600</v>
+      </c>
+      <c r="B363" t="s">
         <v>601</v>
-      </c>
-      <c r="B363" t="s">
-        <v>602</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
+        <v>602</v>
+      </c>
+      <c r="B364" t="s">
         <v>603</v>
-      </c>
-      <c r="B364" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="365" spans="1:2">
       <c r="A365" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B365" t="s">
         <v>605</v>
@@ -9091,28 +9091,28 @@
         <v>606</v>
       </c>
       <c r="B366" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
+        <v>607</v>
+      </c>
+      <c r="B367" t="s">
         <v>608</v>
-      </c>
-      <c r="B367" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
+        <v>609</v>
+      </c>
+      <c r="B368" t="s">
         <v>610</v>
-      </c>
-      <c r="B368" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="369" spans="1:2">
       <c r="A369" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B369" t="s">
         <v>612</v>
@@ -9131,60 +9131,60 @@
         <v>614</v>
       </c>
       <c r="B371" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
+        <v>615</v>
+      </c>
+      <c r="B372" t="s">
         <v>616</v>
-      </c>
-      <c r="B372" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
+        <v>617</v>
+      </c>
+      <c r="B373" t="s">
         <v>618</v>
-      </c>
-      <c r="B373" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
+        <v>619</v>
+      </c>
+      <c r="B374" t="s">
         <v>620</v>
-      </c>
-      <c r="B374" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" t="s">
+        <v>621</v>
+      </c>
+      <c r="B375" t="s">
         <v>622</v>
-      </c>
-      <c r="B375" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="376" spans="1:2">
       <c r="A376" t="s">
+        <v>623</v>
+      </c>
+      <c r="B376" t="s">
         <v>624</v>
-      </c>
-      <c r="B376" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
+        <v>625</v>
+      </c>
+      <c r="B377" t="s">
         <v>626</v>
-      </c>
-      <c r="B377" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B378" t="s">
         <v>628</v>
@@ -9195,12 +9195,12 @@
         <v>629</v>
       </c>
       <c r="B379" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B380" t="s">
         <v>631</v>
@@ -9211,52 +9211,52 @@
         <v>632</v>
       </c>
       <c r="B381" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
+        <v>633</v>
+      </c>
+      <c r="B382" t="s">
         <v>634</v>
-      </c>
-      <c r="B382" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
+        <v>635</v>
+      </c>
+      <c r="B383" t="s">
         <v>636</v>
-      </c>
-      <c r="B383" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" t="s">
+        <v>637</v>
+      </c>
+      <c r="B384" t="s">
         <v>638</v>
-      </c>
-      <c r="B384" t="s">
-        <v>639</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
+        <v>639</v>
+      </c>
+      <c r="B385" t="s">
         <v>640</v>
-      </c>
-      <c r="B385" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
+        <v>641</v>
+      </c>
+      <c r="B386" t="s">
         <v>642</v>
-      </c>
-      <c r="B386" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="387" spans="1:2">
       <c r="A387" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B387" t="s">
         <v>644</v>
@@ -9267,36 +9267,36 @@
         <v>645</v>
       </c>
       <c r="B388" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
+        <v>646</v>
+      </c>
+      <c r="B389" t="s">
         <v>647</v>
-      </c>
-      <c r="B389" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
+        <v>648</v>
+      </c>
+      <c r="B390" t="s">
         <v>649</v>
-      </c>
-      <c r="B390" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" t="s">
+        <v>650</v>
+      </c>
+      <c r="B391" t="s">
         <v>651</v>
-      </c>
-      <c r="B391" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B392" t="s">
         <v>653</v>
@@ -9307,60 +9307,60 @@
         <v>654</v>
       </c>
       <c r="B393" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
+        <v>655</v>
+      </c>
+      <c r="B394" t="s">
         <v>656</v>
-      </c>
-      <c r="B394" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
+        <v>657</v>
+      </c>
+      <c r="B395" t="s">
         <v>658</v>
-      </c>
-      <c r="B395" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
+        <v>659</v>
+      </c>
+      <c r="B396" t="s">
         <v>660</v>
-      </c>
-      <c r="B396" t="s">
-        <v>661</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
+        <v>661</v>
+      </c>
+      <c r="B397" t="s">
         <v>662</v>
-      </c>
-      <c r="B397" t="s">
-        <v>663</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
+        <v>663</v>
+      </c>
+      <c r="B398" t="s">
         <v>664</v>
-      </c>
-      <c r="B398" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
+        <v>665</v>
+      </c>
+      <c r="B399" t="s">
         <v>666</v>
-      </c>
-      <c r="B399" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="B400" t="s">
         <v>668</v>
@@ -9371,20 +9371,20 @@
         <v>669</v>
       </c>
       <c r="B401" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
+        <v>670</v>
+      </c>
+      <c r="B402" t="s">
         <v>671</v>
-      </c>
-      <c r="B402" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B403" t="s">
         <v>673</v>
@@ -9419,12 +9419,12 @@
         <v>677</v>
       </c>
       <c r="B407" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B408" t="s">
         <v>679</v>
@@ -9443,116 +9443,116 @@
         <v>681</v>
       </c>
       <c r="B410" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
+        <v>682</v>
+      </c>
+      <c r="B411" t="s">
         <v>683</v>
-      </c>
-      <c r="B411" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
+        <v>684</v>
+      </c>
+      <c r="B412" t="s">
         <v>685</v>
-      </c>
-      <c r="B412" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="413" spans="1:2">
       <c r="A413" t="s">
+        <v>686</v>
+      </c>
+      <c r="B413" t="s">
         <v>687</v>
-      </c>
-      <c r="B413" t="s">
-        <v>688</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
+        <v>688</v>
+      </c>
+      <c r="B414" t="s">
         <v>689</v>
-      </c>
-      <c r="B414" t="s">
-        <v>690</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
+        <v>690</v>
+      </c>
+      <c r="B415" t="s">
         <v>691</v>
-      </c>
-      <c r="B415" t="s">
-        <v>692</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
+        <v>692</v>
+      </c>
+      <c r="B416" t="s">
         <v>693</v>
-      </c>
-      <c r="B416" t="s">
-        <v>694</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" t="s">
+        <v>694</v>
+      </c>
+      <c r="B417" t="s">
         <v>695</v>
-      </c>
-      <c r="B417" t="s">
-        <v>696</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
+        <v>696</v>
+      </c>
+      <c r="B418" t="s">
         <v>697</v>
-      </c>
-      <c r="B418" t="s">
-        <v>698</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
+        <v>698</v>
+      </c>
+      <c r="B419" t="s">
         <v>699</v>
-      </c>
-      <c r="B419" t="s">
-        <v>700</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
+        <v>700</v>
+      </c>
+      <c r="B420" t="s">
         <v>701</v>
-      </c>
-      <c r="B420" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
+        <v>702</v>
+      </c>
+      <c r="B421" t="s">
         <v>703</v>
-      </c>
-      <c r="B421" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" t="s">
+        <v>704</v>
+      </c>
+      <c r="B422" t="s">
         <v>705</v>
-      </c>
-      <c r="B422" t="s">
-        <v>706</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" t="s">
+        <v>706</v>
+      </c>
+      <c r="B423" t="s">
         <v>707</v>
-      </c>
-      <c r="B423" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="424" spans="1:2">
       <c r="A424" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B424" t="s">
         <v>709</v>
@@ -9563,28 +9563,28 @@
         <v>710</v>
       </c>
       <c r="B425" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="426" spans="1:2">
       <c r="A426" t="s">
+        <v>711</v>
+      </c>
+      <c r="B426" t="s">
         <v>712</v>
-      </c>
-      <c r="B426" t="s">
-        <v>713</v>
       </c>
     </row>
     <row r="427" spans="1:2">
       <c r="A427" t="s">
+        <v>713</v>
+      </c>
+      <c r="B427" t="s">
         <v>714</v>
-      </c>
-      <c r="B427" t="s">
-        <v>715</v>
       </c>
     </row>
     <row r="428" spans="1:2">
       <c r="A428" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B428" t="s">
         <v>716</v>
@@ -9595,36 +9595,36 @@
         <v>717</v>
       </c>
       <c r="B429" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="430" spans="1:2">
       <c r="A430" t="s">
+        <v>718</v>
+      </c>
+      <c r="B430" t="s">
         <v>719</v>
-      </c>
-      <c r="B430" t="s">
-        <v>720</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
+        <v>720</v>
+      </c>
+      <c r="B431" t="s">
         <v>721</v>
-      </c>
-      <c r="B431" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
+        <v>722</v>
+      </c>
+      <c r="B432" t="s">
         <v>723</v>
-      </c>
-      <c r="B432" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B433" t="s">
         <v>725</v>
@@ -9635,20 +9635,20 @@
         <v>726</v>
       </c>
       <c r="B434" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
+        <v>727</v>
+      </c>
+      <c r="B435" t="s">
         <v>728</v>
-      </c>
-      <c r="B435" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B436" t="s">
         <v>730</v>
@@ -9659,12 +9659,12 @@
         <v>731</v>
       </c>
       <c r="B437" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B438" t="s">
         <v>733</v>
@@ -9675,60 +9675,60 @@
         <v>734</v>
       </c>
       <c r="B439" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
+        <v>735</v>
+      </c>
+      <c r="B440" t="s">
         <v>736</v>
-      </c>
-      <c r="B440" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" t="s">
+        <v>737</v>
+      </c>
+      <c r="B441" t="s">
         <v>738</v>
-      </c>
-      <c r="B441" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
+        <v>739</v>
+      </c>
+      <c r="B442" t="s">
         <v>740</v>
-      </c>
-      <c r="B442" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
+        <v>741</v>
+      </c>
+      <c r="B443" t="s">
         <v>742</v>
-      </c>
-      <c r="B443" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" t="s">
+        <v>743</v>
+      </c>
+      <c r="B444" t="s">
         <v>744</v>
-      </c>
-      <c r="B444" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
+        <v>745</v>
+      </c>
+      <c r="B445" t="s">
         <v>746</v>
-      </c>
-      <c r="B445" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B446" t="s">
         <v>748</v>
@@ -9739,12 +9739,12 @@
         <v>749</v>
       </c>
       <c r="B447" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="448" spans="1:2">
       <c r="A448" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B448" t="s">
         <v>751</v>
@@ -9755,12 +9755,12 @@
         <v>752</v>
       </c>
       <c r="B449" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B450" t="s">
         <v>754</v>
@@ -9771,12 +9771,12 @@
         <v>755</v>
       </c>
       <c r="B451" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B452" t="s">
         <v>757</v>
@@ -9787,20 +9787,20 @@
         <v>758</v>
       </c>
       <c r="B453" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
+        <v>759</v>
+      </c>
+      <c r="B454" t="s">
         <v>760</v>
-      </c>
-      <c r="B454" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B455" t="s">
         <v>762</v>
@@ -9811,76 +9811,76 @@
         <v>763</v>
       </c>
       <c r="B456" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
+        <v>764</v>
+      </c>
+      <c r="B457" t="s">
         <v>765</v>
-      </c>
-      <c r="B457" t="s">
-        <v>766</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
+        <v>766</v>
+      </c>
+      <c r="B458" t="s">
         <v>767</v>
-      </c>
-      <c r="B458" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
+        <v>768</v>
+      </c>
+      <c r="B459" t="s">
         <v>769</v>
-      </c>
-      <c r="B459" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="460" spans="1:2">
       <c r="A460" t="s">
+        <v>770</v>
+      </c>
+      <c r="B460" t="s">
         <v>771</v>
-      </c>
-      <c r="B460" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" t="s">
+        <v>772</v>
+      </c>
+      <c r="B461" t="s">
         <v>773</v>
-      </c>
-      <c r="B461" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" t="s">
+        <v>774</v>
+      </c>
+      <c r="B462" t="s">
         <v>775</v>
-      </c>
-      <c r="B462" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
+        <v>776</v>
+      </c>
+      <c r="B463" t="s">
         <v>777</v>
-      </c>
-      <c r="B463" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
+        <v>778</v>
+      </c>
+      <c r="B464" t="s">
         <v>779</v>
-      </c>
-      <c r="B464" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="465" spans="1:2">
       <c r="A465" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B465" t="s">
         <v>781</v>
@@ -9899,7 +9899,7 @@
         <v>783</v>
       </c>
       <c r="B467" t="s">
-        <v>524</v>
+        <v>783</v>
       </c>
     </row>
     <row r="468" spans="1:2">
@@ -9907,7 +9907,7 @@
         <v>784</v>
       </c>
       <c r="B468" t="s">
-        <v>784</v>
+        <v>524</v>
       </c>
     </row>
     <row r="469" spans="1:2">
@@ -9915,15 +9915,15 @@
         <v>785</v>
       </c>
       <c r="B469" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
+        <v>786</v>
+      </c>
+      <c r="B470" t="s">
         <v>787</v>
-      </c>
-      <c r="B470" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="471" spans="1:2">
@@ -9931,20 +9931,20 @@
         <v>788</v>
       </c>
       <c r="B471" t="s">
-        <v>789</v>
+        <v>139</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
+        <v>789</v>
+      </c>
+      <c r="B472" t="s">
         <v>790</v>
-      </c>
-      <c r="B472" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B473" t="s">
         <v>792</v>
@@ -9955,7 +9955,7 @@
         <v>793</v>
       </c>
       <c r="B474" t="s">
-        <v>524</v>
+        <v>793</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -9963,7 +9963,7 @@
         <v>794</v>
       </c>
       <c r="B475" t="s">
-        <v>794</v>
+        <v>524</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -9987,28 +9987,28 @@
         <v>797</v>
       </c>
       <c r="B478" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
+        <v>798</v>
+      </c>
+      <c r="B479" t="s">
         <v>799</v>
-      </c>
-      <c r="B479" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
+        <v>800</v>
+      </c>
+      <c r="B480" t="s">
         <v>801</v>
-      </c>
-      <c r="B480" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B481" t="s">
         <v>803</v>
@@ -10019,12 +10019,12 @@
         <v>804</v>
       </c>
       <c r="B482" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B483" t="s">
         <v>806</v>
@@ -10035,20 +10035,20 @@
         <v>807</v>
       </c>
       <c r="B484" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
+        <v>808</v>
+      </c>
+      <c r="B485" t="s">
         <v>809</v>
-      </c>
-      <c r="B485" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B486" t="s">
         <v>811</v>
@@ -10099,164 +10099,164 @@
         <v>817</v>
       </c>
       <c r="B492" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
+        <v>818</v>
+      </c>
+      <c r="B493" t="s">
         <v>819</v>
-      </c>
-      <c r="B493" t="s">
-        <v>820</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
+        <v>820</v>
+      </c>
+      <c r="B494" t="s">
         <v>821</v>
-      </c>
-      <c r="B494" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" t="s">
+        <v>822</v>
+      </c>
+      <c r="B495" t="s">
         <v>823</v>
-      </c>
-      <c r="B495" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="496" spans="1:2">
       <c r="A496" t="s">
+        <v>824</v>
+      </c>
+      <c r="B496" t="s">
         <v>825</v>
-      </c>
-      <c r="B496" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="497" spans="1:2">
       <c r="A497" t="s">
+        <v>826</v>
+      </c>
+      <c r="B497" t="s">
         <v>827</v>
-      </c>
-      <c r="B497" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="498" spans="1:2">
       <c r="A498" t="s">
+        <v>828</v>
+      </c>
+      <c r="B498" t="s">
         <v>829</v>
-      </c>
-      <c r="B498" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="499" spans="1:2">
       <c r="A499" t="s">
+        <v>830</v>
+      </c>
+      <c r="B499" t="s">
         <v>831</v>
-      </c>
-      <c r="B499" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="500" spans="1:2">
       <c r="A500" t="s">
+        <v>832</v>
+      </c>
+      <c r="B500" t="s">
         <v>833</v>
-      </c>
-      <c r="B500" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="501" spans="1:2">
       <c r="A501" t="s">
+        <v>834</v>
+      </c>
+      <c r="B501" t="s">
         <v>835</v>
-      </c>
-      <c r="B501" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="502" spans="1:2">
       <c r="A502" t="s">
+        <v>836</v>
+      </c>
+      <c r="B502" t="s">
         <v>837</v>
-      </c>
-      <c r="B502" t="s">
-        <v>838</v>
       </c>
     </row>
     <row r="503" spans="1:2">
       <c r="A503" t="s">
+        <v>838</v>
+      </c>
+      <c r="B503" t="s">
         <v>839</v>
-      </c>
-      <c r="B503" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="504" spans="1:2">
       <c r="A504" t="s">
+        <v>840</v>
+      </c>
+      <c r="B504" t="s">
         <v>841</v>
-      </c>
-      <c r="B504" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="505" spans="1:2">
       <c r="A505" t="s">
+        <v>842</v>
+      </c>
+      <c r="B505" t="s">
         <v>843</v>
-      </c>
-      <c r="B505" t="s">
-        <v>844</v>
       </c>
     </row>
     <row r="506" spans="1:2">
       <c r="A506" t="s">
+        <v>844</v>
+      </c>
+      <c r="B506" t="s">
         <v>845</v>
-      </c>
-      <c r="B506" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="507" spans="1:2">
       <c r="A507" t="s">
+        <v>846</v>
+      </c>
+      <c r="B507" t="s">
         <v>847</v>
-      </c>
-      <c r="B507" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="508" spans="1:2">
       <c r="A508" t="s">
+        <v>848</v>
+      </c>
+      <c r="B508" t="s">
         <v>849</v>
-      </c>
-      <c r="B508" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="509" spans="1:2">
       <c r="A509" t="s">
+        <v>850</v>
+      </c>
+      <c r="B509" t="s">
         <v>851</v>
-      </c>
-      <c r="B509" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" t="s">
+        <v>852</v>
+      </c>
+      <c r="B510" t="s">
         <v>853</v>
-      </c>
-      <c r="B510" t="s">
-        <v>854</v>
       </c>
     </row>
     <row r="511" spans="1:2">
       <c r="A511" t="s">
+        <v>854</v>
+      </c>
+      <c r="B511" t="s">
         <v>855</v>
-      </c>
-      <c r="B511" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="512" spans="1:2">
       <c r="A512" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B512" t="s">
         <v>857</v>
@@ -10267,12 +10267,12 @@
         <v>858</v>
       </c>
       <c r="B513" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B514" t="s">
         <v>860</v>
@@ -10299,28 +10299,28 @@
         <v>863</v>
       </c>
       <c r="B517" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
+        <v>864</v>
+      </c>
+      <c r="B518" t="s">
         <v>865</v>
-      </c>
-      <c r="B518" t="s">
-        <v>866</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" t="s">
+        <v>866</v>
+      </c>
+      <c r="B519" t="s">
         <v>867</v>
-      </c>
-      <c r="B519" t="s">
-        <v>868</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B520" t="s">
         <v>869</v>
@@ -10347,28 +10347,28 @@
         <v>872</v>
       </c>
       <c r="B523" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
+        <v>873</v>
+      </c>
+      <c r="B524" t="s">
         <v>874</v>
-      </c>
-      <c r="B524" t="s">
-        <v>875</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
+        <v>875</v>
+      </c>
+      <c r="B525" t="s">
         <v>876</v>
-      </c>
-      <c r="B525" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B526" t="s">
         <v>878</v>
@@ -10379,52 +10379,52 @@
         <v>879</v>
       </c>
       <c r="B527" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" t="s">
+        <v>880</v>
+      </c>
+      <c r="B528" t="s">
         <v>881</v>
-      </c>
-      <c r="B528" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
+        <v>882</v>
+      </c>
+      <c r="B529" t="s">
         <v>883</v>
-      </c>
-      <c r="B529" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
+        <v>884</v>
+      </c>
+      <c r="B530" t="s">
         <v>885</v>
-      </c>
-      <c r="B530" t="s">
-        <v>886</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
+        <v>886</v>
+      </c>
+      <c r="B531" t="s">
         <v>887</v>
-      </c>
-      <c r="B531" t="s">
-        <v>888</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
+        <v>888</v>
+      </c>
+      <c r="B532" t="s">
         <v>889</v>
-      </c>
-      <c r="B532" t="s">
-        <v>890</v>
       </c>
     </row>
     <row r="533" spans="1:2">
       <c r="A533" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B533" t="s">
         <v>891</v>
@@ -10435,20 +10435,20 @@
         <v>892</v>
       </c>
       <c r="B534" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
+        <v>893</v>
+      </c>
+      <c r="B535" t="s">
         <v>894</v>
-      </c>
-      <c r="B535" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B536" t="s">
         <v>896</v>
@@ -10467,12 +10467,12 @@
         <v>898</v>
       </c>
       <c r="B538" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B539" t="s">
         <v>900</v>
@@ -10515,28 +10515,28 @@
         <v>905</v>
       </c>
       <c r="B544" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
+        <v>906</v>
+      </c>
+      <c r="B545" t="s">
         <v>907</v>
-      </c>
-      <c r="B545" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
+        <v>908</v>
+      </c>
+      <c r="B546" t="s">
         <v>909</v>
-      </c>
-      <c r="B546" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B547" t="s">
         <v>911</v>
@@ -10555,12 +10555,12 @@
         <v>913</v>
       </c>
       <c r="B549" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B550" t="s">
         <v>915</v>
@@ -10571,12 +10571,12 @@
         <v>916</v>
       </c>
       <c r="B551" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B552" t="s">
         <v>918</v>
@@ -10603,12 +10603,12 @@
         <v>921</v>
       </c>
       <c r="B555" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B556" t="s">
         <v>923</v>
@@ -10619,68 +10619,68 @@
         <v>924</v>
       </c>
       <c r="B557" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
+        <v>925</v>
+      </c>
+      <c r="B558" t="s">
         <v>926</v>
-      </c>
-      <c r="B558" t="s">
-        <v>927</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
+        <v>927</v>
+      </c>
+      <c r="B559" t="s">
         <v>928</v>
-      </c>
-      <c r="B559" t="s">
-        <v>929</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
+        <v>929</v>
+      </c>
+      <c r="B560" t="s">
         <v>930</v>
-      </c>
-      <c r="B560" t="s">
-        <v>931</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
+        <v>931</v>
+      </c>
+      <c r="B561" t="s">
         <v>932</v>
-      </c>
-      <c r="B561" t="s">
-        <v>933</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
+        <v>933</v>
+      </c>
+      <c r="B562" t="s">
         <v>934</v>
-      </c>
-      <c r="B562" t="s">
-        <v>935</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
+        <v>935</v>
+      </c>
+      <c r="B563" t="s">
         <v>936</v>
-      </c>
-      <c r="B563" t="s">
-        <v>937</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
+        <v>937</v>
+      </c>
+      <c r="B564" t="s">
         <v>938</v>
-      </c>
-      <c r="B564" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B565" t="s">
         <v>940</v>
@@ -10699,20 +10699,20 @@
         <v>942</v>
       </c>
       <c r="B567" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
+        <v>943</v>
+      </c>
+      <c r="B568" t="s">
         <v>944</v>
-      </c>
-      <c r="B568" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B569" t="s">
         <v>946</v>
@@ -10723,20 +10723,20 @@
         <v>947</v>
       </c>
       <c r="B570" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
+        <v>948</v>
+      </c>
+      <c r="B571" t="s">
         <v>949</v>
-      </c>
-      <c r="B571" t="s">
-        <v>950</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B572" t="s">
         <v>951</v>
@@ -10747,28 +10747,28 @@
         <v>952</v>
       </c>
       <c r="B573" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
+        <v>953</v>
+      </c>
+      <c r="B574" t="s">
         <v>954</v>
-      </c>
-      <c r="B574" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
+        <v>955</v>
+      </c>
+      <c r="B575" t="s">
         <v>956</v>
-      </c>
-      <c r="B575" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B576" t="s">
         <v>958</v>
@@ -10779,12 +10779,12 @@
         <v>959</v>
       </c>
       <c r="B577" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B578" t="s">
         <v>961</v>
@@ -10795,12 +10795,12 @@
         <v>962</v>
       </c>
       <c r="B579" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B580" t="s">
         <v>964</v>
@@ -10819,20 +10819,20 @@
         <v>966</v>
       </c>
       <c r="B582" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
+        <v>967</v>
+      </c>
+      <c r="B583" t="s">
         <v>968</v>
-      </c>
-      <c r="B583" t="s">
-        <v>969</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B584" t="s">
         <v>970</v>
@@ -10851,12 +10851,12 @@
         <v>972</v>
       </c>
       <c r="B586" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B587" t="s">
         <v>974</v>
@@ -10867,12 +10867,12 @@
         <v>975</v>
       </c>
       <c r="B588" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B589" t="s">
         <v>977</v>
@@ -10883,20 +10883,20 @@
         <v>978</v>
       </c>
       <c r="B590" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
+        <v>979</v>
+      </c>
+      <c r="B591" t="s">
         <v>980</v>
-      </c>
-      <c r="B591" t="s">
-        <v>981</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B592" t="s">
         <v>982</v>
@@ -10907,52 +10907,52 @@
         <v>983</v>
       </c>
       <c r="B593" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
+        <v>984</v>
+      </c>
+      <c r="B594" t="s">
         <v>985</v>
-      </c>
-      <c r="B594" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
+        <v>986</v>
+      </c>
+      <c r="B595" t="s">
         <v>987</v>
-      </c>
-      <c r="B595" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
+        <v>988</v>
+      </c>
+      <c r="B596" t="s">
         <v>989</v>
-      </c>
-      <c r="B596" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
+        <v>990</v>
+      </c>
+      <c r="B597" t="s">
         <v>991</v>
-      </c>
-      <c r="B597" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
+        <v>992</v>
+      </c>
+      <c r="B598" t="s">
         <v>993</v>
-      </c>
-      <c r="B598" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="B599" t="s">
         <v>995</v>
@@ -10963,68 +10963,68 @@
         <v>996</v>
       </c>
       <c r="B600" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
+        <v>997</v>
+      </c>
+      <c r="B601" t="s">
         <v>998</v>
-      </c>
-      <c r="B601" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
+        <v>999</v>
+      </c>
+      <c r="B602" t="s">
         <v>1000</v>
-      </c>
-      <c r="B602" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B603" t="s">
         <v>1002</v>
-      </c>
-      <c r="B603" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B604" t="s">
         <v>1004</v>
-      </c>
-      <c r="B604" t="s">
-        <v>1005</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B605" t="s">
         <v>1006</v>
-      </c>
-      <c r="B605" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B606" t="s">
         <v>1008</v>
-      </c>
-      <c r="B606" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B607" t="s">
         <v>1010</v>
-      </c>
-      <c r="B607" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B608" t="s">
         <v>1012</v>
@@ -11035,20 +11035,20 @@
         <v>1013</v>
       </c>
       <c r="B609" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B610" t="s">
         <v>1015</v>
-      </c>
-      <c r="B610" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B611" t="s">
         <v>1017</v>
@@ -11059,44 +11059,44 @@
         <v>1018</v>
       </c>
       <c r="B612" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B613" t="s">
         <v>1020</v>
-      </c>
-      <c r="B613" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B614" t="s">
         <v>1022</v>
-      </c>
-      <c r="B614" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B615" t="s">
         <v>1024</v>
-      </c>
-      <c r="B615" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B616" t="s">
         <v>1026</v>
-      </c>
-      <c r="B616" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B617" t="s">
         <v>1028</v>
@@ -11123,12 +11123,12 @@
         <v>1031</v>
       </c>
       <c r="B620" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B621" t="s">
         <v>1033</v>
@@ -11139,28 +11139,28 @@
         <v>1034</v>
       </c>
       <c r="B622" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B623" t="s">
         <v>1036</v>
-      </c>
-      <c r="B623" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B624" t="s">
         <v>1038</v>
-      </c>
-      <c r="B624" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B625" t="s">
         <v>1040</v>
@@ -11171,36 +11171,36 @@
         <v>1041</v>
       </c>
       <c r="B626" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B627" t="s">
         <v>1043</v>
-      </c>
-      <c r="B627" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B628" t="s">
         <v>1045</v>
-      </c>
-      <c r="B628" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B629" t="s">
         <v>1047</v>
-      </c>
-      <c r="B629" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B630" t="s">
         <v>1049</v>
@@ -11275,12 +11275,12 @@
         <v>1058</v>
       </c>
       <c r="B639" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B640" t="s">
         <v>1060</v>
@@ -11299,12 +11299,12 @@
         <v>1062</v>
       </c>
       <c r="B642" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B643" t="s">
         <v>1064</v>
@@ -11331,12 +11331,12 @@
         <v>1067</v>
       </c>
       <c r="B646" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B647" t="s">
         <v>1069</v>
@@ -11371,36 +11371,36 @@
         <v>1073</v>
       </c>
       <c r="B651" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B652" t="s">
         <v>1075</v>
-      </c>
-      <c r="B652" t="s">
-        <v>1076</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B653" t="s">
         <v>1077</v>
-      </c>
-      <c r="B653" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B654" t="s">
         <v>1079</v>
-      </c>
-      <c r="B654" t="s">
-        <v>1080</v>
       </c>
     </row>
     <row r="655" spans="1:2">
       <c r="A655" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B655" t="s">
         <v>1081</v>
@@ -11419,20 +11419,20 @@
         <v>1083</v>
       </c>
       <c r="B657" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B658" t="s">
         <v>1085</v>
-      </c>
-      <c r="B658" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B659" t="s">
         <v>1087</v>
@@ -11451,20 +11451,20 @@
         <v>1089</v>
       </c>
       <c r="B661" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B662" t="s">
         <v>1091</v>
-      </c>
-      <c r="B662" t="s">
-        <v>1092</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B663" t="s">
         <v>1093</v>
@@ -11475,12 +11475,12 @@
         <v>1094</v>
       </c>
       <c r="B664" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B665" t="s">
         <v>1096</v>
@@ -11499,36 +11499,36 @@
         <v>1098</v>
       </c>
       <c r="B667" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B668" t="s">
         <v>1100</v>
-      </c>
-      <c r="B668" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B669" t="s">
         <v>1102</v>
-      </c>
-      <c r="B669" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B670" t="s">
         <v>1104</v>
-      </c>
-      <c r="B670" t="s">
-        <v>1105</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B671" t="s">
         <v>1106</v>
@@ -11571,20 +11571,20 @@
         <v>1111</v>
       </c>
       <c r="B676" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B677" t="s">
         <v>1113</v>
-      </c>
-      <c r="B677" t="s">
-        <v>1114</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B678" t="s">
         <v>1115</v>
@@ -11595,20 +11595,20 @@
         <v>1116</v>
       </c>
       <c r="B679" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B680" t="s">
         <v>1118</v>
-      </c>
-      <c r="B680" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B681" t="s">
         <v>1120</v>
@@ -11619,12 +11619,12 @@
         <v>1121</v>
       </c>
       <c r="B682" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B683" t="s">
         <v>1123</v>
@@ -11643,28 +11643,28 @@
         <v>1125</v>
       </c>
       <c r="B685" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B686" t="s">
         <v>1127</v>
-      </c>
-      <c r="B686" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B687" t="s">
         <v>1129</v>
-      </c>
-      <c r="B687" t="s">
-        <v>1130</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B688" t="s">
         <v>1131</v>
@@ -11683,84 +11683,84 @@
         <v>1133</v>
       </c>
       <c r="B690" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B691" t="s">
         <v>1135</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B692" t="s">
         <v>1137</v>
-      </c>
-      <c r="B692" t="s">
-        <v>1138</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B693" t="s">
         <v>1139</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B694" t="s">
         <v>1141</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B695" t="s">
         <v>1143</v>
-      </c>
-      <c r="B695" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="696" spans="1:2">
       <c r="A696" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B696" t="s">
         <v>1145</v>
-      </c>
-      <c r="B696" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="697" spans="1:2">
       <c r="A697" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B697" t="s">
         <v>1147</v>
-      </c>
-      <c r="B697" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="698" spans="1:2">
       <c r="A698" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B698" t="s">
         <v>1149</v>
-      </c>
-      <c r="B698" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B699" t="s">
         <v>1151</v>
-      </c>
-      <c r="B699" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="700" spans="1:2">
       <c r="A700" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="B700" t="s">
         <v>1153</v>
@@ -11771,44 +11771,44 @@
         <v>1154</v>
       </c>
       <c r="B701" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B702" t="s">
         <v>1156</v>
-      </c>
-      <c r="B702" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B703" t="s">
         <v>1158</v>
-      </c>
-      <c r="B703" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B704" t="s">
         <v>1160</v>
-      </c>
-      <c r="B704" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B705" t="s">
         <v>1162</v>
-      </c>
-      <c r="B705" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B706" t="s">
         <v>1164</v>
@@ -11819,12 +11819,12 @@
         <v>1165</v>
       </c>
       <c r="B707" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B708" t="s">
         <v>1167</v>
@@ -11843,12 +11843,12 @@
         <v>1169</v>
       </c>
       <c r="B710" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B711" t="s">
         <v>1171</v>
@@ -11875,12 +11875,12 @@
         <v>1174</v>
       </c>
       <c r="B714" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B715" t="s">
         <v>1176</v>
@@ -11907,12 +11907,12 @@
         <v>1179</v>
       </c>
       <c r="B718" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B719" t="s">
         <v>1181</v>
@@ -11923,60 +11923,60 @@
         <v>1182</v>
       </c>
       <c r="B720" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B721" t="s">
         <v>1184</v>
-      </c>
-      <c r="B721" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B722" t="s">
         <v>1186</v>
-      </c>
-      <c r="B722" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B723" t="s">
         <v>1188</v>
-      </c>
-      <c r="B723" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B724" t="s">
         <v>1190</v>
-      </c>
-      <c r="B724" t="s">
-        <v>1191</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B725" t="s">
         <v>1192</v>
-      </c>
-      <c r="B725" t="s">
-        <v>1193</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B726" t="s">
         <v>1194</v>
-      </c>
-      <c r="B726" t="s">
-        <v>1195</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B727" t="s">
         <v>1196</v>
@@ -11987,76 +11987,76 @@
         <v>1197</v>
       </c>
       <c r="B728" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B729" t="s">
         <v>1199</v>
-      </c>
-      <c r="B729" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B730" t="s">
         <v>1201</v>
-      </c>
-      <c r="B730" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B731" t="s">
         <v>1203</v>
-      </c>
-      <c r="B731" t="s">
-        <v>1204</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B732" t="s">
         <v>1205</v>
-      </c>
-      <c r="B732" t="s">
-        <v>1206</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B733" t="s">
         <v>1207</v>
-      </c>
-      <c r="B733" t="s">
-        <v>1208</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B734" t="s">
         <v>1209</v>
-      </c>
-      <c r="B734" t="s">
-        <v>1210</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B735" t="s">
         <v>1211</v>
-      </c>
-      <c r="B735" t="s">
-        <v>1212</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B736" t="s">
         <v>1213</v>
-      </c>
-      <c r="B736" t="s">
-        <v>1214</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B737" t="s">
         <v>1215</v>
@@ -12067,28 +12067,28 @@
         <v>1216</v>
       </c>
       <c r="B738" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B739" t="s">
         <v>1218</v>
-      </c>
-      <c r="B739" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B740" t="s">
         <v>1220</v>
-      </c>
-      <c r="B740" t="s">
-        <v>1221</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B741" t="s">
         <v>1222</v>
@@ -12099,12 +12099,12 @@
         <v>1223</v>
       </c>
       <c r="B742" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B743" t="s">
         <v>1225</v>
@@ -12155,20 +12155,20 @@
         <v>1231</v>
       </c>
       <c r="B749" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B750" t="s">
         <v>1233</v>
-      </c>
-      <c r="B750" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B751" t="s">
         <v>1235</v>
@@ -12203,60 +12203,60 @@
         <v>1239</v>
       </c>
       <c r="B755" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B756" t="s">
         <v>1241</v>
-      </c>
-      <c r="B756" t="s">
-        <v>1242</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B757" t="s">
         <v>1243</v>
-      </c>
-      <c r="B757" t="s">
-        <v>1244</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B758" t="s">
         <v>1245</v>
-      </c>
-      <c r="B758" t="s">
-        <v>1246</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B759" t="s">
         <v>1247</v>
-      </c>
-      <c r="B759" t="s">
-        <v>1248</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B760" t="s">
         <v>1249</v>
-      </c>
-      <c r="B760" t="s">
-        <v>1250</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B761" t="s">
         <v>1251</v>
-      </c>
-      <c r="B761" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="762" spans="1:2">
       <c r="A762" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B762" t="s">
         <v>1253</v>
@@ -12275,12 +12275,12 @@
         <v>1255</v>
       </c>
       <c r="B764" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B765" t="s">
         <v>1257</v>
@@ -12299,12 +12299,12 @@
         <v>1259</v>
       </c>
       <c r="B767" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B768" t="s">
         <v>1261</v>
@@ -12323,44 +12323,44 @@
         <v>1263</v>
       </c>
       <c r="B770" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B771" t="s">
         <v>1265</v>
-      </c>
-      <c r="B771" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B772" t="s">
         <v>1267</v>
-      </c>
-      <c r="B772" t="s">
-        <v>1268</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B773" t="s">
         <v>1269</v>
-      </c>
-      <c r="B773" t="s">
-        <v>1270</v>
       </c>
     </row>
     <row r="774" spans="1:2">
       <c r="A774" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B774" t="s">
         <v>1271</v>
-      </c>
-      <c r="B774" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="775" spans="1:2">
       <c r="A775" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B775" t="s">
         <v>1273</v>
@@ -12371,36 +12371,36 @@
         <v>1274</v>
       </c>
       <c r="B776" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B777" t="s">
         <v>1276</v>
-      </c>
-      <c r="B777" t="s">
-        <v>1277</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B778" t="s">
         <v>1278</v>
-      </c>
-      <c r="B778" t="s">
-        <v>1279</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B779" t="s">
         <v>1280</v>
-      </c>
-      <c r="B779" t="s">
-        <v>1281</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B780" t="s">
         <v>1282</v>
@@ -12411,68 +12411,68 @@
         <v>1283</v>
       </c>
       <c r="B781" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B782" t="s">
         <v>1285</v>
-      </c>
-      <c r="B782" t="s">
-        <v>1286</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B783" t="s">
         <v>1287</v>
-      </c>
-      <c r="B783" t="s">
-        <v>1288</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B784" t="s">
         <v>1289</v>
-      </c>
-      <c r="B784" t="s">
-        <v>1290</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B785" t="s">
         <v>1291</v>
-      </c>
-      <c r="B785" t="s">
-        <v>1292</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B786" t="s">
         <v>1293</v>
-      </c>
-      <c r="B786" t="s">
-        <v>1294</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B787" t="s">
         <v>1295</v>
-      </c>
-      <c r="B787" t="s">
-        <v>1296</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B788" t="s">
         <v>1297</v>
-      </c>
-      <c r="B788" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B789" t="s">
         <v>1299</v>
@@ -12499,20 +12499,20 @@
         <v>1302</v>
       </c>
       <c r="B792" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B793" t="s">
         <v>1304</v>
-      </c>
-      <c r="B793" t="s">
-        <v>1305</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B794" t="s">
         <v>1306</v>
@@ -12523,12 +12523,12 @@
         <v>1307</v>
       </c>
       <c r="B795" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B796" t="s">
         <v>1309</v>
@@ -12587,12 +12587,12 @@
         <v>1316</v>
       </c>
       <c r="B803" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B804" t="s">
         <v>1318</v>
@@ -12619,52 +12619,52 @@
         <v>1321</v>
       </c>
       <c r="B807" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B808" t="s">
         <v>1323</v>
-      </c>
-      <c r="B808" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B809" t="s">
         <v>1325</v>
-      </c>
-      <c r="B809" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B810" t="s">
         <v>1327</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1328</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B811" t="s">
         <v>1329</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B812" t="s">
         <v>1331</v>
-      </c>
-      <c r="B812" t="s">
-        <v>1332</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B813" t="s">
         <v>1333</v>
@@ -12691,84 +12691,84 @@
         <v>1336</v>
       </c>
       <c r="B816" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B817" t="s">
         <v>1338</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1339</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B818" t="s">
         <v>1340</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B819" t="s">
         <v>1342</v>
-      </c>
-      <c r="B819" t="s">
-        <v>1343</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B820" t="s">
         <v>1344</v>
-      </c>
-      <c r="B820" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B821" t="s">
         <v>1346</v>
-      </c>
-      <c r="B821" t="s">
-        <v>1347</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B822" t="s">
         <v>1348</v>
-      </c>
-      <c r="B822" t="s">
-        <v>1349</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B823" t="s">
         <v>1350</v>
-      </c>
-      <c r="B823" t="s">
-        <v>1351</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B824" t="s">
         <v>1352</v>
-      </c>
-      <c r="B824" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B825" t="s">
         <v>1354</v>
-      </c>
-      <c r="B825" t="s">
-        <v>1355</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B826" t="s">
         <v>1356</v>
@@ -12779,20 +12779,20 @@
         <v>1357</v>
       </c>
       <c r="B827" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B828" t="s">
         <v>1359</v>
-      </c>
-      <c r="B828" t="s">
-        <v>1360</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
       <c r="B829" t="s">
         <v>1361</v>
@@ -12811,12 +12811,12 @@
         <v>1363</v>
       </c>
       <c r="B831" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B832" t="s">
         <v>1365</v>
@@ -12827,12 +12827,12 @@
         <v>1366</v>
       </c>
       <c r="B833" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
       <c r="B834" t="s">
         <v>1368</v>
@@ -12859,12 +12859,12 @@
         <v>1371</v>
       </c>
       <c r="B837" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="B838" t="s">
         <v>1373</v>
@@ -12907,36 +12907,36 @@
         <v>1378</v>
       </c>
       <c r="B843" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B844" t="s">
         <v>1380</v>
-      </c>
-      <c r="B844" t="s">
-        <v>1381</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B845" t="s">
         <v>1382</v>
-      </c>
-      <c r="B845" t="s">
-        <v>1383</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B846" t="s">
         <v>1384</v>
-      </c>
-      <c r="B846" t="s">
-        <v>1385</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
       <c r="B847" t="s">
         <v>1386</v>
@@ -12947,20 +12947,20 @@
         <v>1387</v>
       </c>
       <c r="B848" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B849" t="s">
         <v>1389</v>
-      </c>
-      <c r="B849" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B850" t="s">
         <v>1391</v>
@@ -12987,108 +12987,108 @@
         <v>1394</v>
       </c>
       <c r="B853" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B854" t="s">
         <v>1396</v>
-      </c>
-      <c r="B854" t="s">
-        <v>1397</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B855" t="s">
         <v>1398</v>
-      </c>
-      <c r="B855" t="s">
-        <v>1399</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B856" t="s">
         <v>1400</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B857" t="s">
         <v>1402</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B858" t="s">
         <v>1404</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B859" t="s">
         <v>1406</v>
-      </c>
-      <c r="B859" t="s">
-        <v>1407</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B860" t="s">
         <v>1408</v>
-      </c>
-      <c r="B860" t="s">
-        <v>1409</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B861" t="s">
         <v>1410</v>
-      </c>
-      <c r="B861" t="s">
-        <v>1411</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B862" t="s">
         <v>1412</v>
-      </c>
-      <c r="B862" t="s">
-        <v>1413</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B863" t="s">
         <v>1414</v>
-      </c>
-      <c r="B863" t="s">
-        <v>1415</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B864" t="s">
         <v>1416</v>
-      </c>
-      <c r="B864" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B865" t="s">
         <v>1418</v>
-      </c>
-      <c r="B865" t="s">
-        <v>1419</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B866" t="s">
         <v>1420</v>
@@ -13115,12 +13115,12 @@
         <v>1423</v>
       </c>
       <c r="B869" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B870" t="s">
         <v>1425</v>
@@ -13131,12 +13131,12 @@
         <v>1426</v>
       </c>
       <c r="B871" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B872" t="s">
         <v>1428</v>
@@ -13187,36 +13187,36 @@
         <v>1434</v>
       </c>
       <c r="B878" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B879" t="s">
         <v>1436</v>
-      </c>
-      <c r="B879" t="s">
-        <v>1437</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B880" t="s">
         <v>1438</v>
-      </c>
-      <c r="B880" t="s">
-        <v>1439</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B881" t="s">
         <v>1440</v>
-      </c>
-      <c r="B881" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B882" t="s">
         <v>1442</v>
@@ -13227,44 +13227,44 @@
         <v>1443</v>
       </c>
       <c r="B883" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B884" t="s">
         <v>1445</v>
-      </c>
-      <c r="B884" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B885" t="s">
         <v>1447</v>
-      </c>
-      <c r="B885" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B886" t="s">
         <v>1449</v>
-      </c>
-      <c r="B886" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B887" t="s">
         <v>1451</v>
-      </c>
-      <c r="B887" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B888" t="s">
         <v>1453</v>
@@ -13275,28 +13275,28 @@
         <v>1454</v>
       </c>
       <c r="B889" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B890" t="s">
         <v>1456</v>
-      </c>
-      <c r="B890" t="s">
-        <v>1457</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B891" t="s">
         <v>1458</v>
-      </c>
-      <c r="B891" t="s">
-        <v>1459</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="B892" t="s">
         <v>1460</v>
@@ -13315,44 +13315,44 @@
         <v>1462</v>
       </c>
       <c r="B894" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B895" t="s">
         <v>1464</v>
-      </c>
-      <c r="B895" t="s">
-        <v>1465</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B896" t="s">
         <v>1466</v>
-      </c>
-      <c r="B896" t="s">
-        <v>1467</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B897" t="s">
         <v>1468</v>
-      </c>
-      <c r="B897" t="s">
-        <v>1469</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B898" t="s">
         <v>1470</v>
-      </c>
-      <c r="B898" t="s">
-        <v>1471</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B899" t="s">
         <v>1472</v>
@@ -13363,12 +13363,12 @@
         <v>1473</v>
       </c>
       <c r="B900" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B901" t="s">
         <v>1475</v>
@@ -13379,36 +13379,36 @@
         <v>1476</v>
       </c>
       <c r="B902" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B903" t="s">
         <v>1478</v>
-      </c>
-      <c r="B903" t="s">
-        <v>1479</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B904" t="s">
         <v>1480</v>
-      </c>
-      <c r="B904" t="s">
-        <v>1481</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B905" t="s">
         <v>1482</v>
-      </c>
-      <c r="B905" t="s">
-        <v>1483</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B906" t="s">
         <v>1484</v>
@@ -13427,44 +13427,44 @@
         <v>1486</v>
       </c>
       <c r="B908" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B909" t="s">
         <v>1488</v>
-      </c>
-      <c r="B909" t="s">
-        <v>1489</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B910" t="s">
         <v>1490</v>
-      </c>
-      <c r="B910" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B911" t="s">
         <v>1492</v>
-      </c>
-      <c r="B911" t="s">
-        <v>1493</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B912" t="s">
         <v>1494</v>
-      </c>
-      <c r="B912" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="B913" t="s">
         <v>1496</v>
@@ -13515,36 +13515,36 @@
         <v>1502</v>
       </c>
       <c r="B919" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B920" t="s">
         <v>1504</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B921" t="s">
         <v>1506</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B922" t="s">
         <v>1508</v>
-      </c>
-      <c r="B922" t="s">
-        <v>1509</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
       <c r="B923" t="s">
         <v>1510</v>
@@ -13571,44 +13571,44 @@
         <v>1513</v>
       </c>
       <c r="B926" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B927" t="s">
         <v>1515</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B928" t="s">
         <v>1517</v>
-      </c>
-      <c r="B928" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B929" t="s">
         <v>1519</v>
-      </c>
-      <c r="B929" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B930" t="s">
         <v>1521</v>
-      </c>
-      <c r="B930" t="s">
-        <v>1522</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="B931" t="s">
         <v>1523</v>
@@ -13627,36 +13627,36 @@
         <v>1525</v>
       </c>
       <c r="B933" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B934" t="s">
         <v>1527</v>
-      </c>
-      <c r="B934" t="s">
-        <v>1528</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B935" t="s">
         <v>1529</v>
-      </c>
-      <c r="B935" t="s">
-        <v>1530</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B936" t="s">
         <v>1531</v>
-      </c>
-      <c r="B936" t="s">
-        <v>1532</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B937" t="s">
         <v>1533</v>
@@ -13667,20 +13667,20 @@
         <v>1534</v>
       </c>
       <c r="B938" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B939" t="s">
         <v>1536</v>
-      </c>
-      <c r="B939" t="s">
-        <v>1537</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
       <c r="B940" t="s">
         <v>1538</v>
@@ -13691,20 +13691,20 @@
         <v>1539</v>
       </c>
       <c r="B941" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B942" t="s">
         <v>1541</v>
-      </c>
-      <c r="B942" t="s">
-        <v>1542</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="B943" t="s">
         <v>1543</v>
@@ -13715,12 +13715,12 @@
         <v>1544</v>
       </c>
       <c r="B944" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="B945" t="s">
         <v>1546</v>
@@ -13731,20 +13731,20 @@
         <v>1547</v>
       </c>
       <c r="B946" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B947" t="s">
         <v>1549</v>
-      </c>
-      <c r="B947" t="s">
-        <v>1550</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="B948" t="s">
         <v>1551</v>
@@ -13755,20 +13755,20 @@
         <v>1552</v>
       </c>
       <c r="B949" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B950" t="s">
         <v>1554</v>
-      </c>
-      <c r="B950" t="s">
-        <v>1555</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B951" t="s">
         <v>1556</v>
@@ -13795,28 +13795,28 @@
         <v>1559</v>
       </c>
       <c r="B954" t="s">
-        <v>1560</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B955" t="s">
         <v>1561</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1562</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B956" t="s">
         <v>1563</v>
-      </c>
-      <c r="B956" t="s">
-        <v>1564</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B957" t="s">
         <v>1565</v>
@@ -13859,36 +13859,36 @@
         <v>1570</v>
       </c>
       <c r="B962" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B963" t="s">
         <v>1572</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1573</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B964" t="s">
         <v>1574</v>
-      </c>
-      <c r="B964" t="s">
-        <v>1575</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B965" t="s">
         <v>1576</v>
-      </c>
-      <c r="B965" t="s">
-        <v>1577</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1578</v>
+        <v>1577</v>
       </c>
       <c r="B966" t="s">
         <v>1578</v>
@@ -13915,52 +13915,52 @@
         <v>1581</v>
       </c>
       <c r="B969" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B970" t="s">
         <v>1583</v>
-      </c>
-      <c r="B970" t="s">
-        <v>1584</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B971" t="s">
         <v>1585</v>
-      </c>
-      <c r="B971" t="s">
-        <v>1586</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B972" t="s">
         <v>1587</v>
-      </c>
-      <c r="B972" t="s">
-        <v>1588</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B973" t="s">
         <v>1589</v>
-      </c>
-      <c r="B973" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B974" t="s">
         <v>1591</v>
-      </c>
-      <c r="B974" t="s">
-        <v>1592</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B975" t="s">
         <v>1593</v>
@@ -13987,12 +13987,12 @@
         <v>1596</v>
       </c>
       <c r="B978" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="B979" t="s">
         <v>1598</v>
@@ -14011,44 +14011,44 @@
         <v>1600</v>
       </c>
       <c r="B981" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B982" t="s">
         <v>1602</v>
-      </c>
-      <c r="B982" t="s">
-        <v>1603</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B983" t="s">
         <v>1604</v>
-      </c>
-      <c r="B983" t="s">
-        <v>1605</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B984" t="s">
         <v>1606</v>
-      </c>
-      <c r="B984" t="s">
-        <v>1607</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B985" t="s">
         <v>1608</v>
-      </c>
-      <c r="B985" t="s">
-        <v>1609</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="B986" t="s">
         <v>1610</v>
@@ -14059,28 +14059,28 @@
         <v>1611</v>
       </c>
       <c r="B987" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B988" t="s">
         <v>1613</v>
-      </c>
-      <c r="B988" t="s">
-        <v>1614</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B989" t="s">
         <v>1615</v>
-      </c>
-      <c r="B989" t="s">
-        <v>1616</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1617</v>
+        <v>1616</v>
       </c>
       <c r="B990" t="s">
         <v>1617</v>
@@ -14091,20 +14091,20 @@
         <v>1618</v>
       </c>
       <c r="B991" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B992" t="s">
         <v>1620</v>
-      </c>
-      <c r="B992" t="s">
-        <v>1621</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1622</v>
+        <v>1621</v>
       </c>
       <c r="B993" t="s">
         <v>1622</v>
@@ -14139,52 +14139,52 @@
         <v>1626</v>
       </c>
       <c r="B997" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B998" t="s">
         <v>1628</v>
-      </c>
-      <c r="B998" t="s">
-        <v>1629</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B999" t="s">
         <v>1630</v>
-      </c>
-      <c r="B999" t="s">
-        <v>1631</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B1000" t="s">
         <v>1632</v>
-      </c>
-      <c r="B1000" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B1001" t="s">
         <v>1634</v>
-      </c>
-      <c r="B1001" t="s">
-        <v>1635</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B1002" t="s">
         <v>1636</v>
-      </c>
-      <c r="B1002" t="s">
-        <v>1637</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B1003" t="s">
         <v>1638</v>
@@ -14195,20 +14195,20 @@
         <v>1639</v>
       </c>
       <c r="B1004" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B1005" t="s">
         <v>1641</v>
-      </c>
-      <c r="B1005" t="s">
-        <v>1642</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="B1006" t="s">
         <v>1643</v>
@@ -14235,12 +14235,12 @@
         <v>1646</v>
       </c>
       <c r="B1009" t="s">
-        <v>1647</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="B1010" t="s">
         <v>1648</v>
@@ -14251,20 +14251,20 @@
         <v>1649</v>
       </c>
       <c r="B1011" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B1012" t="s">
         <v>1651</v>
-      </c>
-      <c r="B1012" t="s">
-        <v>1652</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="B1013" t="s">
         <v>1653</v>
@@ -14283,28 +14283,28 @@
         <v>1655</v>
       </c>
       <c r="B1015" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B1016" t="s">
         <v>1657</v>
-      </c>
-      <c r="B1016" t="s">
-        <v>1658</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B1017" t="s">
         <v>1659</v>
-      </c>
-      <c r="B1017" t="s">
-        <v>1660</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="B1018" t="s">
         <v>1661</v>
@@ -14315,20 +14315,20 @@
         <v>1662</v>
       </c>
       <c r="B1019" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B1020" t="s">
         <v>1664</v>
-      </c>
-      <c r="B1020" t="s">
-        <v>1665</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="B1021" t="s">
         <v>1666</v>
@@ -14339,20 +14339,20 @@
         <v>1667</v>
       </c>
       <c r="B1022" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B1023" t="s">
         <v>1669</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>1670</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="B1024" t="s">
         <v>1671</v>
@@ -14387,20 +14387,20 @@
         <v>1675</v>
       </c>
       <c r="B1028" t="s">
-        <v>1676</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B1029" t="s">
         <v>1677</v>
-      </c>
-      <c r="B1029" t="s">
-        <v>1678</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="B1030" t="s">
         <v>1679</v>
@@ -14411,28 +14411,28 @@
         <v>1680</v>
       </c>
       <c r="B1031" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
+        <v>1681</v>
+      </c>
+      <c r="B1032" t="s">
         <v>1682</v>
-      </c>
-      <c r="B1032" t="s">
-        <v>1683</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B1033" t="s">
         <v>1684</v>
-      </c>
-      <c r="B1033" t="s">
-        <v>1685</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="B1034" t="s">
         <v>1686</v>
@@ -14443,12 +14443,12 @@
         <v>1687</v>
       </c>
       <c r="B1035" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="B1036" t="s">
         <v>1689</v>
@@ -14467,12 +14467,12 @@
         <v>1691</v>
       </c>
       <c r="B1038" t="s">
-        <v>1692</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1693</v>
+        <v>1692</v>
       </c>
       <c r="B1039" t="s">
         <v>1693</v>
@@ -14483,12 +14483,12 @@
         <v>1694</v>
       </c>
       <c r="B1040" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="B1041" t="s">
         <v>1696</v>
@@ -14507,12 +14507,12 @@
         <v>1698</v>
       </c>
       <c r="B1043" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="B1044" t="s">
         <v>1700</v>
@@ -14531,12 +14531,12 @@
         <v>1702</v>
       </c>
       <c r="B1046" t="s">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="B1047" t="s">
         <v>1704</v>
@@ -14547,36 +14547,36 @@
         <v>1705</v>
       </c>
       <c r="B1048" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B1049" t="s">
         <v>1707</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>1708</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
+        <v>1708</v>
+      </c>
+      <c r="B1050" t="s">
         <v>1709</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>1710</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B1051" t="s">
         <v>1711</v>
-      </c>
-      <c r="B1051" t="s">
-        <v>1712</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="B1052" t="s">
         <v>1713</v>
@@ -14587,12 +14587,12 @@
         <v>1714</v>
       </c>
       <c r="B1053" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="B1054" t="s">
         <v>1716</v>
@@ -14603,44 +14603,44 @@
         <v>1717</v>
       </c>
       <c r="B1055" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B1056" t="s">
         <v>1719</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>1720</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B1057" t="s">
         <v>1721</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>1722</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B1058" t="s">
         <v>1723</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>1724</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>1724</v>
+      </c>
+      <c r="B1059" t="s">
         <v>1725</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1726</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="B1060" t="s">
         <v>1727</v>
@@ -14675,52 +14675,52 @@
         <v>1731</v>
       </c>
       <c r="B1064" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B1065" t="s">
         <v>1733</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>1734</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B1066" t="s">
         <v>1735</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>1736</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B1067" t="s">
         <v>1737</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>1738</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B1068" t="s">
         <v>1739</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>1740</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B1069" t="s">
         <v>1741</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>1742</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B1070" t="s">
         <v>1743</v>
@@ -14731,12 +14731,12 @@
         <v>1744</v>
       </c>
       <c r="B1071" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="B1072" t="s">
         <v>1746</v>
@@ -14755,52 +14755,52 @@
         <v>1748</v>
       </c>
       <c r="B1074" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B1075" t="s">
         <v>1750</v>
-      </c>
-      <c r="B1075" t="s">
-        <v>1751</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
+        <v>1751</v>
+      </c>
+      <c r="B1076" t="s">
         <v>1752</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B1077" t="s">
         <v>1754</v>
-      </c>
-      <c r="B1077" t="s">
-        <v>1755</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B1078" t="s">
         <v>1756</v>
-      </c>
-      <c r="B1078" t="s">
-        <v>1757</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B1079" t="s">
         <v>1758</v>
-      </c>
-      <c r="B1079" t="s">
-        <v>1759</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="B1080" t="s">
         <v>1760</v>
@@ -14811,12 +14811,12 @@
         <v>1761</v>
       </c>
       <c r="B1081" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="B1082" t="s">
         <v>1763</v>
@@ -14835,12 +14835,12 @@
         <v>1765</v>
       </c>
       <c r="B1084" t="s">
-        <v>1766</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B1085" t="s">
         <v>1767</v>
@@ -14851,12 +14851,12 @@
         <v>1768</v>
       </c>
       <c r="B1086" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="B1087" t="s">
         <v>1770</v>
@@ -14891,20 +14891,20 @@
         <v>1774</v>
       </c>
       <c r="B1091" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
+        <v>1775</v>
+      </c>
+      <c r="B1092" t="s">
         <v>1776</v>
-      </c>
-      <c r="B1092" t="s">
-        <v>1777</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="B1093" t="s">
         <v>1778</v>
@@ -14923,20 +14923,20 @@
         <v>1780</v>
       </c>
       <c r="B1095" t="s">
-        <v>1781</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
+        <v>1781</v>
+      </c>
+      <c r="B1096" t="s">
         <v>1782</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>1783</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1784</v>
+        <v>1783</v>
       </c>
       <c r="B1097" t="s">
         <v>1784</v>
@@ -14947,36 +14947,36 @@
         <v>1785</v>
       </c>
       <c r="B1098" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
+        <v>1786</v>
+      </c>
+      <c r="B1099" t="s">
         <v>1787</v>
-      </c>
-      <c r="B1099" t="s">
-        <v>1788</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
+        <v>1788</v>
+      </c>
+      <c r="B1100" t="s">
         <v>1789</v>
-      </c>
-      <c r="B1100" t="s">
-        <v>1790</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>1790</v>
+      </c>
+      <c r="B1101" t="s">
         <v>1791</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>1792</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="B1102" t="s">
         <v>1793</v>
@@ -14995,44 +14995,44 @@
         <v>1795</v>
       </c>
       <c r="B1104" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>1796</v>
+      </c>
+      <c r="B1105" t="s">
         <v>1797</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>1798</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
+        <v>1798</v>
+      </c>
+      <c r="B1106" t="s">
         <v>1799</v>
-      </c>
-      <c r="B1106" t="s">
-        <v>1800</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
+        <v>1800</v>
+      </c>
+      <c r="B1107" t="s">
         <v>1801</v>
-      </c>
-      <c r="B1107" t="s">
-        <v>1802</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
+        <v>1802</v>
+      </c>
+      <c r="B1108" t="s">
         <v>1803</v>
-      </c>
-      <c r="B1108" t="s">
-        <v>1804</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1805</v>
+        <v>1804</v>
       </c>
       <c r="B1109" t="s">
         <v>1805</v>
@@ -15043,20 +15043,20 @@
         <v>1806</v>
       </c>
       <c r="B1110" t="s">
-        <v>1807</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
+        <v>1807</v>
+      </c>
+      <c r="B1111" t="s">
         <v>1808</v>
-      </c>
-      <c r="B1111" t="s">
-        <v>1809</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1810</v>
+        <v>1809</v>
       </c>
       <c r="B1112" t="s">
         <v>1810</v>
@@ -15075,12 +15075,12 @@
         <v>1812</v>
       </c>
       <c r="B1114" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="B1115" t="s">
         <v>1814</v>
@@ -15099,20 +15099,20 @@
         <v>1816</v>
       </c>
       <c r="B1117" t="s">
-        <v>1817</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
+        <v>1817</v>
+      </c>
+      <c r="B1118" t="s">
         <v>1818</v>
-      </c>
-      <c r="B1118" t="s">
-        <v>1819</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="B1119" t="s">
         <v>1820</v>
@@ -15123,28 +15123,28 @@
         <v>1821</v>
       </c>
       <c r="B1120" t="s">
-        <v>1822</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>1822</v>
+      </c>
+      <c r="B1121" t="s">
         <v>1823</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>1824</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>1824</v>
+      </c>
+      <c r="B1122" t="s">
         <v>1825</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>1826</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="B1123" t="s">
         <v>1827</v>
@@ -15155,44 +15155,44 @@
         <v>1828</v>
       </c>
       <c r="B1124" t="s">
-        <v>1829</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1829</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1830</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1831</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1831</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1832</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1833</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1833</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1834</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1835</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1836</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1837</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
-        <v>1838</v>
+        <v>1837</v>
       </c>
       <c r="B1129" t="s">
         <v>1838</v>
@@ -15203,108 +15203,108 @@
         <v>1839</v>
       </c>
       <c r="B1130" t="s">
-        <v>1840</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1840</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1841</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1842</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1842</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1843</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1844</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1844</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1845</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1846</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1847</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1848</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>1848</v>
+      </c>
+      <c r="B1135" t="s">
         <v>1849</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>1850</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B1136" t="s">
         <v>1851</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>1852</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>1852</v>
+      </c>
+      <c r="B1137" t="s">
         <v>1853</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>1854</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1855</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1856</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>1856</v>
+      </c>
+      <c r="B1139" t="s">
         <v>1857</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>1858</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B1140" t="s">
         <v>1859</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>1860</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B1141" t="s">
         <v>1861</v>
-      </c>
-      <c r="B1141" t="s">
-        <v>1862</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B1142" t="s">
         <v>1863</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>1864</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="B1143" t="s">
         <v>1865</v>
@@ -15347,20 +15347,20 @@
         <v>1870</v>
       </c>
       <c r="B1148" t="s">
-        <v>1871</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B1149" t="s">
         <v>1872</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>1873</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="B1150" t="s">
         <v>1874</v>
@@ -15387,68 +15387,68 @@
         <v>1877</v>
       </c>
       <c r="B1153" t="s">
-        <v>1878</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B1154" t="s">
         <v>1879</v>
-      </c>
-      <c r="B1154" t="s">
-        <v>1880</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B1155" t="s">
         <v>1881</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>1882</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B1156" t="s">
         <v>1883</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>1884</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B1157" t="s">
         <v>1885</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>1886</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B1158" t="s">
         <v>1887</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>1888</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B1159" t="s">
         <v>1889</v>
-      </c>
-      <c r="B1159" t="s">
-        <v>1890</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B1160" t="s">
         <v>1891</v>
-      </c>
-      <c r="B1160" t="s">
-        <v>1892</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="B1161" t="s">
         <v>1893</v>
@@ -15459,12 +15459,12 @@
         <v>1894</v>
       </c>
       <c r="B1162" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B1163" t="s">
         <v>1896</v>
@@ -15475,36 +15475,36 @@
         <v>1897</v>
       </c>
       <c r="B1164" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B1165" t="s">
         <v>1899</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>1900</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B1166" t="s">
         <v>1901</v>
-      </c>
-      <c r="B1166" t="s">
-        <v>1902</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B1167" t="s">
         <v>1903</v>
-      </c>
-      <c r="B1167" t="s">
-        <v>1904</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B1168" t="s">
         <v>1905</v>
@@ -15547,20 +15547,20 @@
         <v>1910</v>
       </c>
       <c r="B1173" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B1174" t="s">
         <v>1912</v>
-      </c>
-      <c r="B1174" t="s">
-        <v>1913</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B1175" t="s">
         <v>1914</v>
@@ -15579,12 +15579,12 @@
         <v>1916</v>
       </c>
       <c r="B1177" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="B1178" t="s">
         <v>1918</v>
@@ -15627,12 +15627,12 @@
         <v>1923</v>
       </c>
       <c r="B1183" t="s">
-        <v>1924</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1925</v>
+        <v>1924</v>
       </c>
       <c r="B1184" t="s">
         <v>1925</v>
@@ -15667,12 +15667,12 @@
         <v>1929</v>
       </c>
       <c r="B1188" t="s">
-        <v>1930</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="B1189" t="s">
         <v>1931</v>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1934">
   <si>
     <t>en</t>
   </si>
@@ -4322,6 +4322,12 @@
   </si>
   <si>
     <t>Predator</t>
+  </si>
+  <si>
+    <t>Prehistoric Creature</t>
+  </si>
+  <si>
+    <t>Makhluk Pra-sejarah</t>
   </si>
   <si>
     <t>Present</t>
@@ -6159,7 +6165,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1189"/>
+  <dimension ref="A1:B1190"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13227,12 +13233,12 @@
         <v>1443</v>
       </c>
       <c r="B883" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B884" t="s">
         <v>1445</v>
@@ -13275,12 +13281,12 @@
         <v>1454</v>
       </c>
       <c r="B889" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B890" t="s">
         <v>1456</v>
@@ -13307,20 +13313,20 @@
         <v>1461</v>
       </c>
       <c r="B893" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B894" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B895" t="s">
         <v>1464</v>
@@ -13363,12 +13369,12 @@
         <v>1473</v>
       </c>
       <c r="B900" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B901" t="s">
         <v>1475</v>
@@ -13379,12 +13385,12 @@
         <v>1476</v>
       </c>
       <c r="B902" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B903" t="s">
         <v>1478</v>
@@ -13419,20 +13425,20 @@
         <v>1485</v>
       </c>
       <c r="B907" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B908" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B909" t="s">
         <v>1488</v>
@@ -13475,52 +13481,52 @@
         <v>1497</v>
       </c>
       <c r="B914" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B915" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B916" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B917" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B918" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B919" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B920" t="s">
         <v>1504</v>
@@ -13555,28 +13561,28 @@
         <v>1511</v>
       </c>
       <c r="B924" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B925" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B926" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B927" t="s">
         <v>1515</v>
@@ -13619,20 +13625,20 @@
         <v>1524</v>
       </c>
       <c r="B932" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B933" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B934" t="s">
         <v>1527</v>
@@ -13667,12 +13673,12 @@
         <v>1534</v>
       </c>
       <c r="B938" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B939" t="s">
         <v>1536</v>
@@ -13691,12 +13697,12 @@
         <v>1539</v>
       </c>
       <c r="B941" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B942" t="s">
         <v>1541</v>
@@ -13715,12 +13721,12 @@
         <v>1544</v>
       </c>
       <c r="B944" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B945" t="s">
         <v>1546</v>
@@ -13731,12 +13737,12 @@
         <v>1547</v>
       </c>
       <c r="B946" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B947" t="s">
         <v>1549</v>
@@ -13755,12 +13761,12 @@
         <v>1552</v>
       </c>
       <c r="B949" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B950" t="s">
         <v>1554</v>
@@ -13779,28 +13785,28 @@
         <v>1557</v>
       </c>
       <c r="B952" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B953" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B954" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B955" t="s">
         <v>1561</v>
@@ -13827,44 +13833,44 @@
         <v>1566</v>
       </c>
       <c r="B958" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B959" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B960" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B961" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B962" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B963" t="s">
         <v>1572</v>
@@ -13899,28 +13905,28 @@
         <v>1579</v>
       </c>
       <c r="B967" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B968" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B969" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B970" t="s">
         <v>1583</v>
@@ -13971,28 +13977,28 @@
         <v>1594</v>
       </c>
       <c r="B976" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B977" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B978" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B979" t="s">
         <v>1598</v>
@@ -14003,20 +14009,20 @@
         <v>1599</v>
       </c>
       <c r="B980" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B981" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B982" t="s">
         <v>1602</v>
@@ -14059,12 +14065,12 @@
         <v>1611</v>
       </c>
       <c r="B987" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B988" t="s">
         <v>1613</v>
@@ -14091,12 +14097,12 @@
         <v>1618</v>
       </c>
       <c r="B991" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B992" t="s">
         <v>1620</v>
@@ -14115,36 +14121,36 @@
         <v>1623</v>
       </c>
       <c r="B994" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B995" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B996" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B997" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B998" t="s">
         <v>1628</v>
@@ -14195,12 +14201,12 @@
         <v>1639</v>
       </c>
       <c r="B1004" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B1005" t="s">
         <v>1641</v>
@@ -14219,28 +14225,28 @@
         <v>1644</v>
       </c>
       <c r="B1007" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B1008" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B1009" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B1010" t="s">
         <v>1648</v>
@@ -14251,12 +14257,12 @@
         <v>1649</v>
       </c>
       <c r="B1011" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B1012" t="s">
         <v>1651</v>
@@ -14275,20 +14281,20 @@
         <v>1654</v>
       </c>
       <c r="B1014" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B1015" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B1016" t="s">
         <v>1657</v>
@@ -14315,12 +14321,12 @@
         <v>1662</v>
       </c>
       <c r="B1019" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B1020" t="s">
         <v>1664</v>
@@ -14339,12 +14345,12 @@
         <v>1667</v>
       </c>
       <c r="B1022" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B1023" t="s">
         <v>1669</v>
@@ -14363,36 +14369,36 @@
         <v>1672</v>
       </c>
       <c r="B1025" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1026" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B1027" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1028" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B1029" t="s">
         <v>1677</v>
@@ -14411,12 +14417,12 @@
         <v>1680</v>
       </c>
       <c r="B1031" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1032" t="s">
         <v>1682</v>
@@ -14443,12 +14449,12 @@
         <v>1687</v>
       </c>
       <c r="B1035" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1036" t="s">
         <v>1689</v>
@@ -14459,20 +14465,20 @@
         <v>1690</v>
       </c>
       <c r="B1037" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1038" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1039" t="s">
         <v>1693</v>
@@ -14483,12 +14489,12 @@
         <v>1694</v>
       </c>
       <c r="B1040" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1041" t="s">
         <v>1696</v>
@@ -14499,20 +14505,20 @@
         <v>1697</v>
       </c>
       <c r="B1042" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1043" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1044" t="s">
         <v>1700</v>
@@ -14523,20 +14529,20 @@
         <v>1701</v>
       </c>
       <c r="B1045" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1046" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1047" t="s">
         <v>1704</v>
@@ -14547,12 +14553,12 @@
         <v>1705</v>
       </c>
       <c r="B1048" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1049" t="s">
         <v>1707</v>
@@ -14587,12 +14593,12 @@
         <v>1714</v>
       </c>
       <c r="B1053" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1054" t="s">
         <v>1716</v>
@@ -14603,12 +14609,12 @@
         <v>1717</v>
       </c>
       <c r="B1055" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B1056" t="s">
         <v>1719</v>
@@ -14651,36 +14657,36 @@
         <v>1728</v>
       </c>
       <c r="B1061" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="B1062" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="B1063" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B1064" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B1065" t="s">
         <v>1733</v>
@@ -14731,12 +14737,12 @@
         <v>1744</v>
       </c>
       <c r="B1071" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="B1072" t="s">
         <v>1746</v>
@@ -14747,20 +14753,20 @@
         <v>1747</v>
       </c>
       <c r="B1073" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="B1074" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B1075" t="s">
         <v>1750</v>
@@ -14811,12 +14817,12 @@
         <v>1761</v>
       </c>
       <c r="B1081" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="B1082" t="s">
         <v>1763</v>
@@ -14827,20 +14833,20 @@
         <v>1764</v>
       </c>
       <c r="B1083" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="B1084" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B1085" t="s">
         <v>1767</v>
@@ -14851,12 +14857,12 @@
         <v>1768</v>
       </c>
       <c r="B1086" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B1087" t="s">
         <v>1770</v>
@@ -14867,36 +14873,36 @@
         <v>1771</v>
       </c>
       <c r="B1088" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B1089" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B1090" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B1091" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B1092" t="s">
         <v>1776</v>
@@ -14915,20 +14921,20 @@
         <v>1779</v>
       </c>
       <c r="B1094" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B1095" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B1096" t="s">
         <v>1782</v>
@@ -14947,12 +14953,12 @@
         <v>1785</v>
       </c>
       <c r="B1098" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B1099" t="s">
         <v>1787</v>
@@ -14987,20 +14993,20 @@
         <v>1794</v>
       </c>
       <c r="B1103" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="B1104" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="B1105" t="s">
         <v>1797</v>
@@ -15043,12 +15049,12 @@
         <v>1806</v>
       </c>
       <c r="B1110" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="B1111" t="s">
         <v>1808</v>
@@ -15067,20 +15073,20 @@
         <v>1811</v>
       </c>
       <c r="B1113" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="B1114" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B1115" t="s">
         <v>1814</v>
@@ -15091,20 +15097,20 @@
         <v>1815</v>
       </c>
       <c r="B1116" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B1117" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B1118" t="s">
         <v>1818</v>
@@ -15123,12 +15129,12 @@
         <v>1821</v>
       </c>
       <c r="B1120" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B1121" t="s">
         <v>1823</v>
@@ -15155,12 +15161,12 @@
         <v>1828</v>
       </c>
       <c r="B1124" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="B1125" t="s">
         <v>1830</v>
@@ -15203,12 +15209,12 @@
         <v>1839</v>
       </c>
       <c r="B1130" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="B1131" t="s">
         <v>1841</v>
@@ -15315,44 +15321,44 @@
         <v>1866</v>
       </c>
       <c r="B1144" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="B1145" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="B1146" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B1147" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B1148" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B1149" t="s">
         <v>1872</v>
@@ -15371,28 +15377,28 @@
         <v>1875</v>
       </c>
       <c r="B1151" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B1152" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B1153" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B1154" t="s">
         <v>1879</v>
@@ -15459,12 +15465,12 @@
         <v>1894</v>
       </c>
       <c r="B1162" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="B1163" t="s">
         <v>1896</v>
@@ -15475,12 +15481,12 @@
         <v>1897</v>
       </c>
       <c r="B1164" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="B1165" t="s">
         <v>1899</v>
@@ -15515,44 +15521,44 @@
         <v>1906</v>
       </c>
       <c r="B1169" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="B1170" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="B1171" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B1172" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B1173" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B1174" t="s">
         <v>1912</v>
@@ -15571,20 +15577,20 @@
         <v>1915</v>
       </c>
       <c r="B1176" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B1177" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="B1178" t="s">
         <v>1918</v>
@@ -15595,44 +15601,44 @@
         <v>1919</v>
       </c>
       <c r="B1179" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="B1180" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B1181" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B1182" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B1183" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B1184" t="s">
         <v>1925</v>
@@ -15643,43 +15649,51 @@
         <v>1926</v>
       </c>
       <c r="B1185" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1186" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="B1187" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B1188" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B1189" t="s">
         <v>1931</v>
       </c>
     </row>
+    <row r="1190" spans="1:2">
+      <c r="A1190" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B1190" t="s">
+        <v>1933</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1189"/>
+  <autoFilter ref="A1:B1190"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1190</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1936">
   <si>
     <t>en</t>
   </si>
@@ -347,6 +347,12 @@
   </si>
   <si>
     <t>Kembali ke Masa Depan</t>
+  </si>
+  <si>
+    <t>Backrooms (Movie)</t>
+  </si>
+  <si>
+    <t>Backrooms (Film)</t>
   </si>
   <si>
     <t>Bag</t>
@@ -6165,7 +6171,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1190"/>
+  <dimension ref="A1:B1191"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -6721,12 +6727,12 @@
         <v>114</v>
       </c>
       <c r="B69" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B70" t="s">
         <v>116</v>
@@ -6745,44 +6751,44 @@
         <v>119</v>
       </c>
       <c r="B72" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B73" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B74" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B75" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B76" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B77" t="s">
         <v>125</v>
@@ -6809,12 +6815,12 @@
         <v>130</v>
       </c>
       <c r="B80" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B81" t="s">
         <v>132</v>
@@ -6825,12 +6831,12 @@
         <v>133</v>
       </c>
       <c r="B82" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B83" t="s">
         <v>135</v>
@@ -6857,20 +6863,20 @@
         <v>140</v>
       </c>
       <c r="B86" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B87" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B88" t="s">
         <v>143</v>
@@ -6905,12 +6911,12 @@
         <v>150</v>
       </c>
       <c r="B92" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B93" t="s">
         <v>152</v>
@@ -6921,12 +6927,12 @@
         <v>153</v>
       </c>
       <c r="B94" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B95" t="s">
         <v>155</v>
@@ -6945,28 +6951,28 @@
         <v>158</v>
       </c>
       <c r="B97" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B98" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B99" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B100" t="s">
         <v>162</v>
@@ -6985,12 +6991,12 @@
         <v>165</v>
       </c>
       <c r="B102" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B103" t="s">
         <v>167</v>
@@ -7001,12 +7007,12 @@
         <v>168</v>
       </c>
       <c r="B104" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B105" t="s">
         <v>170</v>
@@ -7017,12 +7023,12 @@
         <v>171</v>
       </c>
       <c r="B106" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B107" t="s">
         <v>173</v>
@@ -7033,12 +7039,12 @@
         <v>174</v>
       </c>
       <c r="B108" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B109" t="s">
         <v>176</v>
@@ -7065,20 +7071,20 @@
         <v>181</v>
       </c>
       <c r="B112" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B113" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B114" t="s">
         <v>184</v>
@@ -7097,12 +7103,12 @@
         <v>187</v>
       </c>
       <c r="B116" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B117" t="s">
         <v>189</v>
@@ -7137,36 +7143,36 @@
         <v>196</v>
       </c>
       <c r="B121" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B122" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B123" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B124" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B125" t="s">
         <v>201</v>
@@ -7177,12 +7183,12 @@
         <v>202</v>
       </c>
       <c r="B126" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B127" t="s">
         <v>204</v>
@@ -7217,36 +7223,36 @@
         <v>211</v>
       </c>
       <c r="B131" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B132" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B133" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B134" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B135" t="s">
         <v>216</v>
@@ -7265,20 +7271,20 @@
         <v>219</v>
       </c>
       <c r="B137" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B138" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B139" t="s">
         <v>222</v>
@@ -7297,12 +7303,12 @@
         <v>225</v>
       </c>
       <c r="B141" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B142" t="s">
         <v>227</v>
@@ -7353,12 +7359,12 @@
         <v>238</v>
       </c>
       <c r="B148" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B149" t="s">
         <v>240</v>
@@ -7393,12 +7399,12 @@
         <v>247</v>
       </c>
       <c r="B153" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B154" t="s">
         <v>249</v>
@@ -7449,12 +7455,12 @@
         <v>260</v>
       </c>
       <c r="B160" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B161" t="s">
         <v>262</v>
@@ -7481,12 +7487,12 @@
         <v>267</v>
       </c>
       <c r="B164" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B165" t="s">
         <v>269</v>
@@ -7545,12 +7551,12 @@
         <v>282</v>
       </c>
       <c r="B172" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B173" t="s">
         <v>284</v>
@@ -7593,44 +7599,44 @@
         <v>293</v>
       </c>
       <c r="B178" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B179" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B180" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B181" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B182" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B183" t="s">
         <v>299</v>
@@ -7769,12 +7775,12 @@
         <v>332</v>
       </c>
       <c r="B200" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B201" t="s">
         <v>334</v>
@@ -7817,12 +7823,12 @@
         <v>343</v>
       </c>
       <c r="B206" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B207" t="s">
         <v>345</v>
@@ -7849,12 +7855,12 @@
         <v>350</v>
       </c>
       <c r="B210" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B211" t="s">
         <v>352</v>
@@ -7897,12 +7903,12 @@
         <v>361</v>
       </c>
       <c r="B216" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B217" t="s">
         <v>363</v>
@@ -7921,52 +7927,52 @@
         <v>366</v>
       </c>
       <c r="B219" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B220" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B221" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B222" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B223" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B224" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B225" t="s">
         <v>373</v>
@@ -7977,12 +7983,12 @@
         <v>374</v>
       </c>
       <c r="B226" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B227" t="s">
         <v>376</v>
@@ -7993,12 +7999,12 @@
         <v>377</v>
       </c>
       <c r="B228" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B229" t="s">
         <v>379</v>
@@ -8025,12 +8031,12 @@
         <v>384</v>
       </c>
       <c r="B232" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B233" t="s">
         <v>386</v>
@@ -8049,28 +8055,28 @@
         <v>389</v>
       </c>
       <c r="B235" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B236" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B237" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B238" t="s">
         <v>393</v>
@@ -8113,12 +8119,12 @@
         <v>402</v>
       </c>
       <c r="B243" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B244" t="s">
         <v>404</v>
@@ -8129,12 +8135,12 @@
         <v>405</v>
       </c>
       <c r="B245" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B246" t="s">
         <v>407</v>
@@ -8161,12 +8167,12 @@
         <v>412</v>
       </c>
       <c r="B249" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B250" t="s">
         <v>414</v>
@@ -8185,12 +8191,12 @@
         <v>417</v>
       </c>
       <c r="B252" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B253" t="s">
         <v>419</v>
@@ -8201,20 +8207,20 @@
         <v>420</v>
       </c>
       <c r="B254" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B255" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B256" t="s">
         <v>423</v>
@@ -8233,20 +8239,20 @@
         <v>426</v>
       </c>
       <c r="B258" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B259" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B260" t="s">
         <v>429</v>
@@ -8329,28 +8335,28 @@
         <v>448</v>
       </c>
       <c r="B270" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B271" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B272" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B273" t="s">
         <v>452</v>
@@ -8361,12 +8367,12 @@
         <v>453</v>
       </c>
       <c r="B274" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B275" t="s">
         <v>455</v>
@@ -8377,20 +8383,20 @@
         <v>456</v>
       </c>
       <c r="B276" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B277" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B278" t="s">
         <v>459</v>
@@ -8401,12 +8407,12 @@
         <v>460</v>
       </c>
       <c r="B279" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B280" t="s">
         <v>462</v>
@@ -8433,28 +8439,28 @@
         <v>467</v>
       </c>
       <c r="B283" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B284" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B285" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B286" t="s">
         <v>471</v>
@@ -8465,12 +8471,12 @@
         <v>472</v>
       </c>
       <c r="B287" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B288" t="s">
         <v>474</v>
@@ -8497,12 +8503,12 @@
         <v>479</v>
       </c>
       <c r="B291" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B292" t="s">
         <v>481</v>
@@ -8537,20 +8543,20 @@
         <v>488</v>
       </c>
       <c r="B296" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B297" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B298" t="s">
         <v>491</v>
@@ -8577,36 +8583,36 @@
         <v>496</v>
       </c>
       <c r="B301" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="302" spans="1:2">
       <c r="A302" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B302" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B303" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B304" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B305" t="s">
         <v>501</v>
@@ -8649,20 +8655,20 @@
         <v>510</v>
       </c>
       <c r="B310" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B311" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B312" t="s">
         <v>513</v>
@@ -8681,20 +8687,20 @@
         <v>516</v>
       </c>
       <c r="B314" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B315" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B316" t="s">
         <v>519</v>
@@ -8713,15 +8719,15 @@
         <v>522</v>
       </c>
       <c r="B318" t="s">
-        <v>176</v>
+        <v>523</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B319" t="s">
-        <v>524</v>
+        <v>178</v>
       </c>
     </row>
     <row r="320" spans="1:2">
@@ -8729,12 +8735,12 @@
         <v>525</v>
       </c>
       <c r="B320" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B321" t="s">
         <v>527</v>
@@ -8745,12 +8751,12 @@
         <v>528</v>
       </c>
       <c r="B322" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B323" t="s">
         <v>530</v>
@@ -8769,20 +8775,20 @@
         <v>533</v>
       </c>
       <c r="B325" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B326" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B327" t="s">
         <v>536</v>
@@ -8793,12 +8799,12 @@
         <v>537</v>
       </c>
       <c r="B328" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B329" t="s">
         <v>539</v>
@@ -8825,12 +8831,12 @@
         <v>544</v>
       </c>
       <c r="B332" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B333" t="s">
         <v>546</v>
@@ -8881,20 +8887,20 @@
         <v>557</v>
       </c>
       <c r="B339" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B340" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B341" t="s">
         <v>560</v>
@@ -8905,12 +8911,12 @@
         <v>561</v>
       </c>
       <c r="B342" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B343" t="s">
         <v>563</v>
@@ -8961,12 +8967,12 @@
         <v>574</v>
       </c>
       <c r="B349" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B350" t="s">
         <v>576</v>
@@ -9065,12 +9071,12 @@
         <v>599</v>
       </c>
       <c r="B362" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B363" t="s">
         <v>601</v>
@@ -9097,12 +9103,12 @@
         <v>606</v>
       </c>
       <c r="B366" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B367" t="s">
         <v>608</v>
@@ -9129,20 +9135,20 @@
         <v>613</v>
       </c>
       <c r="B370" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B371" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B372" t="s">
         <v>616</v>
@@ -9201,12 +9207,12 @@
         <v>629</v>
       </c>
       <c r="B379" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B380" t="s">
         <v>631</v>
@@ -9217,12 +9223,12 @@
         <v>632</v>
       </c>
       <c r="B381" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B382" t="s">
         <v>634</v>
@@ -9273,12 +9279,12 @@
         <v>645</v>
       </c>
       <c r="B388" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B389" t="s">
         <v>647</v>
@@ -9313,12 +9319,12 @@
         <v>654</v>
       </c>
       <c r="B393" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B394" t="s">
         <v>656</v>
@@ -9377,12 +9383,12 @@
         <v>669</v>
       </c>
       <c r="B401" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B402" t="s">
         <v>671</v>
@@ -9401,36 +9407,36 @@
         <v>674</v>
       </c>
       <c r="B404" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="405" spans="1:2">
       <c r="A405" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B405" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B406" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B407" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B408" t="s">
         <v>679</v>
@@ -9441,20 +9447,20 @@
         <v>680</v>
       </c>
       <c r="B409" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B410" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B411" t="s">
         <v>683</v>
@@ -9569,12 +9575,12 @@
         <v>710</v>
       </c>
       <c r="B425" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="426" spans="1:2">
       <c r="A426" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B426" t="s">
         <v>712</v>
@@ -9601,12 +9607,12 @@
         <v>717</v>
       </c>
       <c r="B429" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="430" spans="1:2">
       <c r="A430" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B430" t="s">
         <v>719</v>
@@ -9641,12 +9647,12 @@
         <v>726</v>
       </c>
       <c r="B434" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B435" t="s">
         <v>728</v>
@@ -9665,12 +9671,12 @@
         <v>731</v>
       </c>
       <c r="B437" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B438" t="s">
         <v>733</v>
@@ -9681,12 +9687,12 @@
         <v>734</v>
       </c>
       <c r="B439" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="B440" t="s">
         <v>736</v>
@@ -9745,12 +9751,12 @@
         <v>749</v>
       </c>
       <c r="B447" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="448" spans="1:2">
       <c r="A448" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B448" t="s">
         <v>751</v>
@@ -9761,12 +9767,12 @@
         <v>752</v>
       </c>
       <c r="B449" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B450" t="s">
         <v>754</v>
@@ -9777,12 +9783,12 @@
         <v>755</v>
       </c>
       <c r="B451" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B452" t="s">
         <v>757</v>
@@ -9793,12 +9799,12 @@
         <v>758</v>
       </c>
       <c r="B453" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B454" t="s">
         <v>760</v>
@@ -9817,12 +9823,12 @@
         <v>763</v>
       </c>
       <c r="B456" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B457" t="s">
         <v>765</v>
@@ -9897,36 +9903,36 @@
         <v>782</v>
       </c>
       <c r="B466" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B467" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B468" t="s">
-        <v>524</v>
+        <v>785</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B469" t="s">
-        <v>785</v>
+        <v>526</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B470" t="s">
         <v>787</v>
@@ -9937,15 +9943,15 @@
         <v>788</v>
       </c>
       <c r="B471" t="s">
-        <v>139</v>
+        <v>789</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B472" t="s">
-        <v>790</v>
+        <v>141</v>
       </c>
     </row>
     <row r="473" spans="1:2">
@@ -9961,44 +9967,44 @@
         <v>793</v>
       </c>
       <c r="B474" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B475" t="s">
-        <v>524</v>
+        <v>795</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B476" t="s">
-        <v>795</v>
+        <v>526</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B477" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B478" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B479" t="s">
         <v>799</v>
@@ -10025,12 +10031,12 @@
         <v>804</v>
       </c>
       <c r="B482" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B483" t="s">
         <v>806</v>
@@ -10041,12 +10047,12 @@
         <v>807</v>
       </c>
       <c r="B484" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B485" t="s">
         <v>809</v>
@@ -10065,52 +10071,52 @@
         <v>812</v>
       </c>
       <c r="B487" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B488" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B489" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B490" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B491" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B492" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B493" t="s">
         <v>819</v>
@@ -10273,12 +10279,12 @@
         <v>858</v>
       </c>
       <c r="B513" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B514" t="s">
         <v>860</v>
@@ -10289,28 +10295,28 @@
         <v>861</v>
       </c>
       <c r="B515" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B516" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B517" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B518" t="s">
         <v>865</v>
@@ -10337,28 +10343,28 @@
         <v>870</v>
       </c>
       <c r="B521" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B522" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B523" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B524" t="s">
         <v>874</v>
@@ -10385,12 +10391,12 @@
         <v>879</v>
       </c>
       <c r="B527" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B528" t="s">
         <v>881</v>
@@ -10441,12 +10447,12 @@
         <v>892</v>
       </c>
       <c r="B534" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B535" t="s">
         <v>894</v>
@@ -10465,20 +10471,20 @@
         <v>897</v>
       </c>
       <c r="B537" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B538" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B539" t="s">
         <v>900</v>
@@ -10489,44 +10495,44 @@
         <v>901</v>
       </c>
       <c r="B540" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B541" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B542" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B543" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B544" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B545" t="s">
         <v>907</v>
@@ -10553,20 +10559,20 @@
         <v>912</v>
       </c>
       <c r="B548" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B549" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B550" t="s">
         <v>915</v>
@@ -10577,12 +10583,12 @@
         <v>916</v>
       </c>
       <c r="B551" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B552" t="s">
         <v>918</v>
@@ -10593,28 +10599,28 @@
         <v>919</v>
       </c>
       <c r="B553" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B554" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B555" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B556" t="s">
         <v>923</v>
@@ -10625,12 +10631,12 @@
         <v>924</v>
       </c>
       <c r="B557" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B558" t="s">
         <v>926</v>
@@ -10697,20 +10703,20 @@
         <v>941</v>
       </c>
       <c r="B566" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B567" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B568" t="s">
         <v>944</v>
@@ -10729,12 +10735,12 @@
         <v>947</v>
       </c>
       <c r="B570" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B571" t="s">
         <v>949</v>
@@ -10753,12 +10759,12 @@
         <v>952</v>
       </c>
       <c r="B573" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B574" t="s">
         <v>954</v>
@@ -10785,12 +10791,12 @@
         <v>959</v>
       </c>
       <c r="B577" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B578" t="s">
         <v>961</v>
@@ -10801,12 +10807,12 @@
         <v>962</v>
       </c>
       <c r="B579" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B580" t="s">
         <v>964</v>
@@ -10817,20 +10823,20 @@
         <v>965</v>
       </c>
       <c r="B581" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B582" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B583" t="s">
         <v>968</v>
@@ -10849,20 +10855,20 @@
         <v>971</v>
       </c>
       <c r="B585" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B586" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B587" t="s">
         <v>974</v>
@@ -10873,12 +10879,12 @@
         <v>975</v>
       </c>
       <c r="B588" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B589" t="s">
         <v>977</v>
@@ -10889,12 +10895,12 @@
         <v>978</v>
       </c>
       <c r="B590" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B591" t="s">
         <v>980</v>
@@ -10913,12 +10919,12 @@
         <v>983</v>
       </c>
       <c r="B593" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B594" t="s">
         <v>985</v>
@@ -10969,12 +10975,12 @@
         <v>996</v>
       </c>
       <c r="B600" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B601" t="s">
         <v>998</v>
@@ -11041,12 +11047,12 @@
         <v>1013</v>
       </c>
       <c r="B609" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B610" t="s">
         <v>1015</v>
@@ -11065,12 +11071,12 @@
         <v>1018</v>
       </c>
       <c r="B612" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B613" t="s">
         <v>1020</v>
@@ -11113,28 +11119,28 @@
         <v>1029</v>
       </c>
       <c r="B618" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B619" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B620" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B621" t="s">
         <v>1033</v>
@@ -11145,12 +11151,12 @@
         <v>1034</v>
       </c>
       <c r="B622" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B623" t="s">
         <v>1036</v>
@@ -11177,12 +11183,12 @@
         <v>1041</v>
       </c>
       <c r="B626" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B627" t="s">
         <v>1043</v>
@@ -11217,76 +11223,76 @@
         <v>1050</v>
       </c>
       <c r="B631" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B632" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B633" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B634" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B635" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B636" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B637" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B638" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B639" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B640" t="s">
         <v>1060</v>
@@ -11297,20 +11303,20 @@
         <v>1061</v>
       </c>
       <c r="B641" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B642" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B643" t="s">
         <v>1064</v>
@@ -11321,28 +11327,28 @@
         <v>1065</v>
       </c>
       <c r="B644" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B645" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B646" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B647" t="s">
         <v>1069</v>
@@ -11353,36 +11359,36 @@
         <v>1070</v>
       </c>
       <c r="B648" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B649" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B650" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B651" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B652" t="s">
         <v>1075</v>
@@ -11417,20 +11423,20 @@
         <v>1082</v>
       </c>
       <c r="B656" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B657" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B658" t="s">
         <v>1085</v>
@@ -11449,20 +11455,20 @@
         <v>1088</v>
       </c>
       <c r="B660" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B661" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B662" t="s">
         <v>1091</v>
@@ -11481,12 +11487,12 @@
         <v>1094</v>
       </c>
       <c r="B664" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B665" t="s">
         <v>1096</v>
@@ -11497,20 +11503,20 @@
         <v>1097</v>
       </c>
       <c r="B666" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B667" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B668" t="s">
         <v>1100</v>
@@ -11545,44 +11551,44 @@
         <v>1107</v>
       </c>
       <c r="B672" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B673" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B674" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B675" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B676" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B677" t="s">
         <v>1113</v>
@@ -11601,12 +11607,12 @@
         <v>1116</v>
       </c>
       <c r="B679" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B680" t="s">
         <v>1118</v>
@@ -11625,12 +11631,12 @@
         <v>1121</v>
       </c>
       <c r="B682" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B683" t="s">
         <v>1123</v>
@@ -11641,20 +11647,20 @@
         <v>1124</v>
       </c>
       <c r="B684" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B685" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B686" t="s">
         <v>1127</v>
@@ -11681,20 +11687,20 @@
         <v>1132</v>
       </c>
       <c r="B689" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B690" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B691" t="s">
         <v>1135</v>
@@ -11777,12 +11783,12 @@
         <v>1154</v>
       </c>
       <c r="B701" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B702" t="s">
         <v>1156</v>
@@ -11825,12 +11831,12 @@
         <v>1165</v>
       </c>
       <c r="B707" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B708" t="s">
         <v>1167</v>
@@ -11841,20 +11847,20 @@
         <v>1168</v>
       </c>
       <c r="B709" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B710" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B711" t="s">
         <v>1171</v>
@@ -11865,28 +11871,28 @@
         <v>1172</v>
       </c>
       <c r="B712" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B713" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B714" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B715" t="s">
         <v>1176</v>
@@ -11897,28 +11903,28 @@
         <v>1177</v>
       </c>
       <c r="B716" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B717" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B718" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B719" t="s">
         <v>1181</v>
@@ -11929,12 +11935,12 @@
         <v>1182</v>
       </c>
       <c r="B720" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B721" t="s">
         <v>1184</v>
@@ -11993,12 +11999,12 @@
         <v>1197</v>
       </c>
       <c r="B728" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B729" t="s">
         <v>1199</v>
@@ -12073,12 +12079,12 @@
         <v>1216</v>
       </c>
       <c r="B738" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B739" t="s">
         <v>1218</v>
@@ -12105,12 +12111,12 @@
         <v>1223</v>
       </c>
       <c r="B742" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B743" t="s">
         <v>1225</v>
@@ -12121,52 +12127,52 @@
         <v>1226</v>
       </c>
       <c r="B744" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B745" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B746" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B747" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B748" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B749" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B750" t="s">
         <v>1233</v>
@@ -12185,36 +12191,36 @@
         <v>1236</v>
       </c>
       <c r="B752" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B753" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B754" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B755" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B756" t="s">
         <v>1241</v>
@@ -12273,20 +12279,20 @@
         <v>1254</v>
       </c>
       <c r="B763" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B764" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B765" t="s">
         <v>1257</v>
@@ -12297,20 +12303,20 @@
         <v>1258</v>
       </c>
       <c r="B766" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B767" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B768" t="s">
         <v>1261</v>
@@ -12321,20 +12327,20 @@
         <v>1262</v>
       </c>
       <c r="B769" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B770" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B771" t="s">
         <v>1265</v>
@@ -12377,12 +12383,12 @@
         <v>1274</v>
       </c>
       <c r="B776" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B777" t="s">
         <v>1276</v>
@@ -12417,12 +12423,12 @@
         <v>1283</v>
       </c>
       <c r="B781" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B782" t="s">
         <v>1285</v>
@@ -12489,28 +12495,28 @@
         <v>1300</v>
       </c>
       <c r="B790" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B791" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B792" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B793" t="s">
         <v>1304</v>
@@ -12529,12 +12535,12 @@
         <v>1307</v>
       </c>
       <c r="B795" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B796" t="s">
         <v>1309</v>
@@ -12545,60 +12551,60 @@
         <v>1310</v>
       </c>
       <c r="B797" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B798" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B799" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B800" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B801" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B802" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B803" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B804" t="s">
         <v>1318</v>
@@ -12609,28 +12615,28 @@
         <v>1319</v>
       </c>
       <c r="B805" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B806" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B807" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B808" t="s">
         <v>1323</v>
@@ -12681,28 +12687,28 @@
         <v>1334</v>
       </c>
       <c r="B814" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B815" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B816" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B817" t="s">
         <v>1338</v>
@@ -12785,12 +12791,12 @@
         <v>1357</v>
       </c>
       <c r="B827" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B828" t="s">
         <v>1359</v>
@@ -12809,20 +12815,20 @@
         <v>1362</v>
       </c>
       <c r="B830" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B831" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B832" t="s">
         <v>1365</v>
@@ -12833,12 +12839,12 @@
         <v>1366</v>
       </c>
       <c r="B833" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B834" t="s">
         <v>1368</v>
@@ -12849,28 +12855,28 @@
         <v>1369</v>
       </c>
       <c r="B835" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B836" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B837" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B838" t="s">
         <v>1373</v>
@@ -12881,44 +12887,44 @@
         <v>1374</v>
       </c>
       <c r="B839" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B840" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B841" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B842" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B843" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B844" t="s">
         <v>1380</v>
@@ -12953,12 +12959,12 @@
         <v>1387</v>
       </c>
       <c r="B848" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B849" t="s">
         <v>1389</v>
@@ -12977,28 +12983,28 @@
         <v>1392</v>
       </c>
       <c r="B851" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B852" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B853" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B854" t="s">
         <v>1396</v>
@@ -13105,28 +13111,28 @@
         <v>1421</v>
       </c>
       <c r="B867" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B868" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B869" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B870" t="s">
         <v>1425</v>
@@ -13137,12 +13143,12 @@
         <v>1426</v>
       </c>
       <c r="B871" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B872" t="s">
         <v>1428</v>
@@ -13153,52 +13159,52 @@
         <v>1429</v>
       </c>
       <c r="B873" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B874" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B875" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B876" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B877" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B878" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B879" t="s">
         <v>1436</v>
@@ -13241,12 +13247,12 @@
         <v>1445</v>
       </c>
       <c r="B884" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B885" t="s">
         <v>1447</v>
@@ -13289,12 +13295,12 @@
         <v>1456</v>
       </c>
       <c r="B890" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B891" t="s">
         <v>1458</v>
@@ -13321,20 +13327,20 @@
         <v>1463</v>
       </c>
       <c r="B894" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B895" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B896" t="s">
         <v>1466</v>
@@ -13377,12 +13383,12 @@
         <v>1475</v>
       </c>
       <c r="B901" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B902" t="s">
         <v>1477</v>
@@ -13393,12 +13399,12 @@
         <v>1478</v>
       </c>
       <c r="B903" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B904" t="s">
         <v>1480</v>
@@ -13433,20 +13439,20 @@
         <v>1487</v>
       </c>
       <c r="B908" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B909" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B910" t="s">
         <v>1490</v>
@@ -13489,52 +13495,52 @@
         <v>1499</v>
       </c>
       <c r="B915" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B916" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B917" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B918" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B919" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B920" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B921" t="s">
         <v>1506</v>
@@ -13569,28 +13575,28 @@
         <v>1513</v>
       </c>
       <c r="B925" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B926" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B927" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B928" t="s">
         <v>1517</v>
@@ -13633,20 +13639,20 @@
         <v>1526</v>
       </c>
       <c r="B933" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B934" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B935" t="s">
         <v>1529</v>
@@ -13681,12 +13687,12 @@
         <v>1536</v>
       </c>
       <c r="B939" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B940" t="s">
         <v>1538</v>
@@ -13705,12 +13711,12 @@
         <v>1541</v>
       </c>
       <c r="B942" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B943" t="s">
         <v>1543</v>
@@ -13729,12 +13735,12 @@
         <v>1546</v>
       </c>
       <c r="B945" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B946" t="s">
         <v>1548</v>
@@ -13745,12 +13751,12 @@
         <v>1549</v>
       </c>
       <c r="B947" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B948" t="s">
         <v>1551</v>
@@ -13769,12 +13775,12 @@
         <v>1554</v>
       </c>
       <c r="B950" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B951" t="s">
         <v>1556</v>
@@ -13793,28 +13799,28 @@
         <v>1559</v>
       </c>
       <c r="B953" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B954" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B955" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B956" t="s">
         <v>1563</v>
@@ -13841,44 +13847,44 @@
         <v>1568</v>
       </c>
       <c r="B959" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B960" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B961" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B962" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B963" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B964" t="s">
         <v>1574</v>
@@ -13913,28 +13919,28 @@
         <v>1581</v>
       </c>
       <c r="B968" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B969" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B970" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B971" t="s">
         <v>1585</v>
@@ -13985,28 +13991,28 @@
         <v>1596</v>
       </c>
       <c r="B977" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B978" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B979" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B980" t="s">
         <v>1600</v>
@@ -14017,20 +14023,20 @@
         <v>1601</v>
       </c>
       <c r="B981" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B982" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B983" t="s">
         <v>1604</v>
@@ -14073,12 +14079,12 @@
         <v>1613</v>
       </c>
       <c r="B988" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B989" t="s">
         <v>1615</v>
@@ -14105,12 +14111,12 @@
         <v>1620</v>
       </c>
       <c r="B992" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B993" t="s">
         <v>1622</v>
@@ -14129,36 +14135,36 @@
         <v>1625</v>
       </c>
       <c r="B995" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B996" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B997" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B998" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B999" t="s">
         <v>1630</v>
@@ -14209,12 +14215,12 @@
         <v>1641</v>
       </c>
       <c r="B1005" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B1006" t="s">
         <v>1643</v>
@@ -14233,28 +14239,28 @@
         <v>1646</v>
       </c>
       <c r="B1008" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B1009" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B1010" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B1011" t="s">
         <v>1650</v>
@@ -14265,12 +14271,12 @@
         <v>1651</v>
       </c>
       <c r="B1012" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B1013" t="s">
         <v>1653</v>
@@ -14289,20 +14295,20 @@
         <v>1656</v>
       </c>
       <c r="B1015" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B1016" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B1017" t="s">
         <v>1659</v>
@@ -14329,12 +14335,12 @@
         <v>1664</v>
       </c>
       <c r="B1020" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1021" t="s">
         <v>1666</v>
@@ -14353,12 +14359,12 @@
         <v>1669</v>
       </c>
       <c r="B1023" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B1024" t="s">
         <v>1671</v>
@@ -14377,36 +14383,36 @@
         <v>1674</v>
       </c>
       <c r="B1026" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1027" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B1028" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1029" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1030" t="s">
         <v>1679</v>
@@ -14425,12 +14431,12 @@
         <v>1682</v>
       </c>
       <c r="B1032" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1033" t="s">
         <v>1684</v>
@@ -14457,12 +14463,12 @@
         <v>1689</v>
       </c>
       <c r="B1036" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1037" t="s">
         <v>1691</v>
@@ -14473,20 +14479,20 @@
         <v>1692</v>
       </c>
       <c r="B1038" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1039" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1040" t="s">
         <v>1695</v>
@@ -14497,12 +14503,12 @@
         <v>1696</v>
       </c>
       <c r="B1041" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1042" t="s">
         <v>1698</v>
@@ -14513,20 +14519,20 @@
         <v>1699</v>
       </c>
       <c r="B1043" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1044" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1045" t="s">
         <v>1702</v>
@@ -14537,20 +14543,20 @@
         <v>1703</v>
       </c>
       <c r="B1046" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1047" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1048" t="s">
         <v>1706</v>
@@ -14561,12 +14567,12 @@
         <v>1707</v>
       </c>
       <c r="B1049" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1050" t="s">
         <v>1709</v>
@@ -14601,12 +14607,12 @@
         <v>1716</v>
       </c>
       <c r="B1054" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1055" t="s">
         <v>1718</v>
@@ -14617,12 +14623,12 @@
         <v>1719</v>
       </c>
       <c r="B1056" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B1057" t="s">
         <v>1721</v>
@@ -14665,36 +14671,36 @@
         <v>1730</v>
       </c>
       <c r="B1062" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="B1063" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="B1064" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1065" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B1066" t="s">
         <v>1735</v>
@@ -14745,12 +14751,12 @@
         <v>1746</v>
       </c>
       <c r="B1072" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="B1073" t="s">
         <v>1748</v>
@@ -14761,20 +14767,20 @@
         <v>1749</v>
       </c>
       <c r="B1074" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="B1075" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B1076" t="s">
         <v>1752</v>
@@ -14825,12 +14831,12 @@
         <v>1763</v>
       </c>
       <c r="B1082" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="B1083" t="s">
         <v>1765</v>
@@ -14841,20 +14847,20 @@
         <v>1766</v>
       </c>
       <c r="B1084" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="B1085" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B1086" t="s">
         <v>1769</v>
@@ -14865,12 +14871,12 @@
         <v>1770</v>
       </c>
       <c r="B1087" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B1088" t="s">
         <v>1772</v>
@@ -14881,36 +14887,36 @@
         <v>1773</v>
       </c>
       <c r="B1089" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="B1090" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B1091" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B1092" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B1093" t="s">
         <v>1778</v>
@@ -14929,20 +14935,20 @@
         <v>1781</v>
       </c>
       <c r="B1095" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="B1096" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="B1097" t="s">
         <v>1784</v>
@@ -14961,12 +14967,12 @@
         <v>1787</v>
       </c>
       <c r="B1099" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="B1100" t="s">
         <v>1789</v>
@@ -15001,20 +15007,20 @@
         <v>1796</v>
       </c>
       <c r="B1104" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="B1105" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="B1106" t="s">
         <v>1799</v>
@@ -15057,12 +15063,12 @@
         <v>1808</v>
       </c>
       <c r="B1111" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="B1112" t="s">
         <v>1810</v>
@@ -15081,20 +15087,20 @@
         <v>1813</v>
       </c>
       <c r="B1114" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="B1115" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="B1116" t="s">
         <v>1816</v>
@@ -15105,20 +15111,20 @@
         <v>1817</v>
       </c>
       <c r="B1117" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B1118" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B1119" t="s">
         <v>1820</v>
@@ -15137,12 +15143,12 @@
         <v>1823</v>
       </c>
       <c r="B1121" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="B1122" t="s">
         <v>1825</v>
@@ -15169,12 +15175,12 @@
         <v>1830</v>
       </c>
       <c r="B1125" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="B1126" t="s">
         <v>1832</v>
@@ -15217,12 +15223,12 @@
         <v>1841</v>
       </c>
       <c r="B1131" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="B1132" t="s">
         <v>1843</v>
@@ -15329,44 +15335,44 @@
         <v>1868</v>
       </c>
       <c r="B1145" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="B1146" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="B1147" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B1148" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="B1149" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B1150" t="s">
         <v>1874</v>
@@ -15385,28 +15391,28 @@
         <v>1877</v>
       </c>
       <c r="B1152" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="B1153" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="B1154" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1155" t="s">
         <v>1881</v>
@@ -15473,12 +15479,12 @@
         <v>1896</v>
       </c>
       <c r="B1163" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="B1164" t="s">
         <v>1898</v>
@@ -15489,12 +15495,12 @@
         <v>1899</v>
       </c>
       <c r="B1165" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="B1166" t="s">
         <v>1901</v>
@@ -15529,44 +15535,44 @@
         <v>1908</v>
       </c>
       <c r="B1170" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="B1171" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="B1172" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B1173" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B1174" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B1175" t="s">
         <v>1914</v>
@@ -15585,20 +15591,20 @@
         <v>1917</v>
       </c>
       <c r="B1177" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="B1178" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="B1179" t="s">
         <v>1920</v>
@@ -15609,44 +15615,44 @@
         <v>1921</v>
       </c>
       <c r="B1180" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B1181" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B1182" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B1183" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B1184" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B1185" t="s">
         <v>1927</v>
@@ -15657,43 +15663,51 @@
         <v>1928</v>
       </c>
       <c r="B1186" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B1187" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B1188" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B1189" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B1190" t="s">
         <v>1933</v>
       </c>
     </row>
+    <row r="1191" spans="1:2">
+      <c r="A1191" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B1191" t="s">
+        <v>1935</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1190"/>
+  <autoFilter ref="A1:B1191"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1938">
   <si>
     <t>en</t>
   </si>
@@ -1286,6 +1286,12 @@
   </si>
   <si>
     <t>Diablo</t>
+  </si>
+  <si>
+    <t>Die of Death</t>
+  </si>
+  <si>
+    <t>Mati karena Kematian</t>
   </si>
   <si>
     <t>Digimon</t>
@@ -6171,7 +6177,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1191"/>
+  <dimension ref="A1:B1192"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -8223,12 +8229,12 @@
         <v>423</v>
       </c>
       <c r="B256" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B257" t="s">
         <v>425</v>
@@ -8247,20 +8253,20 @@
         <v>428</v>
       </c>
       <c r="B259" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B260" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B261" t="s">
         <v>431</v>
@@ -8343,28 +8349,28 @@
         <v>450</v>
       </c>
       <c r="B271" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B272" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B273" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B274" t="s">
         <v>454</v>
@@ -8375,12 +8381,12 @@
         <v>455</v>
       </c>
       <c r="B275" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B276" t="s">
         <v>457</v>
@@ -8391,20 +8397,20 @@
         <v>458</v>
       </c>
       <c r="B277" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B278" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B279" t="s">
         <v>461</v>
@@ -8415,12 +8421,12 @@
         <v>462</v>
       </c>
       <c r="B280" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B281" t="s">
         <v>464</v>
@@ -8447,28 +8453,28 @@
         <v>469</v>
       </c>
       <c r="B284" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B285" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B286" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B287" t="s">
         <v>473</v>
@@ -8479,12 +8485,12 @@
         <v>474</v>
       </c>
       <c r="B288" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B289" t="s">
         <v>476</v>
@@ -8511,12 +8517,12 @@
         <v>481</v>
       </c>
       <c r="B292" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B293" t="s">
         <v>483</v>
@@ -8551,20 +8557,20 @@
         <v>490</v>
       </c>
       <c r="B297" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B298" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B299" t="s">
         <v>493</v>
@@ -8591,36 +8597,36 @@
         <v>498</v>
       </c>
       <c r="B302" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B303" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B304" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B305" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B306" t="s">
         <v>503</v>
@@ -8663,20 +8669,20 @@
         <v>512</v>
       </c>
       <c r="B311" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B312" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B313" t="s">
         <v>515</v>
@@ -8695,20 +8701,20 @@
         <v>518</v>
       </c>
       <c r="B315" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B316" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B317" t="s">
         <v>521</v>
@@ -8727,15 +8733,15 @@
         <v>524</v>
       </c>
       <c r="B319" t="s">
-        <v>178</v>
+        <v>525</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B320" t="s">
-        <v>526</v>
+        <v>178</v>
       </c>
     </row>
     <row r="321" spans="1:2">
@@ -8743,12 +8749,12 @@
         <v>527</v>
       </c>
       <c r="B321" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B322" t="s">
         <v>529</v>
@@ -8759,12 +8765,12 @@
         <v>530</v>
       </c>
       <c r="B323" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B324" t="s">
         <v>532</v>
@@ -8783,20 +8789,20 @@
         <v>535</v>
       </c>
       <c r="B326" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B327" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B328" t="s">
         <v>538</v>
@@ -8807,12 +8813,12 @@
         <v>539</v>
       </c>
       <c r="B329" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B330" t="s">
         <v>541</v>
@@ -8839,12 +8845,12 @@
         <v>546</v>
       </c>
       <c r="B333" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B334" t="s">
         <v>548</v>
@@ -8895,20 +8901,20 @@
         <v>559</v>
       </c>
       <c r="B340" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B341" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B342" t="s">
         <v>562</v>
@@ -8919,12 +8925,12 @@
         <v>563</v>
       </c>
       <c r="B343" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B344" t="s">
         <v>565</v>
@@ -8975,12 +8981,12 @@
         <v>576</v>
       </c>
       <c r="B350" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B351" t="s">
         <v>578</v>
@@ -9079,12 +9085,12 @@
         <v>601</v>
       </c>
       <c r="B363" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B364" t="s">
         <v>603</v>
@@ -9111,12 +9117,12 @@
         <v>608</v>
       </c>
       <c r="B367" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B368" t="s">
         <v>610</v>
@@ -9143,20 +9149,20 @@
         <v>615</v>
       </c>
       <c r="B371" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B372" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B373" t="s">
         <v>618</v>
@@ -9215,12 +9221,12 @@
         <v>631</v>
       </c>
       <c r="B380" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B381" t="s">
         <v>633</v>
@@ -9231,12 +9237,12 @@
         <v>634</v>
       </c>
       <c r="B382" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B383" t="s">
         <v>636</v>
@@ -9287,12 +9293,12 @@
         <v>647</v>
       </c>
       <c r="B389" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B390" t="s">
         <v>649</v>
@@ -9327,12 +9333,12 @@
         <v>656</v>
       </c>
       <c r="B394" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B395" t="s">
         <v>658</v>
@@ -9391,12 +9397,12 @@
         <v>671</v>
       </c>
       <c r="B402" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B403" t="s">
         <v>673</v>
@@ -9415,36 +9421,36 @@
         <v>676</v>
       </c>
       <c r="B405" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B406" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B407" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B408" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="409" spans="1:2">
       <c r="A409" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B409" t="s">
         <v>681</v>
@@ -9455,20 +9461,20 @@
         <v>682</v>
       </c>
       <c r="B410" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B411" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B412" t="s">
         <v>685</v>
@@ -9583,12 +9589,12 @@
         <v>712</v>
       </c>
       <c r="B426" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="427" spans="1:2">
       <c r="A427" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B427" t="s">
         <v>714</v>
@@ -9615,12 +9621,12 @@
         <v>719</v>
       </c>
       <c r="B430" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B431" t="s">
         <v>721</v>
@@ -9655,12 +9661,12 @@
         <v>728</v>
       </c>
       <c r="B435" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B436" t="s">
         <v>730</v>
@@ -9679,12 +9685,12 @@
         <v>733</v>
       </c>
       <c r="B438" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B439" t="s">
         <v>735</v>
@@ -9695,12 +9701,12 @@
         <v>736</v>
       </c>
       <c r="B440" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="B441" t="s">
         <v>738</v>
@@ -9759,12 +9765,12 @@
         <v>751</v>
       </c>
       <c r="B448" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B449" t="s">
         <v>753</v>
@@ -9775,12 +9781,12 @@
         <v>754</v>
       </c>
       <c r="B450" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="B451" t="s">
         <v>756</v>
@@ -9791,12 +9797,12 @@
         <v>757</v>
       </c>
       <c r="B452" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B453" t="s">
         <v>759</v>
@@ -9807,12 +9813,12 @@
         <v>760</v>
       </c>
       <c r="B454" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B455" t="s">
         <v>762</v>
@@ -9831,12 +9837,12 @@
         <v>765</v>
       </c>
       <c r="B457" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B458" t="s">
         <v>767</v>
@@ -9911,36 +9917,36 @@
         <v>784</v>
       </c>
       <c r="B467" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B468" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B469" t="s">
-        <v>526</v>
+        <v>787</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B470" t="s">
-        <v>787</v>
+        <v>528</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B471" t="s">
         <v>789</v>
@@ -9951,15 +9957,15 @@
         <v>790</v>
       </c>
       <c r="B472" t="s">
-        <v>141</v>
+        <v>791</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B473" t="s">
-        <v>792</v>
+        <v>141</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -9975,44 +9981,44 @@
         <v>795</v>
       </c>
       <c r="B475" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B476" t="s">
-        <v>526</v>
+        <v>797</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B477" t="s">
-        <v>797</v>
+        <v>528</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B478" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B479" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B480" t="s">
         <v>801</v>
@@ -10039,12 +10045,12 @@
         <v>806</v>
       </c>
       <c r="B483" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B484" t="s">
         <v>808</v>
@@ -10055,12 +10061,12 @@
         <v>809</v>
       </c>
       <c r="B485" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B486" t="s">
         <v>811</v>
@@ -10079,52 +10085,52 @@
         <v>814</v>
       </c>
       <c r="B488" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B489" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B490" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B491" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B492" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B493" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B494" t="s">
         <v>821</v>
@@ -10287,12 +10293,12 @@
         <v>860</v>
       </c>
       <c r="B514" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B515" t="s">
         <v>862</v>
@@ -10303,28 +10309,28 @@
         <v>863</v>
       </c>
       <c r="B516" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B517" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B518" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B519" t="s">
         <v>867</v>
@@ -10351,28 +10357,28 @@
         <v>872</v>
       </c>
       <c r="B522" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B523" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B524" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B525" t="s">
         <v>876</v>
@@ -10399,12 +10405,12 @@
         <v>881</v>
       </c>
       <c r="B528" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B529" t="s">
         <v>883</v>
@@ -10455,12 +10461,12 @@
         <v>894</v>
       </c>
       <c r="B535" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B536" t="s">
         <v>896</v>
@@ -10479,20 +10485,20 @@
         <v>899</v>
       </c>
       <c r="B538" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B539" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B540" t="s">
         <v>902</v>
@@ -10503,44 +10509,44 @@
         <v>903</v>
       </c>
       <c r="B541" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B542" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B543" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B544" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B545" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B546" t="s">
         <v>909</v>
@@ -10567,20 +10573,20 @@
         <v>914</v>
       </c>
       <c r="B549" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B550" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B551" t="s">
         <v>917</v>
@@ -10591,12 +10597,12 @@
         <v>918</v>
       </c>
       <c r="B552" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B553" t="s">
         <v>920</v>
@@ -10607,28 +10613,28 @@
         <v>921</v>
       </c>
       <c r="B554" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B555" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B556" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B557" t="s">
         <v>925</v>
@@ -10639,12 +10645,12 @@
         <v>926</v>
       </c>
       <c r="B558" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B559" t="s">
         <v>928</v>
@@ -10711,20 +10717,20 @@
         <v>943</v>
       </c>
       <c r="B567" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B568" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B569" t="s">
         <v>946</v>
@@ -10743,12 +10749,12 @@
         <v>949</v>
       </c>
       <c r="B571" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B572" t="s">
         <v>951</v>
@@ -10767,12 +10773,12 @@
         <v>954</v>
       </c>
       <c r="B574" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B575" t="s">
         <v>956</v>
@@ -10799,12 +10805,12 @@
         <v>961</v>
       </c>
       <c r="B578" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B579" t="s">
         <v>963</v>
@@ -10815,12 +10821,12 @@
         <v>964</v>
       </c>
       <c r="B580" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B581" t="s">
         <v>966</v>
@@ -10831,20 +10837,20 @@
         <v>967</v>
       </c>
       <c r="B582" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B583" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B584" t="s">
         <v>970</v>
@@ -10863,20 +10869,20 @@
         <v>973</v>
       </c>
       <c r="B586" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B587" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B588" t="s">
         <v>976</v>
@@ -10887,12 +10893,12 @@
         <v>977</v>
       </c>
       <c r="B589" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B590" t="s">
         <v>979</v>
@@ -10903,12 +10909,12 @@
         <v>980</v>
       </c>
       <c r="B591" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B592" t="s">
         <v>982</v>
@@ -10927,12 +10933,12 @@
         <v>985</v>
       </c>
       <c r="B594" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B595" t="s">
         <v>987</v>
@@ -10983,12 +10989,12 @@
         <v>998</v>
       </c>
       <c r="B601" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B602" t="s">
         <v>1000</v>
@@ -11055,12 +11061,12 @@
         <v>1015</v>
       </c>
       <c r="B610" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B611" t="s">
         <v>1017</v>
@@ -11079,12 +11085,12 @@
         <v>1020</v>
       </c>
       <c r="B613" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B614" t="s">
         <v>1022</v>
@@ -11127,28 +11133,28 @@
         <v>1031</v>
       </c>
       <c r="B619" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B620" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B621" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B622" t="s">
         <v>1035</v>
@@ -11159,12 +11165,12 @@
         <v>1036</v>
       </c>
       <c r="B623" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B624" t="s">
         <v>1038</v>
@@ -11191,12 +11197,12 @@
         <v>1043</v>
       </c>
       <c r="B627" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B628" t="s">
         <v>1045</v>
@@ -11231,76 +11237,76 @@
         <v>1052</v>
       </c>
       <c r="B632" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B633" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B634" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B635" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B636" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B637" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B638" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B639" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B640" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B641" t="s">
         <v>1062</v>
@@ -11311,20 +11317,20 @@
         <v>1063</v>
       </c>
       <c r="B642" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B643" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B644" t="s">
         <v>1066</v>
@@ -11335,28 +11341,28 @@
         <v>1067</v>
       </c>
       <c r="B645" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B646" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B647" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B648" t="s">
         <v>1071</v>
@@ -11367,36 +11373,36 @@
         <v>1072</v>
       </c>
       <c r="B649" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B650" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B651" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B652" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B653" t="s">
         <v>1077</v>
@@ -11431,20 +11437,20 @@
         <v>1084</v>
       </c>
       <c r="B657" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B658" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B659" t="s">
         <v>1087</v>
@@ -11463,20 +11469,20 @@
         <v>1090</v>
       </c>
       <c r="B661" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B662" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B663" t="s">
         <v>1093</v>
@@ -11495,12 +11501,12 @@
         <v>1096</v>
       </c>
       <c r="B665" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B666" t="s">
         <v>1098</v>
@@ -11511,20 +11517,20 @@
         <v>1099</v>
       </c>
       <c r="B667" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B668" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B669" t="s">
         <v>1102</v>
@@ -11559,44 +11565,44 @@
         <v>1109</v>
       </c>
       <c r="B673" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B674" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B675" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B676" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B677" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B678" t="s">
         <v>1115</v>
@@ -11615,12 +11621,12 @@
         <v>1118</v>
       </c>
       <c r="B680" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B681" t="s">
         <v>1120</v>
@@ -11639,12 +11645,12 @@
         <v>1123</v>
       </c>
       <c r="B683" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B684" t="s">
         <v>1125</v>
@@ -11655,20 +11661,20 @@
         <v>1126</v>
       </c>
       <c r="B685" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B686" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B687" t="s">
         <v>1129</v>
@@ -11695,20 +11701,20 @@
         <v>1134</v>
       </c>
       <c r="B690" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B691" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B692" t="s">
         <v>1137</v>
@@ -11791,12 +11797,12 @@
         <v>1156</v>
       </c>
       <c r="B702" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B703" t="s">
         <v>1158</v>
@@ -11839,12 +11845,12 @@
         <v>1167</v>
       </c>
       <c r="B708" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B709" t="s">
         <v>1169</v>
@@ -11855,20 +11861,20 @@
         <v>1170</v>
       </c>
       <c r="B710" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B711" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B712" t="s">
         <v>1173</v>
@@ -11879,28 +11885,28 @@
         <v>1174</v>
       </c>
       <c r="B713" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B714" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B715" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B716" t="s">
         <v>1178</v>
@@ -11911,28 +11917,28 @@
         <v>1179</v>
       </c>
       <c r="B717" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B718" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B719" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B720" t="s">
         <v>1183</v>
@@ -11943,12 +11949,12 @@
         <v>1184</v>
       </c>
       <c r="B721" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B722" t="s">
         <v>1186</v>
@@ -12007,12 +12013,12 @@
         <v>1199</v>
       </c>
       <c r="B729" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B730" t="s">
         <v>1201</v>
@@ -12087,12 +12093,12 @@
         <v>1218</v>
       </c>
       <c r="B739" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B740" t="s">
         <v>1220</v>
@@ -12119,12 +12125,12 @@
         <v>1225</v>
       </c>
       <c r="B743" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B744" t="s">
         <v>1227</v>
@@ -12135,52 +12141,52 @@
         <v>1228</v>
       </c>
       <c r="B745" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B746" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B747" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B748" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B749" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B750" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B751" t="s">
         <v>1235</v>
@@ -12199,36 +12205,36 @@
         <v>1238</v>
       </c>
       <c r="B753" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B754" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B755" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B756" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B757" t="s">
         <v>1243</v>
@@ -12287,20 +12293,20 @@
         <v>1256</v>
       </c>
       <c r="B764" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B765" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B766" t="s">
         <v>1259</v>
@@ -12311,20 +12317,20 @@
         <v>1260</v>
       </c>
       <c r="B767" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B768" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B769" t="s">
         <v>1263</v>
@@ -12335,20 +12341,20 @@
         <v>1264</v>
       </c>
       <c r="B770" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B771" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B772" t="s">
         <v>1267</v>
@@ -12391,12 +12397,12 @@
         <v>1276</v>
       </c>
       <c r="B777" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B778" t="s">
         <v>1278</v>
@@ -12431,12 +12437,12 @@
         <v>1285</v>
       </c>
       <c r="B782" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B783" t="s">
         <v>1287</v>
@@ -12503,28 +12509,28 @@
         <v>1302</v>
       </c>
       <c r="B791" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B792" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B793" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B794" t="s">
         <v>1306</v>
@@ -12543,12 +12549,12 @@
         <v>1309</v>
       </c>
       <c r="B796" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B797" t="s">
         <v>1311</v>
@@ -12559,60 +12565,60 @@
         <v>1312</v>
       </c>
       <c r="B798" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B799" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B800" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B801" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B802" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B803" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B804" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B805" t="s">
         <v>1320</v>
@@ -12623,28 +12629,28 @@
         <v>1321</v>
       </c>
       <c r="B806" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B807" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B808" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B809" t="s">
         <v>1325</v>
@@ -12695,28 +12701,28 @@
         <v>1336</v>
       </c>
       <c r="B815" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B816" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B817" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B818" t="s">
         <v>1340</v>
@@ -12799,12 +12805,12 @@
         <v>1359</v>
       </c>
       <c r="B828" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B829" t="s">
         <v>1361</v>
@@ -12823,20 +12829,20 @@
         <v>1364</v>
       </c>
       <c r="B831" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B832" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B833" t="s">
         <v>1367</v>
@@ -12847,12 +12853,12 @@
         <v>1368</v>
       </c>
       <c r="B834" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B835" t="s">
         <v>1370</v>
@@ -12863,28 +12869,28 @@
         <v>1371</v>
       </c>
       <c r="B836" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B837" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B838" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B839" t="s">
         <v>1375</v>
@@ -12895,44 +12901,44 @@
         <v>1376</v>
       </c>
       <c r="B840" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B841" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B842" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B843" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B844" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B845" t="s">
         <v>1382</v>
@@ -12967,12 +12973,12 @@
         <v>1389</v>
       </c>
       <c r="B849" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B850" t="s">
         <v>1391</v>
@@ -12991,28 +12997,28 @@
         <v>1394</v>
       </c>
       <c r="B852" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B853" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B854" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B855" t="s">
         <v>1398</v>
@@ -13119,28 +13125,28 @@
         <v>1423</v>
       </c>
       <c r="B868" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B869" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B870" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B871" t="s">
         <v>1427</v>
@@ -13151,12 +13157,12 @@
         <v>1428</v>
       </c>
       <c r="B872" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B873" t="s">
         <v>1430</v>
@@ -13167,52 +13173,52 @@
         <v>1431</v>
       </c>
       <c r="B874" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B875" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B876" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B877" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B878" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B879" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B880" t="s">
         <v>1438</v>
@@ -13255,12 +13261,12 @@
         <v>1447</v>
       </c>
       <c r="B885" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B886" t="s">
         <v>1449</v>
@@ -13303,12 +13309,12 @@
         <v>1458</v>
       </c>
       <c r="B891" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B892" t="s">
         <v>1460</v>
@@ -13335,20 +13341,20 @@
         <v>1465</v>
       </c>
       <c r="B895" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B896" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B897" t="s">
         <v>1468</v>
@@ -13391,12 +13397,12 @@
         <v>1477</v>
       </c>
       <c r="B902" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B903" t="s">
         <v>1479</v>
@@ -13407,12 +13413,12 @@
         <v>1480</v>
       </c>
       <c r="B904" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B905" t="s">
         <v>1482</v>
@@ -13447,20 +13453,20 @@
         <v>1489</v>
       </c>
       <c r="B909" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B910" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B911" t="s">
         <v>1492</v>
@@ -13503,52 +13509,52 @@
         <v>1501</v>
       </c>
       <c r="B916" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B917" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B918" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B919" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B920" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B921" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B922" t="s">
         <v>1508</v>
@@ -13583,28 +13589,28 @@
         <v>1515</v>
       </c>
       <c r="B926" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B927" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B928" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B929" t="s">
         <v>1519</v>
@@ -13647,20 +13653,20 @@
         <v>1528</v>
       </c>
       <c r="B934" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B935" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B936" t="s">
         <v>1531</v>
@@ -13695,12 +13701,12 @@
         <v>1538</v>
       </c>
       <c r="B940" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B941" t="s">
         <v>1540</v>
@@ -13719,12 +13725,12 @@
         <v>1543</v>
       </c>
       <c r="B943" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B944" t="s">
         <v>1545</v>
@@ -13743,12 +13749,12 @@
         <v>1548</v>
       </c>
       <c r="B946" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B947" t="s">
         <v>1550</v>
@@ -13759,12 +13765,12 @@
         <v>1551</v>
       </c>
       <c r="B948" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B949" t="s">
         <v>1553</v>
@@ -13783,12 +13789,12 @@
         <v>1556</v>
       </c>
       <c r="B951" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B952" t="s">
         <v>1558</v>
@@ -13807,28 +13813,28 @@
         <v>1561</v>
       </c>
       <c r="B954" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B955" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B956" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B957" t="s">
         <v>1565</v>
@@ -13855,44 +13861,44 @@
         <v>1570</v>
       </c>
       <c r="B960" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B961" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B962" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B963" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B964" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B965" t="s">
         <v>1576</v>
@@ -13927,28 +13933,28 @@
         <v>1583</v>
       </c>
       <c r="B969" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B970" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B971" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B972" t="s">
         <v>1587</v>
@@ -13999,28 +14005,28 @@
         <v>1598</v>
       </c>
       <c r="B978" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B979" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B980" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B981" t="s">
         <v>1602</v>
@@ -14031,20 +14037,20 @@
         <v>1603</v>
       </c>
       <c r="B982" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B983" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B984" t="s">
         <v>1606</v>
@@ -14087,12 +14093,12 @@
         <v>1615</v>
       </c>
       <c r="B989" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B990" t="s">
         <v>1617</v>
@@ -14119,12 +14125,12 @@
         <v>1622</v>
       </c>
       <c r="B993" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B994" t="s">
         <v>1624</v>
@@ -14143,36 +14149,36 @@
         <v>1627</v>
       </c>
       <c r="B996" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B997" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B998" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B999" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B1000" t="s">
         <v>1632</v>
@@ -14223,12 +14229,12 @@
         <v>1643</v>
       </c>
       <c r="B1006" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B1007" t="s">
         <v>1645</v>
@@ -14247,28 +14253,28 @@
         <v>1648</v>
       </c>
       <c r="B1009" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B1010" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B1011" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B1012" t="s">
         <v>1652</v>
@@ -14279,12 +14285,12 @@
         <v>1653</v>
       </c>
       <c r="B1013" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B1014" t="s">
         <v>1655</v>
@@ -14303,20 +14309,20 @@
         <v>1658</v>
       </c>
       <c r="B1016" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B1017" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B1018" t="s">
         <v>1661</v>
@@ -14343,12 +14349,12 @@
         <v>1666</v>
       </c>
       <c r="B1021" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B1022" t="s">
         <v>1668</v>
@@ -14367,12 +14373,12 @@
         <v>1671</v>
       </c>
       <c r="B1024" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B1025" t="s">
         <v>1673</v>
@@ -14391,36 +14397,36 @@
         <v>1676</v>
       </c>
       <c r="B1027" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1028" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1029" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1030" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1031" t="s">
         <v>1681</v>
@@ -14439,12 +14445,12 @@
         <v>1684</v>
       </c>
       <c r="B1033" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1034" t="s">
         <v>1686</v>
@@ -14471,12 +14477,12 @@
         <v>1691</v>
       </c>
       <c r="B1037" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1038" t="s">
         <v>1693</v>
@@ -14487,20 +14493,20 @@
         <v>1694</v>
       </c>
       <c r="B1039" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1040" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1041" t="s">
         <v>1697</v>
@@ -14511,12 +14517,12 @@
         <v>1698</v>
       </c>
       <c r="B1042" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1043" t="s">
         <v>1700</v>
@@ -14527,20 +14533,20 @@
         <v>1701</v>
       </c>
       <c r="B1044" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1045" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1046" t="s">
         <v>1704</v>
@@ -14551,20 +14557,20 @@
         <v>1705</v>
       </c>
       <c r="B1047" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1048" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1049" t="s">
         <v>1708</v>
@@ -14575,12 +14581,12 @@
         <v>1709</v>
       </c>
       <c r="B1050" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1051" t="s">
         <v>1711</v>
@@ -14615,12 +14621,12 @@
         <v>1718</v>
       </c>
       <c r="B1055" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B1056" t="s">
         <v>1720</v>
@@ -14631,12 +14637,12 @@
         <v>1721</v>
       </c>
       <c r="B1057" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B1058" t="s">
         <v>1723</v>
@@ -14679,36 +14685,36 @@
         <v>1732</v>
       </c>
       <c r="B1063" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="B1064" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="B1065" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B1066" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B1067" t="s">
         <v>1737</v>
@@ -14759,12 +14765,12 @@
         <v>1748</v>
       </c>
       <c r="B1073" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="B1074" t="s">
         <v>1750</v>
@@ -14775,20 +14781,20 @@
         <v>1751</v>
       </c>
       <c r="B1075" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="B1076" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="B1077" t="s">
         <v>1754</v>
@@ -14839,12 +14845,12 @@
         <v>1765</v>
       </c>
       <c r="B1083" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="B1084" t="s">
         <v>1767</v>
@@ -14855,20 +14861,20 @@
         <v>1768</v>
       </c>
       <c r="B1085" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="B1086" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="B1087" t="s">
         <v>1771</v>
@@ -14879,12 +14885,12 @@
         <v>1772</v>
       </c>
       <c r="B1088" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="B1089" t="s">
         <v>1774</v>
@@ -14895,36 +14901,36 @@
         <v>1775</v>
       </c>
       <c r="B1090" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="B1091" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="B1092" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="B1093" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B1094" t="s">
         <v>1780</v>
@@ -14943,20 +14949,20 @@
         <v>1783</v>
       </c>
       <c r="B1096" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="B1097" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="B1098" t="s">
         <v>1786</v>
@@ -14975,12 +14981,12 @@
         <v>1789</v>
       </c>
       <c r="B1100" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="B1101" t="s">
         <v>1791</v>
@@ -15015,20 +15021,20 @@
         <v>1798</v>
       </c>
       <c r="B1105" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="B1106" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="B1107" t="s">
         <v>1801</v>
@@ -15071,12 +15077,12 @@
         <v>1810</v>
       </c>
       <c r="B1112" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="B1113" t="s">
         <v>1812</v>
@@ -15095,20 +15101,20 @@
         <v>1815</v>
       </c>
       <c r="B1115" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="B1116" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="B1117" t="s">
         <v>1818</v>
@@ -15119,20 +15125,20 @@
         <v>1819</v>
       </c>
       <c r="B1118" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="B1119" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="B1120" t="s">
         <v>1822</v>
@@ -15151,12 +15157,12 @@
         <v>1825</v>
       </c>
       <c r="B1122" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="B1123" t="s">
         <v>1827</v>
@@ -15183,12 +15189,12 @@
         <v>1832</v>
       </c>
       <c r="B1126" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="B1127" t="s">
         <v>1834</v>
@@ -15231,12 +15237,12 @@
         <v>1843</v>
       </c>
       <c r="B1132" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="B1133" t="s">
         <v>1845</v>
@@ -15343,44 +15349,44 @@
         <v>1870</v>
       </c>
       <c r="B1146" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="B1147" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="B1148" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B1149" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B1150" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B1151" t="s">
         <v>1876</v>
@@ -15399,28 +15405,28 @@
         <v>1879</v>
       </c>
       <c r="B1153" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="B1154" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="B1155" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B1156" t="s">
         <v>1883</v>
@@ -15487,12 +15493,12 @@
         <v>1898</v>
       </c>
       <c r="B1164" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="B1165" t="s">
         <v>1900</v>
@@ -15503,12 +15509,12 @@
         <v>1901</v>
       </c>
       <c r="B1166" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="B1167" t="s">
         <v>1903</v>
@@ -15543,44 +15549,44 @@
         <v>1910</v>
       </c>
       <c r="B1171" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="B1172" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="B1173" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B1174" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1175" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B1176" t="s">
         <v>1916</v>
@@ -15599,20 +15605,20 @@
         <v>1919</v>
       </c>
       <c r="B1178" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="B1179" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="B1180" t="s">
         <v>1922</v>
@@ -15623,44 +15629,44 @@
         <v>1923</v>
       </c>
       <c r="B1181" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="B1182" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="B1183" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B1184" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1185" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="B1186" t="s">
         <v>1929</v>
@@ -15671,43 +15677,51 @@
         <v>1930</v>
       </c>
       <c r="B1187" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="B1188" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="B1189" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B1190" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="B1191" t="s">
         <v>1935</v>
       </c>
     </row>
+    <row r="1192" spans="1:2">
+      <c r="A1192" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1192" t="s">
+        <v>1937</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1191"/>
+  <autoFilter ref="A1:B1192"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/id/headTags.xlsx
+++ b/lang/id/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1193</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1940">
   <si>
     <t>en</t>
   </si>
@@ -2087,6 +2087,12 @@
   </si>
   <si>
     <t>Font (Oranye)</t>
+  </si>
+  <si>
+    <t>Font (Pale Oak)</t>
+  </si>
+  <si>
+    <t>Jenis huruf (Pale Oak)</t>
   </si>
   <si>
     <t>Font (Pink)</t>
@@ -6177,7 +6183,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1192"/>
+  <dimension ref="A1:B1193"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -9597,12 +9603,12 @@
         <v>714</v>
       </c>
       <c r="B427" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="428" spans="1:2">
       <c r="A428" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B428" t="s">
         <v>716</v>
@@ -9629,12 +9635,12 @@
         <v>721</v>
       </c>
       <c r="B431" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B432" t="s">
         <v>723</v>
@@ -9669,12 +9675,12 @@
         <v>730</v>
       </c>
       <c r="B436" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="B437" t="s">
         <v>732</v>
@@ -9693,12 +9699,12 @@
         <v>735</v>
       </c>
       <c r="B439" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B440" t="s">
         <v>737</v>
@@ -9709,12 +9715,12 @@
         <v>738</v>
       </c>
       <c r="B441" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="B442" t="s">
         <v>740</v>
@@ -9773,12 +9779,12 @@
         <v>753</v>
       </c>
       <c r="B449" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B450" t="s">
         <v>755</v>
@@ -9789,12 +9795,12 @@
         <v>756</v>
       </c>
       <c r="B451" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B452" t="s">
         <v>758</v>
@@ -9805,12 +9811,12 @@
         <v>759</v>
       </c>
       <c r="B453" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B454" t="s">
         <v>761</v>
@@ -9821,12 +9827,12 @@
         <v>762</v>
       </c>
       <c r="B455" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="456" spans="1:2">
       <c r="A456" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B456" t="s">
         <v>764</v>
@@ -9845,12 +9851,12 @@
         <v>767</v>
       </c>
       <c r="B458" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B459" t="s">
         <v>769</v>
@@ -9925,36 +9931,36 @@
         <v>786</v>
       </c>
       <c r="B468" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B469" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B470" t="s">
-        <v>528</v>
+        <v>789</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="B471" t="s">
-        <v>789</v>
+        <v>528</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B472" t="s">
         <v>791</v>
@@ -9965,15 +9971,15 @@
         <v>792</v>
       </c>
       <c r="B473" t="s">
-        <v>141</v>
+        <v>793</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B474" t="s">
-        <v>794</v>
+        <v>141</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -9989,44 +9995,44 @@
         <v>797</v>
       </c>
       <c r="B476" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B477" t="s">
-        <v>528</v>
+        <v>799</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B478" t="s">
-        <v>799</v>
+        <v>528</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B479" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B480" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B481" t="s">
         <v>803</v>
@@ -10053,12 +10059,12 @@
         <v>808</v>
       </c>
       <c r="B484" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B485" t="s">
         <v>810</v>
@@ -10069,12 +10075,12 @@
         <v>811</v>
       </c>
       <c r="B486" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B487" t="s">
         <v>813</v>
@@ -10093,52 +10099,52 @@
         <v>816</v>
       </c>
       <c r="B489" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B490" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B491" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B492" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B493" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B494" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B495" t="s">
         <v>823</v>
@@ -10301,12 +10307,12 @@
         <v>862</v>
       </c>
       <c r="B515" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B516" t="s">
         <v>864</v>
@@ -10317,28 +10323,28 @@
         <v>865</v>
       </c>
       <c r="B517" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B518" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B519" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B520" t="s">
         <v>869</v>
@@ -10365,28 +10371,28 @@
         <v>874</v>
       </c>
       <c r="B523" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B524" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B525" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B526" t="s">
         <v>878</v>
@@ -10413,12 +10419,12 @@
         <v>883</v>
       </c>
       <c r="B529" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B530" t="s">
         <v>885</v>
@@ -10469,12 +10475,12 @@
         <v>896</v>
       </c>
       <c r="B536" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B537" t="s">
         <v>898</v>
@@ -10493,20 +10499,20 @@
         <v>901</v>
       </c>
       <c r="B539" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B540" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B541" t="s">
         <v>904</v>
@@ -10517,44 +10523,44 @@
         <v>905</v>
       </c>
       <c r="B542" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B543" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B544" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B545" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B546" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B547" t="s">
         <v>911</v>
@@ -10581,20 +10587,20 @@
         <v>916</v>
       </c>
       <c r="B550" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B551" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B552" t="s">
         <v>919</v>
@@ -10605,12 +10611,12 @@
         <v>920</v>
       </c>
       <c r="B553" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B554" t="s">
         <v>922</v>
@@ -10621,28 +10627,28 @@
         <v>923</v>
       </c>
       <c r="B555" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B556" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B557" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B558" t="s">
         <v>927</v>
@@ -10653,12 +10659,12 @@
         <v>928</v>
       </c>
       <c r="B559" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B560" t="s">
         <v>930</v>
@@ -10725,20 +10731,20 @@
         <v>945</v>
       </c>
       <c r="B568" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B569" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B570" t="s">
         <v>948</v>
@@ -10757,12 +10763,12 @@
         <v>951</v>
       </c>
       <c r="B572" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B573" t="s">
         <v>953</v>
@@ -10781,12 +10787,12 @@
         <v>956</v>
       </c>
       <c r="B575" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B576" t="s">
         <v>958</v>
@@ -10813,12 +10819,12 @@
         <v>963</v>
       </c>
       <c r="B579" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B580" t="s">
         <v>965</v>
@@ -10829,12 +10835,12 @@
         <v>966</v>
       </c>
       <c r="B581" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B582" t="s">
         <v>968</v>
@@ -10845,20 +10851,20 @@
         <v>969</v>
       </c>
       <c r="B583" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B584" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B585" t="s">
         <v>972</v>
@@ -10877,20 +10883,20 @@
         <v>975</v>
       </c>
       <c r="B587" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B588" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B589" t="s">
         <v>978</v>
@@ -10901,12 +10907,12 @@
         <v>979</v>
       </c>
       <c r="B590" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B591" t="s">
         <v>981</v>
@@ -10917,12 +10923,12 @@
         <v>982</v>
       </c>
       <c r="B592" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B593" t="s">
         <v>984</v>
@@ -10941,12 +10947,12 @@
         <v>987</v>
       </c>
       <c r="B595" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B596" t="s">
         <v>989</v>
@@ -10997,12 +11003,12 @@
         <v>1000</v>
       </c>
       <c r="B602" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B603" t="s">
         <v>1002</v>
@@ -11069,12 +11075,12 @@
         <v>1017</v>
       </c>
       <c r="B611" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B612" t="s">
         <v>1019</v>
@@ -11093,12 +11099,12 @@
         <v>1022</v>
       </c>
       <c r="B614" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B615" t="s">
         <v>1024</v>
@@ -11141,28 +11147,28 @@
         <v>1033</v>
       </c>
       <c r="B620" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B621" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B622" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B623" t="s">
         <v>1037</v>
@@ -11173,12 +11179,12 @@
         <v>1038</v>
       </c>
       <c r="B624" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B625" t="s">
         <v>1040</v>
@@ -11205,12 +11211,12 @@
         <v>1045</v>
       </c>
       <c r="B628" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B629" t="s">
         <v>1047</v>
@@ -11245,76 +11251,76 @@
         <v>1054</v>
       </c>
       <c r="B633" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B634" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B635" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B636" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B637" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B638" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B639" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B640" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B641" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B642" t="s">
         <v>1064</v>
@@ -11325,20 +11331,20 @@
         <v>1065</v>
       </c>
       <c r="B643" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B644" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B645" t="s">
         <v>1068</v>
@@ -11349,28 +11355,28 @@
         <v>1069</v>
       </c>
       <c r="B646" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B647" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B648" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B649" t="s">
         <v>1073</v>
@@ -11381,36 +11387,36 @@
         <v>1074</v>
       </c>
       <c r="B650" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B651" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B652" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B653" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B654" t="s">
         <v>1079</v>
@@ -11445,20 +11451,20 @@
         <v>1086</v>
       </c>
       <c r="B658" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B659" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B660" t="s">
         <v>1089</v>
@@ -11477,20 +11483,20 @@
         <v>1092</v>
       </c>
       <c r="B662" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B663" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B664" t="s">
         <v>1095</v>
@@ -11509,12 +11515,12 @@
         <v>1098</v>
       </c>
       <c r="B666" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B667" t="s">
         <v>1100</v>
@@ -11525,20 +11531,20 @@
         <v>1101</v>
       </c>
       <c r="B668" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B669" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B670" t="s">
         <v>1104</v>
@@ -11573,44 +11579,44 @@
         <v>1111</v>
       </c>
       <c r="B674" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B675" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B676" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B677" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B678" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B679" t="s">
         <v>1117</v>
@@ -11629,12 +11635,12 @@
         <v>1120</v>
       </c>
       <c r="B681" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B682" t="s">
         <v>1122</v>
@@ -11653,12 +11659,12 @@
         <v>1125</v>
       </c>
       <c r="B684" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B685" t="s">
         <v>1127</v>
@@ -11669,20 +11675,20 @@
         <v>1128</v>
       </c>
       <c r="B686" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B687" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B688" t="s">
         <v>1131</v>
@@ -11709,20 +11715,20 @@
         <v>1136</v>
       </c>
       <c r="B691" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B692" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B693" t="s">
         <v>1139</v>
@@ -11805,12 +11811,12 @@
         <v>1158</v>
       </c>
       <c r="B703" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B704" t="s">
         <v>1160</v>
@@ -11853,12 +11859,12 @@
         <v>1169</v>
       </c>
       <c r="B709" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B710" t="s">
         <v>1171</v>
@@ -11869,20 +11875,20 @@
         <v>1172</v>
       </c>
       <c r="B711" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B712" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B713" t="s">
         <v>1175</v>
@@ -11893,28 +11899,28 @@
         <v>1176</v>
       </c>
       <c r="B714" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B715" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B716" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B717" t="s">
         <v>1180</v>
@@ -11925,28 +11931,28 @@
         <v>1181</v>
       </c>
       <c r="B718" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B719" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B720" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B721" t="s">
         <v>1185</v>
@@ -11957,12 +11963,12 @@
         <v>1186</v>
       </c>
       <c r="B722" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B723" t="s">
         <v>1188</v>
@@ -12021,12 +12027,12 @@
         <v>1201</v>
       </c>
       <c r="B730" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B731" t="s">
         <v>1203</v>
@@ -12101,12 +12107,12 @@
         <v>1220</v>
       </c>
       <c r="B740" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B741" t="s">
         <v>1222</v>
@@ -12133,12 +12139,12 @@
         <v>1227</v>
       </c>
       <c r="B744" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B745" t="s">
         <v>1229</v>
@@ -12149,52 +12155,52 @@
         <v>1230</v>
       </c>
       <c r="B746" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B747" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B748" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B749" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B750" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B751" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B752" t="s">
         <v>1237</v>
@@ -12213,36 +12219,36 @@
         <v>1240</v>
       </c>
       <c r="B754" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B755" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B756" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B757" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B758" t="s">
         <v>1245</v>
@@ -12301,20 +12307,20 @@
         <v>1258</v>
       </c>
       <c r="B765" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B766" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B767" t="s">
         <v>1261</v>
@@ -12325,20 +12331,20 @@
         <v>1262</v>
       </c>
       <c r="B768" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B769" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B770" t="s">
         <v>1265</v>
@@ -12349,20 +12355,20 @@
         <v>1266</v>
       </c>
       <c r="B771" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B772" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B773" t="s">
         <v>1269</v>
@@ -12405,12 +12411,12 @@
         <v>1278</v>
       </c>
       <c r="B778" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B779" t="s">
         <v>1280</v>
@@ -12445,12 +12451,12 @@
         <v>1287</v>
       </c>
       <c r="B783" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B784" t="s">
         <v>1289</v>
@@ -12517,28 +12523,28 @@
         <v>1304</v>
       </c>
       <c r="B792" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B793" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B794" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B795" t="s">
         <v>1308</v>
@@ -12557,12 +12563,12 @@
         <v>1311</v>
       </c>
       <c r="B797" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B798" t="s">
         <v>1313</v>
@@ -12573,60 +12579,60 @@
         <v>1314</v>
       </c>
       <c r="B799" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B800" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B801" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B802" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B803" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B804" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B805" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B806" t="s">
         <v>1322</v>
@@ -12637,28 +12643,28 @@
         <v>1323</v>
       </c>
       <c r="B807" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B808" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B809" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B810" t="s">
         <v>1327</v>
@@ -12709,28 +12715,28 @@
         <v>1338</v>
       </c>
       <c r="B816" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B817" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B818" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B819" t="s">
         <v>1342</v>
@@ -12813,12 +12819,12 @@
         <v>1361</v>
       </c>
       <c r="B829" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B830" t="s">
         <v>1363</v>
@@ -12837,20 +12843,20 @@
         <v>1366</v>
       </c>
       <c r="B832" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B833" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B834" t="s">
         <v>1369</v>
@@ -12861,12 +12867,12 @@
         <v>1370</v>
       </c>
       <c r="B835" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B836" t="s">
         <v>1372</v>
@@ -12877,28 +12883,28 @@
         <v>1373</v>
       </c>
       <c r="B837" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B838" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B839" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B840" t="s">
         <v>1377</v>
@@ -12909,44 +12915,44 @@
         <v>1378</v>
       </c>
       <c r="B841" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B842" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B843" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B844" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B845" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B846" t="s">
         <v>1384</v>
@@ -12981,12 +12987,12 @@
         <v>1391</v>
       </c>
       <c r="B850" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B851" t="s">
         <v>1393</v>
@@ -13005,28 +13011,28 @@
         <v>1396</v>
       </c>
       <c r="B853" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B854" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B855" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B856" t="s">
         <v>1400</v>
@@ -13133,28 +13139,28 @@
         <v>1425</v>
       </c>
       <c r="B869" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B870" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B871" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B872" t="s">
         <v>1429</v>
@@ -13165,12 +13171,12 @@
         <v>1430</v>
       </c>
       <c r="B873" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B874" t="s">
         <v>1432</v>
@@ -13181,52 +13187,52 @@
         <v>1433</v>
       </c>
       <c r="B875" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B876" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B877" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B878" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B879" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B880" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B881" t="s">
         <v>1440</v>
@@ -13269,12 +13275,12 @@
         <v>1449</v>
       </c>
       <c r="B886" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B887" t="s">
         <v>1451</v>
@@ -13317,12 +13323,12 @@
         <v>1460</v>
       </c>
       <c r="B892" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B893" t="s">
         <v>1462</v>
@@ -13349,20 +13355,20 @@
         <v>1467</v>
       </c>
       <c r="B896" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B897" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B898" t="s">
         <v>1470</v>
@@ -13405,12 +13411,12 @@
         <v>1479</v>
       </c>
       <c r="B903" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B904" t="s">
         <v>1481</v>
@@ -13421,12 +13427,12 @@
         <v>1482</v>
       </c>
       <c r="B905" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B906" t="s">
         <v>1484</v>
@@ -13461,20 +13467,20 @@
         <v>1491</v>
       </c>
       <c r="B910" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B911" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B912" t="s">
         <v>1494</v>
@@ -13517,52 +13523,52 @@
         <v>1503</v>
       </c>
       <c r="B917" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B918" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B919" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B920" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B921" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B922" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B923" t="s">
         <v>1510</v>
@@ -13597,28 +13603,28 @@
         <v>1517</v>
       </c>
       <c r="B927" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B928" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B929" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B930" t="s">
         <v>1521</v>
@@ -13661,20 +13667,20 @@
         <v>1530</v>
       </c>
       <c r="B935" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B936" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B937" t="s">
         <v>1533</v>
@@ -13709,12 +13715,12 @@
         <v>1540</v>
       </c>
       <c r="B941" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B942" t="s">
         <v>1542</v>
@@ -13733,12 +13739,12 @@
         <v>1545</v>
       </c>
       <c r="B944" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B945" t="s">
         <v>1547</v>
@@ -13757,12 +13763,12 @@
         <v>1550</v>
       </c>
       <c r="B947" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B948" t="s">
         <v>1552</v>
@@ -13773,12 +13779,12 @@
         <v>1553</v>
       </c>
       <c r="B949" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B950" t="s">
         <v>1555</v>
@@ -13797,12 +13803,12 @@
         <v>1558</v>
       </c>
       <c r="B952" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B953" t="s">
         <v>1560</v>
@@ -13821,28 +13827,28 @@
         <v>1563</v>
       </c>
       <c r="B955" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B956" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B957" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B958" t="s">
         <v>1567</v>
@@ -13869,44 +13875,44 @@
         <v>1572</v>
       </c>
       <c r="B961" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B962" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B963" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B964" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B965" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B966" t="s">
         <v>1578</v>
@@ -13941,28 +13947,28 @@
         <v>1585</v>
       </c>
       <c r="B970" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B971" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B972" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B973" t="s">
         <v>1589</v>
@@ -14013,28 +14019,28 @@
         <v>1600</v>
       </c>
       <c r="B979" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B980" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B981" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B982" t="s">
         <v>1604</v>
@@ -14045,20 +14051,20 @@
         <v>1605</v>
       </c>
       <c r="B983" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B984" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B985" t="s">
         <v>1608</v>
@@ -14101,12 +14107,12 @@
         <v>1617</v>
       </c>
       <c r="B990" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B991" t="s">
         <v>1619</v>
@@ -14133,12 +14139,12 @@
         <v>1624</v>
       </c>
       <c r="B994" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B995" t="s">
         <v>1626</v>
@@ -14157,36 +14163,36 @@
         <v>1629</v>
       </c>
       <c r="B997" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B998" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B999" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B1000" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B1001" t="s">
         <v>1634</v>
@@ -14237,12 +14243,12 @@
         <v>1645</v>
       </c>
       <c r="B1007" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B1008" t="s">
         <v>1647</v>
@@ -14261,28 +14267,28 @@
         <v>1650</v>
       </c>
       <c r="B1010" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B1011" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B1012" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B1013" t="s">
         <v>1654</v>
@@ -14293,12 +14299,12 @@
         <v>1655</v>
       </c>
       <c r="B1014" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B1015" t="s">
         <v>1657</v>
@@ -14317,20 +14323,20 @@
         <v>1660</v>
       </c>
       <c r="B1017" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B1018" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B1019" t="s">
         <v>1663</v>
@@ -14357,12 +14363,12 @@
         <v>1668</v>
       </c>
       <c r="B1022" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B1023" t="s">
         <v>1670</v>
@@ -14381,12 +14387,12 @@
         <v>1673</v>
       </c>
       <c r="B1025" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B1026" t="s">
         <v>1675</v>
@@ -14405,36 +14411,36 @@
         <v>1678</v>
       </c>
       <c r="B1028" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1029" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1030" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1031" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1032" t="s">
         <v>1683</v>
@@ -14453,12 +14459,12 @@
         <v>1686</v>
       </c>
       <c r="B1034" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1035" t="s">
         <v>1688</v>
@@ -14485,12 +14491,12 @@
         <v>1693</v>
       </c>
       <c r="B1038" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1039" t="s">
         <v>1695</v>
@@ -14501,20 +14507,20 @@
         <v>1696</v>
       </c>
       <c r="B1040" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1041" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1042" t="s">
         <v>1699</v>
@@ -14525,12 +14531,12 @@
         <v>1700</v>
       </c>
       <c r="B1043" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1044" t="s">
         <v>1702</v>
@@ -14541,20 +14547,20 @@
         <v>1703</v>
       </c>
       <c r="B1045" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1046" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1047" t="s">
         <v>1706</v>
@@ -14565,20 +14571,20 @@
         <v>1707</v>
       </c>
       <c r="B1048" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1049" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1050" t="s">
         <v>1710</v>
@@ -14589,12 +14595,12 @@
         <v>1711</v>
       </c>
       <c r="B1051" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1052" t="s">
         <v>1713</v>
@@ -14629,12 +14635,12 @@
         <v>1720</v>
       </c>
       <c r="B1056" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B1057" t="s">
         <v>1722</v>
@@ -14645,12 +14651,12 @@
         <v>1723</v>
       </c>
       <c r="B1058" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="B1059" t="s">
         <v>1725</v>
@@ -14693,36 +14699,36 @@
         <v>1734</v>
       </c>
       <c r="B1064" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="B1065" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="B1066" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="B1067" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="B1068" t="s">
         <v>1739</v>
@@ -14773,12 +14779,12 @@
         <v>1750</v>
       </c>
       <c r="B1074" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="B1075" t="s">
         <v>1752</v>
@@ -14789,20 +14795,20 @@
         <v>1753</v>
       </c>
       <c r="B1076" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="B1077" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="B1078" t="s">
         <v>1756</v>
@@ -14853,12 +14859,12 @@
         <v>1767</v>
       </c>
       <c r="B1084" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="B1085" t="s">
         <v>1769</v>
@@ -14869,20 +14875,20 @@
         <v>1770</v>
       </c>
       <c r="B1086" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="B1087" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="B1088" t="s">
         <v>1773</v>
@@ -14893,12 +14899,12 @@
         <v>1774</v>
       </c>
       <c r="B1089" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="B1090" t="s">
         <v>1776</v>
@@ -14909,36 +14915,36 @@
         <v>1777</v>
       </c>
       <c r="B1091" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="B1092" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="B1093" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="B1094" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="B1095" t="s">
         <v>1782</v>
@@ -14957,20 +14963,20 @@
         <v>1785</v>
       </c>
       <c r="B1097" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="B1098" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="B1099" t="s">
         <v>1788</v>
@@ -14989,12 +14995,12 @@
         <v>1791</v>
       </c>
       <c r="B1101" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="B1102" t="s">
         <v>1793</v>
@@ -15029,20 +15035,20 @@
         <v>1800</v>
       </c>
       <c r="B1106" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="B1107" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="B1108" t="s">
         <v>1803</v>
@@ -15085,12 +15091,12 @@
         <v>1812</v>
       </c>
       <c r="B1113" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="B1114" t="s">
         <v>1814</v>
@@ -15109,20 +15115,20 @@
         <v>1817</v>
       </c>
       <c r="B1116" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="B1117" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="B1118" t="s">
         <v>1820</v>
@@ -15133,20 +15139,20 @@
         <v>1821</v>
       </c>
       <c r="B1119" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="B1120" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="B1121" t="s">
         <v>1824</v>
@@ -15165,12 +15171,12 @@
         <v>1827</v>
       </c>
       <c r="B1123" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="B1124" t="s">
         <v>1829</v>
@@ -15197,12 +15203,12 @@
         <v>1834</v>
       </c>
       <c r="B1127" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="B1128" t="s">
         <v>1836</v>
@@ -15245,12 +15251,12 @@
         <v>1845</v>
       </c>
       <c r="B1133" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="B1134" t="s">
         <v>1847</v>
@@ -15357,44 +15363,44 @@
         <v>1872</v>
       </c>
       <c r="B1147" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="B1148" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="B1149" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="B1150" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="B1151" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="B1152" t="s">
         <v>1878</v>
@@ -15413,28 +15419,28 @@
         <v>1881</v>
       </c>
       <c r="B1154" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="B1155" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="B1156" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="B1157" t="s">
         <v>1885</v>
@@ -15501,12 +15507,12 @@
         <v>1900</v>
       </c>
       <c r="B1165" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="B1166" t="s">
         <v>1902</v>
@@ -15517,12 +15523,12 @@
         <v>1903</v>
       </c>
       <c r="B1167" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="B1168" t="s">
         <v>1905</v>
@@ -15557,44 +15563,44 @@
         <v>1912</v>
       </c>
       <c r="B1172" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="B1173" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="B1174" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="B1175" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="B1176" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="B1177" t="s">
         <v>1918</v>
@@ -15613,20 +15619,20 @@
         <v>1921</v>
       </c>
       <c r="B1179" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="B1180" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="B1181" t="s">
         <v>1924</v>
@@ -15637,44 +15643,44 @@
         <v>1925</v>
       </c>
       <c r="B1182" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="B1183" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="B1184" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="B1185" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="B1186" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="B1187" t="s">
         <v>1931</v>
@@ -15685,43 +15691,51 @@
         <v>1932</v>
       </c>
       <c r="B1188" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="B1189" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="B1190" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="B1191" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="B1192" t="s">
         <v>1937</v>
       </c>
     </row>
+    <row r="1193" spans="1:2">
+      <c r="A1193" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B1193" t="s">
+        <v>1939</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B1192"/>
+  <autoFilter ref="A1:B1193"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
